--- a/fiches indicateurs.xlsx
+++ b/fiches indicateurs.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="indicateurs" sheetId="1" state="visible" r:id="rId3"/>
@@ -1871,6 +1871,18 @@
     <t xml:space="preserve">aide à la décision</t>
   </si>
   <si>
+    <t xml:space="preserve">Robustesse et résilience technique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Évaluer la capacité de production en période sèche et la présence de dispositifs de secours (stockage, interconnexion) pour garantir la continuité du service.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diagnostic &amp; Modulation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guide la mise en conformité légale et les actions de protection réglementaire.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Poids stratégique de la desserte</t>
   </si>
   <si>
@@ -1878,18 +1890,6 @@
   </si>
   <si>
     <t xml:space="preserve">Définit les priorités d'investissement et l'importance socio-économique de la ressource.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Robustesse et résilience technique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Évaluer la capacité de production en période sèche et la présence de dispositifs de secours (stockage, interconnexion) pour garantir la continuité du service.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diagnostic &amp; Modulation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guide la mise en conformité légale et les actions de protection réglementaire.</t>
   </si>
   <si>
     <t xml:space="preserve">Sécurisation sanitaire et réglementaire</t>
@@ -8713,11 +8713,11 @@
         <v>608</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="1" t="s">
         <v>609</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -8726,28 +8726,28 @@
       <c r="D2" s="1" t="s">
         <v>610</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>495</v>
+      <c r="E2" s="12" t="s">
+        <v>611</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>612</v>
+      <c r="B3" s="12" t="s">
+        <v>613</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>613</v>
-      </c>
-      <c r="E3" s="12" t="s">
         <v>614</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>495</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>615</v>
@@ -8787,7 +8787,7 @@
         <v>620</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>621</v>
@@ -8847,7 +8847,7 @@
         <v>630</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>631</v>
@@ -9013,7 +9013,7 @@
         <v>656</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>657</v>
@@ -9300,10 +9300,10 @@
         <v>26</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="F2" s="1"/>
       <c r="H2" s="1"/>
@@ -9316,10 +9316,10 @@
         <v>44</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="F3" s="1"/>
       <c r="H3" s="1"/>
@@ -9332,10 +9332,10 @@
         <v>53</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="F4" s="1"/>
       <c r="H4" s="1"/>
@@ -9364,10 +9364,10 @@
         <v>71</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="F6" s="1"/>
       <c r="H6" s="1"/>
@@ -9380,10 +9380,10 @@
         <v>80</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="F7" s="1"/>
       <c r="H7" s="1"/>

--- a/fiches indicateurs.xlsx
+++ b/fiches indicateurs.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1850" uniqueCount="696">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1862" uniqueCount="702">
   <si>
     <t xml:space="preserve">fiche_indicateur</t>
   </si>
@@ -62,7 +62,7 @@
     <t xml:space="preserve">objectif</t>
   </si>
   <si>
-    <t xml:space="preserve">modalités</t>
+    <t xml:space="preserve">modalites</t>
   </si>
   <si>
     <t xml:space="preserve">support_spatial</t>
@@ -86,16 +86,16 @@
     <t xml:space="preserve">quantitatif_qualitatif</t>
   </si>
   <si>
-    <t xml:space="preserve">discret_continue</t>
+    <t xml:space="preserve">discret_continu</t>
   </si>
   <si>
     <t xml:space="preserve">relatif_absolu</t>
   </si>
   <si>
-    <t xml:space="preserve">Implantation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">representation</t>
+    <t xml:space="preserve">implantation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">representation_cartographique</t>
   </si>
   <si>
     <t xml:space="preserve">synthese_echanges-1</t>
@@ -137,7 +137,7 @@
     <t xml:space="preserve">Non</t>
   </si>
   <si>
-    <t xml:space="preserve">Classes 3 niveaux (quantiles ou seuils métier)</t>
+    <t xml:space="preserve">Classes 3 niveaux</t>
   </si>
   <si>
     <t xml:space="preserve">Positif (absence = critique / plus = mieux)</t>
@@ -182,9 +182,6 @@
     <t xml:space="preserve">UD</t>
   </si>
   <si>
-    <t xml:space="preserve">Classes 3 niveaux</t>
-  </si>
-  <si>
     <t xml:space="preserve">Plus le réseau est long, plus les enjeux sont élevés → criticité stratégique élevée</t>
   </si>
   <si>
@@ -230,6 +227,9 @@
     <t xml:space="preserve">Catégoriel mappé (1-3)</t>
   </si>
   <si>
+    <t xml:space="preserve">Positif (absence = critique / présence = mieux)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Absence de traitement = criticité forte (bien que si des traitements sont fait c’est que la ressource est déjà impactée par des polluants), traitement complet = criticité faible</t>
   </si>
   <si>
@@ -260,7 +260,7 @@
     <t xml:space="preserve">Attribution d’un statut binaire par unité de distribution, sans agrégation complexe.</t>
   </si>
   <si>
-    <t xml:space="preserve">Binaire (1 &amp; 3)</t>
+    <t xml:space="preserve">2 classes binaires mappé en classe 1 &amp; classe 3</t>
   </si>
   <si>
     <t xml:space="preserve">Absence d’interconnexion = forte criticité (pas de secours), présence = criticité faible (à confirmer)</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">Affectation par unité de distribution puis agrégation au captage.</t>
   </si>
   <si>
-    <t xml:space="preserve">Négatif (plus = enjeu fort)</t>
+    <t xml:space="preserve">Valeur de classe appliquée arbitrairement</t>
   </si>
   <si>
     <t xml:space="preserve">Plus la population est élevée, plus le captage est stratégique → criticité élevée</t>
@@ -329,7 +329,7 @@
     <t xml:space="preserve">Comparer les captages selon leur niveau de protection afin d’identifier ceux les plus exposés aux pressions.</t>
   </si>
   <si>
-    <t xml:space="preserve">Négatif (non protégé = critique)</t>
+    <t xml:space="preserve">Valeur de classe non ordonnée et donc appliquée arbitrairement</t>
   </si>
   <si>
     <t xml:space="preserve">Captage non protégé = forte criticité</t>
@@ -350,9 +350,6 @@
     <t xml:space="preserve">Comparer les captages selon leur vulnérabilité intrinsèque liée à leur nature {un captage superficiel est considéré comme plus vulnérable qu'un forage profond dans les calculs de criticité)</t>
   </si>
   <si>
-    <t xml:space="preserve">Négatif (superficiel = critique)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Captage superficiel = plus vulnérable → criticité forte</t>
   </si>
   <si>
@@ -374,9 +371,6 @@
     <t xml:space="preserve">Attribution directe au captage, sans transformation. Utilisation à titre informatif</t>
   </si>
   <si>
-    <t xml:space="preserve">Neutre (info)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Captage actif = enjeu, secours/inactif = criticité moindre</t>
   </si>
   <si>
@@ -398,7 +392,7 @@
     <t xml:space="preserve">ha</t>
   </si>
   <si>
-    <t xml:space="preserve">Identifier les zones à haute valeur patrimoniale mondiale susceptibles d'être impactées par les pressions sur la ressource en eau.</t>
+    <t xml:space="preserve">Comparer les bassins versants AEP entre eux par rapport à leur taux de couverture par une zone UNESCO</t>
   </si>
   <si>
     <t xml:space="preserve">Calcul surfacique par unité spatiale régulière puis agrégation au bassin versant.</t>
@@ -422,7 +416,7 @@
     <t xml:space="preserve">Superficie des intersections avec parcs, réserves</t>
   </si>
   <si>
-    <t xml:space="preserve">Caractériser le niveau de protection réglementaire du milieu naturel autour des ressources en eau.</t>
+    <t xml:space="preserve">Comparer les bassins versants AEP entre eux par rapport à leur taux de couverture par une zone protégée provinciale</t>
   </si>
   <si>
     <t xml:space="preserve">Présence en zone protégée = criticité faible bien que  enjeu fort</t>
@@ -434,7 +428,7 @@
     <t xml:space="preserve">Superficie des intersections avec les zones d'intérêt biologique et biodiversité spécifique</t>
   </si>
   <si>
-    <t xml:space="preserve">Identifier les zones à forte valeur écologique (Key Biodiversity Areas, Zones Importantes pour la Conservation des Oiseaux).</t>
+    <t xml:space="preserve">Comparer les bassins versants AEP entre eux par rapport à leur taux de couverture par une zone KBA/ZICO</t>
   </si>
   <si>
     <t xml:space="preserve">Présence en KBA/ZICO = criticité faible bien que enjeu fort</t>
@@ -455,13 +449,13 @@
     <t xml:space="preserve">Forte richesse en espèces menacées = criticité faible bien que enjeu fort (à confirmer)</t>
   </si>
   <si>
-    <t xml:space="preserve">Espèces menacées (Forêt sèche)</t>
+    <t xml:space="preserve">Forêt sèche</t>
   </si>
   <si>
     <t xml:space="preserve">Superficie des intersections des patchs de forêt sèche</t>
   </si>
   <si>
-    <t xml:space="preserve">Identifier la présence de forêt sèche, écosystème endémique parmi les plus menacés de Nouvelle-Calédonie.</t>
+    <t xml:space="preserve">Comparer les bassins versants AEP entre eux par rapport à leur taux de couverture par des patch de forêt sèche.</t>
   </si>
   <si>
     <t xml:space="preserve">Négatif (absence = critique) ?</t>
@@ -560,7 +554,7 @@
     <t xml:space="preserve">Surface de terrain sans végétation.</t>
   </si>
   <si>
-    <t xml:space="preserve">Comparer les bassins versants selon l’étendue des surfaces dégradées afin d’identifier les zones les plus sensibles aux ruissellementau et aux transferts de polluants.</t>
+    <t xml:space="preserve">Comparer les bassins versants selon l’étendue des surfaces dégradées afin d’identifier les zones les plus sensibles aux ruissellement et aux transferts de polluants.</t>
   </si>
   <si>
     <t xml:space="preserve">Indicateur MOS privilégié. Homogène et robuste. Calcul surfacique sur BV.</t>
@@ -767,6 +761,9 @@
     <t xml:space="preserve">Déjà normalisé (1-5)</t>
   </si>
   <si>
+    <t xml:space="preserve">Positif (valeur ordonnée si valeur haute = mieux)</t>
+  </si>
+  <si>
     <t xml:space="preserve">NA</t>
   </si>
   <si>
@@ -791,9 +788,6 @@
     <t xml:space="preserve">Utilisation directe de la classe issue du modèle avec agrégation au bassin versant.</t>
   </si>
   <si>
-    <t xml:space="preserve">Déjà normalisé (5 classes)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Déficit ressource = criticité maximale</t>
   </si>
   <si>
@@ -851,7 +845,7 @@
     <t xml:space="preserve">Comptage des prélèvements associés à chaque captage.</t>
   </si>
   <si>
-    <t xml:space="preserve">Plus de prélèvements = pression ressource</t>
+    <t xml:space="preserve">C'est la présence qui est positive, l'absence d'autorisation AODPE est négative</t>
   </si>
   <si>
     <t xml:space="preserve">Indicateur pression captage. Donnée dynamique DAVAR. Intégrable en analyse.</t>
@@ -893,9 +887,6 @@
     <t xml:space="preserve">Attribution d’une classe par captage selon les données disponibles.</t>
   </si>
   <si>
-    <t xml:space="preserve">Croissant</t>
-  </si>
-  <si>
     <t xml:space="preserve">Classe dégradée = criticité élevée</t>
   </si>
   <si>
@@ -998,6 +989,9 @@
     <t xml:space="preserve">A vérifier</t>
   </si>
   <si>
+    <t xml:space="preserve">Prévue en 2026/2027</t>
+  </si>
+  <si>
     <t xml:space="preserve">Données administratives DAVAR – contacter DAVAR</t>
   </si>
   <si>
@@ -1025,7 +1019,7 @@
     <t xml:space="preserve">Données administratives DAVAR </t>
   </si>
   <si>
-    <t xml:space="preserve">Les typologies de captages doivent être standardisées pour assurer une comparaison cohérente ; certaines informations sont descriptives et susceptibles d'évoluer sans impact direct sur la criticité.</t>
+    <t xml:space="preserve">Les typologies de captages doivent être standardisées pour assurer une comparaison cohérente ; certaines informations sont descriptives et susceptibles d'évoluer sans impact direct sur la criticité. Verifier que la données est bien à jour du GEOREP.</t>
   </si>
   <si>
     <t xml:space="preserve">Bilan Besoin Ressource (nom à vérifier)</t>
@@ -1037,13 +1031,13 @@
     <t xml:space="preserve">Donnée issue d’un modèle nécessitant validation et mise à jour régulière.</t>
   </si>
   <si>
-    <t xml:space="preserve">Base de données ATYA (nom à vérifier)</t>
+    <t xml:space="preserve">Base de données ATYA</t>
   </si>
   <si>
     <t xml:space="preserve">Données DASS/ATYA diffusion interne – contacter DASS</t>
   </si>
   <si>
-    <t xml:space="preserve">Disponibilité limitée et complexité d’interprétation des données sanitaires.</t>
+    <t xml:space="preserve">Disponibilité limitée et complexité d’interprétation des données.</t>
   </si>
   <si>
     <t xml:space="preserve">zones inscrites au patrimoine mondial de l'UNESCO</t>
@@ -1265,7 +1259,16 @@
     <t xml:space="preserve">Installations Classées pour la Protection de l'Environnement de la Province Sud</t>
   </si>
   <si>
-    <t xml:space="preserve">Peut être une compilation nécessaire avec les données de la DIMENC</t>
+    <t xml:space="preserve">https://www.province-sud.nc/open/metadonnees/8a8186dd9816d2da019c8d998c7d00a5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quotidienne </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Une Installation Classée pour la Protection de l’Environnement (ICPE) est une activité fixe à caractère industriel ou agricole susceptible de provoquer des pollutions, des nuisances ou des risques, notamment pour la sécurité, la santé des riverains et/ou l’environnement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.province-sud.nc/environnement/risques-et-menaces/icpe/</t>
   </si>
   <si>
     <t xml:space="preserve">Installations Classées pour la Protection de l'Environnement de la Province Nord</t>
@@ -1359,6 +1362,9 @@
     <t xml:space="preserve">https://dimenc.gouv.nc/geologie/diffuser-la-connaissance-geologique/latlas-hydrogeologique-de-nouvelle-caledonie-bdlisa-nc</t>
   </si>
   <si>
+    <t xml:space="preserve">Selon le rapport de production la donnée intègre certaines pressions (MOS). Voir avec la DIMENC pour confirmer.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Géologie au 1/200 000e – DIMENC/SGNC-BRGM 1981</t>
   </si>
   <si>
@@ -1449,6 +1455,9 @@
     <t xml:space="preserve">valeur</t>
   </si>
   <si>
+    <t xml:space="preserve">indicateurs</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fiche n⁰</t>
   </si>
   <si>
@@ -1456,9 +1465,6 @@
   </si>
   <si>
     <t xml:space="preserve">Documentation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">indicateurs</t>
   </si>
   <si>
     <t xml:space="preserve">Identifiant de l’indicateur</t>
@@ -1486,7 +1492,7 @@
     <t xml:space="preserve">Thématique</t>
   </si>
   <si>
-    <t xml:space="preserve">Grande catégorie permettant de regrouper les indicateurs</t>
+    <t xml:space="preserve">Grande catégorie de regroupement métier facilitant la navigation et l'organisation du catalogue (ex: Enjeux AEP, Pressions Anthropiques).</t>
   </si>
   <si>
     <t xml:space="preserve">Enjeux AEP / Enjeux Environnementaux / Pressions Environnementales / Pressions Anthropiques / Vulnérabilité / Pressions Quantitatives / Pressions Qualitatives
@@ -1496,7 +1502,7 @@
     <t xml:space="preserve">Famille</t>
   </si>
   <si>
-    <t xml:space="preserve">Nature de l’indicateur permettant de comprendre son rôle</t>
+    <t xml:space="preserve">Nature fondamentale de l'indicateur définissant son rôle dans le calcul du risque : Enjeu (valeur à protéger), Pression (menace active) ou Vulnérabilité (sensibilité intrinsèque).</t>
   </si>
   <si>
     <t xml:space="preserve">Enjeu / Pression / Vulnérabilité
@@ -1515,7 +1521,7 @@
     <t xml:space="preserve">Description</t>
   </si>
   <si>
-    <t xml:space="preserve">Explication simple décrivant ce que mesure l’indicateur</t>
+    <t xml:space="preserve">Explication vulgarisée décrivant ce que l'indicateur mesure concrètement et comment il est perçu.</t>
   </si>
   <si>
     <t xml:space="preserve">introduction</t>
@@ -1539,7 +1545,7 @@
     <t xml:space="preserve">Unité</t>
   </si>
   <si>
-    <t xml:space="preserve">Unité ou classe de mesure permettant de lire correctement la valeur</t>
+    <t xml:space="preserve">Unité de mesure physique (m3, km, ha) ou libellé de la classe qualitative (Oui/Non, A1/A2/A3) permettant de lire la valeur.</t>
   </si>
   <si>
     <t xml:space="preserve">Analyse</t>
@@ -1548,16 +1554,13 @@
     <t xml:space="preserve">Objectif</t>
   </si>
   <si>
-    <t xml:space="preserve">But de l’indicateur dans la prise de décision</t>
-  </si>
-  <si>
-    <t xml:space="preserve">modalites</t>
+    <t xml:space="preserve">But précis de l'indicateur dans le processus de décision (ex: identifier les ressources les plus limitées en période sèche).</t>
   </si>
   <si>
     <t xml:space="preserve">Modalités de traitement</t>
   </si>
   <si>
-    <t xml:space="preserve">Règles de traitement et d’agrégation des données</t>
+    <t xml:space="preserve">Règles techniques et algorithmes utilisés pour transformer, agréger ou propager la donnée entre les différents supports spatiaux.</t>
   </si>
   <si>
     <t xml:space="preserve">Transformation</t>
@@ -1566,16 +1569,16 @@
     <t xml:space="preserve">Support spatial</t>
   </si>
   <si>
-    <t xml:space="preserve">Entité spatiale à laquelle l’indicateur est directement rattaché</t>
+    <t xml:space="preserve">Entité géographique de référence à laquelle la donnée est rattachée (Captage, Unité de Distribution, Bassin Versant ou Maille).</t>
   </si>
   <si>
     <t xml:space="preserve">UD (Unité de Distribution) / Captage / Périmètre de protection / BV (Bassin versant) / maille (découpage cartographique régulier de type H3)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pondération</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indique si l’indicateur est utilisé dans la pondération multicritère</t>
+    <t xml:space="preserve">Pondération multicritère</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indique si l'indicateur est activement utilisé pour l’analyse multicritère.</t>
   </si>
   <si>
     <t xml:space="preserve">Calcul multicritère</t>
@@ -1584,7 +1587,7 @@
     <t xml:space="preserve">Spatialisation H3</t>
   </si>
   <si>
-    <t xml:space="preserve">Indique si l’indicateur est calculé sur une maille fine H3</t>
+    <t xml:space="preserve">Indique si la donnée est projetée sur une maille hexagonale fine (H3) pour permettre des analyses géographiques croisées.</t>
   </si>
   <si>
     <t xml:space="preserve">Technique</t>
@@ -1593,25 +1596,57 @@
     <t xml:space="preserve">Méthode de normalisation</t>
   </si>
   <si>
-    <t xml:space="preserve">Méthode pour ramener les valeurs sur une échelle commune</t>
+    <t xml:space="preserve">Processus mathématique ou métier (quantiles, seuils, binaire) utilisé pour ramener des données hétérogènes sur une échelle de criticité commune.</t>
   </si>
   <si>
     <t xml:space="preserve">Sens de l’indicateur</t>
   </si>
   <si>
-    <t xml:space="preserve">Indique si une valeur élevée est quelque chose de positif ou de négatif pour le captage</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Orientation statistique ou logique de la donnée. 
+-</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Pour une donnée quantitative </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:  indique si une valeur élevée est bénéfique (Positif, ex: capacité de production) ou préjudiciable (Négatif, ex: surface incendiée).
+- Pour une donnée qualitative : indique si l'état ou la classe de l'indicateur est perçu comme favorable (Positif, ex: présence d'un traitement ou d'un secours) ou défavorable (Négatif, ex: absence de protection réglementaire) pour la gestion du captage</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Positif / Négatif / Neutre</t>
   </si>
   <si>
     <t xml:space="preserve">Définition de la criticité</t>
   </si>
   <si>
-    <t xml:space="preserve">Lien entre la valeur et le niveau de criticité</t>
+    <t xml:space="preserve">Traduction opérationnelle de la valeur : explique le lien de cause à effet entre la donnée et le niveau de risque ou d'enjeu pour le territoire.</t>
   </si>
   <si>
     <t xml:space="preserve">Nature des données</t>
   </si>
   <si>
-    <t xml:space="preserve">Type de donnée</t>
+    <t xml:space="preserve">Distingue les données Quantitatives (chiffrées) des données Qualitatives (textuelles ou catégories).</t>
   </si>
   <si>
     <t xml:space="preserve">visualisation</t>
@@ -1623,7 +1658,7 @@
     <t xml:space="preserve">Discret ou continu</t>
   </si>
   <si>
-    <t xml:space="preserve">Nature des valeurs</t>
+    <t xml:space="preserve">Nature mathématique des valeurs : Discret (nombres entiers, catégories) ou Continu (échelles de mesure fluides).</t>
   </si>
   <si>
     <t xml:space="preserve">Continue / Discrète</t>
@@ -1632,16 +1667,13 @@
     <t xml:space="preserve">Relatif ou absolu</t>
   </si>
   <si>
-    <t xml:space="preserve">Type de mesure (valeur brute ou ratio)</t>
+    <t xml:space="preserve">Type de mesure : Absolu pour une valeur brute (ex: volume) ou Relatif pour un ratio ou un pourcentage (ex: densité).</t>
   </si>
   <si>
     <t xml:space="preserve">Absolu / Relatif</t>
   </si>
   <si>
-    <t xml:space="preserve">implantation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Type d’implantation visuelle sur la carte</t>
+    <t xml:space="preserve">Mode de représentation géométrique sur la carte : Ponctuelle (position précise) ou Zonale (surface).</t>
   </si>
   <si>
     <t xml:space="preserve">Ponctuelle / zonale</t>
@@ -1650,7 +1682,7 @@
     <t xml:space="preserve">Représentation cartographique</t>
   </si>
   <si>
-    <t xml:space="preserve">Mode d’affichage </t>
+    <t xml:space="preserve">Style visuel de restitution (ex: carte choroplèthe, cercles proportionnels, couleur ou symbole).</t>
   </si>
   <si>
     <t xml:space="preserve">Restitution</t>
@@ -1693,25 +1725,25 @@
     <t xml:space="preserve">Origine</t>
   </si>
   <si>
-    <t xml:space="preserve">Origine de la donnée utilisée</t>
+    <t xml:space="preserve">Organisme ou service producteur initial de la donnée brute (ex: DAVAR, DASS, Météo France).</t>
   </si>
   <si>
     <t xml:space="preserve">Distributeur</t>
   </si>
   <si>
-    <t xml:space="preserve">Distributeur de la ressource</t>
+    <t xml:space="preserve">Entité ou plateforme assurant la mise à disposition technique de la donnée (ex: GéoRep).</t>
   </si>
   <si>
     <t xml:space="preserve">URL</t>
   </si>
   <si>
-    <t xml:space="preserve">URL d’accès à la ressource</t>
+    <t xml:space="preserve">Lien direct vers la ressource en ligne ou sa fiche de métadonnées détaillée.</t>
   </si>
   <si>
     <t xml:space="preserve">Disponibilité</t>
   </si>
   <si>
-    <t xml:space="preserve">Disponibilité de la donnée</t>
+    <t xml:space="preserve">Statut d'accès à la source : Disponible (public), Interne (administration) ou À vérifier (sous convention).</t>
   </si>
   <si>
     <t xml:space="preserve">Disponible / Interne / A vérifier</t>
@@ -1726,7 +1758,7 @@
     <t xml:space="preserve">Période d actualisation</t>
   </si>
   <si>
-    <t xml:space="preserve">Fréquence de mise à jour de la donnée</t>
+    <t xml:space="preserve">Fréquence de mise à jour de la donnée par le producteur (ex: quotidienne, annuelle, jamais).</t>
   </si>
   <si>
     <t xml:space="preserve">inconnu / jamais / x jours / x années
@@ -1736,16 +1768,28 @@
     <t xml:space="preserve">Type de source</t>
   </si>
   <si>
-    <t xml:space="preserve">Format de la donnée</t>
+    <t xml:space="preserve">Format technique du fichier de données (Vecteur, Raster, Table).</t>
   </si>
   <si>
     <t xml:space="preserve">vecteur, raster, table, rapport, infographie</t>
   </si>
   <si>
-    <t xml:space="preserve">Contraintes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Limites ou incertitudes liées à la donnée</t>
+    <t xml:space="preserve">Point de vigilance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identification des limites techniques, incertitudes de mesure ou biais d'interprétation liés à la source.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">groupe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vision_strategique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vision stratégique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Définit la finalité opérationnelle de l'indicateur : Pilotage (aide à la décision immédiate), Veille (surveillance des aléas) ou Diagnostic (socle technique et modulation du risque).</t>
   </si>
   <si>
     <t xml:space="preserve">id_relation</t>
@@ -1754,6 +1798,9 @@
     <t xml:space="preserve">commentaire</t>
   </si>
   <si>
+    <t xml:space="preserve">Espèces menacées (Forêt sèche)</t>
+  </si>
+  <si>
     <t xml:space="preserve">doublons TMF</t>
   </si>
   <si>
@@ -1766,6 +1813,9 @@
     <t xml:space="preserve">si utilisation du 200 000</t>
   </si>
   <si>
+    <t xml:space="preserve">Base de données ATYA (nom à vérifier)</t>
+  </si>
+  <si>
     <t xml:space="preserve">theme_id</t>
   </si>
   <si>
@@ -1859,9 +1909,6 @@
     <t xml:space="preserve">id_groupe</t>
   </si>
   <si>
-    <t xml:space="preserve">groupe</t>
-  </si>
-  <si>
     <t xml:space="preserve">theme</t>
   </si>
   <si>
@@ -1877,7 +1924,7 @@
     <t xml:space="preserve">Évaluer la capacité de production en période sèche et la présence de dispositifs de secours (stockage, interconnexion) pour garantir la continuité du service.</t>
   </si>
   <si>
-    <t xml:space="preserve">Diagnostic &amp; Modulation</t>
+    <t xml:space="preserve">Diagnostic</t>
   </si>
   <si>
     <t xml:space="preserve">Guide la mise en conformité légale et les actions de protection réglementaire.</t>
@@ -2168,15 +2215,15 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
       <sz val="10"/>
-      <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
       <sz val="10"/>
+      <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
@@ -2243,19 +2290,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2276,10 +2327,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2440,15 +2487,15 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="117.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="85.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="24.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="38.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="33.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="139"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="44.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="43.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="51.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="18.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="10.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="21" style="1" width="16"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2479,7 +2526,7 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
@@ -2512,7 +2559,7 @@
       <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="3" t="s">
         <v>21</v>
       </c>
       <c r="W1" s="1" t="s">
@@ -2637,13 +2684,13 @@
         <v>34</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="P3" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R3" s="1" t="s">
         <v>38</v>
@@ -2661,7 +2708,7 @@
         <v>42</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2678,10 +2725,10 @@
         <v>25</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>28</v>
@@ -2690,13 +2737,13 @@
         <v>28</v>
       </c>
       <c r="I4" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>57</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>49</v>
@@ -2708,13 +2755,13 @@
         <v>34</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="P4" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R4" s="1" t="s">
         <v>38</v>
@@ -2732,7 +2779,7 @@
         <v>42</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2749,10 +2796,10 @@
         <v>25</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>28</v>
@@ -2761,13 +2808,13 @@
         <v>28</v>
       </c>
       <c r="I5" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="K5" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="L5" s="1" t="s">
         <v>49</v>
@@ -2779,10 +2826,10 @@
         <v>34</v>
       </c>
       <c r="O5" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P5" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="P5" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="Q5" s="1" t="s">
         <v>66</v>
@@ -2853,7 +2900,7 @@
         <v>76</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="Q6" s="1" t="s">
         <v>77</v>
@@ -2921,7 +2968,7 @@
         <v>34</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>85</v>
@@ -3063,7 +3110,7 @@
         <v>34</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P9" s="1" t="s">
         <v>99</v>
@@ -3118,7 +3165,7 @@
       <c r="I10" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="J10" s="4" t="s">
         <v>105</v>
       </c>
       <c r="K10" s="1" t="s">
@@ -3134,13 +3181,13 @@
         <v>34</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="P10" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q10" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="Q10" s="1" t="s">
-        <v>107</v>
       </c>
       <c r="R10" s="1" t="s">
         <v>67</v>
@@ -3158,7 +3205,7 @@
         <v>69</v>
       </c>
       <c r="W10" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3175,10 +3222,10 @@
         <v>25</v>
       </c>
       <c r="E11" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>110</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>28</v>
@@ -3187,13 +3234,13 @@
         <v>28</v>
       </c>
       <c r="I11" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="J11" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="K11" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>113</v>
       </c>
       <c r="L11" s="1" t="s">
         <v>32</v>
@@ -3205,13 +3252,13 @@
         <v>34</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="P11" s="1" t="s">
-        <v>114</v>
+        <v>64</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>99</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="R11" s="1" t="s">
         <v>67</v>
@@ -3229,7 +3276,7 @@
         <v>78</v>
       </c>
       <c r="W11" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3240,34 +3287,34 @@
         <v>100</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H12" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="J12" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="K12" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="L12" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>124</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>34</v>
@@ -3276,13 +3323,13 @@
         <v>33</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="P12" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R12" s="1" t="s">
         <v>38</v>
@@ -3294,10 +3341,10 @@
         <v>40</v>
       </c>
       <c r="U12" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="V12" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3308,34 +3355,34 @@
         <v>101</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I13" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="K13" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="J13" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>123</v>
-      </c>
       <c r="L13" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>34</v>
@@ -3344,13 +3391,13 @@
         <v>33</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="P13" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="R13" s="1" t="s">
         <v>38</v>
@@ -3362,10 +3409,10 @@
         <v>40</v>
       </c>
       <c r="U13" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="V13" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3376,34 +3423,34 @@
         <v>102</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I14" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="K14" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="J14" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>123</v>
-      </c>
       <c r="L14" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>34</v>
@@ -3412,13 +3459,13 @@
         <v>33</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="P14" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="R14" s="1" t="s">
         <v>38</v>
@@ -3430,10 +3477,10 @@
         <v>40</v>
       </c>
       <c r="U14" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="V14" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3444,34 +3491,34 @@
         <v>103</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>82</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>34</v>
@@ -3480,13 +3527,13 @@
         <v>33</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="P15" s="1" t="s">
         <v>36</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="R15" s="1" t="s">
         <v>38</v>
@@ -3498,10 +3545,10 @@
         <v>40</v>
       </c>
       <c r="U15" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="V15" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3512,34 +3559,34 @@
         <v>104</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I16" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="K16" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="J16" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>123</v>
-      </c>
       <c r="L16" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M16" s="1" t="s">
         <v>34</v>
@@ -3548,13 +3595,13 @@
         <v>33</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="R16" s="1" t="s">
         <v>38</v>
@@ -3566,10 +3613,10 @@
         <v>40</v>
       </c>
       <c r="U16" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="V16" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3580,16 +3627,16 @@
         <v>105</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>28</v>
@@ -3598,16 +3645,16 @@
         <v>28</v>
       </c>
       <c r="I17" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="K17" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="J17" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>123</v>
-      </c>
       <c r="L17" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M17" s="1" t="s">
         <v>33</v>
@@ -3616,13 +3663,13 @@
         <v>33</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="R17" s="1" t="s">
         <v>38</v>
@@ -3631,13 +3678,13 @@
         <v>39</v>
       </c>
       <c r="T17" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="U17" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="V17" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3648,16 +3695,16 @@
         <v>106</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>28</v>
@@ -3666,16 +3713,16 @@
         <v>28</v>
       </c>
       <c r="I18" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="K18" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="J18" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>123</v>
-      </c>
       <c r="L18" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>33</v>
@@ -3684,13 +3731,13 @@
         <v>33</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="R18" s="1" t="s">
         <v>38</v>
@@ -3699,13 +3746,13 @@
         <v>39</v>
       </c>
       <c r="T18" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="U18" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="V18" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3716,16 +3763,16 @@
         <v>107</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>28</v>
@@ -3734,16 +3781,16 @@
         <v>28</v>
       </c>
       <c r="I19" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="K19" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="J19" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>123</v>
-      </c>
       <c r="L19" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>33</v>
@@ -3752,13 +3799,13 @@
         <v>33</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="R19" s="1" t="s">
         <v>38</v>
@@ -3767,13 +3814,13 @@
         <v>39</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="U19" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="V19" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3784,16 +3831,16 @@
         <v>200</v>
       </c>
       <c r="C20" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="F20" s="1" t="s">
         <v>162</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>164</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>28</v>
@@ -3802,16 +3849,16 @@
         <v>28</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>33</v>
@@ -3820,13 +3867,13 @@
         <v>33</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="R20" s="1" t="s">
         <v>38</v>
@@ -3838,13 +3885,13 @@
         <v>40</v>
       </c>
       <c r="U20" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="V20" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="W20" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3855,16 +3902,16 @@
         <v>201</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>28</v>
@@ -3873,16 +3920,16 @@
         <v>28</v>
       </c>
       <c r="I21" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="K21" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="J21" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>123</v>
-      </c>
       <c r="L21" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>33</v>
@@ -3891,13 +3938,13 @@
         <v>33</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="R21" s="1" t="s">
         <v>38</v>
@@ -3909,13 +3956,13 @@
         <v>40</v>
       </c>
       <c r="U21" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="V21" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="W21" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3926,16 +3973,16 @@
         <v>202</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>28</v>
@@ -3944,16 +3991,16 @@
         <v>28</v>
       </c>
       <c r="I22" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="K22" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="J22" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>123</v>
-      </c>
       <c r="L22" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>33</v>
@@ -3962,13 +4009,13 @@
         <v>33</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="R22" s="1" t="s">
         <v>38</v>
@@ -3980,13 +4027,13 @@
         <v>40</v>
       </c>
       <c r="U22" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="V22" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="W22" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3997,16 +4044,16 @@
         <v>203</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>28</v>
@@ -4015,16 +4062,16 @@
         <v>28</v>
       </c>
       <c r="I23" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="K23" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="J23" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>123</v>
-      </c>
       <c r="L23" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M23" s="1" t="s">
         <v>33</v>
@@ -4033,13 +4080,13 @@
         <v>33</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="Q23" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="R23" s="1" t="s">
         <v>38</v>
@@ -4051,13 +4098,13 @@
         <v>40</v>
       </c>
       <c r="U23" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="V23" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="W23" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4068,34 +4115,34 @@
         <v>204</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I24" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="K24" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="J24" s="1" t="s">
+      <c r="L24" s="1" t="s">
         <v>185</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="L24" s="1" t="s">
-        <v>187</v>
       </c>
       <c r="M24" s="1" t="s">
         <v>34</v>
@@ -4104,13 +4151,13 @@
         <v>34</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="Q24" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="R24" s="1" t="s">
         <v>38</v>
@@ -4122,13 +4169,13 @@
         <v>40</v>
       </c>
       <c r="U24" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="V24" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="W24" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4139,16 +4186,16 @@
         <v>300</v>
       </c>
       <c r="C25" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>190</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>192</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>28</v>
@@ -4160,13 +4207,13 @@
         <v>82</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M25" s="1" t="s">
         <v>33</v>
@@ -4175,13 +4222,13 @@
         <v>33</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="Q25" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="R25" s="1" t="s">
         <v>38</v>
@@ -4193,13 +4240,13 @@
         <v>40</v>
       </c>
       <c r="U25" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="V25" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="W25" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4210,34 +4257,34 @@
         <v>301</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M26" s="1" t="s">
         <v>33</v>
@@ -4246,13 +4293,13 @@
         <v>33</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="Q26" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="R26" s="1" t="s">
         <v>38</v>
@@ -4264,13 +4311,13 @@
         <v>40</v>
       </c>
       <c r="U26" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="V26" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="W26" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4281,16 +4328,16 @@
         <v>302</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>28</v>
@@ -4302,13 +4349,13 @@
         <v>82</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M27" s="1" t="s">
         <v>33</v>
@@ -4317,13 +4364,13 @@
         <v>33</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="Q27" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="R27" s="1" t="s">
         <v>38</v>
@@ -4335,13 +4382,13 @@
         <v>40</v>
       </c>
       <c r="U27" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="V27" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="W27" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4352,16 +4399,16 @@
         <v>304</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>28</v>
@@ -4373,13 +4420,13 @@
         <v>82</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M28" s="1" t="s">
         <v>33</v>
@@ -4388,13 +4435,13 @@
         <v>33</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="R28" s="1" t="s">
         <v>38</v>
@@ -4406,13 +4453,13 @@
         <v>40</v>
       </c>
       <c r="U28" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="V28" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="W28" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4423,16 +4470,16 @@
         <v>305</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>28</v>
@@ -4444,13 +4491,13 @@
         <v>82</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>33</v>
@@ -4459,13 +4506,13 @@
         <v>33</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="R29" s="1" t="s">
         <v>38</v>
@@ -4477,10 +4524,10 @@
         <v>40</v>
       </c>
       <c r="U29" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="V29" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4491,16 +4538,16 @@
         <v>306</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>28</v>
@@ -4512,13 +4559,13 @@
         <v>46</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M30" s="1" t="s">
         <v>33</v>
@@ -4527,13 +4574,13 @@
         <v>33</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="Q30" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="R30" s="1" t="s">
         <v>38</v>
@@ -4545,10 +4592,10 @@
         <v>40</v>
       </c>
       <c r="U30" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="V30" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4556,28 +4603,28 @@
         <v>400</v>
       </c>
       <c r="C31" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="F31" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="E31" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>228</v>
-      </c>
       <c r="G31" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>28</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M31" s="1" t="s">
         <v>33</v>
@@ -4586,13 +4633,13 @@
         <v>33</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="Q31" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="R31" s="1" t="s">
         <v>38</v>
@@ -4604,16 +4651,16 @@
         <v>40</v>
       </c>
       <c r="U31" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="V31" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="W31" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="X31" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4624,16 +4671,16 @@
         <v>401</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>28</v>
@@ -4642,16 +4689,16 @@
         <v>28</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M32" s="1" t="s">
         <v>33</v>
@@ -4660,13 +4707,13 @@
         <v>33</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="P32" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="Q32" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="R32" s="1" t="s">
         <v>38</v>
@@ -4675,19 +4722,19 @@
         <v>39</v>
       </c>
       <c r="T32" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="U32" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="V32" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="W32" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="32.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="13.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="n">
         <v>32</v>
       </c>
@@ -4695,16 +4742,16 @@
         <v>402</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D33" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="F33" s="3" t="s">
         <v>226</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>228</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>28</v>
@@ -4713,16 +4760,16 @@
         <v>28</v>
       </c>
       <c r="I33" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="K33" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="J33" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>243</v>
-      </c>
       <c r="L33" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M33" s="1" t="s">
         <v>33</v>
@@ -4731,13 +4778,13 @@
         <v>33</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="P33" s="1" t="s">
-        <v>245</v>
+        <v>242</v>
+      </c>
+      <c r="P33" s="2" t="s">
+        <v>243</v>
       </c>
       <c r="Q33" s="1" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="R33" s="1" t="s">
         <v>67</v>
@@ -4749,14 +4796,14 @@
         <v>40</v>
       </c>
       <c r="U33" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="V33" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="W33" s="1"/>
       <c r="X33" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4767,34 +4814,34 @@
         <v>500</v>
       </c>
       <c r="C34" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="D34" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="E34" s="1" t="s">
+      <c r="F34" s="1" t="s">
         <v>248</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>249</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>120</v>
+        <v>28</v>
       </c>
       <c r="I34" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="J34" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="J34" s="1" t="s">
+      <c r="K34" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="K34" s="1" t="s">
-        <v>252</v>
-      </c>
       <c r="L34" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="M34" s="1" t="s">
         <v>33</v>
@@ -4803,13 +4850,13 @@
         <v>34</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="P34" s="1" t="s">
-        <v>159</v>
+        <v>242</v>
+      </c>
+      <c r="P34" s="2" t="s">
+        <v>243</v>
       </c>
       <c r="Q34" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="R34" s="1" t="s">
         <v>67</v>
@@ -4818,16 +4865,16 @@
         <v>68</v>
       </c>
       <c r="T34" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="U34" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="V34" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="W34" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4838,34 +4885,34 @@
         <v>501</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I35" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="K35" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="J35" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="K35" s="1" t="s">
-        <v>260</v>
-      </c>
       <c r="L35" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M35" s="1" t="s">
         <v>33</v>
@@ -4874,13 +4921,13 @@
         <v>33</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="P35" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="Q35" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="R35" s="1" t="s">
         <v>38</v>
@@ -4892,13 +4939,13 @@
         <v>40</v>
       </c>
       <c r="U35" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="V35" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="W35" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4909,16 +4956,16 @@
         <v>502</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>28</v>
@@ -4927,16 +4974,16 @@
         <v>28</v>
       </c>
       <c r="I36" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="K36" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="J36" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="K36" s="1" t="s">
-        <v>267</v>
-      </c>
       <c r="L36" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M36" s="1" t="s">
         <v>33</v>
@@ -4945,13 +4992,13 @@
         <v>34</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="Q36" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="R36" s="1" t="s">
         <v>38</v>
@@ -4963,13 +5010,13 @@
         <v>40</v>
       </c>
       <c r="U36" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="V36" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="n">
         <v>36</v>
       </c>
@@ -4977,16 +5024,16 @@
         <v>503</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>28</v>
@@ -4998,10 +5045,10 @@
         <v>82</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L37" s="1" t="s">
         <v>32</v>
@@ -5013,13 +5060,13 @@
         <v>34</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="P37" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q37" s="1" t="s">
-        <v>273</v>
+        <v>35</v>
+      </c>
+      <c r="P37" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q37" s="3" t="s">
+        <v>271</v>
       </c>
       <c r="R37" s="1" t="s">
         <v>38</v>
@@ -5037,7 +5084,7 @@
         <v>42</v>
       </c>
       <c r="W37" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5048,31 +5095,31 @@
         <v>504</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="L38" s="1" t="s">
         <v>32</v>
@@ -5084,13 +5131,13 @@
         <v>34</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="P38" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="Q38" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="R38" s="1" t="s">
         <v>38</v>
@@ -5108,7 +5155,7 @@
         <v>42</v>
       </c>
       <c r="W38" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5119,16 +5166,16 @@
         <v>505</v>
       </c>
       <c r="C39" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="F39" s="1" t="s">
         <v>281</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>283</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>28</v>
@@ -5137,13 +5184,13 @@
         <v>28</v>
       </c>
       <c r="I39" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="K39" s="1" t="s">
         <v>284</v>
-      </c>
-      <c r="J39" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>286</v>
       </c>
       <c r="L39" s="1" t="s">
         <v>32</v>
@@ -5155,13 +5202,13 @@
         <v>34</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="P39" s="1" t="s">
-        <v>287</v>
+        <v>64</v>
+      </c>
+      <c r="P39" s="2" t="s">
+        <v>243</v>
       </c>
       <c r="Q39" s="1" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="R39" s="1" t="s">
         <v>67</v>
@@ -5179,7 +5226,7 @@
         <v>69</v>
       </c>
       <c r="W39" s="1" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>
@@ -5201,7 +5248,7 @@
   <dimension ref="A1:L38"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="88.58"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="35"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="32.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="32.57"/>
@@ -5213,40 +5260,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>298</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5254,34 +5301,34 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>308</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5289,31 +5336,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="H3" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>315</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5321,34 +5368,34 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="I4" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>321</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5356,34 +5403,34 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="E5" s="1" t="s">
+      <c r="L5" s="1" t="s">
         <v>325</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5391,34 +5438,34 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="L6" s="1" t="s">
         <v>329</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5426,31 +5473,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="L7" s="1" t="s">
         <v>332</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5458,28 +5505,28 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="L8" s="1" t="s">
         <v>335</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5487,31 +5534,31 @@
         <v>100</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="F9" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="H9" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="E9" s="1" t="s">
+      <c r="I9" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="L9" s="1" t="s">
         <v>340</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5519,34 +5566,34 @@
         <v>101</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="H10" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="J10" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="G10" s="1" t="s">
+      <c r="L10" s="1" t="s">
         <v>345</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5554,34 +5601,34 @@
         <v>102</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="F11" s="1" t="s">
+      <c r="H11" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="I11" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="G11" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>309</v>
-      </c>
       <c r="J11" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5589,34 +5636,34 @@
         <v>103</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>353</v>
-      </c>
       <c r="H12" s="1" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5624,34 +5671,34 @@
         <v>104</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="J13" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="E13" s="1" t="s">
+      <c r="L13" s="1" t="s">
         <v>355</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5659,34 +5706,34 @@
         <v>105</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="E14" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="J14" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="L14" s="1" t="s">
         <v>360</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5694,31 +5741,31 @@
         <v>106</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="L15" s="1" t="s">
         <v>363</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5726,34 +5773,34 @@
         <v>107</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="F16" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="J16" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="E16" s="1" t="s">
+      <c r="L16" s="1" t="s">
         <v>368</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="L16" s="1" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5761,34 +5808,34 @@
         <v>108</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="E17" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="F17" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="H17" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="I17" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="F17" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="H17" s="1" t="s">
+      <c r="J17" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="L17" s="1" t="s">
         <v>376</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="L17" s="1" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5796,34 +5843,34 @@
         <v>109</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="F18" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="H18" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="E18" s="1" t="s">
+      <c r="I18" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="J18" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="F18" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="H18" s="1" t="s">
+      <c r="L18" s="1" t="s">
         <v>382</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="L18" s="1" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5831,34 +5878,34 @@
         <v>110</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="F19" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="H19" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="E19" s="1" t="s">
+      <c r="I19" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="J19" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="F19" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="H19" s="1" t="s">
+      <c r="L19" s="1" t="s">
         <v>388</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="L19" s="1" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5866,34 +5913,34 @@
         <v>111</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="J20" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="E20" s="1" t="s">
+      <c r="L20" s="1" t="s">
         <v>392</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5901,34 +5948,34 @@
         <v>112</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="F21" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="G21" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="E21" s="1" t="s">
+      <c r="H21" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="J21" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="G21" s="1" t="s">
+      <c r="L21" s="1" t="s">
         <v>398</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="L21" s="1" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5936,34 +5983,34 @@
         <v>113</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="E22" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="J22" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="L22" s="1" t="s">
         <v>403</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="L22" s="1" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5971,34 +6018,34 @@
         <v>114</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="J23" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="E23" s="1" t="s">
+      <c r="L23" s="1" t="s">
         <v>407</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6006,34 +6053,37 @@
         <v>115</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="H24" s="5" t="s">
         <v>410</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>308</v>
-      </c>
       <c r="I24" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="J24" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="J24" s="4" t="s">
         <v>411</v>
       </c>
+      <c r="K24" s="1" t="s">
+        <v>412</v>
+      </c>
       <c r="L24" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6041,34 +6091,34 @@
         <v>116</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="J25" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="J25" s="4" t="s">
         <v>411</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6076,34 +6126,34 @@
         <v>117</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="J26" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="J26" s="4" t="s">
         <v>411</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6111,34 +6161,34 @@
         <v>118</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D27" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="G27" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="E27" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="F27" s="1" t="s">
+      <c r="H27" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="I27" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="G27" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>309</v>
-      </c>
       <c r="J27" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6146,34 +6196,34 @@
         <v>119</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="L28" s="1" t="s">
         <v>418</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="L28" s="1" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6181,34 +6231,34 @@
         <v>120</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D29" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="G29" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="E29" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="F29" s="1" t="s">
+      <c r="H29" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="I29" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="G29" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>309</v>
-      </c>
       <c r="J29" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6216,34 +6266,34 @@
         <v>129</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F30" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="I30" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="G30" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>309</v>
-      </c>
       <c r="J30" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6251,34 +6301,34 @@
         <v>121</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D31" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="G31" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="E31" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="F31" s="1" t="s">
+      <c r="H31" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="I31" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="G31" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>309</v>
-      </c>
       <c r="J31" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6286,63 +6336,66 @@
         <v>122</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="29.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="n">
         <v>123</v>
       </c>
-      <c r="B33" s="4" t="s">
-        <v>438</v>
+      <c r="B33" s="3" t="s">
+        <v>439</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D33" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>440</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="G33" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="E33" s="5" t="s">
-        <v>439</v>
-      </c>
-      <c r="F33" s="1" t="s">
+      <c r="H33" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="I33" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="G33" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>440</v>
-      </c>
-      <c r="K33" s="3" t="s">
+      <c r="J33" s="4" t="s">
         <v>441</v>
+      </c>
+      <c r="K33" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>443</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6350,34 +6403,34 @@
         <v>124</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D34" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="G34" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="E34" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>307</v>
-      </c>
       <c r="H34" s="1" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6385,34 +6438,34 @@
         <v>125</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D35" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="G35" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="E35" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>307</v>
-      </c>
       <c r="H35" s="1" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6420,34 +6473,34 @@
         <v>126</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D36" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="G36" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="E36" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="F36" s="1" t="s">
+      <c r="H36" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="I36" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="G36" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>309</v>
-      </c>
       <c r="J36" s="1" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6455,34 +6508,34 @@
         <v>127</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C37" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="F37" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="G37" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="E37" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>307</v>
-      </c>
       <c r="H37" s="1" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6490,34 +6543,34 @@
         <v>128</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F38" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="I38" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="G38" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>309</v>
-      </c>
       <c r="J38" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
   </sheetData>
@@ -6541,8 +6594,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:H1048576"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="14.3" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="20.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="34.71"/>
@@ -6552,869 +6605,896 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="56.29"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>466</v>
-      </c>
-      <c r="D1" s="4" t="s">
         <v>467</v>
       </c>
+      <c r="C1" s="7" t="s">
+        <v>468</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>469</v>
+      </c>
       <c r="E1" s="1" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>470</v>
-      </c>
-      <c r="H1" s="4" t="s">
         <v>471</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1" s="7" t="s">
+        <v>472</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>474</v>
+      </c>
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>472</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>473</v>
+      <c r="C2" s="8" t="s">
+        <v>475</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>476</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="G2" s="7"/>
+      <c r="H2" s="3"/>
+    </row>
+    <row r="3" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
         <v>474</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="G2" s="6"/>
-      <c r="H2" s="4"/>
-    </row>
-    <row r="3" customFormat="false" ht="66.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>475</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>476</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>477</v>
+      <c r="C3" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>479</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>479</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="66.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G3" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>481</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>482</v>
+      <c r="C4" s="9" t="s">
+        <v>483</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>484</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>479</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G4" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>484</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>485</v>
+      <c r="C5" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>487</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G5" s="4" t="s">
-        <v>479</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G5" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>487</v>
+      <c r="C6" s="3" t="s">
+        <v>489</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="4" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G6" s="3" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>490</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>491</v>
+      <c r="C7" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>493</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>474</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>475</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>493</v>
+      <c r="C8" s="3" t="s">
+        <v>495</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G8" s="4" t="s">
-        <v>496</v>
+      <c r="G8" s="3" t="s">
+        <v>498</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>498</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>499</v>
+      <c r="C9" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>501</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="4" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G9" s="3" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>502</v>
+      <c r="C10" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>504</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G10" s="4" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G10" s="3" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>504</v>
-      </c>
-      <c r="D11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>505</v>
       </c>
+      <c r="D11" s="2" t="s">
+        <v>506</v>
+      </c>
       <c r="E11" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G11" s="4" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G11" s="3" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>507</v>
-      </c>
-      <c r="D12" s="1" t="s">
+      <c r="C12" s="3" t="s">
         <v>508</v>
       </c>
+      <c r="D12" s="2" t="s">
+        <v>509</v>
+      </c>
       <c r="E12" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G12" s="4" t="s">
-        <v>479</v>
+      <c r="G12" s="3" t="s">
+        <v>481</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="D13" s="1" t="s">
         <v>511</v>
       </c>
+      <c r="D13" s="2" t="s">
+        <v>512</v>
+      </c>
       <c r="E13" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G13" s="4" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G13" s="3" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>513</v>
-      </c>
-      <c r="D14" s="1" t="s">
+      <c r="C14" s="3" t="s">
         <v>514</v>
       </c>
+      <c r="D14" s="2" t="s">
+        <v>515</v>
+      </c>
       <c r="E14" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G14" s="4" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G14" s="3" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>516</v>
-      </c>
-      <c r="D15" s="1" t="s">
+      <c r="C15" s="3" t="s">
         <v>517</v>
       </c>
+      <c r="D15" s="2" t="s">
+        <v>518</v>
+      </c>
       <c r="E15" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G15" s="4" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G15" s="3" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>518</v>
-      </c>
-      <c r="D16" s="1" t="s">
+      <c r="C16" s="3" t="s">
         <v>519</v>
       </c>
+      <c r="D16" s="3" t="s">
+        <v>520</v>
+      </c>
       <c r="E16" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G16" s="4" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G16" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>520</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>521</v>
+      <c r="C17" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>523</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G17" s="4" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G17" s="3" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="4" t="s">
-        <v>522</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>523</v>
+      <c r="C18" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>525</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G18" s="4" t="s">
-        <v>524</v>
+      <c r="G18" s="3" t="s">
+        <v>526</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="4" t="s">
-        <v>526</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>527</v>
+      <c r="C19" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>529</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G19" s="4" t="s">
-        <v>524</v>
+      <c r="G19" s="3" t="s">
+        <v>526</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="4" t="s">
-        <v>529</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>530</v>
+      <c r="C20" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>532</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G20" s="4" t="s">
-        <v>524</v>
+      <c r="G20" s="3" t="s">
+        <v>526</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>474</v>
+      </c>
       <c r="B21" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="C21" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>533</v>
+      <c r="C21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>534</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G21" s="4" t="s">
-        <v>524</v>
+      <c r="G21" s="3" t="s">
+        <v>526</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="B22" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="B22" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="4" t="s">
-        <v>535</v>
-      </c>
-      <c r="D22" s="1" t="s">
+      <c r="C22" s="3" t="s">
         <v>536</v>
       </c>
+      <c r="D22" s="2" t="s">
+        <v>537</v>
+      </c>
       <c r="E22" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G22" s="4" t="s">
-        <v>524</v>
+      <c r="G22" s="3" t="s">
+        <v>526</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="4" t="s">
-        <v>539</v>
+      <c r="C23" s="3" t="s">
+        <v>540</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="G23" s="4"/>
-    </row>
-    <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>118</v>
+      </c>
+      <c r="G23" s="3"/>
+    </row>
+    <row r="24" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>540</v>
-      </c>
       <c r="E24" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="G24" s="4"/>
-    </row>
-    <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>118</v>
+      </c>
+      <c r="G24" s="3"/>
+    </row>
+    <row r="25" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>543</v>
-      </c>
-      <c r="D25" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="C25" s="9" t="s">
         <v>544</v>
       </c>
+      <c r="D25" s="9" t="s">
+        <v>545</v>
+      </c>
       <c r="E25" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G25" s="4" t="s">
-        <v>479</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G25" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>546</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>546</v>
+        <v>288</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>547</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>547</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>118</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="D28" s="1" t="s">
         <v>550</v>
       </c>
+      <c r="D28" s="2" t="s">
+        <v>551</v>
+      </c>
       <c r="E28" s="1" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G28" s="4" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G28" s="3" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>551</v>
-      </c>
-      <c r="D29" s="1" t="s">
         <v>552</v>
       </c>
+      <c r="D29" s="2" t="s">
+        <v>553</v>
+      </c>
       <c r="E29" s="1" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G29" s="4" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G29" s="3" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>553</v>
-      </c>
-      <c r="D30" s="1" t="s">
         <v>554</v>
       </c>
+      <c r="D30" s="2" t="s">
+        <v>555</v>
+      </c>
       <c r="E30" s="1" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G30" s="4" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G30" s="3" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="D31" s="1" t="s">
         <v>556</v>
       </c>
+      <c r="D31" s="2" t="s">
+        <v>557</v>
+      </c>
       <c r="E31" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G31" s="4" t="s">
-        <v>496</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G31" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="H31" s="11" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G32" s="4" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G32" s="3" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="D33" s="1" t="s">
         <v>561</v>
       </c>
+      <c r="D33" s="2" t="s">
+        <v>562</v>
+      </c>
       <c r="E33" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G33" s="4" t="s">
-        <v>479</v>
-      </c>
-      <c r="H33" s="11" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G33" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="H33" s="12" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>563</v>
-      </c>
-      <c r="D34" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>564</v>
       </c>
+      <c r="D34" s="2" t="s">
+        <v>565</v>
+      </c>
       <c r="E34" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G34" s="4" t="s">
-        <v>479</v>
+      <c r="G34" s="3" t="s">
+        <v>481</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>566</v>
-      </c>
-      <c r="D35" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>567</v>
       </c>
+      <c r="D35" s="2" t="s">
+        <v>568</v>
+      </c>
       <c r="E35" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G35" s="4" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="12"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-    </row>
-    <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="12"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-    </row>
-    <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="12"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-    </row>
-    <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="12"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
-    </row>
+      <c r="G35" s="3" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>570</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B37" s="5"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+    </row>
+    <row r="38" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B38" s="5"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+    </row>
+    <row r="39" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B39" s="5"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -7440,7 +7520,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -7449,16 +7529,16 @@
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7475,7 +7555,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>33</v>
@@ -7495,7 +7575,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>33</v>
@@ -7509,13 +7589,13 @@
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>2</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>33</v>
@@ -7529,13 +7609,13 @@
         <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>2</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>33</v>
@@ -7555,7 +7635,7 @@
         <v>2</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>33</v>
@@ -7575,7 +7655,7 @@
         <v>2</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>33</v>
@@ -7595,7 +7675,7 @@
         <v>3</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>33</v>
@@ -7615,7 +7695,7 @@
         <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>33</v>
@@ -7635,7 +7715,7 @@
         <v>5</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>33</v>
@@ -7649,13 +7729,13 @@
         <v>10</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>5</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>33</v>
@@ -7669,13 +7749,13 @@
         <v>100</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>100</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>33</v>
@@ -7689,13 +7769,13 @@
         <v>101</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>101</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>33</v>
@@ -7709,13 +7789,13 @@
         <v>101</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>102</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>33</v>
@@ -7729,13 +7809,13 @@
         <v>101</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>103</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>33</v>
@@ -7749,13 +7829,13 @@
         <v>102</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>104</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>33</v>
@@ -7769,13 +7849,13 @@
         <v>103</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>105</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>33</v>
@@ -7789,13 +7869,13 @@
         <v>104</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>141</v>
+        <v>575</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>106</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>33</v>
@@ -7809,19 +7889,19 @@
         <v>105</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>107</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7832,19 +7912,19 @@
         <v>105</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D20" s="1" t="n">
         <v>108</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7855,13 +7935,13 @@
         <v>106</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D21" s="1" t="n">
         <v>109</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>33</v>
@@ -7875,19 +7955,19 @@
         <v>107</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D22" s="1" t="n">
         <v>107</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7898,13 +7978,13 @@
         <v>200</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D23" s="1" t="n">
         <v>110</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>33</v>
@@ -7918,13 +7998,13 @@
         <v>201</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D24" s="1" t="n">
         <v>111</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>34</v>
@@ -7938,19 +8018,19 @@
         <v>202</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D25" s="1" t="n">
         <v>107</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7961,13 +8041,13 @@
         <v>202</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D26" s="1" t="n">
         <v>108</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>33</v>
@@ -7981,13 +8061,13 @@
         <v>203</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D27" s="1" t="n">
         <v>112</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>33</v>
@@ -8001,13 +8081,13 @@
         <v>204</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D28" s="1" t="n">
         <v>113</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>33</v>
@@ -8021,16 +8101,16 @@
         <v>300</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D29" s="1" t="n">
         <v>114</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>33</v>
+        <v>118</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8041,13 +8121,13 @@
         <v>300</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D30" s="1" t="n">
         <v>115</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>33</v>
@@ -8061,13 +8141,13 @@
         <v>300</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D31" s="1" t="n">
         <v>116</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>33</v>
@@ -8081,13 +8161,13 @@
         <v>300</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D32" s="1" t="n">
         <v>117</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>33</v>
@@ -8101,13 +8181,13 @@
         <v>301</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D33" s="1" t="n">
         <v>107</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>33</v>
@@ -8121,13 +8201,13 @@
         <v>301</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D34" s="1" t="n">
         <v>118</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>33</v>
@@ -8141,16 +8221,16 @@
         <v>301</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D35" s="1" t="n">
         <v>119</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8161,13 +8241,13 @@
         <v>302</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D36" s="1" t="n">
         <v>120</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>33</v>
@@ -8181,13 +8261,13 @@
         <v>302</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D37" s="1" t="n">
         <v>129</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>33</v>
@@ -8201,13 +8281,13 @@
         <v>304</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D38" s="1" t="n">
         <v>128</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>33</v>
@@ -8221,13 +8301,13 @@
         <v>305</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D39" s="1" t="n">
         <v>121</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>33</v>
@@ -8241,13 +8321,13 @@
         <v>305</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D40" s="1" t="n">
         <v>122</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>33</v>
@@ -8261,13 +8341,13 @@
         <v>306</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D41" s="1" t="n">
         <v>121</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>33</v>
@@ -8280,14 +8360,14 @@
       <c r="B42" s="1" t="n">
         <v>402</v>
       </c>
-      <c r="C42" s="4" t="s">
-        <v>240</v>
+      <c r="C42" s="3" t="s">
+        <v>238</v>
       </c>
       <c r="D42" s="1" t="n">
         <v>123</v>
       </c>
-      <c r="E42" s="4" t="s">
-        <v>438</v>
+      <c r="E42" s="3" t="s">
+        <v>439</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>33</v>
@@ -8301,13 +8381,13 @@
         <v>401</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D43" s="1" t="n">
         <v>124</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>33</v>
@@ -8321,19 +8401,19 @@
         <v>401</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D44" s="1" t="n">
         <v>125</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>34</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8344,13 +8424,13 @@
         <v>500</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D45" s="1" t="n">
         <v>6</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>33</v>
@@ -8364,13 +8444,13 @@
         <v>501</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D46" s="1" t="n">
         <v>126</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>33</v>
@@ -8384,13 +8464,13 @@
         <v>502</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D47" s="1" t="n">
         <v>127</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>33</v>
@@ -8404,13 +8484,13 @@
         <v>503</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D48" s="1" t="n">
         <v>3</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>33</v>
@@ -8424,13 +8504,13 @@
         <v>504</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D49" s="1" t="n">
         <v>3</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>33</v>
@@ -8444,13 +8524,13 @@
         <v>505</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D50" s="1" t="n">
         <v>7</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>335</v>
+        <v>580</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>33</v>
@@ -8483,25 +8563,25 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>574</v>
+        <v>581</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>576</v>
+        <v>583</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>578</v>
+        <v>585</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8515,16 +8595,16 @@
         <v>25</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>579</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>580</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>581</v>
+        <v>586</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>588</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="I2" s="1"/>
     </row>
@@ -8533,22 +8613,22 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>583</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>584</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>585</v>
+        <v>590</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>592</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>586</v>
+        <v>593</v>
       </c>
       <c r="I3" s="1"/>
     </row>
@@ -8557,22 +8637,22 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>588</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>589</v>
+        <v>594</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>596</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>590</v>
+        <v>597</v>
       </c>
       <c r="I4" s="1"/>
     </row>
@@ -8581,19 +8661,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>591</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>592</v>
+        <v>598</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>599</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>593</v>
+        <v>600</v>
       </c>
       <c r="I5" s="1"/>
     </row>
@@ -8602,19 +8682,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>594</v>
+        <v>601</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="I6" s="1"/>
     </row>
@@ -8623,22 +8703,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>597</v>
+        <v>604</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>598</v>
+        <v>605</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>599</v>
+        <v>606</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>600</v>
+        <v>607</v>
       </c>
       <c r="I7" s="1"/>
     </row>
@@ -8647,19 +8727,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>601</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>602</v>
+        <v>608</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>609</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="I8" s="1"/>
     </row>
@@ -8685,92 +8765,93 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="29.56"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="37.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="29.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="60.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="22.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="92.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="27.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="84.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="29.91"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>604</v>
+        <v>611</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>605</v>
+        <v>569</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>468</v>
+        <v>503</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>570</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>610</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>611</v>
+        <v>616</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>617</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="12" t="s">
-        <v>613</v>
+      <c r="B3" s="5" t="s">
+        <v>619</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>618</v>
+        <v>497</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>624</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8778,19 +8859,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>620</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>611</v>
+        <v>626</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>617</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8798,19 +8879,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8818,19 +8899,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8838,19 +8919,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>630</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>611</v>
+        <v>636</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>617</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8858,19 +8939,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8878,19 +8959,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8898,19 +8979,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8918,85 +8999,85 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="41" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>644</v>
+      <c r="B13" s="3" t="s">
+        <v>650</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>645</v>
+        <v>188</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>651</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>647</v>
+      <c r="B14" s="3" t="s">
+        <v>653</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>649</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>650</v>
+        <v>655</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>656</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>651</v>
+      <c r="B15" s="3" t="s">
+        <v>657</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>654</v>
+        <v>659</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>660</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9004,39 +9085,39 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>656</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>611</v>
+        <v>662</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>617</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>658</v>
+      <c r="B17" s="3" t="s">
+        <v>664</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
     </row>
   </sheetData>
@@ -9065,145 +9146,145 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>671</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>665</v>
-      </c>
       <c r="D4" s="1" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>203</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9283,13 +9364,13 @@
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>604</v>
+        <v>611</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="F1" s="1"/>
-      <c r="G1" s="12"/>
+      <c r="G1" s="5"/>
       <c r="H1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9303,7 +9384,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="F2" s="1"/>
       <c r="H2" s="1"/>
@@ -9318,8 +9399,8 @@
       <c r="C3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>613</v>
+      <c r="D3" s="3" t="s">
+        <v>619</v>
       </c>
       <c r="F3" s="1"/>
       <c r="H3" s="1"/>
@@ -9329,13 +9410,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="F4" s="1"/>
       <c r="H4" s="1"/>
@@ -9345,13 +9426,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="F5" s="1"/>
       <c r="H5" s="1"/>
@@ -9367,7 +9448,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="F6" s="1"/>
       <c r="H6" s="1"/>
@@ -9382,8 +9463,8 @@
       <c r="C7" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>613</v>
+      <c r="D7" s="3" t="s">
+        <v>619</v>
       </c>
       <c r="F7" s="1"/>
       <c r="H7" s="1"/>
@@ -9399,7 +9480,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="F8" s="1"/>
       <c r="H8" s="1"/>
@@ -9415,7 +9496,7 @@
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="F9" s="1"/>
       <c r="H9" s="1"/>
@@ -9431,7 +9512,7 @@
         <v>4</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="F10" s="1"/>
       <c r="H10" s="1"/>
@@ -9441,13 +9522,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>4</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="F11" s="1"/>
       <c r="H11" s="1"/>
@@ -9457,16 +9538,16 @@
         <v>100</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>5</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="F12" s="1"/>
-      <c r="G12" s="12"/>
+      <c r="G12" s="5"/>
       <c r="H12" s="1"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9474,16 +9555,16 @@
         <v>101</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>5</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="F13" s="1"/>
-      <c r="G13" s="12"/>
+      <c r="G13" s="5"/>
       <c r="H13" s="1"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9491,16 +9572,16 @@
         <v>102</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>6</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="F14" s="1"/>
-      <c r="G14" s="12"/>
+      <c r="G14" s="5"/>
       <c r="H14" s="1"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9508,13 +9589,13 @@
         <v>103</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>6</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="F15" s="1"/>
       <c r="H15" s="1"/>
@@ -9524,13 +9605,13 @@
         <v>104</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>141</v>
+        <v>575</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>6</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="F16" s="1"/>
       <c r="H16" s="1"/>
@@ -9540,13 +9621,13 @@
         <v>105</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>7</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="F17" s="1"/>
       <c r="H17" s="1"/>
@@ -9556,13 +9637,13 @@
         <v>106</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>7</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="F18" s="1"/>
       <c r="H18" s="1"/>
@@ -9572,13 +9653,13 @@
         <v>107</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C19" s="1" t="n">
         <v>9</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9586,13 +9667,13 @@
         <v>200</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C20" s="1" t="n">
         <v>8</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -9602,13 +9683,13 @@
         <v>201</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C21" s="1" t="n">
         <v>9</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9616,13 +9697,13 @@
         <v>202</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>9</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9630,13 +9711,13 @@
         <v>203</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>9</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9644,13 +9725,13 @@
         <v>204</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>8</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9658,13 +9739,13 @@
         <v>300</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>10</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9672,13 +9753,13 @@
         <v>301</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C26" s="1" t="n">
         <v>10</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9686,13 +9767,13 @@
         <v>302</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>11</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9700,13 +9781,13 @@
         <v>304</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C28" s="1" t="n">
         <v>11</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9714,13 +9795,13 @@
         <v>305</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C29" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="D29" s="4" t="s">
-        <v>694</v>
+      <c r="D29" s="3" t="s">
+        <v>700</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9728,13 +9809,13 @@
         <v>306</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C30" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="D30" s="4" t="s">
-        <v>694</v>
+      <c r="D30" s="3" t="s">
+        <v>700</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9742,13 +9823,13 @@
         <v>402</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C31" s="1" t="n">
         <v>15</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9756,13 +9837,13 @@
         <v>401</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C32" s="1" t="n">
         <v>15</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9770,13 +9851,13 @@
         <v>500</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C33" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="D33" s="4" t="s">
-        <v>647</v>
+      <c r="D33" s="3" t="s">
+        <v>653</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9784,13 +9865,13 @@
         <v>501</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C34" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="D34" s="4" t="s">
-        <v>651</v>
+      <c r="D34" s="3" t="s">
+        <v>657</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9798,13 +9879,13 @@
         <v>502</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C35" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="D35" s="4" t="s">
-        <v>651</v>
+      <c r="D35" s="3" t="s">
+        <v>657</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9812,13 +9893,13 @@
         <v>503</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C36" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="D36" s="4" t="s">
-        <v>647</v>
+      <c r="D36" s="3" t="s">
+        <v>653</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9826,13 +9907,13 @@
         <v>504</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C37" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="D37" s="4" t="s">
-        <v>647</v>
+      <c r="D37" s="3" t="s">
+        <v>653</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9840,13 +9921,13 @@
         <v>505</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C38" s="1" t="n">
         <v>16</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
     </row>
   </sheetData>

--- a/fiches indicateurs.xlsx
+++ b/fiches indicateurs.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="indicateurs" sheetId="1" state="visible" r:id="rId3"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1862" uniqueCount="702">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1862" uniqueCount="703">
   <si>
     <t xml:space="preserve">fiche_indicateur</t>
   </si>
@@ -1408,6 +1408,9 @@
   </si>
   <si>
     <t xml:space="preserve">https://georep.nc/node/1323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tous les mois</t>
   </si>
   <si>
     <t xml:space="preserve">Informations brutes géologiques et techniques des ouvrages souterrains – DIMENC/SGNC</t>
@@ -6526,16 +6529,16 @@
         <v>304</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>305</v>
+        <v>459</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>305</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6543,13 +6546,13 @@
         <v>128</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>428</v>
@@ -6561,16 +6564,16 @@
         <v>304</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>306</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
   </sheetData>
@@ -6607,45 +6610,45 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>118</v>
@@ -6655,448 +6658,448 @@
     </row>
     <row r="3" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>118</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>20</v>
@@ -7105,62 +7108,62 @@
         <v>20</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>118</v>
@@ -7169,19 +7172,19 @@
     </row>
     <row r="24" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>541</v>
-      </c>
       <c r="E24" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>118</v>
@@ -7190,290 +7193,290 @@
     </row>
     <row r="25" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>287</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>288</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>118</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>296</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>118</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>289</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>290</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>291</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>292</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>293</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>294</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H33" s="12" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>295</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>298</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7520,7 +7523,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -7538,7 +7541,7 @@
         <v>6</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7869,7 +7872,7 @@
         <v>104</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>106</v>
@@ -7901,7 +7904,7 @@
         <v>33</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7924,7 +7927,7 @@
         <v>33</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7967,7 +7970,7 @@
         <v>33</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8030,7 +8033,7 @@
         <v>33</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8287,7 +8290,7 @@
         <v>128</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>33</v>
@@ -8413,7 +8416,7 @@
         <v>34</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8530,7 +8533,7 @@
         <v>7</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>33</v>
@@ -8563,25 +8566,25 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8595,16 +8598,16 @@
         <v>25</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="I2" s="1"/>
     </row>
@@ -8619,16 +8622,16 @@
         <v>25</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="I3" s="1"/>
     </row>
@@ -8643,16 +8646,16 @@
         <v>160</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="I4" s="1"/>
     </row>
@@ -8667,13 +8670,13 @@
         <v>160</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="I5" s="1"/>
     </row>
@@ -8688,13 +8691,13 @@
         <v>224</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="I6" s="1"/>
     </row>
@@ -8706,19 +8709,19 @@
         <v>246</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>160</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="I7" s="1"/>
     </row>
@@ -8733,13 +8736,13 @@
         <v>160</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="I8" s="1"/>
     </row>
@@ -8773,25 +8776,25 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8799,19 +8802,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8819,19 +8822,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8839,19 +8842,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8859,19 +8862,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8879,19 +8882,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>115</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8899,19 +8902,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>115</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8919,19 +8922,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>115</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8939,19 +8942,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>159</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8959,19 +8962,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>159</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8979,19 +8982,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>188</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8999,19 +9002,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>188</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="41" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9019,19 +9022,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>188</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9039,22 +9042,22 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>246</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9062,22 +9065,22 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>246</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9085,19 +9088,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>223</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9105,19 +9108,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>279</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
   </sheetData>
@@ -9146,145 +9149,145 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>203</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9364,10 +9367,10 @@
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="5"/>
@@ -9384,7 +9387,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="F2" s="1"/>
       <c r="H2" s="1"/>
@@ -9400,7 +9403,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="F3" s="1"/>
       <c r="H3" s="1"/>
@@ -9416,7 +9419,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="F4" s="1"/>
       <c r="H4" s="1"/>
@@ -9432,7 +9435,7 @@
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="F5" s="1"/>
       <c r="H5" s="1"/>
@@ -9448,7 +9451,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="F6" s="1"/>
       <c r="H6" s="1"/>
@@ -9464,7 +9467,7 @@
         <v>2</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="F7" s="1"/>
       <c r="H7" s="1"/>
@@ -9480,7 +9483,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="F8" s="1"/>
       <c r="H8" s="1"/>
@@ -9496,7 +9499,7 @@
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="F9" s="1"/>
       <c r="H9" s="1"/>
@@ -9512,7 +9515,7 @@
         <v>4</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="F10" s="1"/>
       <c r="H10" s="1"/>
@@ -9528,7 +9531,7 @@
         <v>4</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="F11" s="1"/>
       <c r="H11" s="1"/>
@@ -9544,7 +9547,7 @@
         <v>5</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="5"/>
@@ -9561,7 +9564,7 @@
         <v>5</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="5"/>
@@ -9578,7 +9581,7 @@
         <v>6</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="5"/>
@@ -9595,7 +9598,7 @@
         <v>6</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="F15" s="1"/>
       <c r="H15" s="1"/>
@@ -9605,13 +9608,13 @@
         <v>104</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>6</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="F16" s="1"/>
       <c r="H16" s="1"/>
@@ -9627,7 +9630,7 @@
         <v>7</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="F17" s="1"/>
       <c r="H17" s="1"/>
@@ -9643,7 +9646,7 @@
         <v>7</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="F18" s="1"/>
       <c r="H18" s="1"/>
@@ -9659,7 +9662,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9673,7 +9676,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -9689,7 +9692,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9703,7 +9706,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9717,7 +9720,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9731,7 +9734,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9745,7 +9748,7 @@
         <v>10</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9759,7 +9762,7 @@
         <v>10</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9773,7 +9776,7 @@
         <v>11</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9787,7 +9790,7 @@
         <v>11</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9801,7 +9804,7 @@
         <v>12</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9815,7 +9818,7 @@
         <v>12</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9829,7 +9832,7 @@
         <v>15</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9843,7 +9846,7 @@
         <v>15</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9857,7 +9860,7 @@
         <v>13</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9871,7 +9874,7 @@
         <v>14</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9885,7 +9888,7 @@
         <v>14</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9899,7 +9902,7 @@
         <v>13</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9913,7 +9916,7 @@
         <v>13</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9927,7 +9930,7 @@
         <v>16</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
   </sheetData>

--- a/fiches indicateurs.xlsx
+++ b/fiches indicateurs.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1862" uniqueCount="703">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1864" uniqueCount="706">
   <si>
     <t xml:space="preserve">fiche_indicateur</t>
   </si>
@@ -1022,10 +1022,43 @@
     <t xml:space="preserve">Les typologies de captages doivent être standardisées pour assurer une comparaison cohérente ; certaines informations sont descriptives et susceptibles d'évoluer sans impact direct sur la criticité. Verifier que la données est bien à jour du GEOREP.</t>
   </si>
   <si>
-    <t xml:space="preserve">Bilan Besoin Ressource (nom à vérifier)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bilan DAVAR diffusion interne – contacter DAVAR</t>
+    <t xml:space="preserve">Bilan Besoin Ressource</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.arcgis.com/home/item.html?id=6d48f295daf5471a842054d9e050765d</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">La couche BBR (bilan besoin / ressources) est calculée à partir des débits caractéristiques d’étiage médian (DCE2) auquel sont soustraits l'ensemble des </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">prélèvements d’eau autorisés</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">https://georep.nc/actualites/nouvelle-donnee-en-hydrologie-le-bilan-besoin-ressource</t>
   </si>
   <si>
     <t xml:space="preserve">Donnée issue d’un modèle nécessitant validation et mise à jour régulière.</t>
@@ -1816,6 +1849,9 @@
     <t xml:space="preserve">si utilisation du 200 000</t>
   </si>
   <si>
+    <t xml:space="preserve">Bilan Besoin Ressource (nom à vérifier)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Base de données ATYA (nom à vérifier)</t>
   </si>
   <si>
@@ -2189,7 +2225,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -2215,6 +2251,13 @@
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
@@ -2280,7 +2323,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2301,15 +2344,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2325,11 +2372,11 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5471,7 +5518,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
@@ -5485,10 +5532,13 @@
         <v>301</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>312</v>
+        <v>303</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>304</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>305</v>
@@ -5496,11 +5546,14 @@
       <c r="I7" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>331</v>
+      <c r="J7" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>333</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5508,7 +5561,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>300</v>
@@ -5526,10 +5579,10 @@
         <v>305</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5537,16 +5590,16 @@
         <v>100</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>301</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>303</v>
@@ -5555,13 +5608,13 @@
         <v>304</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>306</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5569,13 +5622,13 @@
         <v>101</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>317</v>
@@ -5584,7 +5637,7 @@
         <v>303</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>305</v>
@@ -5593,10 +5646,10 @@
         <v>306</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5604,13 +5657,13 @@
         <v>102</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>317</v>
@@ -5619,7 +5672,7 @@
         <v>303</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>305</v>
@@ -5628,10 +5681,10 @@
         <v>306</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5639,13 +5692,13 @@
         <v>103</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>317</v>
@@ -5654,7 +5707,7 @@
         <v>318</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>305</v>
@@ -5663,10 +5716,10 @@
         <v>306</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5674,16 +5727,16 @@
         <v>104</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>301</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>303</v>
@@ -5692,16 +5745,16 @@
         <v>304</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>306</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5709,13 +5762,13 @@
         <v>105</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>317</v>
@@ -5733,10 +5786,10 @@
         <v>306</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5744,16 +5797,16 @@
         <v>106</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>301</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>303</v>
@@ -5768,7 +5821,7 @@
         <v>306</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5776,16 +5829,16 @@
         <v>107</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>301</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>303</v>
@@ -5794,16 +5847,16 @@
         <v>304</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>306</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5811,16 +5864,16 @@
         <v>108</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>303</v>
@@ -5829,16 +5882,16 @@
         <v>304</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5846,16 +5899,16 @@
         <v>109</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>303</v>
@@ -5864,16 +5917,16 @@
         <v>304</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5881,16 +5934,16 @@
         <v>110</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>303</v>
@@ -5899,16 +5952,16 @@
         <v>304</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>306</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5916,34 +5969,34 @@
         <v>111</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>303</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5951,34 +6004,34 @@
         <v>112</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>301</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>303</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>305</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5986,13 +6039,13 @@
         <v>113</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>311</v>
@@ -6010,10 +6063,10 @@
         <v>306</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6021,16 +6074,16 @@
         <v>114</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>301</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>303</v>
@@ -6045,10 +6098,10 @@
         <v>306</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6056,37 +6109,37 @@
         <v>115</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>303</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>410</v>
+        <v>345</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>412</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>306</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6094,13 +6147,13 @@
         <v>116</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>317</v>
@@ -6109,7 +6162,7 @@
         <v>318</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>305</v>
@@ -6118,10 +6171,10 @@
         <v>306</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6129,13 +6182,13 @@
         <v>117</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>317</v>
@@ -6144,7 +6197,7 @@
         <v>318</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>305</v>
@@ -6153,10 +6206,10 @@
         <v>306</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6164,16 +6217,16 @@
         <v>118</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>301</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>303</v>
@@ -6188,10 +6241,10 @@
         <v>306</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6199,16 +6252,16 @@
         <v>119</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>301</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>303</v>
@@ -6223,10 +6276,10 @@
         <v>306</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6234,16 +6287,16 @@
         <v>120</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>301</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>303</v>
@@ -6258,10 +6311,10 @@
         <v>306</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6269,16 +6322,16 @@
         <v>129</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>303</v>
@@ -6287,16 +6340,16 @@
         <v>304</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>306</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6304,16 +6357,16 @@
         <v>121</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>301</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>303</v>
@@ -6328,10 +6381,10 @@
         <v>306</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6339,7 +6392,7 @@
         <v>122</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>300</v>
@@ -6357,10 +6410,10 @@
         <v>306</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="29.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6368,16 +6421,16 @@
         <v>123</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="E33" s="6" t="s">
-        <v>440</v>
+      <c r="E33" s="7" t="s">
+        <v>442</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>303</v>
@@ -6392,13 +6445,13 @@
         <v>306</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6406,16 +6459,16 @@
         <v>124</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>301</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>303</v>
@@ -6427,13 +6480,13 @@
         <v>305</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6441,16 +6494,16 @@
         <v>125</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>301</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>303</v>
@@ -6462,13 +6515,13 @@
         <v>305</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6476,16 +6529,16 @@
         <v>126</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>301</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>303</v>
@@ -6500,10 +6553,10 @@
         <v>306</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6511,7 +6564,7 @@
         <v>127</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>300</v>
@@ -6520,7 +6573,7 @@
         <v>301</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>303</v>
@@ -6529,16 +6582,16 @@
         <v>304</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>305</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6546,16 +6599,16 @@
         <v>128</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>303</v>
@@ -6564,22 +6617,23 @@
         <v>304</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>306</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L38"/>
   <hyperlinks>
-    <hyperlink ref="E33" r:id="rId1" display="https://georep-dtsi-sgt.opendata.arcgis.com/documents/d7ab36bb69954aea882a63993428357a/about"/>
+    <hyperlink ref="J7" r:id="rId1" display="prélèvements d’eau autorisés"/>
+    <hyperlink ref="E33" r:id="rId2" display="https://georep-dtsi-sgt.opendata.arcgis.com/documents/d7ab36bb69954aea882a63993428357a/about"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -6588,7 +6642,7 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
-  <drawing r:id="rId2"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -6610,496 +6664,496 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>468</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>469</v>
+        <v>470</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>471</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>473</v>
+        <v>474</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>475</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="8" t="s">
-        <v>476</v>
+      <c r="C2" s="9" t="s">
+        <v>478</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="G2" s="7"/>
+      <c r="G2" s="8"/>
       <c r="H2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="9" t="s">
-        <v>479</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>480</v>
+      <c r="C3" s="10" t="s">
+        <v>481</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>482</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="9" t="s">
-        <v>484</v>
+      <c r="C4" s="10" t="s">
+        <v>486</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>118</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>20</v>
@@ -7108,62 +7162,62 @@
         <v>20</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>118</v>
@@ -7172,19 +7226,19 @@
     </row>
     <row r="24" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>118</v>
@@ -7193,306 +7247,306 @@
     </row>
     <row r="25" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="C25" s="9" t="s">
-        <v>545</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>546</v>
+      <c r="C25" s="10" t="s">
+        <v>547</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>548</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="C26" s="10" t="s">
-        <v>548</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>548</v>
+      <c r="C26" s="11" t="s">
+        <v>550</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>550</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>118</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>296</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>118</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>289</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>290</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>291</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>292</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>499</v>
-      </c>
-      <c r="H31" s="11" t="s">
-        <v>559</v>
+        <v>501</v>
+      </c>
+      <c r="H31" s="12" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>293</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>294</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>482</v>
-      </c>
-      <c r="H33" s="12" t="s">
-        <v>564</v>
+        <v>484</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>566</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>295</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>298</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>570</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>571</v>
+        <v>572</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>573</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="5"/>
+      <c r="B37" s="6"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
     </row>
     <row r="38" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="5"/>
+      <c r="B38" s="6"/>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
     </row>
     <row r="39" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="5"/>
+      <c r="B39" s="6"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
@@ -7523,7 +7577,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -7541,7 +7595,7 @@
         <v>6</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7758,7 +7812,7 @@
         <v>100</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>33</v>
@@ -7778,7 +7832,7 @@
         <v>101</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>33</v>
@@ -7798,7 +7852,7 @@
         <v>102</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>33</v>
@@ -7818,7 +7872,7 @@
         <v>103</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>33</v>
@@ -7838,7 +7892,7 @@
         <v>104</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>33</v>
@@ -7858,7 +7912,7 @@
         <v>105</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>33</v>
@@ -7872,13 +7926,13 @@
         <v>104</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>106</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>33</v>
@@ -7898,13 +7952,13 @@
         <v>107</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>33</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7921,13 +7975,13 @@
         <v>108</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>33</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7944,7 +7998,7 @@
         <v>109</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>33</v>
@@ -7964,13 +8018,13 @@
         <v>107</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>33</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7987,7 +8041,7 @@
         <v>110</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>33</v>
@@ -8007,7 +8061,7 @@
         <v>111</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>34</v>
@@ -8027,13 +8081,13 @@
         <v>107</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>33</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8050,7 +8104,7 @@
         <v>108</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>33</v>
@@ -8070,7 +8124,7 @@
         <v>112</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>33</v>
@@ -8090,7 +8144,7 @@
         <v>113</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>33</v>
@@ -8110,7 +8164,7 @@
         <v>114</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>118</v>
@@ -8130,7 +8184,7 @@
         <v>115</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>33</v>
@@ -8150,7 +8204,7 @@
         <v>116</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>33</v>
@@ -8170,7 +8224,7 @@
         <v>117</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>33</v>
@@ -8190,7 +8244,7 @@
         <v>107</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>33</v>
@@ -8210,7 +8264,7 @@
         <v>118</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>33</v>
@@ -8230,7 +8284,7 @@
         <v>119</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>34</v>
@@ -8250,7 +8304,7 @@
         <v>120</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>33</v>
@@ -8270,7 +8324,7 @@
         <v>129</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>33</v>
@@ -8290,7 +8344,7 @@
         <v>128</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>33</v>
@@ -8310,7 +8364,7 @@
         <v>121</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>33</v>
@@ -8330,7 +8384,7 @@
         <v>122</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>33</v>
@@ -8350,7 +8404,7 @@
         <v>121</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>33</v>
@@ -8370,7 +8424,7 @@
         <v>123</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>33</v>
@@ -8390,7 +8444,7 @@
         <v>124</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>33</v>
@@ -8410,13 +8464,13 @@
         <v>125</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>34</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8433,7 +8487,7 @@
         <v>6</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>330</v>
+        <v>583</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>33</v>
@@ -8453,7 +8507,7 @@
         <v>126</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>33</v>
@@ -8473,7 +8527,7 @@
         <v>127</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>33</v>
@@ -8533,7 +8587,7 @@
         <v>7</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>33</v>
@@ -8566,25 +8620,25 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8598,16 +8652,16 @@
         <v>25</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="I2" s="1"/>
     </row>
@@ -8622,16 +8676,16 @@
         <v>25</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="I3" s="1"/>
     </row>
@@ -8646,16 +8700,16 @@
         <v>160</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="I4" s="1"/>
     </row>
@@ -8670,13 +8724,13 @@
         <v>160</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="I5" s="1"/>
     </row>
@@ -8691,13 +8745,13 @@
         <v>224</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="I6" s="1"/>
     </row>
@@ -8709,19 +8763,19 @@
         <v>246</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>160</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="I7" s="1"/>
     </row>
@@ -8736,13 +8790,13 @@
         <v>160</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="I8" s="1"/>
     </row>
@@ -8776,25 +8830,25 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>571</v>
+        <v>506</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>573</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8802,39 +8856,39 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>617</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>618</v>
+        <v>620</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>621</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>620</v>
+      <c r="B3" s="6" t="s">
+        <v>623</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8842,19 +8896,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8862,19 +8916,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>627</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>618</v>
+        <v>630</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>621</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8882,19 +8936,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>115</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8902,19 +8956,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>115</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>634</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>631</v>
-      </c>
       <c r="F7" s="1" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8922,19 +8976,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>115</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>637</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>618</v>
+        <v>640</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>621</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8942,19 +8996,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>159</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8962,19 +9016,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>159</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8982,19 +9036,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>188</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9002,19 +9056,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>188</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="41" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9022,19 +9076,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>188</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9042,22 +9096,22 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>246</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9065,22 +9119,22 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>246</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9088,19 +9142,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>223</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>663</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>618</v>
+        <v>666</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>621</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9108,19 +9162,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>279</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
     </row>
   </sheetData>
@@ -9149,145 +9203,145 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>675</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>672</v>
-      </c>
       <c r="D3" s="1" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>203</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9367,13 +9421,13 @@
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="F1" s="1"/>
-      <c r="G1" s="5"/>
+      <c r="G1" s="6"/>
       <c r="H1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9387,7 +9441,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="F2" s="1"/>
       <c r="H2" s="1"/>
@@ -9403,7 +9457,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="F3" s="1"/>
       <c r="H3" s="1"/>
@@ -9419,7 +9473,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="F4" s="1"/>
       <c r="H4" s="1"/>
@@ -9435,7 +9489,7 @@
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="F5" s="1"/>
       <c r="H5" s="1"/>
@@ -9451,7 +9505,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="F6" s="1"/>
       <c r="H6" s="1"/>
@@ -9467,7 +9521,7 @@
         <v>2</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="F7" s="1"/>
       <c r="H7" s="1"/>
@@ -9483,7 +9537,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="F8" s="1"/>
       <c r="H8" s="1"/>
@@ -9499,7 +9553,7 @@
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="F9" s="1"/>
       <c r="H9" s="1"/>
@@ -9515,7 +9569,7 @@
         <v>4</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="F10" s="1"/>
       <c r="H10" s="1"/>
@@ -9531,7 +9585,7 @@
         <v>4</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="F11" s="1"/>
       <c r="H11" s="1"/>
@@ -9547,10 +9601,10 @@
         <v>5</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="F12" s="1"/>
-      <c r="G12" s="5"/>
+      <c r="G12" s="6"/>
       <c r="H12" s="1"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9564,10 +9618,10 @@
         <v>5</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="F13" s="1"/>
-      <c r="G13" s="5"/>
+      <c r="G13" s="6"/>
       <c r="H13" s="1"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9581,10 +9635,10 @@
         <v>6</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="F14" s="1"/>
-      <c r="G14" s="5"/>
+      <c r="G14" s="6"/>
       <c r="H14" s="1"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9598,7 +9652,7 @@
         <v>6</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="F15" s="1"/>
       <c r="H15" s="1"/>
@@ -9608,13 +9662,13 @@
         <v>104</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>6</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="F16" s="1"/>
       <c r="H16" s="1"/>
@@ -9630,7 +9684,7 @@
         <v>7</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="F17" s="1"/>
       <c r="H17" s="1"/>
@@ -9646,7 +9700,7 @@
         <v>7</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="F18" s="1"/>
       <c r="H18" s="1"/>
@@ -9662,7 +9716,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9676,7 +9730,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -9692,7 +9746,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9706,7 +9760,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9720,7 +9774,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9734,7 +9788,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9748,7 +9802,7 @@
         <v>10</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9762,7 +9816,7 @@
         <v>10</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9776,7 +9830,7 @@
         <v>11</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9790,7 +9844,7 @@
         <v>11</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9804,7 +9858,7 @@
         <v>12</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9818,7 +9872,7 @@
         <v>12</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9832,7 +9886,7 @@
         <v>15</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9846,7 +9900,7 @@
         <v>15</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9860,7 +9914,7 @@
         <v>13</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9874,7 +9928,7 @@
         <v>14</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9888,7 +9942,7 @@
         <v>14</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9902,7 +9956,7 @@
         <v>13</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9916,7 +9970,7 @@
         <v>13</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9930,7 +9984,7 @@
         <v>16</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
     </row>
   </sheetData>

--- a/fiches indicateurs.xlsx
+++ b/fiches indicateurs.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="indicateurs" sheetId="1" state="visible" r:id="rId3"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1864" uniqueCount="706">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1868" uniqueCount="709">
   <si>
     <t xml:space="preserve">fiche_indicateur</t>
   </si>
@@ -2201,6 +2201,15 @@
   </si>
   <si>
     <t xml:space="preserve">Risque de données non homogènes si l'on croise la "Surface érosion" de l'OEIL avec le "Terrain nu" issu du MOS ,  le MOS est privilégié pour sa robustesse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1, 500, 503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le BBR intègre le volume de prélèvement autorisé et le débits caractéristiques d’étiage médian (DCE2).</t>
   </si>
   <si>
     <t xml:space="preserve">Sous-groupe d'objectif</t>
@@ -5518,7 +5527,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
@@ -9344,6 +9353,20 @@
         <v>700</v>
       </c>
     </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="D11" s="0" t="s">
+        <v>703</v>
+      </c>
+    </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
@@ -9424,7 +9447,7 @@
         <v>615</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="6"/>
@@ -9569,7 +9592,7 @@
         <v>4</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="F10" s="1"/>
       <c r="H10" s="1"/>
@@ -9585,7 +9608,7 @@
         <v>4</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="F11" s="1"/>
       <c r="H11" s="1"/>
@@ -9716,7 +9739,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9858,7 +9881,7 @@
         <v>12</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9872,7 +9895,7 @@
         <v>12</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9984,7 +10007,7 @@
         <v>16</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
     </row>
   </sheetData>

--- a/fiches indicateurs.xlsx
+++ b/fiches indicateurs.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="indicateurs" sheetId="1" state="visible" r:id="rId3"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1868" uniqueCount="709">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1869" uniqueCount="710">
   <si>
     <t xml:space="preserve">fiche_indicateur</t>
   </si>
@@ -1028,34 +1028,7 @@
     <t xml:space="preserve">https://www.arcgis.com/home/item.html?id=6d48f295daf5471a842054d9e050765d</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">La couche BBR (bilan besoin / ressources) est calculée à partir des débits caractéristiques d’étiage médian (DCE2) auquel sont soustraits l'ensemble des </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">prélèvements d’eau autorisés</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
+    <t xml:space="preserve">La couche BBR (bilan besoin / ressources) est calculée à partir des débits caractéristiques d’étiage médian (DCE2) auquel sont soustraits l'ensemble des prélèvements d’eau autorisés.</t>
   </si>
   <si>
     <t xml:space="preserve">https://georep.nc/actualites/nouvelle-donnee-en-hydrologie-le-bilan-besoin-ressource</t>
@@ -1788,7 +1761,10 @@
     <t xml:space="preserve">Couverture spatiale</t>
   </si>
   <si>
-    <t xml:space="preserve">Couverture spatiale de la donnée</t>
+    <t xml:space="preserve">Désigne l'étendue géographique ou l'emprise territoriale sur laquelle la donnée source est disponible et valide. Cet attribut permet à l'utilisateur de savoir si l'indicateur est calculé sur l'ensemble de la Nouvelle-Calédonie, sur une province spécifique (ex: Province Sud) ou uniquement sur un périmètre restreint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nouvelle-Calédonie / provinces / communes … </t>
   </si>
   <si>
     <t xml:space="preserve">Période d actualisation</t>
@@ -2332,7 +2308,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2353,7 +2329,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2383,6 +2359,10 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -5527,7 +5507,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
@@ -6641,7 +6621,7 @@
   </sheetData>
   <autoFilter ref="A1:L38"/>
   <hyperlinks>
-    <hyperlink ref="J7" r:id="rId1" display="prélèvements d’eau autorisés"/>
+    <hyperlink ref="J7" r:id="rId1" display="La couche BBR (bilan besoin / ressources) est calculée à partir des débits caractéristiques d’étiage médian (DCE2) auquel sont soustraits l'ensemble des prélèvements d’eau autorisés."/>
     <hyperlink ref="E33" r:id="rId2" display="https://georep-dtsi-sgt.opendata.arcgis.com/documents/d7ab36bb69954aea882a63993428357a/about"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -7431,7 +7411,7 @@
       <c r="C32" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D32" s="13" t="s">
         <v>563</v>
       </c>
       <c r="E32" s="1" t="s">
@@ -7442,6 +7422,9 @@
       </c>
       <c r="G32" s="3" t="s">
         <v>501</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>564</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7452,10 +7435,10 @@
         <v>294</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>552</v>
@@ -7466,8 +7449,8 @@
       <c r="G33" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="H33" s="13" t="s">
-        <v>566</v>
+      <c r="H33" s="14" t="s">
+        <v>567</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7478,10 +7461,10 @@
         <v>295</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>519</v>
@@ -7493,7 +7476,7 @@
         <v>484</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7504,10 +7487,10 @@
         <v>298</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>500</v>
@@ -7521,16 +7504,16 @@
     </row>
     <row r="36" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>500</v>
@@ -7586,7 +7569,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -7604,7 +7587,7 @@
         <v>6</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7935,7 +7918,7 @@
         <v>104</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>106</v>
@@ -7967,7 +7950,7 @@
         <v>33</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7990,7 +7973,7 @@
         <v>33</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8033,7 +8016,7 @@
         <v>33</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8096,7 +8079,7 @@
         <v>33</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8479,7 +8462,7 @@
         <v>34</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8496,7 +8479,7 @@
         <v>6</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>33</v>
@@ -8596,7 +8579,7 @@
         <v>7</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>33</v>
@@ -8629,25 +8612,25 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>489</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8661,16 +8644,16 @@
         <v>25</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="I2" s="1"/>
     </row>
@@ -8685,16 +8668,16 @@
         <v>25</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="I3" s="1"/>
     </row>
@@ -8709,16 +8692,16 @@
         <v>160</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="I4" s="1"/>
     </row>
@@ -8733,13 +8716,13 @@
         <v>160</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="I5" s="1"/>
     </row>
@@ -8754,13 +8737,13 @@
         <v>224</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="I6" s="1"/>
     </row>
@@ -8772,19 +8755,19 @@
         <v>246</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>160</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="I7" s="1"/>
     </row>
@@ -8799,13 +8782,13 @@
         <v>160</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="I8" s="1"/>
     </row>
@@ -8839,25 +8822,25 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>506</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8865,19 +8848,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8885,19 +8868,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>500</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8905,19 +8888,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>500</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8925,19 +8908,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8945,19 +8928,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>115</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8965,19 +8948,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>115</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8985,19 +8968,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>115</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9005,19 +8988,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>159</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9025,19 +9008,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>159</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9045,19 +9028,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>188</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>500</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9065,19 +9048,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>188</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="41" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9085,19 +9068,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>188</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9105,22 +9088,22 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>246</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>500</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9128,22 +9111,22 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>246</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9151,19 +9134,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>223</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9171,19 +9154,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>279</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>500</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
   </sheetData>
@@ -9212,13 +9195,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>472</v>
@@ -9226,145 +9209,145 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>203</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>675</v>
-      </c>
-      <c r="D11" s="0" t="s">
-        <v>703</v>
+        <v>676</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>704</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9444,10 +9427,10 @@
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="6"/>
@@ -9464,7 +9447,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="F2" s="1"/>
       <c r="H2" s="1"/>
@@ -9480,7 +9463,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="F3" s="1"/>
       <c r="H3" s="1"/>
@@ -9496,7 +9479,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="F4" s="1"/>
       <c r="H4" s="1"/>
@@ -9512,7 +9495,7 @@
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="F5" s="1"/>
       <c r="H5" s="1"/>
@@ -9528,7 +9511,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="F6" s="1"/>
       <c r="H6" s="1"/>
@@ -9544,7 +9527,7 @@
         <v>2</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="F7" s="1"/>
       <c r="H7" s="1"/>
@@ -9560,7 +9543,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="F8" s="1"/>
       <c r="H8" s="1"/>
@@ -9576,7 +9559,7 @@
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="F9" s="1"/>
       <c r="H9" s="1"/>
@@ -9592,7 +9575,7 @@
         <v>4</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="F10" s="1"/>
       <c r="H10" s="1"/>
@@ -9608,7 +9591,7 @@
         <v>4</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="F11" s="1"/>
       <c r="H11" s="1"/>
@@ -9624,7 +9607,7 @@
         <v>5</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="6"/>
@@ -9641,7 +9624,7 @@
         <v>5</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="6"/>
@@ -9658,7 +9641,7 @@
         <v>6</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="6"/>
@@ -9675,7 +9658,7 @@
         <v>6</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="F15" s="1"/>
       <c r="H15" s="1"/>
@@ -9685,13 +9668,13 @@
         <v>104</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>6</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="F16" s="1"/>
       <c r="H16" s="1"/>
@@ -9707,7 +9690,7 @@
         <v>7</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="F17" s="1"/>
       <c r="H17" s="1"/>
@@ -9723,7 +9706,7 @@
         <v>7</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="F18" s="1"/>
       <c r="H18" s="1"/>
@@ -9739,7 +9722,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9753,7 +9736,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -9769,7 +9752,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9783,7 +9766,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9797,7 +9780,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9811,7 +9794,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9825,7 +9808,7 @@
         <v>10</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9839,7 +9822,7 @@
         <v>10</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9853,7 +9836,7 @@
         <v>11</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9867,7 +9850,7 @@
         <v>11</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9881,7 +9864,7 @@
         <v>12</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9895,7 +9878,7 @@
         <v>12</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9909,7 +9892,7 @@
         <v>15</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9923,7 +9906,7 @@
         <v>15</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9937,7 +9920,7 @@
         <v>13</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9951,7 +9934,7 @@
         <v>14</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9965,7 +9948,7 @@
         <v>14</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9979,7 +9962,7 @@
         <v>13</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9993,7 +9976,7 @@
         <v>13</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10007,7 +9990,7 @@
         <v>16</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
   </sheetData>

--- a/fiches indicateurs.xlsx
+++ b/fiches indicateurs.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="indicateurs" sheetId="1" state="visible" r:id="rId3"/>
@@ -16,6 +16,7 @@
     <sheet name="groupes" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="vigilances" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="relation groupe objectifs" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Famille" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">sources!$A$1:$L$38</definedName>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1869" uniqueCount="710">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1882" uniqueCount="719">
   <si>
     <t xml:space="preserve">fiche_indicateur</t>
   </si>
@@ -833,7 +834,7 @@
     <t xml:space="preserve">Niveau bas = forte criticité quantitative</t>
   </si>
   <si>
-    <t xml:space="preserve">AODPE nombre</t>
+    <t xml:space="preserve">Nombre de prélèvement AODPE</t>
   </si>
   <si>
     <t xml:space="preserve">Nombre de prélèvements d’eau autorisés.</t>
@@ -851,7 +852,23 @@
     <t xml:space="preserve">Indicateur pression captage. Donnée dynamique DAVAR. Intégrable en analyse.</t>
   </si>
   <si>
-    <t xml:space="preserve">AODPE volume</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Volume des p</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">rélèvements AODPE</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">Volume total d’eau prélevé.</t>
@@ -1828,6 +1845,12 @@
     <t xml:space="preserve">Bilan Besoin Ressource (nom à vérifier)</t>
   </si>
   <si>
+    <t xml:space="preserve">AODPE nombre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AODPE volume</t>
+  </si>
+  <si>
     <t xml:space="preserve">Base de données ATYA (nom à vérifier)</t>
   </si>
   <si>
@@ -2201,6 +2224,27 @@
   </si>
   <si>
     <t xml:space="preserve">État sanitaire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette famille regroupe les indicateurs qui caractérisent la valeur stratégique et la résilience des systèmes d’eau potable. Ils servent de « contrepoids » aux menaces pour déterminer la criticité globale d'un captage en quantifiant ce qui doit être protégé (population, infrastructures, biodiversité dépendante)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qu'est-ce qu'on protège ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette famille identifie les menaces actives et les aléas, d’origine humaine ou naturelle, susceptibles d’affaiblir les ressources. Elle mesure l'intensité des agressions (incendies, urbanisation, prélèvements) que subit le bassin versant et qui peuvent rompre les processus naturels de régulation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qu'est-ce qui menace ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette famille définit le socle physique immuable et les caractéristiques internes des captages qui expliquent leur sensibilité intrinsèque. Contrairement aux pressions, elle ne mesure pas un événement mais la prédisposition naturelle du terrain (géologie, type d'ouvrage) à laisser circuler ou non des polluants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">à quel point le système est sensible ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contexte / État</t>
   </si>
 </sst>
 </file>
@@ -2210,7 +2254,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -2237,6 +2281,11 @@
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2308,7 +2357,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2330,7 +2379,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -2338,10 +2387,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2357,7 +2410,7 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2365,8 +2418,12 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -5139,7 +5196,7 @@
       <c r="D38" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="E38" s="5" t="s">
         <v>273</v>
       </c>
       <c r="F38" s="1" t="s">
@@ -5535,7 +5592,7 @@
       <c r="I7" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="J7" s="6" t="s">
         <v>332</v>
       </c>
       <c r="K7" s="1" t="s">
@@ -6115,7 +6172,7 @@
       <c r="G24" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="H24" s="6" t="s">
+      <c r="H24" s="7" t="s">
         <v>412</v>
       </c>
       <c r="I24" s="1" t="s">
@@ -6418,7 +6475,7 @@
       <c r="D33" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="E33" s="7" t="s">
+      <c r="E33" s="8" t="s">
         <v>442</v>
       </c>
       <c r="F33" s="1" t="s">
@@ -6658,7 +6715,7 @@
       <c r="B1" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="9" t="s">
         <v>471</v>
       </c>
       <c r="D1" s="3" t="s">
@@ -6670,7 +6727,7 @@
       <c r="F1" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="9" t="s">
         <v>475</v>
       </c>
       <c r="H1" s="3" t="s">
@@ -6684,7 +6741,7 @@
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="10" t="s">
         <v>478</v>
       </c>
       <c r="D2" s="3" t="s">
@@ -6696,7 +6753,7 @@
       <c r="F2" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="G2" s="8"/>
+      <c r="G2" s="9"/>
       <c r="H2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6706,10 +6763,10 @@
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="11" t="s">
         <v>481</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="11" t="s">
         <v>482</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -6732,7 +6789,7 @@
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="11" t="s">
         <v>486</v>
       </c>
       <c r="D4" s="2" t="s">
@@ -7241,10 +7298,10 @@
       <c r="B25" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="11" t="s">
         <v>547</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="D25" s="11" t="s">
         <v>548</v>
       </c>
       <c r="E25" s="1" t="s">
@@ -7267,10 +7324,10 @@
       <c r="B26" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C26" s="12" t="s">
         <v>550</v>
       </c>
-      <c r="D26" s="11" t="s">
+      <c r="D26" s="12" t="s">
         <v>550</v>
       </c>
       <c r="E26" s="1" t="s">
@@ -7397,7 +7454,7 @@
       <c r="G31" s="3" t="s">
         <v>501</v>
       </c>
-      <c r="H31" s="12" t="s">
+      <c r="H31" s="13" t="s">
         <v>561</v>
       </c>
     </row>
@@ -7411,7 +7468,7 @@
       <c r="C32" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="D32" s="13" t="s">
+      <c r="D32" s="14" t="s">
         <v>563</v>
       </c>
       <c r="E32" s="1" t="s">
@@ -7449,7 +7506,7 @@
       <c r="G33" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="H33" s="14" t="s">
+      <c r="H33" s="15" t="s">
         <v>567</v>
       </c>
     </row>
@@ -7506,7 +7563,7 @@
       <c r="A36" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="7" t="s">
         <v>574</v>
       </c>
       <c r="C36" s="3" t="s">
@@ -7526,19 +7583,19 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="6"/>
+      <c r="B37" s="7"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
     </row>
     <row r="38" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="6"/>
+      <c r="B38" s="7"/>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
     </row>
     <row r="39" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="6"/>
+      <c r="B39" s="7"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
@@ -8533,7 +8590,7 @@
         <v>503</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>267</v>
+        <v>585</v>
       </c>
       <c r="D48" s="1" t="n">
         <v>3</v>
@@ -8553,7 +8610,7 @@
         <v>504</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>273</v>
+        <v>586</v>
       </c>
       <c r="D49" s="1" t="n">
         <v>3</v>
@@ -8579,7 +8636,7 @@
         <v>7</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>33</v>
@@ -8612,25 +8669,25 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>489</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8644,16 +8701,16 @@
         <v>25</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="I2" s="1"/>
     </row>
@@ -8668,16 +8725,16 @@
         <v>25</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="I3" s="1"/>
     </row>
@@ -8692,16 +8749,16 @@
         <v>160</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="I4" s="1"/>
     </row>
@@ -8716,13 +8773,13 @@
         <v>160</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="I5" s="1"/>
     </row>
@@ -8737,13 +8794,13 @@
         <v>224</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="I6" s="1"/>
     </row>
@@ -8755,19 +8812,19 @@
         <v>246</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>160</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="I7" s="1"/>
     </row>
@@ -8782,13 +8839,13 @@
         <v>160</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="I8" s="1"/>
     </row>
@@ -8822,25 +8879,25 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>573</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="7" t="s">
         <v>574</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8848,39 +8905,39 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>621</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>622</v>
+        <v>623</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>624</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>624</v>
+      <c r="B3" s="7" t="s">
+        <v>626</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>500</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8888,19 +8945,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>500</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8908,19 +8965,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>631</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>622</v>
+        <v>633</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>624</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8928,19 +8985,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>115</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8948,19 +9005,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>115</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8968,19 +9025,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>115</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>622</v>
+        <v>643</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>624</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8988,19 +9045,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>159</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9008,19 +9065,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>159</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9028,19 +9085,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>188</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>500</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9048,19 +9105,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>188</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="41" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9068,19 +9125,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>188</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9088,22 +9145,22 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>246</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>500</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9111,22 +9168,22 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>246</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9134,19 +9191,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>223</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>667</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>622</v>
+        <v>669</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>624</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9154,19 +9211,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>279</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>500</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
   </sheetData>
@@ -9198,10 +9255,10 @@
         <v>577</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>472</v>
@@ -9209,145 +9266,145 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>678</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>676</v>
-      </c>
       <c r="D3" s="1" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>203</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9427,13 +9484,13 @@
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="F1" s="1"/>
-      <c r="G1" s="6"/>
+      <c r="G1" s="7"/>
       <c r="H1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9447,7 +9504,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="F2" s="1"/>
       <c r="H2" s="1"/>
@@ -9463,7 +9520,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="F3" s="1"/>
       <c r="H3" s="1"/>
@@ -9479,7 +9536,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="F4" s="1"/>
       <c r="H4" s="1"/>
@@ -9495,7 +9552,7 @@
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="F5" s="1"/>
       <c r="H5" s="1"/>
@@ -9511,7 +9568,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="F6" s="1"/>
       <c r="H6" s="1"/>
@@ -9527,7 +9584,7 @@
         <v>2</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="F7" s="1"/>
       <c r="H7" s="1"/>
@@ -9543,7 +9600,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="F8" s="1"/>
       <c r="H8" s="1"/>
@@ -9559,7 +9616,7 @@
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="F9" s="1"/>
       <c r="H9" s="1"/>
@@ -9575,7 +9632,7 @@
         <v>4</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="F10" s="1"/>
       <c r="H10" s="1"/>
@@ -9591,7 +9648,7 @@
         <v>4</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="F11" s="1"/>
       <c r="H11" s="1"/>
@@ -9607,10 +9664,10 @@
         <v>5</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="F12" s="1"/>
-      <c r="G12" s="6"/>
+      <c r="G12" s="7"/>
       <c r="H12" s="1"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9624,10 +9681,10 @@
         <v>5</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="F13" s="1"/>
-      <c r="G13" s="6"/>
+      <c r="G13" s="7"/>
       <c r="H13" s="1"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9641,10 +9698,10 @@
         <v>6</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="F14" s="1"/>
-      <c r="G14" s="6"/>
+      <c r="G14" s="7"/>
       <c r="H14" s="1"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9658,7 +9715,7 @@
         <v>6</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="F15" s="1"/>
       <c r="H15" s="1"/>
@@ -9674,7 +9731,7 @@
         <v>6</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="F16" s="1"/>
       <c r="H16" s="1"/>
@@ -9690,7 +9747,7 @@
         <v>7</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="F17" s="1"/>
       <c r="H17" s="1"/>
@@ -9706,7 +9763,7 @@
         <v>7</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="F18" s="1"/>
       <c r="H18" s="1"/>
@@ -9722,7 +9779,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9736,7 +9793,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -9752,7 +9809,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9766,7 +9823,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9780,7 +9837,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9794,7 +9851,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9808,7 +9865,7 @@
         <v>10</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9822,7 +9879,7 @@
         <v>10</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9836,7 +9893,7 @@
         <v>11</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9850,7 +9907,7 @@
         <v>11</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9864,7 +9921,7 @@
         <v>12</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9878,7 +9935,7 @@
         <v>12</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9892,7 +9949,7 @@
         <v>15</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9906,7 +9963,7 @@
         <v>15</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9920,7 +9977,7 @@
         <v>13</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9934,7 +9991,7 @@
         <v>14</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9948,7 +10005,7 @@
         <v>14</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9956,13 +10013,13 @@
         <v>503</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>267</v>
+        <v>585</v>
       </c>
       <c r="C36" s="1" t="n">
         <v>13</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9970,13 +10027,13 @@
         <v>504</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>273</v>
+        <v>586</v>
       </c>
       <c r="C37" s="1" t="n">
         <v>13</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9990,7 +10047,79 @@
         <v>16</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>709</v>
+        <v>711</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="28.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="42.89"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>712</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>714</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="75.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>716</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>718</v>
       </c>
     </row>
   </sheetData>

--- a/fiches indicateurs.xlsx
+++ b/fiches indicateurs.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="indicateurs" sheetId="1" state="visible" r:id="rId3"/>
@@ -16,7 +16,7 @@
     <sheet name="groupes" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="vigilances" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="relation groupe objectifs" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="Famille" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Familles" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">sources!$A$1:$L$38</definedName>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1882" uniqueCount="719">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1879" uniqueCount="720">
   <si>
     <t xml:space="preserve">fiche_indicateur</t>
   </si>
@@ -495,6 +495,12 @@
     <t xml:space="preserve">Fort couvert forestier = faible criticité</t>
   </si>
   <si>
+    <t xml:space="preserve">Pressions Anthropiques</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pression</t>
+  </si>
+  <si>
     <t xml:space="preserve">Occupation sol (surfaces agricoles)</t>
   </si>
   <si>
@@ -513,9 +519,6 @@
     <t xml:space="preserve">Pressions Environnementales</t>
   </si>
   <si>
-    <t xml:space="preserve">Pression</t>
-  </si>
-  <si>
     <t xml:space="preserve">Incendies cumulés</t>
   </si>
   <si>
@@ -597,9 +600,6 @@
     <t xml:space="preserve">Donnée incertaine. Source non identifiée. Indicateur non prioritaire.</t>
   </si>
   <si>
-    <t xml:space="preserve">Pressions Anthropiques</t>
-  </si>
-  <si>
     <t xml:space="preserve">ICPE</t>
   </si>
   <si>
@@ -852,23 +852,7 @@
     <t xml:space="preserve">Indicateur pression captage. Donnée dynamique DAVAR. Intégrable en analyse.</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Volume des p</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">rélèvements AODPE</t>
-    </r>
+    <t xml:space="preserve">Volume des prélèvements AODPE</t>
   </si>
   <si>
     <t xml:space="preserve">Volume total d’eau prélevé.</t>
@@ -1082,6 +1066,9 @@
   </si>
   <si>
     <t xml:space="preserve">PSUD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.province-sud.nc/open/metadonnees/8a8186dd9816d2da019c8d998c7700a0</t>
   </si>
   <si>
     <t xml:space="preserve">Province Sud</t>
@@ -1809,147 +1796,117 @@
     <t xml:space="preserve">Identification des limites techniques, incertitudes de mesure ou biais d'interprétation liés à la source.</t>
   </si>
   <si>
+    <t xml:space="preserve">Diagnostic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">→ Comprendre l’état</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pilotage </t>
+  </si>
+  <si>
+    <t xml:space="preserve">→ agir / décider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veille </t>
+  </si>
+  <si>
+    <t xml:space="preserve">→ surveiller / anticiper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id_relation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commentaire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Espèces menacées (Forêt sèche)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">doublons TMF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non identifié comme prioritaire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">doublons dynamique world</t>
+  </si>
+  <si>
+    <t xml:space="preserve">si utilisation du 200 000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bilan Besoin Ressource (nom à vérifier)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AODPE nombre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AODPE volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base de données ATYA (nom à vérifier)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id_theme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Libelle_objectif</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Définition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Importance stratégique AEP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caractérise l’importance stratégique des ressources en eau potable en termes de disponibilité, de capacité et de résilience technique et réglementaire pour l’alimentation de la population.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valeur écologique et réglementaire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caractérise la valeur écologique, patrimoniale et réglementaire des milieux naturels autour des captages, ainsi que leur rôle de protection (filtration, limitation de l’érosion) et leur niveau de reconnaissance et de préservation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aléas et perturbations naturelles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caractérise les phénomènes naturels susceptibles d’altérer les milieux et d’impacter la qualité et la pérennité de la ressource en eau.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impacts des activités humaines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caractérise les pressions exercées par les activités humaines, l’occupation du sol et les infrastructures sur les ressources en eau.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sensibilité naturelle du milieu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caractérise la sensibilité naturelle des milieux aux transferts d’eau et de polluants, en fonction de leurs propriétés physiques indépendantes des pressions externes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tension sur la ressource en eau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caractérise les déséquilibres entre la disponibilité de la ressource en eau et les usages humains, notamment à travers l’intensité des prélèvements.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Évaluation de la qualité de l’eau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caractérise l’état de qualité de l’eau et les facteurs susceptibles de l’altérer (physico-chimiques, bactériologiques ou réglementaires).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id_groupe</t>
+  </si>
+  <si>
     <t xml:space="preserve">groupe</t>
   </si>
   <si>
     <t xml:space="preserve">vision_strategique</t>
   </si>
   <si>
-    <t xml:space="preserve">Vision stratégique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Définit la finalité opérationnelle de l'indicateur : Pilotage (aide à la décision immédiate), Veille (surveillance des aléas) ou Diagnostic (socle technique et modulation du risque).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id_relation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">commentaire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Espèces menacées (Forêt sèche)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">doublons TMF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non identifié comme prioritaire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">doublons dynamique world</t>
-  </si>
-  <si>
-    <t xml:space="preserve">si utilisation du 200 000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bilan Besoin Ressource (nom à vérifier)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AODPE nombre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AODPE volume</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base de données ATYA (nom à vérifier)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">theme_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Libelle_objectif</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Définition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">objectifs indicateur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rôle analyse multicritère</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regroupe les indicateurs qui mesurent la disponibilité, la capacité et la résilience des systèmes d’eau potable. Il s’agit de quantifier ce qui peut être mobilisé.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Les indicateurs de la famille Enjeux AEP (Alimentation en Eau Potable) ont pour objectif global de caractériser la valeur stratégique et la vulnérabilité / résilience technique et règlementaire des ressources en eau pour la population.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dans le cadre d'une analyse multicritère, ces indicateurs servent de contrepoids aux "menaces" (pressions environnementales ou anthropiques) pour déterminer une criticité globale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">source, support spatial (captage / UD / BV), hiérarchie captage-UD-BV, criticité vs résilience, rôle opérationnel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Couvre les indicateurs de zonage réglementaire, de statut de protection et de reconnaissance environnementale. Ces indicateurs servent à mesurer les contraintes et les enjeux de préservation autour et en amont des captages.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La famille des Enjeux Environnementaux a pour objectif global de caractériser la valeur patrimoniale, écologique et protectrice du milieu naturel entourant les ressources en eau. On cherche à savoir si l'environnement naturel joue son rôle de filtre et de protection contre l'érosion et le ruissellement ; à quantifier les éléments de biodiversité spécifiques qui dépendent directement du bon état du bassin versant et de mesurer le niveau de protection déjà existant et la reconnaissance internationale de la zone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dans l'analyse multicritère d'Hydroscope, ces indicateurs permettent d'identifier les zones où la préservation de la ressource est indissociable de la conservation de la biodiversité</t>
-  </si>
-  <si>
-    <t xml:space="preserve">statut juridique, couverture territoriale, complémentarité des périmètres, contraintes locales/nationales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regroupe les aléas naturels et les phénomènes susceptibles d’affaiblir les ressources et les infrastructures. Ces indicateurs renseignent l’exposition et l’impact potentiel sur la gestion des captages.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La famille des Pressions Environnementales a pour objectif global de caractériser les perturbations et les dégradations du milieu naturel susceptibles d'impacter la qualité et la pérennité de la ressource en eau. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dans l'analyse multicritère d'Hydroscope, ces indicateurs identifient les zones où les processus naturels de régulation (comme la filtration par le sol ou la protection par la végétation) sont défaillants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type d’aléa, périodicité, support spatial, lien vulnérabilité/pression</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regroupe les indicateurs de gestion humaine du territoire, de l’urbanisation et des activités qui pèsent sur les milieux aquatiques. Ces données traduisent les pressions directes et les usages du sol.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La famille des Pressions Anthropiques a pour objectif global de caractériser l'impact des activités humaines et des infrastructures sur le milieu naturel entourant les ressources en eau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nature des pressions, dynamique, connectivité, risques de doublons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regroupe les caractéristiques internes du milieu et des captages qui expliquent leur vulnérabilité au risque.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La famille de la Vulnérabilité intrinsèque a pour objectif global de caractériser la prédisposition naturelle du terrain à laisser circuler l'eau et les polluants vers les ressources en eau. Contrairement aux pressions qui sont liées à des événements ou des activités humaines, cet axe mesure les caractéristiques physiques immuables du sol qui facilitent ou freinent les transferts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">facteurs de sensibilité, exposition structurelle, dépendance au contexte naturel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Disponibilité et intensité d'usage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regroupe les indicateurs mesurant l’intensité et l’importance des usages ou des prélèvements autorisé ou effectués.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La famille des Pressions Quantitatives a pour objectif global de caractériser l’équilibre entre l’eau disponible dans le milieu naturel et les besoins humains identifiés. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">unités, seuils, agrégation, intensité territoriale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regroupe les indicateurs décrivant des contraintes non volumétriques, des statuts et de la qualité.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La famille des Pressions Qualitatives a pour objectif global de caractériser l'état sanitaire et la dégradation de la qualité physico-chimique ou bactériologique de l'eau.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">statut administratif, classes réglementaires, critères binaires, qualité perçue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id_groupe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">theme</t>
-  </si>
-  <si>
     <t xml:space="preserve">explication_role</t>
   </si>
   <si>
@@ -1959,15 +1916,15 @@
     <t xml:space="preserve">Robustesse et résilience technique</t>
   </si>
   <si>
-    <t xml:space="preserve">Évaluer la capacité de production en période sèche et la présence de dispositifs de secours (stockage, interconnexion) pour garantir la continuité du service.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diagnostic</t>
+    <t xml:space="preserve">Évaluer la capacité du système AEP à assurer la continuité du service (production, stockage, interconnexion)</t>
   </si>
   <si>
     <t xml:space="preserve">Guide la mise en conformité légale et les actions de protection réglementaire.</t>
   </si>
   <si>
+    <t xml:space="preserve">Identifier les besoins de sécurisation et de renforcement des infrastructures</t>
+  </si>
+  <si>
     <t xml:space="preserve">Poids stratégique de la desserte</t>
   </si>
   <si>
@@ -1980,243 +1937,246 @@
     <t xml:space="preserve">Sécurisation sanitaire et réglementaire</t>
   </si>
   <si>
-    <t xml:space="preserve">Mesurer le niveau de conformité administrative (AODPE) et de protection physique (PPE/Traitement) pour identifier les risques d'exposition aux pollutions.</t>
+    <t xml:space="preserve">Évaluer le niveau de conformité réglementaire et de protection sanitaire des captages</t>
   </si>
   <si>
     <t xml:space="preserve">Mesurer le niveau de conformité administrative (AODPE) et de protection physique (PPE/Traitement) afin d'identifier les risques d'exposition aux pollutions</t>
   </si>
   <si>
+    <t xml:space="preserve">Prioriser les mises en conformité et les actions de protection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vulnérabilité technique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Différencier les ressources selon leur nature (ouvrage) et leur usage actuel pour affiner la comparaison entre les points d'eau.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caractérise la sensibilité propre de l'ouvrage (ex: forage vs captage superficiel).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valeur patrimoniale et réglementaire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repérer les bassins versants inscrits dans des périmètres de reconnaissance mondiale ou locale (UNESCO, aires protégées) nécessitant une gestion exemplaire.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veille</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assure le suivi des engagements de conservation et des contraintes réglementaires associées.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Richesse biologique et rareté</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Localiser les zones de biodiversité critique (KBA, espèces menacées) qui dépendent du maintien de la qualité de la ressource en eau.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surveille l'état des écosystèmes sensibles dépendants de la ressource en eau.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">État écologique et rôle protecteur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualifier l'intégrité de la couverture végétale naturelle agissant comme un filtre et un régulateur naturel contre le ruissellement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mesure la capacité naturelle du milieu à protéger la ressource par filtration.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perturbations majeures du milieu (Aléa)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier les bassins dont l'équilibre écologique a été rompu par des événements destructeurs comme les incendies.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Permet une réaction rapide face aux chocs brutaux impactant le bassin versant.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fragilité des sols et transferts (chronique)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Détecter les zones de sols nus ou instables qui favorisent le transport de sédiments et de polluants vers les points de captage.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assure la surveillance de la dégradation structurelle et lente des sols.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Activités à risque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recenser les implantations industrielles (ICPE) ou minières pouvant générer des pollutions accidentelles ou chroniques.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oriente les contrôles de la police de l'eau et la surveillance des sites industriels.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Niveau d'artificialisation et densité</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantifier l'emprise du bâti et de l'habitat pour évaluer la pression directe exercée par l'occupation humaine sur le milieu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suit l'évolution de l'empreinte humaine et de l'imperméabilisation des sols.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructures et risques de dégradation des eaux </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier les points de contact entre les réseaux de transport et le milieu hydrographique pour localiser les zones à risque de pollution (ruissellement routier, accidents) et de dégradation de la qualité des cours d'eau (sédimentation, modification des écoulements)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cible les points de vigilance pour prévenir les pollutions liées au ruissellement routier.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tension des usages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier les situations de déséquilibre entre les besoins humains et l'eau disponible en croisant les prélèvements réels et le diagnostic de déficit. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relève du pilotage : déclenche les restrictions ou les limitations de nouvelles autorisations.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relève du pilotage. Si cet indicateur est rouge (trop de prélèvements autorisés), cela signifie qu'il faut limiter les nouvelles autorisations (AODPE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apports naturels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contextualiser la ressource disponible (pluie, nappes).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relève de la veille : observation du contexte climatique pour la gestion de crise.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relève de la veille. Si cet indicateur est rouge (sécheresse), on est dans la gestion de crise climatique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sensibilité naturelle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualifier la propension naturelle du terrain à laisser circuler les polluants vers les eaux souterraines ou superficielles selon ses propriétés géologiques.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Définit le socle physique immuable qui module (amplifie ou réduit) l'impact des pressions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">État sanitaire et suivi de la qualité</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier les captages dont la qualité de l'eau est dégradée afin de prioriser les actions de gestion ou de protection. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sert de diagnostic de confirmation pour valider l'impact réel des pressions sur la ressource.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ids_indicateurs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type_vigilance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">501, 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Redondance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Pluviométrie est jugée redondante avec la Capacité de production, car une baisse de pluie se traduit déjà par une baisse de débit mesurée au captage.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">401, 400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Géologie présente un risque élevé de redondance avec l'IDPR, ce dernier étant calculé à partir de données hydrologiques et géologiques.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">301, 202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'Activité minière (identifiée via le MOS) peut faire doublon avec l'indicateur Terrain nu, sur-représentant ainsi la pression physique sur le sol.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">304, 302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les Habitations (données ISEE) sont un complément du bâti (Urbanisation) </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> elles peuvent être fusionnées pour simplifier l'analyse de la pression anthropique [6].</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incohérence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le Glissement de terrain est classé en Pression mais fait débat pour un déplacement vers la famille Vulnérabilité (aléa lié à la nature du terrain).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le sens de l'Interconnexion n'est pas tranché : elle peut être vue comme un secours (positif) ou comme un vecteur de propagation de pollution (négatif).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105, 106, 202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utilisation concurrente de plusieurs sources (MOS, TMF, Dynamic World) pour le couvert végétal et le sol nu ,  risque de doublons techniques.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2, 3, 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risque de doublons ou de sur-comptage si plusieurs captages sont rattachés à une même Unité de Distribution (UD) pour le réseau, les réservoirs ou la population.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201, 202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risque de données non homogènes si l'on croise la "Surface érosion" de l'OEIL avec le "Terrain nu" issu du MOS ,  le MOS est privilégié pour sa robustesse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1, 500, 503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le BBR intègre le volume de prélèvement autorisé et le débits caractéristiques d’étiage médian (DCE2).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sous-groupe d'objectif</t>
+  </si>
+  <si>
     <t xml:space="preserve">Vulnérabilité technique et contexte</t>
   </si>
   <si>
-    <t xml:space="preserve">Différencier les ressources selon leur nature (ouvrage) et leur usage actuel pour affiner la comparaison entre les points d'eau.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caractérise la sensibilité propre de l'ouvrage (ex: forage vs captage superficiel).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valeur patrimoniale et réglementaire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Repérer les bassins versants inscrits dans des périmètres de reconnaissance mondiale ou locale (UNESCO, aires protégées) nécessitant une gestion exemplaire.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Veille</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assure le suivi des engagements de conservation et des contraintes réglementaires associées.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Richesse biologique et rareté</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Localiser les zones de biodiversité critique (KBA, espèces menacées) qui dépendent du maintien de la qualité de la ressource en eau.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Surveille l'état des écosystèmes sensibles dépendants de la ressource en eau.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">État écologique et rôle protecteur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualifier l'intégrité de la couverture végétale naturelle agissant comme un filtre et un régulateur naturel contre le ruissellement.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mesure la capacité naturelle du milieu à protéger la ressource par filtration.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perturbations majeures du milieu (Aléa)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier les bassins dont l'équilibre écologique a été rompu par des événements destructeurs comme les incendies.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Permet une réaction rapide face aux chocs brutaux impactant le bassin versant.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fragilité des sols et transferts (chronique)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Détecter les zones de sols nus ou instables qui favorisent le transport de sédiments et de polluants vers les points de captage.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assure la surveillance de la dégradation structurelle et lente des sols.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Activités à risque</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recenser les implantations industrielles (ICPE) ou minières pouvant générer des pollutions accidentelles ou chroniques.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oriente les contrôles de la police de l'eau et la surveillance des sites industriels.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Niveau d'artificialisation et densité</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantifier l'emprise du bâti et de l'habitat pour évaluer la pression directe exercée par l'occupation humaine sur le milieu.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suit l'évolution de l'empreinte humaine et de l'imperméabilisation des sols.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructures et risques de dégradation des eaux </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier les points de contact entre les réseaux de transport et le milieu hydrographique pour localiser les zones à risque de pollution (ruissellement routier, accidents) et de dégradation de la qualité des cours d'eau (sédimentation, modification des écoulements)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cible les points de vigilance pour prévenir les pollutions liées au ruissellement routier.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tension des usages</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier les situations de déséquilibre entre les besoins humains et l'eau disponible en croisant les prélèvements réels et le diagnostic de déficit. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Relève du pilotage : déclenche les restrictions ou les limitations de nouvelles autorisations.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Relève du pilotage. Si cet indicateur est rouge (trop de prélèvements autorisés), cela signifie qu'il faut limiter les nouvelles autorisations (AODPE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apports naturels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contextualiser la ressource disponible (pluie, nappes).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Relève de la veille : observation du contexte climatique pour la gestion de crise.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Relève de la veille. Si cet indicateur est rouge (sécheresse), on est dans la gestion de crise climatique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sensibilité naturelle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualifier la propension naturelle du terrain à laisser circuler les polluants vers les eaux souterraines ou superficielles selon ses propriétés géologiques.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Définit le socle physique immuable qui module (amplifie ou réduit) l'impact des pressions.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">État sanitaire et suivi de la qualité</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier les captages dont la qualité de l'eau est dégradée afin de prioriser les actions de gestion ou de protection. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sert de diagnostic de confirmation pour valider l'impact réel des pressions sur la ressource.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ids_indicateurs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type_vigilance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">501, 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Redondance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Pluviométrie est jugée redondante avec la Capacité de production, car une baisse de pluie se traduit déjà par une baisse de débit mesurée au captage.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">401, 400</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Géologie présente un risque élevé de redondance avec l'IDPR, ce dernier étant calculé à partir de données hydrologiques et géologiques.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">301, 202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L'Activité minière (identifiée via le MOS) peut faire doublon avec l'indicateur Terrain nu, sur-représentant ainsi la pression physique sur le sol.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">304, 302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Les Habitations (données ISEE) sont un complément du bâti (Urbanisation) </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> elles peuvent être fusionnées pour simplifier l'analyse de la pression anthropique [6].</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incohérence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Le Glissement de terrain est classé en Pression mais fait débat pour un déplacement vers la famille Vulnérabilité (aléa lié à la nature du terrain).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Le sens de l'Interconnexion n'est pas tranché : elle peut être vue comme un secours (positif) ou comme un vecteur de propagation de pollution (négatif).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105, 106, 202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Utilisation concurrente de plusieurs sources (MOS, TMF, Dynamic World) pour le couvert végétal et le sol nu ,  risque de doublons techniques.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2, 3, 6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Risque de doublons ou de sur-comptage si plusieurs captages sont rattachés à une même Unité de Distribution (UD) pour le réseau, les réservoirs ou la population.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">201, 202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Risque de données non homogènes si l'on croise la "Surface érosion" de l'OEIL avec le "Terrain nu" issu du MOS ,  le MOS est privilégié pour sa robustesse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1, 500, 503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Le BBR intègre le volume de prélèvement autorisé et le débits caractéristiques d’étiage médian (DCE2).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sous-groupe d'objectif</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contextualisation</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fragilité des sols et transferts</t>
   </si>
   <si>
@@ -2226,25 +2186,52 @@
     <t xml:space="preserve">État sanitaire</t>
   </si>
   <si>
-    <t xml:space="preserve">Cette famille regroupe les indicateurs qui caractérisent la valeur stratégique et la résilience des systèmes d’eau potable. Ils servent de « contrepoids » aux menaces pour déterminer la criticité globale d'un captage en quantifiant ce qui doit être protégé (population, infrastructures, biodiversité dépendante)</t>
+    <t xml:space="preserve">id_famille</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nom_famille</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rôle dans le calcul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regroupe les indicateurs qui caractérisent la valeur stratégique et la résilience des systèmes d’eau potable. Ils permettent de quantifier ce qui doit être protégé (population, infrastructures, biodiversité dépendante) et constituent le contrepoids des menaces dans l’analyse de criticité.</t>
   </si>
   <si>
     <t xml:space="preserve">qu'est-ce qu'on protège ?</t>
   </si>
   <si>
-    <t xml:space="preserve">Cette famille identifie les menaces actives et les aléas, d’origine humaine ou naturelle, susceptibles d’affaiblir les ressources. Elle mesure l'intensité des agressions (incendies, urbanisation, prélèvements) que subit le bassin versant et qui peuvent rompre les processus naturels de régulation</t>
+    <t xml:space="preserve">pondération positive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regroupe les indicateurs qui caractérisent les menaces et les aléas, d’origine naturelle ou anthropique, susceptibles d’altérer les ressources en eau. Ils mesurent l’intensité des perturbations subies par le bassin versant (incendies, urbanisation, prélèvements).</t>
   </si>
   <si>
     <t xml:space="preserve">qu'est-ce qui menace ?</t>
   </si>
   <si>
-    <t xml:space="preserve">Cette famille définit le socle physique immuable et les caractéristiques internes des captages qui expliquent leur sensibilité intrinsèque. Contrairement aux pressions, elle ne mesure pas un événement mais la prédisposition naturelle du terrain (géologie, type d'ouvrage) à laisser circuler ou non des polluants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">à quel point le système est sensible ?</t>
+    <t xml:space="preserve">pondération négative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regroupe les indicateurs qui caractérisent la sensibilité intrinsèque des milieux et des captages, en fonction de leurs propriétés physiques (géologie, type d’ouvrage). Contrairement aux pressions, elle ne décrit pas un événement mais une prédisposition naturelle aux transferts d’eau et de polluants.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quel est la sensibilité ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">facteur amplificateur</t>
   </si>
   <si>
     <t xml:space="preserve">Contexte / État</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regroupe les indicateurs décrivant le cadre structurel (géographique, technique, réglementaire) et l’état initial du milieu. Ces éléments n’entrent pas directement dans le calcul de criticité mais permettent d’interpréter et de contextualiser les résultats.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quel est le contexte ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hors calcul</t>
   </si>
 </sst>
 </file>
@@ -2254,7 +2241,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -2284,15 +2271,16 @@
     </font>
     <font>
       <sz val="10"/>
+      <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -2302,14 +2290,19 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
+      <sz val="12"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
@@ -2357,7 +2350,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2379,18 +2372,18 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2410,8 +2403,12 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -2422,8 +2419,8 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -3859,16 +3856,16 @@
         <v>107</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>115</v>
+        <v>154</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>25</v>
+        <v>155</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>28</v>
@@ -3880,7 +3877,7 @@
         <v>119</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="K19" s="1" t="s">
         <v>121</v>
@@ -3898,10 +3895,10 @@
         <v>35</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="R19" s="1" t="s">
         <v>38</v>
@@ -3927,16 +3924,16 @@
         <v>200</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>28</v>
@@ -3948,10 +3945,10 @@
         <v>119</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L20" s="1" t="s">
         <v>122</v>
@@ -3966,10 +3963,10 @@
         <v>35</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="R20" s="1" t="s">
         <v>38</v>
@@ -3987,7 +3984,7 @@
         <v>125</v>
       </c>
       <c r="W20" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3998,16 +3995,16 @@
         <v>201</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>28</v>
@@ -4019,7 +4016,7 @@
         <v>119</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K21" s="1" t="s">
         <v>121</v>
@@ -4037,10 +4034,10 @@
         <v>35</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="R21" s="1" t="s">
         <v>38</v>
@@ -4058,7 +4055,7 @@
         <v>125</v>
       </c>
       <c r="W21" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4069,16 +4066,16 @@
         <v>202</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>28</v>
@@ -4090,7 +4087,7 @@
         <v>119</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K22" s="1" t="s">
         <v>121</v>
@@ -4108,10 +4105,10 @@
         <v>35</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="R22" s="1" t="s">
         <v>38</v>
@@ -4129,7 +4126,7 @@
         <v>125</v>
       </c>
       <c r="W22" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4140,16 +4137,16 @@
         <v>203</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>28</v>
@@ -4161,7 +4158,7 @@
         <v>119</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K23" s="1" t="s">
         <v>121</v>
@@ -4179,10 +4176,10 @@
         <v>35</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q23" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="R23" s="1" t="s">
         <v>38</v>
@@ -4200,7 +4197,7 @@
         <v>125</v>
       </c>
       <c r="W23" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4211,16 +4208,16 @@
         <v>204</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>28</v>
@@ -4229,16 +4226,16 @@
         <v>118</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M24" s="1" t="s">
         <v>34</v>
@@ -4250,10 +4247,10 @@
         <v>35</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q24" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="R24" s="1" t="s">
         <v>38</v>
@@ -4271,7 +4268,7 @@
         <v>125</v>
       </c>
       <c r="W24" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4282,10 +4279,10 @@
         <v>300</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>189</v>
@@ -4321,7 +4318,7 @@
         <v>35</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q25" s="1" t="s">
         <v>193</v>
@@ -4353,10 +4350,10 @@
         <v>301</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>195</v>
@@ -4392,7 +4389,7 @@
         <v>35</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q26" s="1" t="s">
         <v>199</v>
@@ -4424,10 +4421,10 @@
         <v>302</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>201</v>
@@ -4463,7 +4460,7 @@
         <v>35</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q27" s="1" t="s">
         <v>205</v>
@@ -4495,10 +4492,10 @@
         <v>304</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>207</v>
@@ -4534,7 +4531,7 @@
         <v>35</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q28" s="1" t="s">
         <v>211</v>
@@ -4566,10 +4563,10 @@
         <v>305</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>213</v>
@@ -4605,7 +4602,7 @@
         <v>35</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q29" s="1" t="s">
         <v>217</v>
@@ -4634,10 +4631,10 @@
         <v>306</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>218</v>
@@ -4673,7 +4670,7 @@
         <v>35</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q30" s="1" t="s">
         <v>222</v>
@@ -4732,7 +4729,7 @@
         <v>228</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q31" s="1" t="s">
         <v>229</v>
@@ -4806,7 +4803,7 @@
         <v>35</v>
       </c>
       <c r="P32" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q32" s="1" t="s">
         <v>236</v>
@@ -4913,7 +4910,7 @@
         <v>246</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>247</v>
@@ -4937,7 +4934,7 @@
         <v>251</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M34" s="1" t="s">
         <v>33</v>
@@ -4984,7 +4981,7 @@
         <v>246</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>254</v>
@@ -5055,7 +5052,7 @@
         <v>246</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>261</v>
@@ -5123,7 +5120,7 @@
         <v>246</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>267</v>
@@ -5194,9 +5191,9 @@
         <v>246</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="E38" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="E38" s="2" t="s">
         <v>273</v>
       </c>
       <c r="F38" s="1" t="s">
@@ -5230,7 +5227,7 @@
         <v>35</v>
       </c>
       <c r="P38" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q38" s="1" t="s">
         <v>277</v>
@@ -5265,7 +5262,7 @@
         <v>279</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>280</v>
@@ -5592,7 +5589,7 @@
       <c r="I7" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="J7" s="6" t="s">
+      <c r="J7" s="5" t="s">
         <v>332</v>
       </c>
       <c r="K7" s="1" t="s">
@@ -5676,14 +5673,14 @@
       <c r="D10" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>317</v>
+      <c r="E10" s="6" t="s">
+        <v>345</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>303</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>305</v>
@@ -5692,10 +5689,10 @@
         <v>306</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5703,13 +5700,13 @@
         <v>102</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>317</v>
@@ -5718,7 +5715,7 @@
         <v>303</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>305</v>
@@ -5727,10 +5724,10 @@
         <v>306</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5738,13 +5735,13 @@
         <v>103</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>317</v>
@@ -5753,7 +5750,7 @@
         <v>318</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>305</v>
@@ -5762,10 +5759,10 @@
         <v>306</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5773,7 +5770,7 @@
         <v>104</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>339</v>
@@ -5782,7 +5779,7 @@
         <v>301</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>303</v>
@@ -5797,10 +5794,10 @@
         <v>306</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5808,13 +5805,13 @@
         <v>105</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>317</v>
@@ -5832,10 +5829,10 @@
         <v>306</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5843,7 +5840,7 @@
         <v>106</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>339</v>
@@ -5852,7 +5849,7 @@
         <v>301</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>303</v>
@@ -5867,7 +5864,7 @@
         <v>306</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5875,16 +5872,16 @@
         <v>107</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>301</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>303</v>
@@ -5899,10 +5896,10 @@
         <v>306</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5910,16 +5907,16 @@
         <v>108</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>303</v>
@@ -5928,16 +5925,16 @@
         <v>304</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5945,16 +5942,16 @@
         <v>109</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>303</v>
@@ -5963,16 +5960,16 @@
         <v>304</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5980,16 +5977,16 @@
         <v>110</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>303</v>
@@ -5998,16 +5995,16 @@
         <v>304</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>306</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6015,34 +6012,34 @@
         <v>111</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>303</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>341</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6050,34 +6047,34 @@
         <v>112</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>301</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>303</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>305</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6085,13 +6082,13 @@
         <v>113</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>311</v>
@@ -6109,10 +6106,10 @@
         <v>306</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6120,16 +6117,16 @@
         <v>114</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>301</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>303</v>
@@ -6144,10 +6141,10 @@
         <v>306</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6155,7 +6152,7 @@
         <v>115</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>344</v>
@@ -6164,28 +6161,28 @@
         <v>344</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>303</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>306</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6193,13 +6190,13 @@
         <v>116</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>317</v>
@@ -6208,7 +6205,7 @@
         <v>318</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>305</v>
@@ -6217,10 +6214,10 @@
         <v>306</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6228,13 +6225,13 @@
         <v>117</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>317</v>
@@ -6243,7 +6240,7 @@
         <v>318</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>305</v>
@@ -6252,10 +6249,10 @@
         <v>306</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6263,16 +6260,16 @@
         <v>118</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>301</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>303</v>
@@ -6287,10 +6284,10 @@
         <v>306</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6298,16 +6295,16 @@
         <v>119</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>301</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>303</v>
@@ -6322,10 +6319,10 @@
         <v>306</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6333,16 +6330,16 @@
         <v>120</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>301</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>303</v>
@@ -6357,10 +6354,10 @@
         <v>306</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6368,16 +6365,16 @@
         <v>129</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>303</v>
@@ -6386,16 +6383,16 @@
         <v>304</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>306</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6403,16 +6400,16 @@
         <v>121</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>301</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>303</v>
@@ -6427,10 +6424,10 @@
         <v>306</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6438,7 +6435,7 @@
         <v>122</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>300</v>
@@ -6456,10 +6453,10 @@
         <v>306</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="29.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6467,16 +6464,16 @@
         <v>123</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>301</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>303</v>
@@ -6491,13 +6488,13 @@
         <v>306</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6505,16 +6502,16 @@
         <v>124</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>301</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>303</v>
@@ -6526,13 +6523,13 @@
         <v>305</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6540,16 +6537,16 @@
         <v>125</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>301</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>303</v>
@@ -6561,13 +6558,13 @@
         <v>305</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6575,16 +6572,16 @@
         <v>126</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>301</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>303</v>
@@ -6599,10 +6596,10 @@
         <v>306</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6610,7 +6607,7 @@
         <v>127</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>300</v>
@@ -6619,7 +6616,7 @@
         <v>301</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>303</v>
@@ -6628,16 +6625,16 @@
         <v>304</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>305</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6645,16 +6642,16 @@
         <v>128</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>303</v>
@@ -6663,23 +6660,24 @@
         <v>304</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>306</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L38"/>
   <hyperlinks>
     <hyperlink ref="J7" r:id="rId1" display="La couche BBR (bilan besoin / ressources) est calculée à partir des débits caractéristiques d’étiage médian (DCE2) auquel sont soustraits l'ensemble des prélèvements d’eau autorisés."/>
-    <hyperlink ref="E33" r:id="rId2" display="https://georep-dtsi-sgt.opendata.arcgis.com/documents/d7ab36bb69954aea882a63993428357a/about"/>
+    <hyperlink ref="E10" r:id="rId2" display="https://www.province-sud.nc/open/metadonnees/8a8186dd9816d2da019c8d998c7700a0"/>
+    <hyperlink ref="E33" r:id="rId3" display="https://georep-dtsi-sgt.opendata.arcgis.com/documents/d7ab36bb69954aea882a63993428357a/about"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -6688,7 +6686,7 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
-  <drawing r:id="rId3"/>
+  <drawing r:id="rId4"/>
 </worksheet>
 </file>
 
@@ -6710,45 +6708,45 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>118</v>
@@ -6758,448 +6756,448 @@
     </row>
     <row r="3" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>118</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>20</v>
@@ -7208,62 +7206,62 @@
         <v>20</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>118</v>
@@ -7272,19 +7270,19 @@
     </row>
     <row r="24" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>544</v>
-      </c>
       <c r="E24" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>118</v>
@@ -7293,313 +7291,306 @@
     </row>
     <row r="25" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>287</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>288</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>118</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>296</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>118</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>289</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>290</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>291</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>292</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>293</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="D32" s="14" t="s">
         <v>563</v>
       </c>
+      <c r="D32" s="3" t="s">
+        <v>564</v>
+      </c>
       <c r="E32" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>294</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>484</v>
-      </c>
-      <c r="H33" s="15" t="s">
-        <v>567</v>
+        <v>485</v>
+      </c>
+      <c r="H33" s="14" t="s">
+        <v>568</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>295</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>298</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="s">
-        <v>573</v>
-      </c>
-      <c r="B36" s="7" t="s">
+      <c r="B36" s="7"/>
+      <c r="C36" s="15" t="s">
         <v>574</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="D36" s="16" t="s">
         <v>575</v>
       </c>
-      <c r="D36" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>500</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>501</v>
-      </c>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
     </row>
     <row r="37" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="7"/>
-      <c r="D37" s="3"/>
+      <c r="C37" s="15" t="s">
+        <v>576</v>
+      </c>
+      <c r="D37" s="16" t="s">
+        <v>577</v>
+      </c>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
     </row>
     <row r="38" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="7"/>
-      <c r="D38" s="3"/>
+      <c r="C38" s="15" t="s">
+        <v>578</v>
+      </c>
+      <c r="D38" s="16" t="s">
+        <v>579</v>
+      </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
     </row>
-    <row r="39" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="7"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
-    </row>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -7626,7 +7617,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -7644,7 +7635,7 @@
         <v>6</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7901,7 +7892,7 @@
         <v>102</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>33</v>
@@ -7921,7 +7912,7 @@
         <v>103</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>33</v>
@@ -7941,7 +7932,7 @@
         <v>104</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>33</v>
@@ -7961,7 +7952,7 @@
         <v>105</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>33</v>
@@ -7975,13 +7966,13 @@
         <v>104</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>106</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>33</v>
@@ -8001,13 +7992,13 @@
         <v>107</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>33</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8024,13 +8015,13 @@
         <v>108</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>33</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8047,7 +8038,7 @@
         <v>109</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>33</v>
@@ -8061,19 +8052,19 @@
         <v>107</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D22" s="1" t="n">
         <v>107</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>33</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8084,13 +8075,13 @@
         <v>200</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D23" s="1" t="n">
         <v>110</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>33</v>
@@ -8104,13 +8095,13 @@
         <v>201</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D24" s="1" t="n">
         <v>111</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>34</v>
@@ -8124,19 +8115,19 @@
         <v>202</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D25" s="1" t="n">
         <v>107</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>33</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8147,13 +8138,13 @@
         <v>202</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D26" s="1" t="n">
         <v>108</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>33</v>
@@ -8167,13 +8158,13 @@
         <v>203</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D27" s="1" t="n">
         <v>112</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>33</v>
@@ -8187,13 +8178,13 @@
         <v>204</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D28" s="1" t="n">
         <v>113</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>33</v>
@@ -8213,7 +8204,7 @@
         <v>114</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>118</v>
@@ -8233,7 +8224,7 @@
         <v>115</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>33</v>
@@ -8253,7 +8244,7 @@
         <v>116</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>33</v>
@@ -8273,7 +8264,7 @@
         <v>117</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>33</v>
@@ -8293,7 +8284,7 @@
         <v>107</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>33</v>
@@ -8313,7 +8304,7 @@
         <v>118</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>33</v>
@@ -8333,7 +8324,7 @@
         <v>119</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>34</v>
@@ -8353,7 +8344,7 @@
         <v>120</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>33</v>
@@ -8373,7 +8364,7 @@
         <v>129</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>33</v>
@@ -8393,7 +8384,7 @@
         <v>128</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>33</v>
@@ -8413,7 +8404,7 @@
         <v>121</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>33</v>
@@ -8433,7 +8424,7 @@
         <v>122</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>33</v>
@@ -8453,13 +8444,13 @@
         <v>121</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="n">
         <v>41</v>
       </c>
@@ -8473,7 +8464,7 @@
         <v>123</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>33</v>
@@ -8493,7 +8484,7 @@
         <v>124</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>33</v>
@@ -8513,13 +8504,13 @@
         <v>125</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>34</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8536,7 +8527,7 @@
         <v>6</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>33</v>
@@ -8556,7 +8547,7 @@
         <v>126</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>33</v>
@@ -8576,7 +8567,7 @@
         <v>127</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>33</v>
@@ -8590,7 +8581,7 @@
         <v>503</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D48" s="1" t="n">
         <v>3</v>
@@ -8610,7 +8601,7 @@
         <v>504</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="D49" s="1" t="n">
         <v>3</v>
@@ -8636,7 +8627,7 @@
         <v>7</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>33</v>
@@ -8659,35 +8650,29 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="1" width="28.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="42.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="1" width="46.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="46.25"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>590</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>591</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8697,22 +8682,17 @@
       <c r="B2" s="1" t="s">
         <v>24</v>
       </c>
+      <c r="C2" s="17" t="s">
+        <v>594</v>
+      </c>
       <c r="D2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>593</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>594</v>
-      </c>
-      <c r="G2" s="3" t="s">
+      <c r="E2" s="15" t="s">
         <v>595</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>596</v>
-      </c>
-      <c r="I2" s="1"/>
+      <c r="F2" s="3"/>
+      <c r="H2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
@@ -8721,112 +8701,90 @@
       <c r="B3" s="1" t="s">
         <v>115</v>
       </c>
+      <c r="C3" s="17" t="s">
+        <v>596</v>
+      </c>
       <c r="D3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="15" t="s">
         <v>597</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>599</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>600</v>
-      </c>
-      <c r="I3" s="1"/>
-    </row>
-    <row r="4" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F3" s="3"/>
+      <c r="H3" s="1"/>
+    </row>
+    <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>598</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>601</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>602</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>603</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>604</v>
-      </c>
-      <c r="I4" s="1"/>
-    </row>
-    <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>155</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>599</v>
+      </c>
+      <c r="F4" s="3"/>
+      <c r="H4" s="1"/>
+    </row>
+    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>188</v>
+        <v>154</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>600</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>605</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>606</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>607</v>
-      </c>
-      <c r="I5" s="1"/>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>155</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>601</v>
+      </c>
+      <c r="H5" s="1"/>
+    </row>
+    <row r="6" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>223</v>
       </c>
+      <c r="C6" s="17" t="s">
+        <v>602</v>
+      </c>
       <c r="D6" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>608</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>609</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>610</v>
-      </c>
-      <c r="I6" s="1"/>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E6" s="15" t="s">
+        <v>603</v>
+      </c>
+      <c r="H6" s="1"/>
+    </row>
+    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>611</v>
+      <c r="C7" s="17" t="s">
+        <v>604</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>612</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>613</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>614</v>
-      </c>
-      <c r="I7" s="1"/>
+        <v>155</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>605</v>
+      </c>
+      <c r="H7" s="1"/>
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
@@ -8835,19 +8793,16 @@
       <c r="B8" s="1" t="s">
         <v>279</v>
       </c>
+      <c r="C8" s="17" t="s">
+        <v>606</v>
+      </c>
       <c r="D8" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>615</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>616</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>617</v>
-      </c>
-      <c r="I8" s="1"/>
+        <v>155</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>607</v>
+      </c>
+      <c r="H8" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -8865,79 +8820,92 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="29.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="37.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="29.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="92.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="27.59"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="84.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="29.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="37.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="9.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="29.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="92.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="27.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="84.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="29.91"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>618</v>
+        <v>608</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>573</v>
+        <v>609</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>619</v>
+        <v>591</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>574</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>620</v>
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>610</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>611</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>622</v>
-      </c>
-      <c r="C2" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>623</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>624</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E2" s="15" t="s">
+        <v>614</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>574</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>626</v>
-      </c>
-      <c r="C3" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>627</v>
-      </c>
       <c r="E3" s="1" t="s">
-        <v>500</v>
+        <v>618</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>628</v>
+        <v>501</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>619</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8945,19 +8913,25 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>629</v>
-      </c>
-      <c r="C4" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>630</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>500</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>631</v>
+      <c r="E4" s="15" t="s">
+        <v>621</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="H4" s="15" t="s">
+        <v>623</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8965,19 +8939,22 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>632</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>24</v>
+        <v>624</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>5</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>633</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>624</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>634</v>
+        <v>223</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>574</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>626</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8985,19 +8962,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>635</v>
-      </c>
-      <c r="C6" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>636</v>
-      </c>
       <c r="E6" s="1" t="s">
-        <v>637</v>
+        <v>628</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>638</v>
+        <v>629</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>630</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9005,19 +8985,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>639</v>
-      </c>
-      <c r="C7" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>640</v>
-      </c>
       <c r="E7" s="1" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>641</v>
+        <v>629</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>633</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9025,19 +9008,22 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>642</v>
-      </c>
-      <c r="C8" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>643</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>624</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>644</v>
+      <c r="E8" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>574</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>636</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9045,19 +9031,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>645</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>159</v>
+        <v>637</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>646</v>
+        <v>161</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>647</v>
+        <v>629</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>639</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9065,19 +9054,22 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>648</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>159</v>
+        <v>640</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>649</v>
+        <v>161</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>650</v>
+        <v>629</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>642</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9085,19 +9077,22 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>651</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>188</v>
+        <v>643</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>4</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>652</v>
+        <v>154</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>500</v>
+        <v>644</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>653</v>
+        <v>501</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>645</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9105,19 +9100,22 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>654</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>188</v>
+        <v>646</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>4</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>655</v>
+        <v>154</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>637</v>
+        <v>647</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>656</v>
+        <v>629</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>648</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="41" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9125,19 +9123,22 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>657</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>658</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>637</v>
+        <v>649</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>650</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>659</v>
+        <v>629</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>651</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9145,22 +9146,25 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>660</v>
-      </c>
-      <c r="C14" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>661</v>
-      </c>
       <c r="E14" s="1" t="s">
-        <v>500</v>
+        <v>653</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>662</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>663</v>
+        <v>501</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>655</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9168,22 +9172,25 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>664</v>
-      </c>
-      <c r="C15" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>665</v>
-      </c>
       <c r="E15" s="1" t="s">
-        <v>637</v>
+        <v>657</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>666</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>667</v>
+        <v>629</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>659</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9191,39 +9198,45 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>668</v>
-      </c>
-      <c r="C16" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>669</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>624</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E16" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>574</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>671</v>
-      </c>
-      <c r="C17" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>672</v>
-      </c>
       <c r="E17" s="1" t="s">
-        <v>500</v>
+        <v>664</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>673</v>
+        <v>501</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>665</v>
       </c>
     </row>
   </sheetData>
@@ -9252,159 +9265,159 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>674</v>
+        <v>666</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>675</v>
+        <v>667</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>678</v>
+        <v>670</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>679</v>
+        <v>671</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>680</v>
+        <v>672</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>681</v>
+        <v>673</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>678</v>
+        <v>670</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>682</v>
+        <v>674</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>684</v>
+        <v>676</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>678</v>
+        <v>670</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>685</v>
+        <v>677</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>686</v>
+        <v>678</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>678</v>
+        <v>670</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>688</v>
+        <v>680</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>689</v>
+        <v>681</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>690</v>
+        <v>682</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>203</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>691</v>
+        <v>683</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>692</v>
+        <v>684</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>693</v>
+        <v>685</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>691</v>
+        <v>683</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>694</v>
+        <v>686</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>695</v>
+        <v>687</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>696</v>
+        <v>688</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>678</v>
+        <v>670</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>698</v>
+        <v>690</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>699</v>
+        <v>691</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>691</v>
+        <v>683</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>700</v>
+        <v>692</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>701</v>
+        <v>693</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>702</v>
+        <v>694</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>678</v>
+        <v>670</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>703</v>
+        <v>695</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>704</v>
+        <v>696</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>705</v>
+        <v>697</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>678</v>
+        <v>670</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>706</v>
+        <v>698</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9484,10 +9497,10 @@
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>618</v>
+        <v>608</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>707</v>
+        <v>699</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="7"/>
@@ -9504,7 +9517,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="F2" s="1"/>
       <c r="H2" s="1"/>
@@ -9520,7 +9533,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>626</v>
+        <v>617</v>
       </c>
       <c r="F3" s="1"/>
       <c r="H3" s="1"/>
@@ -9536,7 +9549,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="F4" s="1"/>
       <c r="H4" s="1"/>
@@ -9552,7 +9565,7 @@
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>629</v>
+        <v>620</v>
       </c>
       <c r="F5" s="1"/>
       <c r="H5" s="1"/>
@@ -9568,7 +9581,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="F6" s="1"/>
       <c r="H6" s="1"/>
@@ -9584,7 +9597,7 @@
         <v>2</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>626</v>
+        <v>617</v>
       </c>
       <c r="F7" s="1"/>
       <c r="H7" s="1"/>
@@ -9600,7 +9613,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>629</v>
+        <v>620</v>
       </c>
       <c r="F8" s="1"/>
       <c r="H8" s="1"/>
@@ -9616,7 +9629,7 @@
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>629</v>
+        <v>620</v>
       </c>
       <c r="F9" s="1"/>
       <c r="H9" s="1"/>
@@ -9632,7 +9645,7 @@
         <v>4</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>708</v>
+        <v>700</v>
       </c>
       <c r="F10" s="1"/>
       <c r="H10" s="1"/>
@@ -9648,7 +9661,7 @@
         <v>4</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>708</v>
+        <v>700</v>
       </c>
       <c r="F11" s="1"/>
       <c r="H11" s="1"/>
@@ -9664,7 +9677,7 @@
         <v>5</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="7"/>
@@ -9681,7 +9694,7 @@
         <v>5</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="7"/>
@@ -9698,7 +9711,7 @@
         <v>6</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="7"/>
@@ -9715,7 +9728,7 @@
         <v>6</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="F15" s="1"/>
       <c r="H15" s="1"/>
@@ -9725,13 +9738,13 @@
         <v>104</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>6</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="F16" s="1"/>
       <c r="H16" s="1"/>
@@ -9747,7 +9760,7 @@
         <v>7</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>642</v>
+        <v>634</v>
       </c>
       <c r="F17" s="1"/>
       <c r="H17" s="1"/>
@@ -9763,7 +9776,7 @@
         <v>7</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>642</v>
+        <v>634</v>
       </c>
       <c r="F18" s="1"/>
       <c r="H18" s="1"/>
@@ -9773,13 +9786,13 @@
         <v>107</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C19" s="1" t="n">
         <v>9</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>709</v>
+        <v>701</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9787,13 +9800,13 @@
         <v>200</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C20" s="1" t="n">
         <v>8</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -9803,13 +9816,13 @@
         <v>201</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C21" s="1" t="n">
         <v>9</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>648</v>
+        <v>640</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9817,13 +9830,13 @@
         <v>202</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>9</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>648</v>
+        <v>640</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9831,13 +9844,13 @@
         <v>203</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>9</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9845,13 +9858,13 @@
         <v>204</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>8</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>648</v>
+        <v>640</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9865,7 +9878,7 @@
         <v>10</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>651</v>
+        <v>643</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9879,7 +9892,7 @@
         <v>10</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>651</v>
+        <v>643</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9893,7 +9906,7 @@
         <v>11</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>654</v>
+        <v>646</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9907,7 +9920,7 @@
         <v>11</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>654</v>
+        <v>646</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9921,7 +9934,7 @@
         <v>12</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9935,7 +9948,7 @@
         <v>12</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9949,7 +9962,7 @@
         <v>15</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>668</v>
+        <v>660</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9963,7 +9976,7 @@
         <v>15</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>668</v>
+        <v>660</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9977,7 +9990,7 @@
         <v>13</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>660</v>
+        <v>652</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9991,7 +10004,7 @@
         <v>14</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>664</v>
+        <v>656</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10005,7 +10018,7 @@
         <v>14</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>664</v>
+        <v>656</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10013,13 +10026,13 @@
         <v>503</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="C36" s="1" t="n">
         <v>13</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>660</v>
+        <v>652</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10027,13 +10040,13 @@
         <v>504</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="C37" s="1" t="n">
         <v>13</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>660</v>
+        <v>652</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10047,7 +10060,7 @@
         <v>16</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>711</v>
+        <v>703</v>
       </c>
     </row>
   </sheetData>
@@ -10066,60 +10079,97 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="28.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="42.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="28.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="42.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="25.62"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>489</v>
+    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
+        <v>704</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>590</v>
-      </c>
-      <c r="C1" s="0" t="s">
+        <v>705</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="E1" s="15" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="C2" s="15" t="s">
+        <v>707</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>710</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="E3" s="15" t="s">
         <v>712</v>
       </c>
-      <c r="C2" s="14" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C4" s="15" t="s">
         <v>713</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="B3" s="14" t="s">
+      <c r="D4" s="2" t="s">
         <v>714</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="E4" s="15" t="s">
         <v>715</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="75.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="B4" s="14" t="s">
+    <row r="5" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>716</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C5" s="15" t="s">
         <v>717</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="D5" s="0" t="s">
         <v>718</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>719</v>
       </c>
     </row>
   </sheetData>

--- a/fiches indicateurs.xlsx
+++ b/fiches indicateurs.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="indicateurs" sheetId="1" state="visible" r:id="rId3"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1879" uniqueCount="720">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1884" uniqueCount="717">
   <si>
     <t xml:space="preserve">fiche_indicateur</t>
   </si>
@@ -339,6 +339,12 @@
     <t xml:space="preserve">Indicateur captage. Statut (oui/en cours/non). Instruction longue. Critère important de vulnérabilité réglementaire.</t>
   </si>
   <si>
+    <t xml:space="preserve">Vulnérabilité Intrinsèque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vulnérabilité</t>
+  </si>
+  <si>
     <t xml:space="preserve">Type ouvrage</t>
   </si>
   <si>
@@ -702,12 +708,6 @@
     <t xml:space="preserve">Fort linéaire routier = fragmentation et imperméabilisation élevées</t>
   </si>
   <si>
-    <t xml:space="preserve">Vulnérabilité Intrinsèque</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vulnérabilité</t>
-  </si>
-  <si>
     <t xml:space="preserve">IDPR</t>
   </si>
   <si>
@@ -1056,7 +1056,10 @@
     <t xml:space="preserve">https://georep-dtsi-sgt.opendata.arcgis.com/maps/e17f6c38b47a435e9e73c102a7a1b933/about</t>
   </si>
   <si>
-    <t xml:space="preserve">jamais</t>
+    <t xml:space="preserve">ponctuelle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zone terrestres, qui représentent les bassins versants débouchant dans les zones inscrites dites "zones de bien"</t>
   </si>
   <si>
     <t xml:space="preserve">Périmètres parfois imprécis à l'échelle locale.</t>
@@ -1796,24 +1799,6 @@
     <t xml:space="preserve">Identification des limites techniques, incertitudes de mesure ou biais d'interprétation liés à la source.</t>
   </si>
   <si>
-    <t xml:space="preserve">Diagnostic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">→ Comprendre l’état</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pilotage </t>
-  </si>
-  <si>
-    <t xml:space="preserve">→ agir / décider</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Veille </t>
-  </si>
-  <si>
-    <t xml:space="preserve">→ surveiller / anticiper</t>
-  </si>
-  <si>
     <t xml:space="preserve">id_relation</t>
   </si>
   <si>
@@ -1919,6 +1904,9 @@
     <t xml:space="preserve">Évaluer la capacité du système AEP à assurer la continuité du service (production, stockage, interconnexion)</t>
   </si>
   <si>
+    <t xml:space="preserve">Comprendre</t>
+  </si>
+  <si>
     <t xml:space="preserve">Guide la mise en conformité légale et les actions de protection réglementaire.</t>
   </si>
   <si>
@@ -1931,6 +1919,9 @@
     <t xml:space="preserve">Identifier les ressources dont la défaillance impacterait le plus grand nombre d'habitants ou le plus important linéaire d'infrastructures de distribution.</t>
   </si>
   <si>
+    <t xml:space="preserve">Agir</t>
+  </si>
+  <si>
     <t xml:space="preserve">Définit les priorités d'investissement et l'importance socio-économique de la ressource.</t>
   </si>
   <si>
@@ -1955,13 +1946,16 @@
     <t xml:space="preserve">Caractérise la sensibilité propre de l'ouvrage (ex: forage vs captage superficiel).</t>
   </si>
   <si>
+    <t xml:space="preserve">Affiner la comparaison des captages et adapter les stratégies de gestion</t>
+  </si>
+  <si>
     <t xml:space="preserve">Valeur patrimoniale et réglementaire</t>
   </si>
   <si>
     <t xml:space="preserve">Repérer les bassins versants inscrits dans des périmètres de reconnaissance mondiale ou locale (UNESCO, aires protégées) nécessitant une gestion exemplaire.</t>
   </si>
   <si>
-    <t xml:space="preserve">Veille</t>
+    <t xml:space="preserve">Surveiller</t>
   </si>
   <si>
     <t xml:space="preserve">Assure le suivi des engagements de conservation et des contraintes réglementaires associées.</t>
@@ -2033,25 +2027,25 @@
     <t xml:space="preserve">Tension des usages</t>
   </si>
   <si>
-    <t xml:space="preserve">Identifier les situations de déséquilibre entre les besoins humains et l'eau disponible en croisant les prélèvements réels et le diagnostic de déficit. </t>
+    <t xml:space="preserve">Identifier les situations de déséquilibre entre prélèvements et ressource disponible</t>
   </si>
   <si>
     <t xml:space="preserve">Relève du pilotage : déclenche les restrictions ou les limitations de nouvelles autorisations.</t>
   </si>
   <si>
-    <t xml:space="preserve">Relève du pilotage. Si cet indicateur est rouge (trop de prélèvements autorisés), cela signifie qu'il faut limiter les nouvelles autorisations (AODPE)</t>
+    <t xml:space="preserve">Déclencher des restrictions ou limiter les nouvelles autorisations</t>
   </si>
   <si>
     <t xml:space="preserve">Apports naturels</t>
   </si>
   <si>
-    <t xml:space="preserve">Contextualiser la ressource disponible (pluie, nappes).</t>
+    <t xml:space="preserve">Suivre les conditions hydrologiques influençant la disponibilité de la ressource</t>
   </si>
   <si>
     <t xml:space="preserve">Relève de la veille : observation du contexte climatique pour la gestion de crise.</t>
   </si>
   <si>
-    <t xml:space="preserve">Relève de la veille. Si cet indicateur est rouge (sécheresse), on est dans la gestion de crise climatique</t>
+    <t xml:space="preserve">Anticiper les situations de crise (sécheresse)</t>
   </si>
   <si>
     <t xml:space="preserve">Sensibilité naturelle</t>
@@ -2066,12 +2060,15 @@
     <t xml:space="preserve">État sanitaire et suivi de la qualité</t>
   </si>
   <si>
-    <t xml:space="preserve">Identifier les captages dont la qualité de l'eau est dégradée afin de prioriser les actions de gestion ou de protection. </t>
+    <t xml:space="preserve">Identifier les captages présentant une dégradation de la qualité de l’eau</t>
   </si>
   <si>
     <t xml:space="preserve">Sert de diagnostic de confirmation pour valider l'impact réel des pressions sur la ressource.</t>
   </si>
   <si>
+    <t xml:space="preserve">Prioriser les actions correctives et confirmer l’impact des pressions</t>
+  </si>
+  <si>
     <t xml:space="preserve">ids_indicateurs</t>
   </si>
   <si>
@@ -2096,7 +2093,7 @@
     <t xml:space="preserve">401, 400</t>
   </si>
   <si>
-    <t xml:space="preserve">La Géologie présente un risque élevé de redondance avec l'IDPR, ce dernier étant calculé à partir de données hydrologiques et géologiques.</t>
+    <t xml:space="preserve">La Géologie présente un risque élevé de redondance avec la vulnérabilité intrinsèque des eaux souterraines , ce dernier étant calculé à partir de données hydrologiques et géologiques.</t>
   </si>
   <si>
     <t xml:space="preserve">R3</t>
@@ -2114,10 +2111,7 @@
     <t xml:space="preserve">304, 302</t>
   </si>
   <si>
-    <t xml:space="preserve">Les Habitations (données ISEE) sont un complément du bâti (Urbanisation) </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> elles peuvent être fusionnées pour simplifier l'analyse de la pression anthropique [6].</t>
+    <t xml:space="preserve">Les Habitations (données ISEE) sont un complément du bâti (Urbanisation)   elles peuvent être fusionnées pour simplifier l'analyse de la pression anthropique.</t>
   </si>
   <si>
     <t xml:space="preserve">R5</t>
@@ -2175,9 +2169,6 @@
   </si>
   <si>
     <t xml:space="preserve">Vulnérabilité technique et contexte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fragilité des sols et transferts</t>
   </si>
   <si>
     <t xml:space="preserve">Infrastructures et risques de dégradation des eaux</t>
@@ -2350,7 +2341,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2372,6 +2363,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2411,16 +2406,16 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -3238,16 +3233,16 @@
         <v>9</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>24</v>
+        <v>102</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>28</v>
@@ -3256,10 +3251,10 @@
         <v>28</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>91</v>
@@ -3280,7 +3275,7 @@
         <v>99</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="R10" s="1" t="s">
         <v>67</v>
@@ -3298,7 +3293,7 @@
         <v>69</v>
       </c>
       <c r="W10" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3309,16 +3304,16 @@
         <v>10</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>24</v>
+        <v>102</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>28</v>
@@ -3327,13 +3322,13 @@
         <v>28</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="L11" s="1" t="s">
         <v>32</v>
@@ -3351,7 +3346,7 @@
         <v>99</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="R11" s="1" t="s">
         <v>67</v>
@@ -3369,7 +3364,7 @@
         <v>78</v>
       </c>
       <c r="W11" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3380,34 +3375,34 @@
         <v>100</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>34</v>
@@ -3422,7 +3417,7 @@
         <v>36</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="R12" s="1" t="s">
         <v>38</v>
@@ -3434,10 +3429,10 @@
         <v>40</v>
       </c>
       <c r="U12" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="V12" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3448,34 +3443,34 @@
         <v>101</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>34</v>
@@ -3490,7 +3485,7 @@
         <v>36</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="R13" s="1" t="s">
         <v>38</v>
@@ -3502,10 +3497,10 @@
         <v>40</v>
       </c>
       <c r="U13" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="V13" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3516,34 +3511,34 @@
         <v>102</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>34</v>
@@ -3558,7 +3553,7 @@
         <v>36</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="R14" s="1" t="s">
         <v>38</v>
@@ -3570,10 +3565,10 @@
         <v>40</v>
       </c>
       <c r="U14" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="V14" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3584,34 +3579,34 @@
         <v>103</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>82</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>34</v>
@@ -3626,7 +3621,7 @@
         <v>36</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="R15" s="1" t="s">
         <v>38</v>
@@ -3638,10 +3633,10 @@
         <v>40</v>
       </c>
       <c r="U15" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="V15" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3652,34 +3647,34 @@
         <v>104</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="M16" s="1" t="s">
         <v>34</v>
@@ -3691,10 +3686,10 @@
         <v>35</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="R16" s="1" t="s">
         <v>38</v>
@@ -3706,10 +3701,10 @@
         <v>40</v>
       </c>
       <c r="U16" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="V16" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3720,16 +3715,16 @@
         <v>105</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>28</v>
@@ -3738,16 +3733,16 @@
         <v>28</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="M17" s="1" t="s">
         <v>33</v>
@@ -3759,10 +3754,10 @@
         <v>35</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="R17" s="1" t="s">
         <v>38</v>
@@ -3771,13 +3766,13 @@
         <v>39</v>
       </c>
       <c r="T17" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="U17" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="V17" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3788,16 +3783,16 @@
         <v>106</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>28</v>
@@ -3806,16 +3801,16 @@
         <v>28</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>33</v>
@@ -3827,10 +3822,10 @@
         <v>35</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="R18" s="1" t="s">
         <v>38</v>
@@ -3839,13 +3834,13 @@
         <v>39</v>
       </c>
       <c r="T18" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="U18" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="V18" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3856,16 +3851,16 @@
         <v>107</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>28</v>
@@ -3874,16 +3869,16 @@
         <v>28</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>33</v>
@@ -3895,10 +3890,10 @@
         <v>35</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="R19" s="1" t="s">
         <v>38</v>
@@ -3907,13 +3902,13 @@
         <v>39</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="U19" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="V19" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3924,16 +3919,16 @@
         <v>200</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>28</v>
@@ -3942,16 +3937,16 @@
         <v>28</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>33</v>
@@ -3963,10 +3958,10 @@
         <v>35</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="R20" s="1" t="s">
         <v>38</v>
@@ -3978,13 +3973,13 @@
         <v>40</v>
       </c>
       <c r="U20" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="V20" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="W20" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3995,16 +3990,16 @@
         <v>201</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>28</v>
@@ -4013,16 +4008,16 @@
         <v>28</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>33</v>
@@ -4034,10 +4029,10 @@
         <v>35</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="R21" s="1" t="s">
         <v>38</v>
@@ -4049,13 +4044,13 @@
         <v>40</v>
       </c>
       <c r="U21" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="V21" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="W21" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4066,16 +4061,16 @@
         <v>202</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>28</v>
@@ -4084,16 +4079,16 @@
         <v>28</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>33</v>
@@ -4105,10 +4100,10 @@
         <v>35</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="R22" s="1" t="s">
         <v>38</v>
@@ -4120,13 +4115,13 @@
         <v>40</v>
       </c>
       <c r="U22" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="V22" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="W22" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4137,16 +4132,16 @@
         <v>203</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>28</v>
@@ -4155,16 +4150,16 @@
         <v>28</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="M23" s="1" t="s">
         <v>33</v>
@@ -4176,10 +4171,10 @@
         <v>35</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q23" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="R23" s="1" t="s">
         <v>38</v>
@@ -4191,13 +4186,13 @@
         <v>40</v>
       </c>
       <c r="U23" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="V23" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="W23" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4208,34 +4203,34 @@
         <v>204</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="M24" s="1" t="s">
         <v>34</v>
@@ -4247,10 +4242,10 @@
         <v>35</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q24" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="R24" s="1" t="s">
         <v>38</v>
@@ -4262,13 +4257,13 @@
         <v>40</v>
       </c>
       <c r="U24" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="V24" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="W24" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4279,16 +4274,16 @@
         <v>300</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>28</v>
@@ -4300,13 +4295,13 @@
         <v>82</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="M25" s="1" t="s">
         <v>33</v>
@@ -4318,10 +4313,10 @@
         <v>35</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q25" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="R25" s="1" t="s">
         <v>38</v>
@@ -4333,13 +4328,13 @@
         <v>40</v>
       </c>
       <c r="U25" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="V25" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="W25" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4350,34 +4345,34 @@
         <v>301</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="M26" s="1" t="s">
         <v>33</v>
@@ -4389,10 +4384,10 @@
         <v>35</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q26" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="R26" s="1" t="s">
         <v>38</v>
@@ -4404,13 +4399,13 @@
         <v>40</v>
       </c>
       <c r="U26" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="V26" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="W26" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4421,16 +4416,16 @@
         <v>302</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>28</v>
@@ -4442,13 +4437,13 @@
         <v>82</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="M27" s="1" t="s">
         <v>33</v>
@@ -4460,10 +4455,10 @@
         <v>35</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q27" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="R27" s="1" t="s">
         <v>38</v>
@@ -4475,13 +4470,13 @@
         <v>40</v>
       </c>
       <c r="U27" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="V27" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="W27" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4492,16 +4487,16 @@
         <v>304</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>28</v>
@@ -4513,13 +4508,13 @@
         <v>82</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="M28" s="1" t="s">
         <v>33</v>
@@ -4531,10 +4526,10 @@
         <v>35</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="R28" s="1" t="s">
         <v>38</v>
@@ -4546,13 +4541,13 @@
         <v>40</v>
       </c>
       <c r="U28" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="V28" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="W28" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4563,16 +4558,16 @@
         <v>305</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>28</v>
@@ -4584,13 +4579,13 @@
         <v>82</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>33</v>
@@ -4602,10 +4597,10 @@
         <v>35</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="R29" s="1" t="s">
         <v>38</v>
@@ -4617,10 +4612,10 @@
         <v>40</v>
       </c>
       <c r="U29" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="V29" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4631,16 +4626,16 @@
         <v>306</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>28</v>
@@ -4652,13 +4647,13 @@
         <v>46</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="M30" s="1" t="s">
         <v>33</v>
@@ -4670,10 +4665,10 @@
         <v>35</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q30" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="R30" s="1" t="s">
         <v>38</v>
@@ -4685,10 +4680,10 @@
         <v>40</v>
       </c>
       <c r="U30" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="V30" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4696,10 +4691,10 @@
         <v>400</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>223</v>
+        <v>102</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>224</v>
+        <v>103</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>225</v>
@@ -4708,7 +4703,7 @@
         <v>226</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>28</v>
@@ -4717,7 +4712,7 @@
         <v>227</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="M31" s="1" t="s">
         <v>33</v>
@@ -4729,7 +4724,7 @@
         <v>228</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q31" s="1" t="s">
         <v>229</v>
@@ -4744,10 +4739,10 @@
         <v>40</v>
       </c>
       <c r="U31" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="V31" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="W31" s="1" t="s">
         <v>230</v>
@@ -4764,10 +4759,10 @@
         <v>401</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>223</v>
+        <v>102</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>224</v>
+        <v>103</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>232</v>
@@ -4782,7 +4777,7 @@
         <v>28</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J32" s="1" t="s">
         <v>234</v>
@@ -4791,7 +4786,7 @@
         <v>235</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="M32" s="1" t="s">
         <v>33</v>
@@ -4803,7 +4798,7 @@
         <v>35</v>
       </c>
       <c r="P32" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q32" s="1" t="s">
         <v>236</v>
@@ -4815,13 +4810,13 @@
         <v>39</v>
       </c>
       <c r="T32" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="U32" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="V32" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="W32" s="1" t="s">
         <v>237</v>
@@ -4835,10 +4830,10 @@
         <v>402</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>223</v>
+        <v>102</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>224</v>
+        <v>103</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>238</v>
@@ -4862,7 +4857,7 @@
         <v>241</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="M33" s="1" t="s">
         <v>33</v>
@@ -4889,7 +4884,7 @@
         <v>40</v>
       </c>
       <c r="U33" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="V33" s="1" t="s">
         <v>244</v>
@@ -4910,7 +4905,7 @@
         <v>246</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>247</v>
@@ -4934,7 +4929,7 @@
         <v>251</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="M34" s="1" t="s">
         <v>33</v>
@@ -4958,13 +4953,13 @@
         <v>68</v>
       </c>
       <c r="T34" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="U34" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="V34" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="W34" s="1" t="s">
         <v>253</v>
@@ -4981,7 +4976,7 @@
         <v>246</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>254</v>
@@ -4993,7 +4988,7 @@
         <v>28</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>256</v>
@@ -5005,7 +5000,7 @@
         <v>258</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="M35" s="1" t="s">
         <v>33</v>
@@ -5017,7 +5012,7 @@
         <v>35</v>
       </c>
       <c r="P35" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Q35" s="1" t="s">
         <v>259</v>
@@ -5032,10 +5027,10 @@
         <v>40</v>
       </c>
       <c r="U35" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="V35" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="W35" s="1" t="s">
         <v>260</v>
@@ -5052,7 +5047,7 @@
         <v>246</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>261</v>
@@ -5076,7 +5071,7 @@
         <v>265</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="M36" s="1" t="s">
         <v>33</v>
@@ -5088,7 +5083,7 @@
         <v>35</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Q36" s="1" t="s">
         <v>266</v>
@@ -5103,10 +5098,10 @@
         <v>40</v>
       </c>
       <c r="U36" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="V36" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5120,7 +5115,7 @@
         <v>246</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>267</v>
@@ -5156,7 +5151,7 @@
         <v>35</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Q37" s="3" t="s">
         <v>271</v>
@@ -5191,7 +5186,7 @@
         <v>246</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>273</v>
@@ -5203,7 +5198,7 @@
         <v>28</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>54</v>
@@ -5227,7 +5222,7 @@
         <v>35</v>
       </c>
       <c r="P38" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q38" s="1" t="s">
         <v>277</v>
@@ -5262,7 +5257,7 @@
         <v>279</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>280</v>
@@ -5656,8 +5651,11 @@
       <c r="I9" s="1" t="s">
         <v>306</v>
       </c>
+      <c r="J9" s="6" t="s">
+        <v>342</v>
+      </c>
       <c r="L9" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5665,22 +5663,22 @@
         <v>101</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="E10" s="6" t="s">
         <v>345</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>346</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>303</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>305</v>
@@ -5689,10 +5687,10 @@
         <v>306</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5700,13 +5698,13 @@
         <v>102</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>317</v>
@@ -5715,7 +5713,7 @@
         <v>303</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>305</v>
@@ -5724,10 +5722,10 @@
         <v>306</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5735,13 +5733,13 @@
         <v>103</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>317</v>
@@ -5750,7 +5748,7 @@
         <v>318</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>305</v>
@@ -5759,10 +5757,10 @@
         <v>306</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5770,7 +5768,7 @@
         <v>104</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>339</v>
@@ -5779,7 +5777,7 @@
         <v>301</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>303</v>
@@ -5794,10 +5792,10 @@
         <v>306</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5805,13 +5803,13 @@
         <v>105</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>317</v>
@@ -5829,10 +5827,10 @@
         <v>306</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5840,7 +5838,7 @@
         <v>106</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>339</v>
@@ -5849,7 +5847,7 @@
         <v>301</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>303</v>
@@ -5864,7 +5862,7 @@
         <v>306</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5872,16 +5870,16 @@
         <v>107</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>301</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>303</v>
@@ -5896,10 +5894,10 @@
         <v>306</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5907,16 +5905,16 @@
         <v>108</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>303</v>
@@ -5925,16 +5923,16 @@
         <v>304</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5942,16 +5940,16 @@
         <v>109</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>303</v>
@@ -5960,16 +5958,16 @@
         <v>304</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5977,16 +5975,16 @@
         <v>110</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>303</v>
@@ -5995,16 +5993,16 @@
         <v>304</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>306</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6012,34 +6010,34 @@
         <v>111</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>303</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>341</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6047,34 +6045,34 @@
         <v>112</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>301</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>303</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>305</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6082,13 +6080,13 @@
         <v>113</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>311</v>
@@ -6106,10 +6104,10 @@
         <v>306</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6117,16 +6115,16 @@
         <v>114</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>301</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>303</v>
@@ -6141,10 +6139,10 @@
         <v>306</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6152,37 +6150,37 @@
         <v>115</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>303</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>413</v>
+        <v>347</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>414</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>306</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6190,13 +6188,13 @@
         <v>116</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>317</v>
@@ -6205,7 +6203,7 @@
         <v>318</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>305</v>
@@ -6214,10 +6212,10 @@
         <v>306</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6225,13 +6223,13 @@
         <v>117</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>317</v>
@@ -6240,7 +6238,7 @@
         <v>318</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>305</v>
@@ -6249,10 +6247,10 @@
         <v>306</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6260,16 +6258,16 @@
         <v>118</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>301</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>303</v>
@@ -6284,10 +6282,10 @@
         <v>306</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6295,16 +6293,16 @@
         <v>119</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>301</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>303</v>
@@ -6319,10 +6317,10 @@
         <v>306</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6330,16 +6328,16 @@
         <v>120</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>301</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>303</v>
@@ -6354,10 +6352,10 @@
         <v>306</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6365,16 +6363,16 @@
         <v>129</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>303</v>
@@ -6383,16 +6381,16 @@
         <v>304</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>306</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6400,16 +6398,16 @@
         <v>121</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>301</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>303</v>
@@ -6424,10 +6422,10 @@
         <v>306</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6435,7 +6433,7 @@
         <v>122</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>300</v>
@@ -6453,10 +6451,10 @@
         <v>306</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="29.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6464,16 +6462,16 @@
         <v>123</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="E33" s="8" t="s">
-        <v>443</v>
+      <c r="E33" s="9" t="s">
+        <v>444</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>303</v>
@@ -6488,13 +6486,13 @@
         <v>306</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6502,16 +6500,16 @@
         <v>124</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>301</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>303</v>
@@ -6523,13 +6521,13 @@
         <v>305</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6537,16 +6535,16 @@
         <v>125</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>301</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>303</v>
@@ -6558,13 +6556,13 @@
         <v>305</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6572,16 +6570,16 @@
         <v>126</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>301</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>303</v>
@@ -6596,10 +6594,10 @@
         <v>306</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6607,7 +6605,7 @@
         <v>127</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>300</v>
@@ -6616,7 +6614,7 @@
         <v>301</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>303</v>
@@ -6625,16 +6623,16 @@
         <v>304</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>305</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6642,16 +6640,16 @@
         <v>128</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>303</v>
@@ -6660,16 +6658,16 @@
         <v>304</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>306</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
   </sheetData>
@@ -6708,496 +6706,496 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="C1" s="9" t="s">
         <v>472</v>
       </c>
+      <c r="C1" s="10" t="s">
+        <v>473</v>
+      </c>
       <c r="D1" s="3" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="G1" s="9" t="s">
         <v>476</v>
       </c>
+      <c r="G1" s="10" t="s">
+        <v>477</v>
+      </c>
       <c r="H1" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="10" t="s">
-        <v>479</v>
+      <c r="C2" s="11" t="s">
+        <v>480</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="G2" s="9"/>
+        <v>120</v>
+      </c>
+      <c r="G2" s="10"/>
       <c r="H2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="11" t="s">
-        <v>482</v>
-      </c>
-      <c r="D3" s="11" t="s">
+      <c r="C3" s="12" t="s">
         <v>483</v>
       </c>
+      <c r="D3" s="12" t="s">
+        <v>484</v>
+      </c>
       <c r="E3" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="11" t="s">
-        <v>487</v>
+      <c r="C4" s="12" t="s">
+        <v>488</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>20</v>
@@ -7206,387 +7204,375 @@
         <v>20</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>545</v>
-      </c>
       <c r="E24" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G24" s="3"/>
     </row>
     <row r="25" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="C25" s="11" t="s">
-        <v>548</v>
-      </c>
-      <c r="D25" s="11" t="s">
+      <c r="C25" s="12" t="s">
         <v>549</v>
       </c>
+      <c r="D25" s="12" t="s">
+        <v>550</v>
+      </c>
       <c r="E25" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="C26" s="12" t="s">
-        <v>551</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>551</v>
+      <c r="C26" s="13" t="s">
+        <v>552</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>552</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>296</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>289</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>290</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>291</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>292</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>562</v>
+        <v>503</v>
+      </c>
+      <c r="H31" s="14" t="s">
+        <v>563</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>293</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>294</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>485</v>
-      </c>
-      <c r="H33" s="14" t="s">
-        <v>568</v>
+        <v>486</v>
+      </c>
+      <c r="H33" s="15" t="s">
+        <v>569</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>295</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>298</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="7"/>
-      <c r="C36" s="15" t="s">
-        <v>574</v>
-      </c>
-      <c r="D36" s="16" t="s">
-        <v>575</v>
-      </c>
+      <c r="B36" s="8"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="16"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
     </row>
     <row r="37" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="7"/>
-      <c r="C37" s="15" t="s">
-        <v>576</v>
-      </c>
-      <c r="D37" s="16" t="s">
-        <v>577</v>
-      </c>
+      <c r="B37" s="8"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="16"/>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
     </row>
     <row r="38" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="7"/>
-      <c r="C38" s="15" t="s">
-        <v>578</v>
-      </c>
-      <c r="D38" s="16" t="s">
-        <v>579</v>
-      </c>
+      <c r="B38" s="8"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="16"/>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
     </row>
@@ -7617,7 +7603,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -7635,7 +7621,7 @@
         <v>6</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7806,7 +7792,7 @@
         <v>9</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>5</v>
@@ -7826,7 +7812,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>5</v>
@@ -7846,7 +7832,7 @@
         <v>100</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>100</v>
@@ -7866,13 +7852,13 @@
         <v>101</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>101</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>33</v>
@@ -7886,13 +7872,13 @@
         <v>101</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>102</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>33</v>
@@ -7906,13 +7892,13 @@
         <v>101</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>103</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>33</v>
@@ -7926,13 +7912,13 @@
         <v>102</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>104</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>33</v>
@@ -7946,13 +7932,13 @@
         <v>103</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>105</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>33</v>
@@ -7966,13 +7952,13 @@
         <v>104</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>106</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>33</v>
@@ -7986,19 +7972,19 @@
         <v>105</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>107</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>33</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8009,19 +7995,19 @@
         <v>105</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D20" s="1" t="n">
         <v>108</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>33</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8032,13 +8018,13 @@
         <v>106</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D21" s="1" t="n">
         <v>109</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>33</v>
@@ -8052,19 +8038,19 @@
         <v>107</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D22" s="1" t="n">
         <v>107</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>33</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8075,13 +8061,13 @@
         <v>200</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D23" s="1" t="n">
         <v>110</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>33</v>
@@ -8095,16 +8081,16 @@
         <v>201</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D24" s="1" t="n">
         <v>111</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8115,19 +8101,19 @@
         <v>202</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D25" s="1" t="n">
         <v>107</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>33</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8138,13 +8124,13 @@
         <v>202</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D26" s="1" t="n">
         <v>108</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>33</v>
@@ -8158,13 +8144,13 @@
         <v>203</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D27" s="1" t="n">
         <v>112</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>33</v>
@@ -8178,13 +8164,13 @@
         <v>204</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D28" s="1" t="n">
         <v>113</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>33</v>
@@ -8198,16 +8184,16 @@
         <v>300</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D29" s="1" t="n">
         <v>114</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8218,13 +8204,13 @@
         <v>300</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D30" s="1" t="n">
         <v>115</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>33</v>
@@ -8238,13 +8224,13 @@
         <v>300</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D31" s="1" t="n">
         <v>116</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>33</v>
@@ -8258,13 +8244,13 @@
         <v>300</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D32" s="1" t="n">
         <v>117</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>33</v>
@@ -8278,13 +8264,13 @@
         <v>301</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D33" s="1" t="n">
         <v>107</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>33</v>
@@ -8298,13 +8284,13 @@
         <v>301</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D34" s="1" t="n">
         <v>118</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>33</v>
@@ -8318,13 +8304,13 @@
         <v>301</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D35" s="1" t="n">
         <v>119</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>34</v>
@@ -8338,13 +8324,13 @@
         <v>302</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D36" s="1" t="n">
         <v>120</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>33</v>
@@ -8358,13 +8344,13 @@
         <v>302</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D37" s="1" t="n">
         <v>129</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>33</v>
@@ -8378,13 +8364,13 @@
         <v>304</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D38" s="1" t="n">
         <v>128</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>33</v>
@@ -8398,13 +8384,13 @@
         <v>305</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D39" s="1" t="n">
         <v>121</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>33</v>
@@ -8418,13 +8404,13 @@
         <v>305</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D40" s="1" t="n">
         <v>122</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>33</v>
@@ -8438,13 +8424,13 @@
         <v>306</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D41" s="1" t="n">
         <v>121</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>33</v>
@@ -8464,7 +8450,7 @@
         <v>123</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>33</v>
@@ -8484,7 +8470,7 @@
         <v>124</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>33</v>
@@ -8504,13 +8490,13 @@
         <v>125</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>34</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8527,7 +8513,7 @@
         <v>6</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>33</v>
@@ -8547,7 +8533,7 @@
         <v>126</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>33</v>
@@ -8567,7 +8553,7 @@
         <v>127</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>33</v>
@@ -8581,7 +8567,7 @@
         <v>503</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="D48" s="1" t="n">
         <v>3</v>
@@ -8601,7 +8587,7 @@
         <v>504</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="D49" s="1" t="n">
         <v>3</v>
@@ -8627,7 +8613,7 @@
         <v>7</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>33</v>
@@ -8660,19 +8646,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8683,13 +8669,13 @@
         <v>24</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="15" t="s">
-        <v>595</v>
+      <c r="E2" s="6" t="s">
+        <v>590</v>
       </c>
       <c r="F2" s="3"/>
       <c r="H2" s="1"/>
@@ -8699,16 +8685,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="15" t="s">
-        <v>597</v>
+      <c r="E3" s="6" t="s">
+        <v>592</v>
       </c>
       <c r="F3" s="3"/>
       <c r="H3" s="1"/>
@@ -8718,16 +8704,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>599</v>
+        <v>157</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>594</v>
       </c>
       <c r="F4" s="3"/>
       <c r="H4" s="1"/>
@@ -8737,16 +8723,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>601</v>
+        <v>157</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>596</v>
       </c>
       <c r="H5" s="1"/>
     </row>
@@ -8755,16 +8741,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>223</v>
+        <v>102</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>603</v>
+        <v>103</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>598</v>
       </c>
       <c r="H6" s="1"/>
     </row>
@@ -8776,13 +8762,13 @@
         <v>246</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>605</v>
+        <v>157</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>600</v>
       </c>
       <c r="H7" s="1"/>
     </row>
@@ -8794,13 +8780,13 @@
         <v>279</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>607</v>
+        <v>157</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>602</v>
       </c>
       <c r="H8" s="1"/>
     </row>
@@ -8835,28 +8821,28 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>610</v>
+        <v>508</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>605</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8864,7 +8850,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>1</v>
@@ -8872,48 +8858,51 @@
       <c r="D2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="15" t="s">
-        <v>614</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>574</v>
+      <c r="E2" s="6" t="s">
+        <v>609</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>610</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>615</v>
-      </c>
-      <c r="H2" s="15" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>611</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>617</v>
-      </c>
-      <c r="C3" s="7" t="n">
+      <c r="B3" s="8" t="s">
+        <v>613</v>
+      </c>
+      <c r="C3" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>501</v>
+        <v>615</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>616</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>1</v>
@@ -8921,40 +8910,43 @@
       <c r="D4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="15" t="s">
-        <v>621</v>
+      <c r="E4" s="6" t="s">
+        <v>618</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>501</v>
+        <v>615</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>622</v>
-      </c>
-      <c r="H4" s="15" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>619</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="32.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>5</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>223</v>
+        <v>102</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>625</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>574</v>
+        <v>622</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>610</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>626</v>
+        <v>623</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>624</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8962,22 +8954,25 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="F6" s="18" t="s">
+        <v>627</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>628</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>629</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>630</v>
+      <c r="H6" s="1" t="s">
+        <v>628</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8985,22 +8980,25 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>632</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>629</v>
+        <v>630</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>627</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>633</v>
+        <v>631</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>631</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9008,22 +9006,25 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>635</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>574</v>
+        <v>633</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>610</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>636</v>
+        <v>634</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>634</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9031,22 +9032,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>638</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>629</v>
+        <v>636</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>627</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>639</v>
+        <v>637</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>637</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9054,22 +9058,25 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>629</v>
+        <v>639</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>627</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>642</v>
+        <v>640</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>640</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9077,22 +9084,25 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>4</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>501</v>
+        <v>615</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>645</v>
+        <v>643</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>643</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9100,22 +9110,25 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>4</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>647</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>629</v>
+        <v>645</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>627</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>646</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="41" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9123,30 +9136,33 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="C13" s="3" t="n">
         <v>4</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>650</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>629</v>
+        <v>648</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>627</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>649</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C14" s="3" t="n">
         <v>6</v>
@@ -9155,24 +9171,24 @@
         <v>246</v>
       </c>
       <c r="E14" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="H14" s="3" t="s">
         <v>653</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>654</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="15" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>7</v>
@@ -9180,17 +9196,17 @@
       <c r="D15" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" s="6" t="s">
+        <v>655</v>
+      </c>
+      <c r="F15" s="18" t="s">
+        <v>627</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="H15" s="6" t="s">
         <v>657</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>629</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>658</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>659</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9198,30 +9214,30 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>5</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>223</v>
+        <v>102</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>661</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>574</v>
+        <v>659</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>610</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>7</v>
@@ -9229,14 +9245,17 @@
       <c r="D17" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E17" s="6" t="s">
+        <v>662</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="H17" s="6" t="s">
         <v>664</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>665</v>
       </c>
     </row>
   </sheetData>
@@ -9260,164 +9279,162 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="46.03"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="134.94"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>666</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>667</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>668</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>669</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>670</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>671</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>672</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>673</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>670</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>674</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>675</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>676</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>670</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>677</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>678</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>679</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>670</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>680</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>681</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>203</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>687</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>688</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>670</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>689</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>690</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>691</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>683</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>693</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>694</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>670</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>695</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>696</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>697</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>670</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>698</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9497,13 +9514,13 @@
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="F1" s="1"/>
-      <c r="G1" s="7"/>
+      <c r="G1" s="8"/>
       <c r="H1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9517,7 +9534,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="F2" s="1"/>
       <c r="H2" s="1"/>
@@ -9533,7 +9550,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="F3" s="1"/>
       <c r="H3" s="1"/>
@@ -9549,7 +9566,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="F4" s="1"/>
       <c r="H4" s="1"/>
@@ -9565,7 +9582,7 @@
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="F5" s="1"/>
       <c r="H5" s="1"/>
@@ -9581,7 +9598,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="F6" s="1"/>
       <c r="H6" s="1"/>
@@ -9597,7 +9614,7 @@
         <v>2</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="F7" s="1"/>
       <c r="H7" s="1"/>
@@ -9613,7 +9630,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="F8" s="1"/>
       <c r="H8" s="1"/>
@@ -9629,7 +9646,7 @@
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="F9" s="1"/>
       <c r="H9" s="1"/>
@@ -9639,13 +9656,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>4</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="F10" s="1"/>
       <c r="H10" s="1"/>
@@ -9655,13 +9672,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>4</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="F11" s="1"/>
       <c r="H11" s="1"/>
@@ -9671,16 +9688,16 @@
         <v>100</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>5</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="F12" s="1"/>
-      <c r="G12" s="7"/>
+      <c r="G12" s="8"/>
       <c r="H12" s="1"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9688,16 +9705,16 @@
         <v>101</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>5</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="F13" s="1"/>
-      <c r="G13" s="7"/>
+      <c r="G13" s="8"/>
       <c r="H13" s="1"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9705,16 +9722,16 @@
         <v>102</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>6</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="F14" s="1"/>
-      <c r="G14" s="7"/>
+      <c r="G14" s="8"/>
       <c r="H14" s="1"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9722,13 +9739,13 @@
         <v>103</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>6</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="F15" s="1"/>
       <c r="H15" s="1"/>
@@ -9738,13 +9755,13 @@
         <v>104</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>6</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="F16" s="1"/>
       <c r="H16" s="1"/>
@@ -9754,13 +9771,13 @@
         <v>105</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>7</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="F17" s="1"/>
       <c r="H17" s="1"/>
@@ -9770,13 +9787,13 @@
         <v>106</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>7</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="F18" s="1"/>
       <c r="H18" s="1"/>
@@ -9786,13 +9803,13 @@
         <v>107</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>701</v>
+        <v>641</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9800,13 +9817,13 @@
         <v>200</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C20" s="1" t="n">
         <v>8</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -9816,13 +9833,13 @@
         <v>201</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C21" s="1" t="n">
         <v>9</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9830,13 +9847,13 @@
         <v>202</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>9</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9844,13 +9861,13 @@
         <v>203</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>9</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9858,13 +9875,13 @@
         <v>204</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>8</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9872,13 +9889,13 @@
         <v>300</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>10</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9886,13 +9903,13 @@
         <v>301</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C26" s="1" t="n">
         <v>10</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9900,13 +9917,13 @@
         <v>302</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>11</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9914,13 +9931,13 @@
         <v>304</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C28" s="1" t="n">
         <v>11</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9928,13 +9945,13 @@
         <v>305</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C29" s="1" t="n">
         <v>12</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9942,13 +9959,13 @@
         <v>306</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C30" s="1" t="n">
         <v>12</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9962,7 +9979,7 @@
         <v>15</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9976,7 +9993,7 @@
         <v>15</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9990,7 +10007,7 @@
         <v>13</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10004,7 +10021,7 @@
         <v>14</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10018,7 +10035,7 @@
         <v>14</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10026,13 +10043,13 @@
         <v>503</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="C36" s="1" t="n">
         <v>13</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10040,13 +10057,13 @@
         <v>504</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="C37" s="1" t="n">
         <v>13</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10060,7 +10077,7 @@
         <v>16</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
     </row>
   </sheetData>
@@ -10089,19 +10106,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="15" t="s">
-        <v>706</v>
+      <c r="E1" s="6" t="s">
+        <v>703</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10111,14 +10128,14 @@
       <c r="B2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="15" t="s">
-        <v>707</v>
+      <c r="C2" s="6" t="s">
+        <v>704</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>708</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>709</v>
+        <v>705</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>706</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10126,16 +10143,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>710</v>
+        <v>157</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>707</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>711</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>712</v>
+        <v>708</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>709</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10143,16 +10160,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>713</v>
+        <v>103</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>710</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>714</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>715</v>
+        <v>711</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>712</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10160,16 +10177,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>714</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>715</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>716</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>717</v>
-      </c>
-      <c r="D5" s="0" t="s">
-        <v>718</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>719</v>
       </c>
     </row>
   </sheetData>

--- a/fiches indicateurs.xlsx
+++ b/fiches indicateurs.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="indicateurs" sheetId="1" state="visible" r:id="rId3"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1884" uniqueCount="717">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2004" uniqueCount="741">
   <si>
     <t xml:space="preserve">fiche_indicateur</t>
   </si>
@@ -339,6 +339,45 @@
     <t xml:space="preserve">Indicateur captage. Statut (oui/en cours/non). Instruction longue. Critère important de vulnérabilité réglementaire.</t>
   </si>
   <si>
+    <t xml:space="preserve">Statut du foncier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Typologie permet d'identifier le type de propriétaire de la parcelle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRIVE, TERRE COUTUMIERE, COLLECTIVITE, mixte (plusieurs types) ou non renseigné</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comparer les captages selon leur implantation sur dans le cadastre afin de déterminer de potentiel vulnérabilité réglementaire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Captage sur terrain privé = forte criticité</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zonal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plan d’Urbanisme Directeur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type d’occupation et  dynamiques d’aménagement du territoire (zones urbanisées, à urbaniser, naturelles, zones à enjeux, terrain agricole constructible ou non)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">non</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comparer les captages selon les perspectives actuelles et futures de l’aménagement du territoire sur la ressource en eau </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calcul surfacique par unité spatiale régulière puis agrégation au bassin versant.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">maille</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carte choroplèthe</t>
+  </si>
+  <si>
     <t xml:space="preserve">Vulnérabilité Intrinsèque</t>
   </si>
   <si>
@@ -393,30 +432,15 @@
     <t xml:space="preserve">Superficie des intersections avec les zones inscrites au patrimoine mondial de l'UNESCO</t>
   </si>
   <si>
-    <t xml:space="preserve">non</t>
-  </si>
-  <si>
     <t xml:space="preserve">ha</t>
   </si>
   <si>
     <t xml:space="preserve">Comparer les bassins versants AEP entre eux par rapport à leur taux de couverture par une zone UNESCO</t>
   </si>
   <si>
-    <t xml:space="preserve">Calcul surfacique par unité spatiale régulière puis agrégation au bassin versant.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">maille</t>
-  </si>
-  <si>
     <t xml:space="preserve">Présence d’une partie du bassin versant dans zone UNESCO = criticité faible bien que enjeu fort</t>
   </si>
   <si>
-    <t xml:space="preserve">Zonal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carte choroplèthe</t>
-  </si>
-  <si>
     <t xml:space="preserve">Zones protégées provinciales</t>
   </si>
   <si>
@@ -501,10 +525,10 @@
     <t xml:space="preserve">Fort couvert forestier = faible criticité</t>
   </si>
   <si>
-    <t xml:space="preserve">Pressions Anthropiques</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pression</t>
+    <t xml:space="preserve">MENACES ANTHROPIQUES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menace</t>
   </si>
   <si>
     <t xml:space="preserve">Occupation sol (surfaces agricoles)</t>
@@ -522,7 +546,7 @@
     <t xml:space="preserve">Forte surface agricole = pression potentielle élevée</t>
   </si>
   <si>
-    <t xml:space="preserve">Pressions Environnementales</t>
+    <t xml:space="preserve">MENACES NATURELLES</t>
   </si>
   <si>
     <t xml:space="preserve">Incendies cumulés</t>
@@ -708,12 +732,177 @@
     <t xml:space="preserve">Fort linéaire routier = fragmentation et imperméabilisation élevées</t>
   </si>
   <si>
+    <t xml:space="preserve">Géologie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type de sol et de roche. Propriété des sols correspondant (infiltrant / intermédiaire / ruisselant)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comparer les bassins versants selon les propriétés des sols afin de qualifier leur comportement hydrologique.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regroupement des classes géologiques en catégories simplifiées.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sols infiltrant = moins critique, ruisselants = plus critique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indicateur simplifié (grandes classes). Risque redondance avec IDPR. À agréger.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vulnérabilité intrinsèque des eaux souterraines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Niveau de sensibilité naturelle du terrain à laisser passer l’eau.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indice (1 à 5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comparer les bassins versants selon leur vulnérabilité intrinsèque afin d’identifier les zones les plus sensibles aux transferts.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Étude à réaliser pour définir les modalités de production de l’indicateur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Déjà normalisé (1-5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positif (valeur ordonnée si valeur haute = mieux)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C’est l’indicateur qui est le plus proche d’un IDPR mais qui ne l’est pas. Se base sur la carte géologique au 1/50000.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pressions Quantitatives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BBR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bilan Besoin Ressource, Écart entre l’eau disponible et les besoins.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Classe (non impacté / impacté / très impacté / déficitaire / très déficitaire)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comparer les bassins versants selon l’équilibre ressource/besoins afin d’identifier les situations de tension ou de déficit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utilisation directe de la classe issue du modèle avec agrégation au bassin versant.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Déficit ressource = criticité maximale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indicateur clé (5 classes). Carte BV (vert à rouge). Base analyse multicritère stratégique.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pluviométrie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantité de pluie reçue.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comparer les bassins versants selon les apports en eau afin de contextualiser la disponibilité de la ressource.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calcul de la moyenne spatiale par bassin versant.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faible pluie = forte criticité</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Donnée régionalisée. Redondance avec capacité production. À discuter.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Niveau nappes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suivi piézométrique des eaux souterraines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">m NGF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suivre l'évolution du niveau des nappes phréatiques pour détecter les tensions quantitatives.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agrégation des données piézométriques par bassin versant ou maille.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Niveau bas = forte criticité quantitative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre de prélèvement AODPE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre de prélèvements d’eau autorisés.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comparer les captages selon le nombre de prélèvements afin d’évaluer la pression d’usage.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comptage des prélèvements associés à chaque captage.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est la présence qui est positive, l'absence d'autorisation AODPE est négative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indicateur pression captage. Donnée dynamique DAVAR. Intégrable en analyse.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Volume des prélèvements AODPE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Volume total d’eau prélevé.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comparer les captages selon les volumes prélevés afin d’évaluer l’intensité de la pression quantitative.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Somme des volumes autorisés associés à chaque captage.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Volume élevé = pression forte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complément du nombre. Permet comparaison avec ressource disponible.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pressions Qualitatives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualité eau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualité de l’eau (bonne à mauvaise).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Classe (A1 / A2 / A3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comparer les captages selon leur qualité afin d’identifier ceux nécessitant des actions de gestion ou de protection.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attribution d’une classe par captage selon les données disponibles.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Classe dégradée = criticité élevée</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Donnée complexe et peu disponible. Difficilement intégrable dans modèle actuel.</t>
+  </si>
+  <si>
     <t xml:space="preserve">IDPR</t>
   </si>
   <si>
-    <t xml:space="preserve">Niveau de sensibilité naturelle du terrain à laisser passer l’eau.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Indice (0 à 4)</t>
   </si>
   <si>
@@ -727,171 +916,6 @@
   </si>
   <si>
     <t xml:space="preserve">Cette indicateur n’est pas produit par la DIMENC actuellement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Géologie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Type de sol et de roche. Propriété des sols correspondant (infiltrant / intermédiaire / ruisselant)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comparer les bassins versants selon les propriétés des sols afin de qualifier leur comportement hydrologique.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regroupement des classes géologiques en catégories simplifiées.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sols infiltrant = moins critique, ruisselants = plus critique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indicateur simplifié (grandes classes). Risque redondance avec IDPR. À agréger.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vulnérabilité intrinsèque des eaux souterraines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indice (1 à 5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comparer les bassins versants selon leur vulnérabilité intrinsèque afin d’identifier les zones les plus sensibles aux transferts.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Étude à réaliser pour définir les modalités de production de l’indicateur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Déjà normalisé (1-5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Positif (valeur ordonnée si valeur haute = mieux)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C’est l’indicateur qui est le plus proche d’un IDPR mais qui ne l’est pas. Se base sur la carte géologique au 1/50000.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pressions Quantitatives</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BBR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bilan Besoin Ressource, Écart entre l’eau disponible et les besoins.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Classe (non impacté / impacté / très impacté / déficitaire / très déficitaire)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comparer les bassins versants selon l’équilibre ressource/besoins afin d’identifier les situations de tension ou de déficit.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Utilisation directe de la classe issue du modèle avec agrégation au bassin versant.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Déficit ressource = criticité maximale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indicateur clé (5 classes). Carte BV (vert à rouge). Base analyse multicritère stratégique.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pluviométrie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantité de pluie reçue.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comparer les bassins versants selon les apports en eau afin de contextualiser la disponibilité de la ressource.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calcul de la moyenne spatiale par bassin versant.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Faible pluie = forte criticité</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Donnée régionalisée. Redondance avec capacité production. À discuter.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Niveau nappes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suivi piézométrique des eaux souterraines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m NGF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suivre l'évolution du niveau des nappes phréatiques pour détecter les tensions quantitatives.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agrégation des données piézométriques par bassin versant ou maille.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Niveau bas = forte criticité quantitative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nombre de prélèvement AODPE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nombre de prélèvements d’eau autorisés.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comparer les captages selon le nombre de prélèvements afin d’évaluer la pression d’usage.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comptage des prélèvements associés à chaque captage.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C'est la présence qui est positive, l'absence d'autorisation AODPE est négative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indicateur pression captage. Donnée dynamique DAVAR. Intégrable en analyse.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Volume des prélèvements AODPE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Volume total d’eau prélevé.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comparer les captages selon les volumes prélevés afin d’évaluer l’intensité de la pression quantitative.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Somme des volumes autorisés associés à chaque captage.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Volume élevé = pression forte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Complément du nombre. Permet comparaison avec ressource disponible.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pressions Qualitatives</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualité eau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualité de l’eau (bonne à mauvaise).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Classe (A1 / A2 / A3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comparer les captages selon leur qualité afin d’identifier ceux nécessitant des actions de gestion ou de protection.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Attribution d’une classe par captage selon les données disponibles.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Classe dégradée = criticité élevée</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Donnée complexe et peu disponible. Difficilement intégrable dans modèle actuel.</t>
   </si>
   <si>
     <t xml:space="preserve">id_ressource</t>
@@ -1445,6 +1469,33 @@
   </si>
   <si>
     <t xml:space="preserve">Dépendance à la qualité et à l'actualisation de la BD TOPO ; l'exhaustivité varie selon les communes, pouvant introduire des biais dans les comparaisons territoriales.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parcelle cadastrale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://cadastre.gouv.nc/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les contours (limites) des parcelles ne sont pas diffusés librement. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PUD des communes de la province SUD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.province-sud.nc/open/metadonnees/8a8186dd9816d2da019c8d998c9d00b2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le Plan d’Urbanisme Directeur (PUD) est un document d’urbanisme, qui établit un projet global d’urbanisme et d’aménagement et fixe les règles générales d’utilisation du sol à l’échelle de la commune.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.province-sud.nc/cartosudweb/app/carte/geolocalisation-des-autorisations-d'urbanisme#page-content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Certaines communes n’ont pas de PUD intégrés (ex.YATE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PUD des communes de la province Nord</t>
   </si>
   <si>
     <t xml:space="preserve">table</t>
@@ -1832,6 +1883,21 @@
     <t xml:space="preserve">Base de données ATYA (nom à vérifier)</t>
   </si>
   <si>
+    <t xml:space="preserve">statut foncier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parcelles cadastrales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PUD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PUD PSUD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PUD PNORD</t>
+  </si>
+  <si>
     <t xml:space="preserve">id_theme</t>
   </si>
   <si>
@@ -1862,7 +1928,7 @@
     <t xml:space="preserve">Impacts des activités humaines</t>
   </si>
   <si>
-    <t xml:space="preserve">Caractérise les pressions exercées par les activités humaines, l’occupation du sol et les infrastructures sur les ressources en eau.</t>
+    <t xml:space="preserve">Caractérise les menaces exercées par les activités humaines, l’occupation du sol et les infrastructures sur les ressources en eau.</t>
   </si>
   <si>
     <t xml:space="preserve">Sensibilité naturelle du milieu</t>
@@ -2168,7 +2234,13 @@
     <t xml:space="preserve">Sous-groupe d'objectif</t>
   </si>
   <si>
+    <t xml:space="preserve">id_groupe_V2</t>
+  </si>
+  <si>
     <t xml:space="preserve">Vulnérabilité technique et contexte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statut foncier</t>
   </si>
   <si>
     <t xml:space="preserve">Infrastructures et risques de dégradation des eaux</t>
@@ -2232,7 +2304,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -2255,6 +2327,13 @@
       <family val="0"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -2268,28 +2347,10 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <sz val="12"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <i val="true"/>
@@ -2341,7 +2402,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2359,6 +2420,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2366,7 +2431,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2374,15 +2439,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2398,24 +2455,20 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2562,7 +2615,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:X39"/>
+  <dimension ref="A1:X1048576"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="15.18"/>
@@ -3226,23 +3279,20 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="n">
-        <v>9</v>
-      </c>
       <c r="B10" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="F10" s="4" t="s">
         <v>103</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>105</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>28</v>
@@ -3250,11 +3300,11 @@
       <c r="H10" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I10" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>107</v>
+      <c r="I10" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>105</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>91</v>
@@ -3266,7 +3316,7 @@
         <v>33</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O10" s="1" t="s">
         <v>64</v>
@@ -3275,7 +3325,7 @@
         <v>99</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="R10" s="1" t="s">
         <v>67</v>
@@ -3287,258 +3337,250 @@
         <v>40</v>
       </c>
       <c r="U10" s="1" t="s">
-        <v>41</v>
+        <v>107</v>
       </c>
       <c r="V10" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="W10" s="1" t="s">
+      <c r="W10" s="1"/>
+    </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F11" s="6" t="s">
         <v>109</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>111</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I11" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="I11" s="5"/>
+      <c r="J11" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="K11" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="L11" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="K11" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="M11" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q11" s="1" t="s">
-        <v>115</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="P11" s="2"/>
       <c r="R11" s="1" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="S11" s="1" t="s">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="T11" s="1" t="s">
         <v>40</v>
       </c>
       <c r="U11" s="1" t="s">
-        <v>41</v>
+        <v>107</v>
       </c>
       <c r="V11" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="W11" s="1" t="s">
-        <v>116</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="W11" s="1"/>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" s="1" t="s">
+      <c r="F12" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>119</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="J12" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="K12" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q12" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="J12" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O12" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="P12" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q12" s="1" t="s">
-        <v>125</v>
-      </c>
       <c r="R12" s="1" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="T12" s="1" t="s">
         <v>40</v>
       </c>
       <c r="U12" s="1" t="s">
-        <v>126</v>
+        <v>41</v>
       </c>
       <c r="V12" s="1" t="s">
-        <v>127</v>
+        <v>69</v>
+      </c>
+      <c r="W12" s="1" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>25</v>
+        <v>116</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>120</v>
+        <v>28</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>130</v>
+        <v>125</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>126</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>124</v>
+        <v>32</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>34</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="P13" s="1" t="s">
-        <v>36</v>
+        <v>64</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>99</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="T13" s="1" t="s">
         <v>40</v>
       </c>
       <c r="U13" s="1" t="s">
-        <v>126</v>
+        <v>41</v>
       </c>
       <c r="V13" s="1" t="s">
-        <v>127</v>
+        <v>78</v>
+      </c>
+      <c r="W13" s="1" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E14" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>133</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="J14" s="1" t="s">
         <v>134</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>34</v>
@@ -3565,21 +3607,21 @@
         <v>40</v>
       </c>
       <c r="U14" s="1" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="V14" s="1" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B15" s="1" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>25</v>
@@ -3594,19 +3636,19 @@
         <v>28</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J15" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="J15" s="3" t="s">
         <v>138</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>139</v>
+        <v>112</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>34</v>
@@ -3621,60 +3663,60 @@
         <v>36</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="R15" s="1" t="s">
         <v>38</v>
       </c>
       <c r="S15" s="1" t="s">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="T15" s="1" t="s">
         <v>40</v>
       </c>
       <c r="U15" s="1" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="V15" s="1" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B16" s="1" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E16" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>141</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>142</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="M16" s="1" t="s">
         <v>34</v>
@@ -3686,10 +3728,10 @@
         <v>35</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>144</v>
+        <v>36</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="R16" s="1" t="s">
         <v>38</v>
@@ -3701,51 +3743,51 @@
         <v>40</v>
       </c>
       <c r="U16" s="1" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="V16" s="1" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B17" s="1" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>121</v>
+        <v>82</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>123</v>
+        <v>147</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N17" s="1" t="s">
         <v>33</v>
@@ -3754,66 +3796,66 @@
         <v>35</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>149</v>
+        <v>36</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="R17" s="1" t="s">
         <v>38</v>
       </c>
       <c r="S17" s="1" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="T17" s="1" t="s">
-        <v>151</v>
+        <v>40</v>
       </c>
       <c r="U17" s="1" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="V17" s="1" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B18" s="1" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N18" s="1" t="s">
         <v>33</v>
@@ -3822,10 +3864,10 @@
         <v>35</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="R18" s="1" t="s">
         <v>38</v>
@@ -3834,33 +3876,33 @@
         <v>39</v>
       </c>
       <c r="T18" s="1" t="s">
-        <v>151</v>
+        <v>40</v>
       </c>
       <c r="U18" s="1" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="V18" s="1" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B19" s="1" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>156</v>
+        <v>130</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>157</v>
+        <v>25</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>28</v>
@@ -3869,16 +3911,16 @@
         <v>28</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>33</v>
@@ -3890,10 +3932,10 @@
         <v>35</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="R19" s="1" t="s">
         <v>38</v>
@@ -3902,33 +3944,33 @@
         <v>39</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="U19" s="1" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="V19" s="1" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B20" s="1" t="n">
-        <v>200</v>
+        <v>106</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>163</v>
+        <v>130</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>157</v>
+        <v>25</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>28</v>
@@ -3937,16 +3979,16 @@
         <v>28</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>167</v>
+        <v>112</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>33</v>
@@ -3958,10 +4000,10 @@
         <v>35</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="R20" s="1" t="s">
         <v>38</v>
@@ -3970,36 +4012,33 @@
         <v>39</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>40</v>
+        <v>159</v>
       </c>
       <c r="U20" s="1" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="V20" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="W20" s="1" t="s">
-        <v>169</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B21" s="1" t="n">
-        <v>201</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>163</v>
+        <v>107</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>164</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>28</v>
@@ -4008,16 +4047,16 @@
         <v>28</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>33</v>
@@ -4029,10 +4068,10 @@
         <v>35</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="R21" s="1" t="s">
         <v>38</v>
@@ -4041,36 +4080,33 @@
         <v>39</v>
       </c>
       <c r="T21" s="1" t="s">
-        <v>40</v>
+        <v>159</v>
       </c>
       <c r="U21" s="1" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="V21" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="W21" s="1" t="s">
-        <v>174</v>
+        <v>114</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B22" s="1" t="n">
-        <v>202</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>163</v>
+        <v>200</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>171</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>28</v>
@@ -4079,16 +4115,16 @@
         <v>28</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>123</v>
+        <v>175</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>33</v>
@@ -4100,10 +4136,10 @@
         <v>35</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="R22" s="1" t="s">
         <v>38</v>
@@ -4115,33 +4151,33 @@
         <v>40</v>
       </c>
       <c r="U22" s="1" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="V22" s="1" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="W22" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B23" s="1" t="n">
-        <v>203</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>163</v>
+        <v>201</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>171</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="E23" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>179</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>180</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>28</v>
@@ -4150,16 +4186,16 @@
         <v>28</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="M23" s="1" t="s">
         <v>33</v>
@@ -4171,10 +4207,10 @@
         <v>35</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="Q23" s="1" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="R23" s="1" t="s">
         <v>38</v>
@@ -4186,10 +4222,10 @@
         <v>40</v>
       </c>
       <c r="U23" s="1" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="V23" s="1" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="W23" s="1" t="s">
         <v>182</v>
@@ -4197,16 +4233,16 @@
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B24" s="1" t="n">
-        <v>204</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>163</v>
+        <v>202</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>171</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>183</v>
@@ -4218,72 +4254,72 @@
         <v>28</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>120</v>
+        <v>28</v>
       </c>
       <c r="I24" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="J24" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="J24" s="1" t="s">
-        <v>186</v>
-      </c>
       <c r="K24" s="1" t="s">
-        <v>187</v>
+        <v>112</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>188</v>
+        <v>113</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O24" s="1" t="s">
         <v>35</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="Q24" s="1" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="R24" s="1" t="s">
         <v>38</v>
       </c>
       <c r="S24" s="1" t="s">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="T24" s="1" t="s">
         <v>40</v>
       </c>
       <c r="U24" s="1" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="V24" s="1" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="W24" s="1" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B25" s="1" t="n">
-        <v>300</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>156</v>
+        <v>203</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>171</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>28</v>
@@ -4292,16 +4328,16 @@
         <v>28</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>82</v>
+        <v>133</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>194</v>
+        <v>112</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="M25" s="1" t="s">
         <v>33</v>
@@ -4313,119 +4349,119 @@
         <v>35</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="Q25" s="1" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="R25" s="1" t="s">
         <v>38</v>
       </c>
       <c r="S25" s="1" t="s">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="T25" s="1" t="s">
         <v>40</v>
       </c>
       <c r="U25" s="1" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="V25" s="1" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="W25" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B26" s="1" t="n">
-        <v>301</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>156</v>
+        <v>204</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>171</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>121</v>
+        <v>193</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>124</v>
+        <v>196</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O26" s="1" t="s">
         <v>35</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="Q26" s="1" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="R26" s="1" t="s">
         <v>38</v>
       </c>
       <c r="S26" s="1" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="T26" s="1" t="s">
         <v>40</v>
       </c>
       <c r="U26" s="1" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="V26" s="1" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="W26" s="1" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B27" s="1" t="n">
-        <v>302</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>156</v>
+        <v>300</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>164</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>28</v>
@@ -4437,13 +4473,13 @@
         <v>82</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="M27" s="1" t="s">
         <v>33</v>
@@ -4455,10 +4491,10 @@
         <v>35</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="Q27" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="R27" s="1" t="s">
         <v>38</v>
@@ -4470,51 +4506,51 @@
         <v>40</v>
       </c>
       <c r="U27" s="1" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="V27" s="1" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="W27" s="1" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B28" s="1" t="n">
-        <v>304</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>156</v>
+        <v>301</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>164</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>82</v>
+        <v>133</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="M28" s="1" t="s">
         <v>33</v>
@@ -4526,48 +4562,48 @@
         <v>35</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="R28" s="1" t="s">
         <v>38</v>
       </c>
       <c r="S28" s="1" t="s">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="T28" s="1" t="s">
         <v>40</v>
       </c>
       <c r="U28" s="1" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="V28" s="1" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="W28" s="1" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B29" s="1" t="n">
-        <v>305</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>156</v>
+        <v>302</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>164</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>28</v>
@@ -4579,13 +4615,13 @@
         <v>82</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>33</v>
@@ -4597,10 +4633,10 @@
         <v>35</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="R29" s="1" t="s">
         <v>38</v>
@@ -4612,30 +4648,33 @@
         <v>40</v>
       </c>
       <c r="U29" s="1" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="V29" s="1" t="s">
-        <v>127</v>
+        <v>114</v>
+      </c>
+      <c r="W29" s="1" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B30" s="1" t="n">
-        <v>306</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>156</v>
+        <v>304</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>164</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>28</v>
@@ -4644,16 +4683,16 @@
         <v>28</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="M30" s="1" t="s">
         <v>33</v>
@@ -4665,54 +4704,66 @@
         <v>35</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="Q30" s="1" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="R30" s="1" t="s">
         <v>38</v>
       </c>
       <c r="S30" s="1" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="T30" s="1" t="s">
         <v>40</v>
       </c>
       <c r="U30" s="1" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="V30" s="1" t="s">
-        <v>127</v>
+        <v>114</v>
+      </c>
+      <c r="W30" s="1" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="n">
+        <v>29</v>
+      </c>
       <c r="B31" s="1" t="n">
-        <v>400</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>102</v>
+        <v>305</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>164</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>120</v>
+        <v>28</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>28</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>227</v>
+        <v>82</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>226</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="M31" s="1" t="s">
         <v>33</v>
@@ -4721,54 +4772,48 @@
         <v>33</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>228</v>
+        <v>35</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="Q31" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="R31" s="1" t="s">
         <v>38</v>
       </c>
       <c r="S31" s="1" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="T31" s="1" t="s">
         <v>40</v>
       </c>
       <c r="U31" s="1" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="V31" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="W31" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="X31" s="1" t="s">
-        <v>231</v>
+        <v>114</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B32" s="1" t="n">
-        <v>401</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>102</v>
+        <v>306</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>164</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>28</v>
@@ -4777,16 +4822,16 @@
         <v>28</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>121</v>
+        <v>46</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="M32" s="1" t="s">
         <v>33</v>
@@ -4798,10 +4843,10 @@
         <v>35</v>
       </c>
       <c r="P32" s="1" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="Q32" s="1" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="R32" s="1" t="s">
         <v>38</v>
@@ -4810,36 +4855,33 @@
         <v>39</v>
       </c>
       <c r="T32" s="1" t="s">
-        <v>151</v>
+        <v>40</v>
       </c>
       <c r="U32" s="1" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="V32" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="W32" s="1" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="13.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B33" s="1" t="n">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>226</v>
+        <v>116</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>234</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>28</v>
@@ -4847,17 +4889,17 @@
       <c r="H33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I33" s="2" t="s">
-        <v>239</v>
+      <c r="I33" s="1" t="s">
+        <v>133</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="M33" s="1" t="s">
         <v>33</v>
@@ -4866,52 +4908,51 @@
         <v>33</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="P33" s="2" t="s">
-        <v>243</v>
+        <v>35</v>
+      </c>
+      <c r="P33" s="1" t="s">
+        <v>169</v>
       </c>
       <c r="Q33" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="R33" s="1" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="S33" s="1" t="s">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="T33" s="1" t="s">
-        <v>40</v>
+        <v>159</v>
       </c>
       <c r="U33" s="1" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="V33" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="W33" s="1"/>
-      <c r="X33" s="1" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>114</v>
+      </c>
+      <c r="W33" s="1" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="13.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B34" s="1" t="n">
-        <v>500</v>
+        <v>402</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>246</v>
+        <v>115</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>248</v>
+        <v>116</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>240</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>28</v>
@@ -4919,32 +4960,32 @@
       <c r="H34" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I34" s="1" t="s">
-        <v>249</v>
+      <c r="I34" s="2" t="s">
+        <v>241</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>188</v>
+        <v>113</v>
       </c>
       <c r="M34" s="1" t="s">
         <v>33</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q34" s="1" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="R34" s="1" t="s">
         <v>67</v>
@@ -4953,140 +4994,141 @@
         <v>68</v>
       </c>
       <c r="T34" s="1" t="s">
-        <v>151</v>
+        <v>40</v>
       </c>
       <c r="U34" s="1" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="V34" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="W34" s="1" t="s">
-        <v>253</v>
+        <v>246</v>
+      </c>
+      <c r="W34" s="1"/>
+      <c r="X34" s="1" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B35" s="1" t="n">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>120</v>
+        <v>28</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>124</v>
+        <v>196</v>
       </c>
       <c r="M35" s="1" t="s">
         <v>33</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="P35" s="1" t="s">
-        <v>149</v>
+        <v>244</v>
+      </c>
+      <c r="P35" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="Q35" s="1" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="R35" s="1" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="S35" s="1" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="T35" s="1" t="s">
-        <v>40</v>
+        <v>159</v>
       </c>
       <c r="U35" s="1" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="V35" s="1" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="W35" s="1" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B36" s="1" t="n">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="M36" s="1" t="s">
         <v>33</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O36" s="1" t="s">
         <v>35</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="Q36" s="1" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="R36" s="1" t="s">
         <v>38</v>
@@ -5098,30 +5140,33 @@
         <v>40</v>
       </c>
       <c r="U36" s="1" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="V36" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>114</v>
+      </c>
+      <c r="W36" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B37" s="1" t="n">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>28</v>
@@ -5130,16 +5175,16 @@
         <v>28</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>82</v>
+        <v>265</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>32</v>
+        <v>113</v>
       </c>
       <c r="M37" s="1" t="s">
         <v>33</v>
@@ -5150,64 +5195,61 @@
       <c r="O37" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P37" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q37" s="3" t="s">
-        <v>271</v>
+      <c r="P37" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q37" s="1" t="s">
+        <v>268</v>
       </c>
       <c r="R37" s="1" t="s">
         <v>38</v>
       </c>
       <c r="S37" s="1" t="s">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="T37" s="1" t="s">
         <v>40</v>
       </c>
       <c r="U37" s="1" t="s">
-        <v>41</v>
+        <v>107</v>
       </c>
       <c r="V37" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="W37" s="1" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B38" s="1" t="n">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>273</v>
+        <v>165</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>269</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>120</v>
+        <v>28</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="L38" s="1" t="s">
         <v>32</v>
@@ -5221,17 +5263,17 @@
       <c r="O38" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P38" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q38" s="1" t="s">
-        <v>277</v>
+      <c r="P38" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q38" s="3" t="s">
+        <v>273</v>
       </c>
       <c r="R38" s="1" t="s">
         <v>38</v>
       </c>
       <c r="S38" s="1" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="T38" s="1" t="s">
         <v>40</v>
@@ -5243,42 +5285,42 @@
         <v>42</v>
       </c>
       <c r="W38" s="1" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B39" s="1" t="n">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>279</v>
+        <v>248</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>280</v>
+        <v>165</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>275</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>282</v>
+        <v>54</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="L39" s="1" t="s">
         <v>32</v>
@@ -5290,19 +5332,19 @@
         <v>34</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="P39" s="2" t="s">
-        <v>243</v>
+        <v>35</v>
+      </c>
+      <c r="P39" s="1" t="s">
+        <v>169</v>
       </c>
       <c r="Q39" s="1" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="R39" s="1" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="S39" s="1" t="s">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="T39" s="1" t="s">
         <v>40</v>
@@ -5311,12 +5353,149 @@
         <v>41</v>
       </c>
       <c r="V39" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="W39" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="1" t="n">
+        <v>505</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M40" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N40" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="O40" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P40" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="Q40" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="R40" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="S40" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="T40" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="U40" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="V40" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="W39" s="1" t="s">
-        <v>286</v>
-      </c>
-    </row>
+      <c r="W40" s="1" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="1" t="n">
+        <v>400</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M41" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N41" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O41" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="P41" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q41" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="R41" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="S41" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="T41" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="U41" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="V41" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="W41" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="X41" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -5333,7 +5512,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="88.58"/>
@@ -5348,40 +5527,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5389,34 +5568,34 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5424,31 +5603,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5456,34 +5635,34 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5491,34 +5670,34 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5526,34 +5705,34 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5561,37 +5740,37 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>332</v>
+        <v>313</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>340</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5599,28 +5778,28 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5628,34 +5807,34 @@
         <v>100</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>342</v>
+        <v>314</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>350</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5663,34 +5842,34 @@
         <v>101</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>346</v>
+        <v>353</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>354</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5698,34 +5877,34 @@
         <v>102</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5733,34 +5912,34 @@
         <v>103</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5768,34 +5947,34 @@
         <v>104</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5803,34 +5982,34 @@
         <v>105</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5838,31 +6017,31 @@
         <v>106</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5870,34 +6049,34 @@
         <v>107</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5905,34 +6084,34 @@
         <v>108</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5940,34 +6119,34 @@
         <v>109</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5975,34 +6154,34 @@
         <v>110</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6010,34 +6189,34 @@
         <v>111</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6045,34 +6224,34 @@
         <v>112</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6080,34 +6259,34 @@
         <v>113</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="E22" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="F22" s="1" t="s">
-        <v>303</v>
-      </c>
       <c r="G22" s="1" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6115,34 +6294,34 @@
         <v>114</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6150,37 +6329,37 @@
         <v>115</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="H24" s="8" t="s">
-        <v>414</v>
+        <v>355</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>422</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="J24" s="4" t="s">
-        <v>415</v>
+        <v>314</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>423</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6188,34 +6367,34 @@
         <v>116</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="J25" s="4" t="s">
-        <v>415</v>
+        <v>314</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>423</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6223,34 +6402,34 @@
         <v>117</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="J26" s="4" t="s">
-        <v>415</v>
+        <v>314</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>423</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6258,34 +6437,34 @@
         <v>118</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6293,34 +6472,34 @@
         <v>119</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6328,34 +6507,34 @@
         <v>120</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6363,34 +6542,34 @@
         <v>129</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6398,34 +6577,34 @@
         <v>121</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6433,28 +6612,28 @@
         <v>122</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="29.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6462,37 +6641,37 @@
         <v>123</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>444</v>
+        <v>309</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>452</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="J33" s="4" t="s">
-        <v>445</v>
-      </c>
-      <c r="K33" s="4" t="s">
-        <v>446</v>
+        <v>314</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="K33" s="5" t="s">
+        <v>454</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6500,34 +6679,34 @@
         <v>124</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6535,34 +6714,34 @@
         <v>125</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6570,34 +6749,34 @@
         <v>126</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6605,34 +6784,34 @@
         <v>127</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6640,35 +6819,138 @@
         <v>128</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>470</v>
-      </c>
+        <v>478</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="1" t="n">
+        <v>130</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="1" t="n">
+        <v>131</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>483</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="J40" s="5" t="s">
+        <v>484</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="1" t="n">
+        <v>132</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="J41" s="5" t="s">
+        <v>484</v>
+      </c>
+      <c r="K41" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L38"/>
@@ -6676,6 +6958,7 @@
     <hyperlink ref="J7" r:id="rId1" display="La couche BBR (bilan besoin / ressources) est calculée à partir des débits caractéristiques d’étiage médian (DCE2) auquel sont soustraits l'ensemble des prélèvements d’eau autorisés."/>
     <hyperlink ref="E10" r:id="rId2" display="https://www.province-sud.nc/open/metadonnees/8a8186dd9816d2da019c8d998c7700a0"/>
     <hyperlink ref="E33" r:id="rId3" display="https://georep-dtsi-sgt.opendata.arcgis.com/documents/d7ab36bb69954aea882a63993428357a/about"/>
+    <hyperlink ref="E40" r:id="rId4" display="https://www.province-sud.nc/open/metadonnees/8a8186dd9816d2da019c8d998c9d00b2"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -6684,7 +6967,7 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
-  <drawing r:id="rId4"/>
+  <drawing r:id="rId5"/>
 </worksheet>
 </file>
 
@@ -6706,496 +6989,496 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>471</v>
+        <v>488</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>473</v>
+        <v>489</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>490</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>474</v>
+        <v>491</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>475</v>
+        <v>492</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>477</v>
+        <v>493</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>494</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>478</v>
+        <v>495</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>479</v>
+        <v>496</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="11" t="s">
-        <v>480</v>
+      <c r="C2" s="10" t="s">
+        <v>497</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>481</v>
+        <v>498</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>482</v>
+        <v>499</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="G2" s="10"/>
+        <v>110</v>
+      </c>
+      <c r="G2" s="9"/>
       <c r="H2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>479</v>
+        <v>496</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="12" t="s">
-        <v>483</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>484</v>
+      <c r="C3" s="11" t="s">
+        <v>500</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>501</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>485</v>
+        <v>502</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>487</v>
+        <v>504</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>479</v>
+        <v>496</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="12" t="s">
-        <v>488</v>
+      <c r="C4" s="11" t="s">
+        <v>505</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>489</v>
+        <v>506</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>485</v>
+        <v>502</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>490</v>
+        <v>507</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>479</v>
+        <v>496</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>491</v>
+        <v>508</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>492</v>
+        <v>509</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>485</v>
+        <v>502</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>493</v>
+        <v>510</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>479</v>
+        <v>496</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>494</v>
+        <v>511</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>495</v>
+        <v>512</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>485</v>
+        <v>502</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>496</v>
+        <v>513</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>479</v>
+        <v>496</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>497</v>
+        <v>514</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>498</v>
+        <v>515</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>482</v>
+        <v>499</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>499</v>
+        <v>516</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>479</v>
+        <v>496</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>500</v>
+        <v>517</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>501</v>
+        <v>518</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>502</v>
+        <v>519</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>503</v>
+        <v>520</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>504</v>
+        <v>521</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>479</v>
+        <v>496</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>505</v>
+        <v>522</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>506</v>
+        <v>523</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>479</v>
+        <v>496</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>508</v>
+        <v>525</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>509</v>
+        <v>526</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>502</v>
+        <v>519</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>503</v>
+        <v>520</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>479</v>
+        <v>496</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>510</v>
+        <v>527</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>511</v>
+        <v>528</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>512</v>
+        <v>529</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>503</v>
+        <v>520</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>479</v>
+        <v>496</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>514</v>
+        <v>531</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>515</v>
+        <v>532</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>479</v>
+        <v>496</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>516</v>
+        <v>533</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>517</v>
+        <v>534</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>518</v>
+        <v>535</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>479</v>
+        <v>496</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>519</v>
+        <v>536</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>521</v>
+        <v>538</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>479</v>
+        <v>496</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>522</v>
+        <v>539</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>523</v>
+        <v>540</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>518</v>
+        <v>535</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>503</v>
+        <v>520</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>479</v>
+        <v>496</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>524</v>
+        <v>541</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>525</v>
+        <v>542</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>518</v>
+        <v>535</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>503</v>
+        <v>520</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>526</v>
+        <v>543</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>479</v>
+        <v>496</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>527</v>
+        <v>544</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>528</v>
+        <v>545</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>518</v>
+        <v>535</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>503</v>
+        <v>520</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>479</v>
+        <v>496</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>529</v>
+        <v>546</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>530</v>
+        <v>547</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>521</v>
+        <v>538</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>531</v>
+        <v>548</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>532</v>
+        <v>549</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>479</v>
+        <v>496</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>533</v>
+        <v>550</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>534</v>
+        <v>551</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>521</v>
+        <v>538</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>531</v>
+        <v>548</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>535</v>
+        <v>552</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>479</v>
+        <v>496</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>536</v>
+        <v>553</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>537</v>
+        <v>554</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>521</v>
+        <v>538</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>531</v>
+        <v>548</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>538</v>
+        <v>555</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>479</v>
+        <v>496</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>20</v>
@@ -7204,375 +7487,375 @@
         <v>20</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>539</v>
+        <v>556</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>521</v>
+        <v>538</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>531</v>
+        <v>548</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>540</v>
+        <v>557</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>479</v>
-      </c>
-      <c r="B22" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>541</v>
+        <v>558</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>542</v>
+        <v>559</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>543</v>
+        <v>560</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>531</v>
+        <v>548</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>544</v>
+        <v>561</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>479</v>
+        <v>496</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>545</v>
+        <v>562</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>546</v>
+        <v>563</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>502</v>
+        <v>519</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="G23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>479</v>
+        <v>496</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>547</v>
+        <v>564</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>546</v>
+        <v>563</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>502</v>
+        <v>519</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="G24" s="3"/>
     </row>
     <row r="25" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>548</v>
+        <v>565</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>549</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>550</v>
+        <v>295</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>566</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>567</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>485</v>
+        <v>502</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>551</v>
+        <v>568</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>548</v>
+        <v>565</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="C26" s="13" t="s">
-        <v>552</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>552</v>
+        <v>296</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>569</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>569</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>485</v>
+        <v>502</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>548</v>
+        <v>565</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>497</v>
+        <v>514</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>553</v>
+        <v>570</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>554</v>
+        <v>571</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>503</v>
+        <v>520</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>548</v>
+        <v>565</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>555</v>
+        <v>572</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>556</v>
+        <v>573</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>482</v>
+        <v>499</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>548</v>
+        <v>565</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>557</v>
+        <v>574</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>558</v>
+        <v>575</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>482</v>
+        <v>499</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>548</v>
+        <v>565</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>559</v>
+        <v>576</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>560</v>
+        <v>577</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>482</v>
+        <v>499</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>548</v>
+        <v>565</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>561</v>
+        <v>578</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>562</v>
+        <v>579</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>502</v>
+        <v>519</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>503</v>
-      </c>
-      <c r="H31" s="14" t="s">
-        <v>563</v>
+        <v>520</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>580</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>548</v>
+        <v>565</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>564</v>
+        <v>581</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>565</v>
+        <v>582</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>502</v>
+        <v>519</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>503</v>
+        <v>520</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>566</v>
+        <v>583</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>548</v>
+        <v>565</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>567</v>
+        <v>584</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>568</v>
+        <v>585</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>554</v>
+        <v>571</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="H33" s="15" t="s">
-        <v>569</v>
+        <v>503</v>
+      </c>
+      <c r="H33" s="14" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>548</v>
+        <v>565</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>570</v>
+        <v>587</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>571</v>
+        <v>588</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>521</v>
+        <v>538</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>572</v>
+        <v>589</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>548</v>
+        <v>565</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>573</v>
+        <v>590</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>574</v>
+        <v>591</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>502</v>
+        <v>519</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>503</v>
+        <v>520</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="8"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="16"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
     </row>
     <row r="37" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="8"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="16"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
     </row>
     <row r="38" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="8"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="16"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
     </row>
@@ -7603,7 +7886,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -7612,16 +7895,16 @@
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>576</v>
+        <v>593</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7638,7 +7921,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>33</v>
@@ -7658,7 +7941,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>33</v>
@@ -7678,7 +7961,7 @@
         <v>2</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>33</v>
@@ -7698,7 +7981,7 @@
         <v>2</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>33</v>
@@ -7718,7 +8001,7 @@
         <v>2</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>33</v>
@@ -7738,7 +8021,7 @@
         <v>2</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>33</v>
@@ -7758,7 +8041,7 @@
         <v>3</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>33</v>
@@ -7778,7 +8061,7 @@
         <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>33</v>
@@ -7792,13 +8075,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>5</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>33</v>
@@ -7812,13 +8095,13 @@
         <v>10</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>5</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>33</v>
@@ -7832,13 +8115,13 @@
         <v>100</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>100</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>33</v>
@@ -7852,13 +8135,13 @@
         <v>101</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>101</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>33</v>
@@ -7872,13 +8155,13 @@
         <v>101</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>102</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>33</v>
@@ -7892,13 +8175,13 @@
         <v>101</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>103</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>33</v>
@@ -7912,13 +8195,13 @@
         <v>102</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>104</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>33</v>
@@ -7932,13 +8215,13 @@
         <v>103</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>105</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>33</v>
@@ -7952,13 +8235,13 @@
         <v>104</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>577</v>
+        <v>594</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>106</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>33</v>
@@ -7972,19 +8255,19 @@
         <v>105</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>107</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>33</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>578</v>
+        <v>595</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7995,19 +8278,19 @@
         <v>105</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="D20" s="1" t="n">
         <v>108</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>33</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>578</v>
+        <v>595</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8018,13 +8301,13 @@
         <v>106</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="D21" s="1" t="n">
         <v>109</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>33</v>
@@ -8038,19 +8321,19 @@
         <v>107</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="D22" s="1" t="n">
         <v>107</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>33</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>579</v>
+        <v>596</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8061,13 +8344,13 @@
         <v>200</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="D23" s="1" t="n">
         <v>110</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>33</v>
@@ -8081,13 +8364,13 @@
         <v>201</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="D24" s="1" t="n">
         <v>111</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>33</v>
@@ -8101,19 +8384,19 @@
         <v>202</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="D25" s="1" t="n">
         <v>107</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>33</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>580</v>
+        <v>597</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8124,13 +8407,13 @@
         <v>202</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="D26" s="1" t="n">
         <v>108</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>33</v>
@@ -8144,13 +8427,13 @@
         <v>203</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D27" s="1" t="n">
         <v>112</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>33</v>
@@ -8164,13 +8447,13 @@
         <v>204</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="D28" s="1" t="n">
         <v>113</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>33</v>
@@ -8184,16 +8467,16 @@
         <v>300</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="D29" s="1" t="n">
         <v>114</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8204,13 +8487,13 @@
         <v>300</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="D30" s="1" t="n">
         <v>115</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>33</v>
@@ -8224,13 +8507,13 @@
         <v>300</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="D31" s="1" t="n">
         <v>116</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>33</v>
@@ -8244,13 +8527,13 @@
         <v>300</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="D32" s="1" t="n">
         <v>117</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>33</v>
@@ -8264,13 +8547,13 @@
         <v>301</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="D33" s="1" t="n">
         <v>107</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>33</v>
@@ -8284,13 +8567,13 @@
         <v>301</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="D34" s="1" t="n">
         <v>118</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>33</v>
@@ -8304,13 +8587,13 @@
         <v>301</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="D35" s="1" t="n">
         <v>119</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>34</v>
@@ -8324,13 +8607,13 @@
         <v>302</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="D36" s="1" t="n">
         <v>120</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>33</v>
@@ -8344,13 +8627,13 @@
         <v>302</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="D37" s="1" t="n">
         <v>129</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>33</v>
@@ -8364,13 +8647,13 @@
         <v>304</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="D38" s="1" t="n">
         <v>128</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>33</v>
@@ -8384,13 +8667,13 @@
         <v>305</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="D39" s="1" t="n">
         <v>121</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>33</v>
@@ -8404,13 +8687,13 @@
         <v>305</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="D40" s="1" t="n">
         <v>122</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>33</v>
@@ -8424,19 +8707,19 @@
         <v>306</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="D41" s="1" t="n">
         <v>121</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="n">
         <v>41</v>
       </c>
@@ -8444,13 +8727,13 @@
         <v>402</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D42" s="1" t="n">
         <v>123</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>33</v>
@@ -8464,13 +8747,13 @@
         <v>401</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D43" s="1" t="n">
         <v>124</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>33</v>
@@ -8484,19 +8767,19 @@
         <v>401</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D44" s="1" t="n">
         <v>125</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>34</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>581</v>
+        <v>598</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8507,13 +8790,13 @@
         <v>500</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D45" s="1" t="n">
         <v>6</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>582</v>
+        <v>599</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>33</v>
@@ -8527,13 +8810,13 @@
         <v>501</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D46" s="1" t="n">
         <v>126</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>33</v>
@@ -8547,13 +8830,13 @@
         <v>502</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D47" s="1" t="n">
         <v>127</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>33</v>
@@ -8567,13 +8850,13 @@
         <v>503</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>583</v>
+        <v>600</v>
       </c>
       <c r="D48" s="1" t="n">
         <v>3</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>33</v>
@@ -8587,13 +8870,13 @@
         <v>504</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>584</v>
+        <v>601</v>
       </c>
       <c r="D49" s="1" t="n">
         <v>3</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>33</v>
@@ -8607,15 +8890,75 @@
         <v>505</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D50" s="1" t="n">
         <v>7</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>585</v>
+        <v>602</v>
       </c>
       <c r="F50" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="D51" s="1" t="n">
+        <v>130</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="1" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="D52" s="1" t="n">
+        <v>131</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="1" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="D53" s="1" t="n">
+        <v>131</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="F53" s="1" t="s">
         <v>33</v>
       </c>
     </row>
@@ -8636,7 +8979,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="1" width="28.29"/>
@@ -8644,57 +8987,57 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="46.25"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="32.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>586</v>
+        <v>608</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>587</v>
+        <v>609</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>491</v>
+        <v>508</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="87.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="17" t="s">
-        <v>589</v>
+      <c r="C2" s="15" t="s">
+        <v>611</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>590</v>
+      <c r="E2" s="3" t="s">
+        <v>612</v>
       </c>
       <c r="F2" s="3"/>
       <c r="H2" s="1"/>
     </row>
-    <row r="3" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>591</v>
+        <v>130</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>613</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>592</v>
+      <c r="E3" s="3" t="s">
+        <v>614</v>
       </c>
       <c r="F3" s="3"/>
       <c r="H3" s="1"/>
@@ -8703,17 +9046,17 @@
       <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>593</v>
+      <c r="B4" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>615</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>594</v>
+        <v>165</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>616</v>
       </c>
       <c r="F4" s="3"/>
       <c r="H4" s="1"/>
@@ -8722,17 +9065,17 @@
       <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>595</v>
+      <c r="B5" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>617</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>596</v>
+        <v>165</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>618</v>
       </c>
       <c r="H5" s="1"/>
     </row>
@@ -8741,16 +9084,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>597</v>
+        <v>115</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>619</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>598</v>
+        <v>116</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>620</v>
       </c>
       <c r="H6" s="1"/>
     </row>
@@ -8759,16 +9102,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>599</v>
+        <v>248</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>621</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>600</v>
+        <v>165</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>622</v>
       </c>
       <c r="H7" s="1"/>
     </row>
@@ -8777,18 +9120,25 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>601</v>
+        <v>281</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>623</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>602</v>
+        <v>165</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>624</v>
       </c>
       <c r="H8" s="1"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="16"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -8821,28 +9171,28 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>603</v>
+        <v>625</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>604</v>
+        <v>626</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>586</v>
+        <v>608</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>605</v>
+        <v>525</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>627</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>606</v>
+        <v>628</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>607</v>
+        <v>629</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8850,7 +9200,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>608</v>
+        <v>630</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>1</v>
@@ -8858,51 +9208,51 @@
       <c r="D2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>609</v>
-      </c>
-      <c r="F2" s="16" t="s">
-        <v>610</v>
+      <c r="E2" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>632</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>611</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>612</v>
+        <v>633</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>634</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>613</v>
-      </c>
-      <c r="C3" s="8" t="n">
+      <c r="B3" s="4" t="s">
+        <v>635</v>
+      </c>
+      <c r="C3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>614</v>
+        <v>636</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>615</v>
+        <v>637</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>616</v>
+        <v>638</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>617</v>
+        <v>639</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>1</v>
@@ -8910,43 +9260,43 @@
       <c r="D4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>618</v>
+      <c r="E4" s="3" t="s">
+        <v>640</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>615</v>
+        <v>637</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>619</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="32.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>641</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>621</v>
+        <v>643</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>5</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>622</v>
-      </c>
-      <c r="F5" s="16" t="s">
-        <v>610</v>
+        <v>644</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>632</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>623</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>624</v>
+        <v>645</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>646</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8954,25 +9304,25 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>625</v>
+        <v>647</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>626</v>
-      </c>
-      <c r="F6" s="18" t="s">
-        <v>627</v>
+        <v>648</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>649</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>628</v>
+        <v>650</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>628</v>
+        <v>650</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8980,25 +9330,25 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>629</v>
+        <v>651</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>630</v>
-      </c>
-      <c r="F7" s="18" t="s">
-        <v>627</v>
+        <v>652</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>649</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>631</v>
+        <v>653</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>631</v>
+        <v>653</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9006,25 +9356,25 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>632</v>
+        <v>654</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>633</v>
-      </c>
-      <c r="F8" s="16" t="s">
-        <v>610</v>
+        <v>655</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>632</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>634</v>
+        <v>656</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>634</v>
+        <v>656</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9032,25 +9382,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>635</v>
+        <v>657</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>163</v>
+      <c r="D9" s="2" t="s">
+        <v>171</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>636</v>
-      </c>
-      <c r="F9" s="18" t="s">
-        <v>627</v>
+        <v>658</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>649</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>637</v>
+        <v>659</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>637</v>
+        <v>659</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9058,25 +9408,25 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>638</v>
+        <v>660</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>163</v>
+      <c r="D10" s="2" t="s">
+        <v>171</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>639</v>
-      </c>
-      <c r="F10" s="18" t="s">
-        <v>627</v>
+        <v>661</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>649</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>640</v>
+        <v>662</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>640</v>
+        <v>662</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9084,25 +9434,25 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>641</v>
+        <v>663</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>156</v>
+      <c r="D11" s="3" t="s">
+        <v>164</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>642</v>
+        <v>664</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>615</v>
+        <v>637</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>643</v>
+        <v>665</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>643</v>
+        <v>665</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9110,25 +9460,25 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>644</v>
+        <v>666</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>156</v>
+      <c r="D12" s="3" t="s">
+        <v>164</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>645</v>
-      </c>
-      <c r="F12" s="18" t="s">
-        <v>627</v>
+        <v>667</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>649</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>646</v>
+        <v>668</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>646</v>
+        <v>668</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="41" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9136,77 +9486,77 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>647</v>
+        <v>669</v>
       </c>
       <c r="C13" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>156</v>
+      <c r="D13" s="3" t="s">
+        <v>164</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>648</v>
-      </c>
-      <c r="F13" s="18" t="s">
-        <v>627</v>
+        <v>670</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>649</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>649</v>
+        <v>671</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>650</v>
+        <v>672</v>
       </c>
       <c r="C14" s="3" t="n">
         <v>6</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>651</v>
+        <v>673</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>615</v>
+        <v>637</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>652</v>
+        <v>674</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>654</v>
+        <v>676</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>7</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>655</v>
-      </c>
-      <c r="F15" s="18" t="s">
-        <v>627</v>
+        <v>248</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>677</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>649</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>656</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>657</v>
+        <v>678</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>679</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9214,48 +9564,48 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>658</v>
+        <v>680</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>5</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>659</v>
-      </c>
-      <c r="F16" s="16" t="s">
-        <v>610</v>
+        <v>681</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>632</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>661</v>
+        <v>683</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>7</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>662</v>
+        <v>281</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>684</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>615</v>
+        <v>637</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>663</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>664</v>
+        <v>685</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>686</v>
       </c>
     </row>
   </sheetData>
@@ -9279,208 +9629,197 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="46.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="46.03"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="134.94"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>665</v>
+        <v>687</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>666</v>
+        <v>688</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>474</v>
+        <v>491</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>667</v>
+        <v>689</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>668</v>
+        <v>690</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>669</v>
+        <v>691</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>670</v>
+        <v>692</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>671</v>
+        <v>693</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>672</v>
+        <v>694</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>669</v>
+        <v>691</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>673</v>
+        <v>695</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>674</v>
+        <v>696</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>675</v>
+        <v>697</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>669</v>
+        <v>691</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>676</v>
+        <v>698</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>677</v>
+        <v>699</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>678</v>
+        <v>700</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>669</v>
+        <v>691</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>679</v>
+        <v>701</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>680</v>
+        <v>702</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>203</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>681</v>
+        <v>703</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>682</v>
+        <v>704</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>683</v>
+        <v>705</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>681</v>
+        <v>703</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>684</v>
+        <v>706</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>685</v>
+        <v>707</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>686</v>
+        <v>708</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>669</v>
+        <v>691</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>687</v>
+        <v>709</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>688</v>
+        <v>710</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>689</v>
+        <v>711</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>681</v>
+        <v>703</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>690</v>
+        <v>712</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>691</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>692</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>669</v>
-      </c>
       <c r="D10" s="1" t="s">
-        <v>693</v>
+        <v>715</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>694</v>
+        <v>716</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>695</v>
+        <v>717</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>669</v>
+        <v>691</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>696</v>
+        <v>718</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
       <c r="F32" s="1"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -9498,12 +9837,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="38.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="33.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="1" width="38.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="33.27"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9514,14 +9853,20 @@
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>603</v>
+        <v>625</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>697</v>
-      </c>
-      <c r="F1" s="1"/>
-      <c r="G1" s="8"/>
+        <v>719</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>719</v>
+      </c>
       <c r="H1" s="1"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
@@ -9534,10 +9879,16 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>608</v>
-      </c>
-      <c r="F2" s="1"/>
+        <v>630</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>630</v>
+      </c>
       <c r="H2" s="1"/>
+      <c r="J2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
@@ -9550,10 +9901,16 @@
         <v>2</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>613</v>
-      </c>
-      <c r="F3" s="1"/>
+        <v>635</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>635</v>
+      </c>
       <c r="H3" s="1"/>
+      <c r="J3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
@@ -9566,10 +9923,16 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>608</v>
-      </c>
-      <c r="F4" s="1"/>
+        <v>630</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>630</v>
+      </c>
       <c r="H4" s="1"/>
+      <c r="J4" s="1"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
@@ -9582,10 +9945,16 @@
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>617</v>
-      </c>
-      <c r="F5" s="1"/>
+        <v>639</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>639</v>
+      </c>
       <c r="H5" s="1"/>
+      <c r="J5" s="1"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
@@ -9598,10 +9967,16 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>608</v>
-      </c>
-      <c r="F6" s="1"/>
+        <v>630</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>630</v>
+      </c>
       <c r="H6" s="1"/>
+      <c r="J6" s="1"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
@@ -9614,10 +9989,16 @@
         <v>2</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>613</v>
-      </c>
-      <c r="F7" s="1"/>
+        <v>635</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>635</v>
+      </c>
       <c r="H7" s="1"/>
+      <c r="J7" s="1"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
@@ -9630,10 +10011,16 @@
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>617</v>
-      </c>
-      <c r="F8" s="1"/>
+        <v>639</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>639</v>
+      </c>
       <c r="H8" s="1"/>
+      <c r="J8" s="1"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
@@ -9646,438 +10033,662 @@
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>617</v>
-      </c>
-      <c r="F9" s="1"/>
+        <v>639</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>639</v>
+      </c>
       <c r="H9" s="1"/>
+      <c r="J9" s="1"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="0" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>4</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>698</v>
-      </c>
-      <c r="F10" s="1"/>
+        <v>721</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>721</v>
+      </c>
       <c r="H10" s="1"/>
+      <c r="J10" s="1"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="0" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>4</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>698</v>
-      </c>
-      <c r="F11" s="1"/>
+        <v>721</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>721</v>
+      </c>
       <c r="H11" s="1"/>
+      <c r="J11" s="1"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
-        <v>100</v>
+        <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>118</v>
+        <v>722</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>625</v>
-      </c>
-      <c r="F12" s="1"/>
-      <c r="G12" s="8"/>
+        <v>639</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>639</v>
+      </c>
       <c r="H12" s="1"/>
+      <c r="J12" s="1"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
-        <v>101</v>
+        <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>625</v>
-      </c>
-      <c r="F13" s="1"/>
-      <c r="G13" s="8"/>
+        <v>639</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>639</v>
+      </c>
       <c r="H13" s="1"/>
+      <c r="J13" s="1"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>629</v>
-      </c>
-      <c r="F14" s="1"/>
-      <c r="G14" s="8"/>
+        <v>647</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>647</v>
+      </c>
       <c r="H14" s="1"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="1"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>136</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>629</v>
-      </c>
-      <c r="F15" s="1"/>
+        <v>647</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>647</v>
+      </c>
       <c r="H15" s="1"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="1"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>577</v>
+        <v>140</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>6</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>629</v>
-      </c>
-      <c r="F16" s="1"/>
+        <v>651</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>651</v>
+      </c>
       <c r="H16" s="1"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="1"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>632</v>
-      </c>
-      <c r="F17" s="1"/>
+        <v>651</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>651</v>
+      </c>
       <c r="H17" s="1"/>
+      <c r="J17" s="1"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>152</v>
+        <v>594</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>632</v>
-      </c>
-      <c r="F18" s="1"/>
+        <v>651</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>651</v>
+      </c>
       <c r="H18" s="1"/>
+      <c r="J18" s="1"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>641</v>
-      </c>
+        <v>654</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="H19" s="1"/>
+      <c r="J19" s="1"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
-        <v>200</v>
+        <v>106</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>635</v>
+        <v>654</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>654</v>
       </c>
       <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
-        <v>201</v>
+        <v>107</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>638</v>
+        <v>663</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>663</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>638</v>
-      </c>
+        <v>657</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>9</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>635</v>
+        <v>660</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>660</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="n">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>183</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>638</v>
+        <v>660</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>660</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="n">
-        <v>300</v>
+        <v>203</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>641</v>
+        <v>657</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>657</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="n">
-        <v>301</v>
+        <v>204</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>641</v>
+        <v>660</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>660</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="n">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>644</v>
+        <v>663</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>663</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="n">
+        <v>301</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C28" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="n">
+        <v>302</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C29" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="n">
         <v>304</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="C28" s="1" t="n">
+      <c r="B30" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C30" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="D28" s="1" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="n">
+      <c r="D30" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="n">
         <v>305</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C29" s="1" t="n">
+      <c r="B31" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C31" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="n">
+      <c r="D31" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="n">
         <v>306</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="C30" s="1" t="n">
+      <c r="B32" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C32" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="D30" s="3" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="n">
-        <v>402</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="C31" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="n">
-        <v>401</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="C32" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>658</v>
+      <c r="D32" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>723</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="n">
-        <v>500</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>247</v>
+        <v>401</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>239</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>650</v>
+        <v>15</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>680</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="n">
-        <v>501</v>
+        <v>402</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>254</v>
+        <v>233</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>654</v>
+        <v>15</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>680</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="n">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>654</v>
+        <v>672</v>
+      </c>
+      <c r="E35" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>672</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="n">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>583</v>
+        <v>256</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>650</v>
+        <v>676</v>
+      </c>
+      <c r="E36" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>676</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="n">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>584</v>
+        <v>263</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>650</v>
+        <v>676</v>
+      </c>
+      <c r="E37" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>676</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="n">
+        <v>503</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="C38" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>672</v>
+      </c>
+      <c r="E38" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="1" t="n">
+        <v>504</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="C39" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>672</v>
+      </c>
+      <c r="E39" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="1" t="n">
         <v>505</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="C38" s="1" t="n">
+      <c r="B40" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C40" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="D38" s="1" t="s">
-        <v>700</v>
+      <c r="D40" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="E40" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>724</v>
       </c>
     </row>
   </sheetData>
@@ -10101,24 +10712,24 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="28.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="42.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="25.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="25.62"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>701</v>
+        <v>725</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>702</v>
+        <v>726</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>588</v>
+        <v>610</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="6" t="s">
-        <v>703</v>
+      <c r="E1" s="3" t="s">
+        <v>727</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10128,48 +10739,48 @@
       <c r="B2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>704</v>
+      <c r="C2" s="3" t="s">
+        <v>728</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>705</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>729</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="87.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>707</v>
+        <v>165</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>731</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>708</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>732</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="89.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>710</v>
+        <v>116</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>734</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>711</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>712</v>
+        <v>735</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>736</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10177,16 +10788,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>713</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>714</v>
-      </c>
-      <c r="D5" s="0" t="s">
-        <v>715</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>716</v>
+        <v>737</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>738</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>740</v>
       </c>
     </row>
   </sheetData>

--- a/fiches indicateurs.xlsx
+++ b/fiches indicateurs.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="7"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="indicateurs" sheetId="1" state="visible" r:id="rId3"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2004" uniqueCount="741">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2046" uniqueCount="753">
   <si>
     <t xml:space="preserve">fiche_indicateur</t>
   </si>
@@ -357,379 +357,398 @@
     <t xml:space="preserve">Zonal</t>
   </si>
   <si>
+    <t xml:space="preserve">Vulnérabilité Intrinsèque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vulnérabilité</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type ouvrage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type de captage (captage, forage, tranchée drainante).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Classe (forage / captage / tranchée drainante)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comparer les captages selon leur vulnérabilité intrinsèque liée à leur nature {un captage superficiel est considéré comme plus vulnérable qu'un forage profond dans les calculs de criticité)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Captage superficiel = plus vulnérable → criticité forte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impact direct sur vulnérabilité (forage &lt; superficiel). Peut être intégré dans la pondération selon le type.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statut captage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statut d’utilisation (actif, secours, abandonné).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Classe (actif, secours, inactif, abandonné).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distinguer les captages selon leur statut afin de contextualiser leur valeur dans la comparaison.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attribution directe au captage, sans transformation. Utilisation à titre informatif</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Captage actif = enjeu, secours/inactif = criticité moindre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information descriptive captage. Utile pour interface mais pas forcément intégré dans calcul multicritère.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enjeux Environnementaux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zones UNESCO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Superficie des intersections avec les zones inscrites au patrimoine mondial de l'UNESCO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">non</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comparer les bassins versants AEP entre eux par rapport à leur taux de couverture par une zone UNESCO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calcul surfacique par unité spatiale régulière puis agrégation au bassin versant.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">maille</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Présence d’une partie du bassin versant dans zone UNESCO = criticité faible bien que enjeu fort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carte choroplèthe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zones protégées provinciales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Superficie des intersections avec parcs, réserves</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comparer les bassins versants AEP entre eux par rapport à leur taux de couverture par une zone protégée provinciale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Présence en zone protégée = criticité faible bien que  enjeu fort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KBA / ZICO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Superficie des intersections avec les zones d'intérêt biologique et biodiversité spécifique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comparer les bassins versants AEP entre eux par rapport à leur taux de couverture par une zone KBA/ZICO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Présence en KBA/ZICO = criticité faible bien que enjeu fort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Espèces menacées</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre / présence d'espèces rares ou micro-endémisme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mesurer la richesse spécifique menacée dépendante de la ressource en eau.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calcul du nombre d’espèce menacé par unité spatiale régulière puis agrégation au bassin versant.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forte richesse en espèces menacées = criticité faible bien que enjeu fort (à confirmer)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Espèces rares et menacées dont f</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">orêt sèche</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Superficie des intersections des patchs de forêt sèche additionné aux zones potentielles de présence d’éspèces rares et menacées</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comparer les bassins versants AEP entre eux par rapport à leur taux de couverture par des patch d’espèces rares et menacées dont les forêt sèches.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Négatif (absence = critique) ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Présence de forêt sèche  = criticité faible bien que enjeu fort (à confirmer)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Occupation sol (couvert végétal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Superficie des intersections avec des zones de couvert végétal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caractériser la présence de couvert végétal comme indicateur de bon état écologique du milieu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positif (plus = mieux)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fort couvert végétal = faible criticité</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relatif</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Occupation sol (couvert forestier)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Superficie des intersections avec des zones de couverture forestière non perturbée et dégradée</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Évaluer l'état de la couverture forestière, protectrice de la ressource en eau.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fort couvert forestier = faible criticité</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MENACES ANTHROPIQUES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Occupation sol (surfaces agricoles)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Superficie des intersections avec des zones agricoles par type (terres arables, agropastorales, pépinières, sylviculture)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mesurer l'emprise agricole, source potentielle de pression sur la qualité et la quantité de la ressource.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Négatif (plus = critique)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forte surface agricole = pression potentielle élevée</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MENACES NATURELLES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incendies cumulés</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surface totale touchée par les incendies.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comparer les bassins versants selon leur historique d’incendies afin d’identifier les milieux les perturbés.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cumul des surfaces brûlées sur une année et agrégation par bassin versant.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forte surface brûlée = forte pression → criticité élevée</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cumul surfacique VIIRS, simplement iintégrable en pression environnementale.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surface érosion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surface des zones où le sol est abîmé ou fragile.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comparer les bassins versants selon leur sensibilité à l’érosion afin d’identifier les ressources exposées à des dégradations du milieu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plus de sol nu = plus d’érosion → criticité élevée</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Donnée non homogène territoire si utilisation de la donnée « formes érosives » de l’OEIL. Préférence donnée homogène → MOS. Indicateur secondaire.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terrain nu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surface de terrain sans végétation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comparer les bassins versants selon l’étendue des surfaces dégradées afin d’identifier les zones les plus sensibles aux ruissellement et aux transferts de polluants.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indicateur MOS privilégié. Homogène et robuste. Calcul surfacique sur BV.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glissement terrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zones exposées aux glissements de terrain.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comparer les bassins versants selon leur instabilité afin d’identifier les zones à risque pour la ressource.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carte issue analyse multicritère DIMENC. Déplacé en vulnérabilité ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Espèces exotiques envahissantes (EEE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Présence d´espèces exotiques envahissantes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comparer les bassins versants selon la présence d’espèces envahissantes afin d’identifier des pressions écologiques potentielles.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intégration conditionnée à la disponibilité des données, sans méthode définie à ce stade.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Présence forte = pression écologique élevée</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Donnée incertaine. Source non identifiée. Indicateur non prioritaire.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICPE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre de sites industriels à risque.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comparer les bassins versants selon la densité d’activités à risque afin d’identifier les sources potentielles de pollution.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comptage des installations par unité spatiale avec possibilité de typologie.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plus d’ICPE = risque pollution → criticité élevée</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Données dispersées (provinces). Besoin typologie ICPE. Difficulté accès + structuration.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">re</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Activité minière</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surface occupée par les activités minières.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comparer les bassins versants selon l’emprise minière afin d’identifier les pressions fortes sur la ressource.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calcul des surfaces d’emprise puis agrégation par bassin versant.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surface minière élevée = pression forte → criticité élevée</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Donnée DIMENC non publique. Alternative via MOS (redondance sol nu). Accès incertain.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Urbanisation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre de bâtiments présents.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comparer les bassins versants selon leur niveau d’artificialisation afin d’identifier les pressions liées aux activités humaines.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comptage des bâtiments par unité spatiale puis agrégation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plus de bâti = pression → criticité élevée</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Donnée BD TOPO. Indicateur pression anthropique. Possibilité typologie bâtis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Habitations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre de logements.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comparer les bassins versants selon la densité d’habitat afin d’affiner l’analyse des pressions humaines.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comptage ou estimation des logements par unité spatiale.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Densité humaine = pression accrue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Donnée ISEE. Complément du bâti. Peut rester séparé ou fusionné selon usage.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Franchissements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre d'ouvrages croisant le réseau hydrographique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier les points de franchissement (ponts, buses, gués) comme facteurs de perturbation du réseau hydrographique. Chaque pont, buse ou gué est un point où une pollution routière (hydrocarbures, transport de matières dangereuses) peut entrer directement dans le cours d'eau en amont d'un captage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comptage des intersections entre les ouvrages linéaires (routes, pistes) et le réseau hydrographique.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre élevé de franchissements = pression sur continuité écologique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linéaire routes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distance de linéaire total de voiries par type (RT, RP, Piste)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mesurer la densité du réseau routier comme indicateur de pression sur les milieux naturels et la ressource en eau. Une forte densité de routes et de pistes (souvent non classées et plus érosives) augmente l'apport de sédiments dans les cours d'eau (turbidité, engrangement) et donne l'accès à des zones sensibles et peut potentiellement provoquer des pollutions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calcul de la longueur de voiries par maille, ventilé par type.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fort linéaire routier = fragmentation et imperméabilisation élevées</t>
+  </si>
+  <si>
     <t xml:space="preserve">Plan d’Urbanisme Directeur</t>
   </si>
   <si>
     <t xml:space="preserve">Type d’occupation et  dynamiques d’aménagement du territoire (zones urbanisées, à urbaniser, naturelles, zones à enjeux, terrain agricole constructible ou non)</t>
   </si>
   <si>
-    <t xml:space="preserve">non</t>
-  </si>
-  <si>
     <t xml:space="preserve">Comparer les captages selon les perspectives actuelles et futures de l’aménagement du territoire sur la ressource en eau </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calcul surfacique par unité spatiale régulière puis agrégation au bassin versant.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">maille</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carte choroplèthe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vulnérabilité Intrinsèque</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vulnérabilité</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Type ouvrage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Type de captage (captage, forage, tranchée drainante).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Classe (forage / captage / tranchée drainante)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comparer les captages selon leur vulnérabilité intrinsèque liée à leur nature {un captage superficiel est considéré comme plus vulnérable qu'un forage profond dans les calculs de criticité)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Captage superficiel = plus vulnérable → criticité forte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Impact direct sur vulnérabilité (forage &lt; superficiel). Peut être intégré dans la pondération selon le type.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Statut captage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Statut d’utilisation (actif, secours, abandonné).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Classe (actif, secours, inactif, abandonné).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Distinguer les captages selon leur statut afin de contextualiser leur valeur dans la comparaison.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Attribution directe au captage, sans transformation. Utilisation à titre informatif</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Captage actif = enjeu, secours/inactif = criticité moindre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information descriptive captage. Utile pour interface mais pas forcément intégré dans calcul multicritère.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enjeux Environnementaux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zones UNESCO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Superficie des intersections avec les zones inscrites au patrimoine mondial de l'UNESCO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comparer les bassins versants AEP entre eux par rapport à leur taux de couverture par une zone UNESCO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Présence d’une partie du bassin versant dans zone UNESCO = criticité faible bien que enjeu fort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zones protégées provinciales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Superficie des intersections avec parcs, réserves</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comparer les bassins versants AEP entre eux par rapport à leur taux de couverture par une zone protégée provinciale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Présence en zone protégée = criticité faible bien que  enjeu fort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KBA / ZICO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Superficie des intersections avec les zones d'intérêt biologique et biodiversité spécifique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comparer les bassins versants AEP entre eux par rapport à leur taux de couverture par une zone KBA/ZICO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Présence en KBA/ZICO = criticité faible bien que enjeu fort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Espèces menacées</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nombre / présence d'espèces rares ou micro-endémisme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mesurer la richesse spécifique menacée dépendante de la ressource en eau.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calcul du nombre d’espèce menacé par unité spatiale régulière puis agrégation au bassin versant.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forte richesse en espèces menacées = criticité faible bien que enjeu fort (à confirmer)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forêt sèche</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Superficie des intersections des patchs de forêt sèche</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comparer les bassins versants AEP entre eux par rapport à leur taux de couverture par des patch de forêt sèche.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Négatif (absence = critique) ?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Présence de forêt sèche  = criticité faible bien que enjeu fort (à confirmer)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Occupation sol (couvert végétal)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Superficie des intersections avec des zones de couvert végétal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caractériser la présence de couvert végétal comme indicateur de bon état écologique du milieu.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Positif (plus = mieux)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fort couvert végétal = faible criticité</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Relatif</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Occupation sol (couvert forestier)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Superficie des intersections avec des zones de couverture forestière non perturbée et dégradée</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Évaluer l'état de la couverture forestière, protectrice de la ressource en eau.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fort couvert forestier = faible criticité</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MENACES ANTHROPIQUES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Menace</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Occupation sol (surfaces agricoles)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Superficie des intersections avec des zones agricoles par type (terres arables, agropastorales, pépinières, sylviculture)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mesurer l'emprise agricole, source potentielle de pression sur la qualité et la quantité de la ressource.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Négatif (plus = critique)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forte surface agricole = pression potentielle élevée</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MENACES NATURELLES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incendies cumulés</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Surface totale touchée par les incendies.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comparer les bassins versants selon leur historique d’incendies afin d’identifier les milieux les perturbés.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cumul des surfaces brûlées sur une année et agrégation par bassin versant.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forte surface brûlée = forte pression → criticité élevée</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cumul surfacique VIIRS, simplement iintégrable en pression environnementale.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Surface érosion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Surface des zones où le sol est abîmé ou fragile.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comparer les bassins versants selon leur sensibilité à l’érosion afin d’identifier les ressources exposées à des dégradations du milieu.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plus de sol nu = plus d’érosion → criticité élevée</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Donnée non homogène territoire si utilisation de la donnée « formes érosives » de l’OEIL. Préférence donnée homogène → MOS. Indicateur secondaire.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terrain nu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Surface de terrain sans végétation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comparer les bassins versants selon l’étendue des surfaces dégradées afin d’identifier les zones les plus sensibles aux ruissellement et aux transferts de polluants.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indicateur MOS privilégié. Homogène et robuste. Calcul surfacique sur BV.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glissement terrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zones exposées aux glissements de terrain.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comparer les bassins versants selon leur instabilité afin d’identifier les zones à risque pour la ressource.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carte issue analyse multicritère DIMENC. Déplacé en vulnérabilité ?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Espèces exotiques envahissantes (EEE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Présence d´espèces exotiques envahissantes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comparer les bassins versants selon la présence d’espèces envahissantes afin d’identifier des pressions écologiques potentielles.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intégration conditionnée à la disponibilité des données, sans méthode définie à ce stade.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Présence forte = pression écologique élevée</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Donnée incertaine. Source non identifiée. Indicateur non prioritaire.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICPE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nombre de sites industriels à risque.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comparer les bassins versants selon la densité d’activités à risque afin d’identifier les sources potentielles de pollution.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comptage des installations par unité spatiale avec possibilité de typologie.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plus d’ICPE = risque pollution → criticité élevée</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Données dispersées (provinces). Besoin typologie ICPE. Difficulté accès + structuration.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Activité minière</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Surface occupée par les activités minières.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comparer les bassins versants selon l’emprise minière afin d’identifier les pressions fortes sur la ressource.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calcul des surfaces d’emprise puis agrégation par bassin versant.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Surface minière élevée = pression forte → criticité élevée</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Donnée DIMENC non publique. Alternative via MOS (redondance sol nu). Accès incertain.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Urbanisation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nombre de bâtiments présents.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comparer les bassins versants selon leur niveau d’artificialisation afin d’identifier les pressions liées aux activités humaines.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comptage des bâtiments par unité spatiale puis agrégation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plus de bâti = pression → criticité élevée</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Donnée BD TOPO. Indicateur pression anthropique. Possibilité typologie bâtis.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Habitations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nombre de logements.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comparer les bassins versants selon la densité d’habitat afin d’affiner l’analyse des pressions humaines.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comptage ou estimation des logements par unité spatiale.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Densité humaine = pression accrue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Donnée ISEE. Complément du bâti. Peut rester séparé ou fusionné selon usage.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Franchissements</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nombre d'ouvrages croisant le réseau hydrographique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier les points de franchissement (ponts, buses, gués) comme facteurs de perturbation du réseau hydrographique. Chaque pont, buse ou gué est un point où une pollution routière (hydrocarbures, transport de matières dangereuses) peut entrer directement dans le cours d'eau en amont d'un captage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comptage des intersections entre les ouvrages linéaires (routes, pistes) et le réseau hydrographique.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nombre élevé de franchissements = pression sur continuité écologique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linéaire routes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Distance de linéaire total de voiries par type (RT, RP, Piste)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mesurer la densité du réseau routier comme indicateur de pression sur les milieux naturels et la ressource en eau. Une forte densité de routes et de pistes (souvent non classées et plus érosives) augmente l'apport de sédiments dans les cours d'eau (turbidité, engrangement) et donne l'accès à des zones sensibles et peut potentiellement provoquer des pollutions.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calcul de la longueur de voiries par maille, ventilé par type.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fort linéaire routier = fragmentation et imperméabilisation élevées</t>
   </si>
   <si>
     <t xml:space="preserve">Géologie</t>
@@ -1856,7 +1875,7 @@
     <t xml:space="preserve">commentaire</t>
   </si>
   <si>
-    <t xml:space="preserve">Espèces menacées (Forêt sèche)</t>
+    <t xml:space="preserve">Espèces rares et menacées</t>
   </si>
   <si>
     <t xml:space="preserve">doublons TMF</t>
@@ -2135,6 +2154,36 @@
     <t xml:space="preserve">Prioriser les actions correctives et confirmer l’impact des pressions</t>
   </si>
   <si>
+    <t xml:space="preserve">Importance captage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Niveau infrastrutures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vulnérabilité structurelle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sécurité sanitaire et reglementaire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zone naturelle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zones protégés </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Permettre aux gestionnaire de solliciter des fonds pour la restauration de zone à haute valeur environnementales reconnues et réglementés</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Activités à risque </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infractrustures et usages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perturbations environnementales </t>
+  </si>
+  <si>
     <t xml:space="preserve">ids_indicateurs</t>
   </si>
   <si>
@@ -2241,6 +2290,9 @@
   </si>
   <si>
     <t xml:space="preserve">Statut foncier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zone d’exploitation minière</t>
   </si>
   <si>
     <t xml:space="preserve">Infrastructures et risques de dégradation des eaux</t>
@@ -2304,7 +2356,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="12">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -2341,6 +2393,11 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -2359,13 +2416,111 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB3CAC7"/>
+        <bgColor rgb="FFB6D7A8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9FC5E8"/>
+        <bgColor rgb="FFB3CAC7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4472C4"/>
+        <bgColor rgb="FF666699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFE2F3"/>
+        <bgColor rgb="FFC9DAF8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9DAF8"/>
+        <bgColor rgb="FFCFE2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93C47D"/>
+        <bgColor rgb="FFB6D7A8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3BC29F"/>
+        <bgColor rgb="FF339966"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB6D7A8"/>
+        <bgColor rgb="FFB3CAC7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA9999"/>
+        <bgColor rgb="FFFF8080"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC55A11"/>
+        <bgColor rgb="FFED7D31"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4CCCC"/>
+        <bgColor rgb="FFF9CB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFFFFF99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED7D31"/>
+        <bgColor rgb="FFFF8080"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9CB9C"/>
+        <bgColor rgb="FFF4CCCC"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -2402,7 +2557,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="36">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2427,15 +2582,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2455,20 +2614,92 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2497,6 +2728,66 @@
       </fill>
     </dxf>
   </dxfs>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFF4CCCC"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFB3CAC7"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFF2CC"/>
+      <rgbColor rgb="FFCFE2F3"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFC9DAF8"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFB6D7A8"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF9FC5E8"/>
+      <rgbColor rgb="FFEA9999"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFF9CB9C"/>
+      <rgbColor rgb="FF4472C4"/>
+      <rgbColor rgb="FF3BC29F"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFED7D31"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF93C47D"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FFC55A11"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -2615,7 +2906,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:X1048576"/>
+  <dimension ref="A1:X42"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="15.18"/>
@@ -3344,64 +3635,26 @@
       </c>
       <c r="W10" s="1"/>
     </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="I11" s="5"/>
-      <c r="J11" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O11" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="P11" s="2"/>
-      <c r="R11" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="S11" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="T11" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="U11" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="V11" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="W11" s="1"/>
+    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0"/>
+      <c r="B11" s="0"/>
+      <c r="C11" s="0"/>
+      <c r="D11" s="0"/>
+      <c r="E11" s="0"/>
+      <c r="F11" s="0"/>
+      <c r="G11" s="0"/>
+      <c r="H11" s="0"/>
+      <c r="I11" s="0"/>
+      <c r="J11" s="0"/>
+      <c r="K11" s="0"/>
+      <c r="N11" s="0"/>
+      <c r="O11" s="0"/>
+      <c r="P11" s="0"/>
+      <c r="Q11" s="0"/>
+      <c r="R11" s="0"/>
+      <c r="S11" s="0"/>
+      <c r="U11" s="0"/>
+      <c r="V11" s="0"/>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
@@ -3411,16 +3664,16 @@
         <v>9</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>28</v>
@@ -3429,10 +3682,10 @@
         <v>28</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>91</v>
@@ -3453,7 +3706,7 @@
         <v>99</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="R12" s="1" t="s">
         <v>67</v>
@@ -3471,7 +3724,7 @@
         <v>69</v>
       </c>
       <c r="W12" s="1" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3482,16 +3735,16 @@
         <v>10</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>123</v>
-      </c>
       <c r="F13" s="1" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>28</v>
@@ -3500,13 +3753,13 @@
         <v>28</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="L13" s="1" t="s">
         <v>32</v>
@@ -3524,7 +3777,7 @@
         <v>99</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="R13" s="1" t="s">
         <v>67</v>
@@ -3542,7 +3795,7 @@
         <v>78</v>
       </c>
       <c r="W13" s="1" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3553,34 +3806,34 @@
         <v>100</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>34</v>
@@ -3595,7 +3848,7 @@
         <v>36</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="R14" s="1" t="s">
         <v>38</v>
@@ -3610,7 +3863,7 @@
         <v>107</v>
       </c>
       <c r="V14" s="1" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3621,34 +3874,34 @@
         <v>101</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>34</v>
@@ -3663,7 +3916,7 @@
         <v>36</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="R15" s="1" t="s">
         <v>38</v>
@@ -3678,7 +3931,7 @@
         <v>107</v>
       </c>
       <c r="V15" s="1" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3689,34 +3942,34 @@
         <v>102</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="M16" s="1" t="s">
         <v>34</v>
@@ -3731,7 +3984,7 @@
         <v>36</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="R16" s="1" t="s">
         <v>38</v>
@@ -3746,7 +3999,7 @@
         <v>107</v>
       </c>
       <c r="V16" s="1" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3757,34 +4010,34 @@
         <v>103</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>28</v>
+        <v>126</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>82</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="M17" s="1" t="s">
         <v>34</v>
@@ -3799,7 +4052,7 @@
         <v>36</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="R17" s="1" t="s">
         <v>38</v>
@@ -3814,7 +4067,7 @@
         <v>107</v>
       </c>
       <c r="V17" s="1" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3825,34 +4078,34 @@
         <v>104</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>149</v>
+      <c r="E18" s="6" t="s">
+        <v>146</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>34</v>
@@ -3864,10 +4117,10 @@
         <v>35</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="R18" s="1" t="s">
         <v>38</v>
@@ -3882,7 +4135,7 @@
         <v>107</v>
       </c>
       <c r="V18" s="1" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3893,16 +4146,16 @@
         <v>105</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>28</v>
@@ -3911,16 +4164,16 @@
         <v>28</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>33</v>
@@ -3932,10 +4185,10 @@
         <v>35</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="R19" s="1" t="s">
         <v>38</v>
@@ -3944,13 +4197,13 @@
         <v>39</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="U19" s="1" t="s">
         <v>107</v>
       </c>
       <c r="V19" s="1" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3961,16 +4214,16 @@
         <v>106</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>28</v>
@@ -3979,16 +4232,16 @@
         <v>28</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>33</v>
@@ -4000,10 +4253,10 @@
         <v>35</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="R20" s="1" t="s">
         <v>38</v>
@@ -4012,13 +4265,13 @@
         <v>39</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="U20" s="1" t="s">
         <v>107</v>
       </c>
       <c r="V20" s="1" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4029,16 +4282,16 @@
         <v>107</v>
       </c>
       <c r="C21" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>164</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>167</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>28</v>
@@ -4047,16 +4300,16 @@
         <v>28</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>33</v>
@@ -4068,10 +4321,10 @@
         <v>35</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="R21" s="1" t="s">
         <v>38</v>
@@ -4080,13 +4333,13 @@
         <v>39</v>
       </c>
       <c r="T21" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="U21" s="1" t="s">
         <v>107</v>
       </c>
       <c r="V21" s="1" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4097,16 +4350,16 @@
         <v>200</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>28</v>
@@ -4115,16 +4368,16 @@
         <v>28</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>33</v>
@@ -4136,10 +4389,10 @@
         <v>35</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="R22" s="1" t="s">
         <v>38</v>
@@ -4154,10 +4407,10 @@
         <v>107</v>
       </c>
       <c r="V22" s="1" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="W22" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4168,16 +4421,16 @@
         <v>201</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>28</v>
@@ -4186,16 +4439,16 @@
         <v>28</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="M23" s="1" t="s">
         <v>33</v>
@@ -4207,10 +4460,10 @@
         <v>35</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="Q23" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="R23" s="1" t="s">
         <v>38</v>
@@ -4225,10 +4478,10 @@
         <v>107</v>
       </c>
       <c r="V23" s="1" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="W23" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4239,16 +4492,16 @@
         <v>202</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>28</v>
@@ -4257,16 +4510,16 @@
         <v>28</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="M24" s="1" t="s">
         <v>33</v>
@@ -4278,10 +4531,10 @@
         <v>35</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="Q24" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="R24" s="1" t="s">
         <v>38</v>
@@ -4296,10 +4549,10 @@
         <v>107</v>
       </c>
       <c r="V24" s="1" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="W24" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4310,16 +4563,16 @@
         <v>203</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>28</v>
@@ -4328,16 +4581,16 @@
         <v>28</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="M25" s="1" t="s">
         <v>33</v>
@@ -4349,10 +4602,10 @@
         <v>35</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="Q25" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="R25" s="1" t="s">
         <v>38</v>
@@ -4367,10 +4620,10 @@
         <v>107</v>
       </c>
       <c r="V25" s="1" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="W25" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4381,34 +4634,34 @@
         <v>204</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="I26" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="L26" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="L26" s="1" t="s">
-        <v>196</v>
       </c>
       <c r="M26" s="1" t="s">
         <v>34</v>
@@ -4420,10 +4673,10 @@
         <v>35</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="Q26" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="R26" s="1" t="s">
         <v>38</v>
@@ -4438,10 +4691,10 @@
         <v>107</v>
       </c>
       <c r="V26" s="1" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="W26" s="1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4452,16 +4705,16 @@
         <v>300</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>28</v>
@@ -4473,13 +4726,13 @@
         <v>82</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="M27" s="1" t="s">
         <v>33</v>
@@ -4491,10 +4744,10 @@
         <v>35</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="Q27" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="R27" s="1" t="s">
         <v>38</v>
@@ -4509,48 +4762,48 @@
         <v>107</v>
       </c>
       <c r="V27" s="1" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="W27" s="1" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="B28" s="1" t="n">
-        <v>301</v>
+      <c r="B28" s="1" t="s">
+        <v>202</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="M28" s="1" t="s">
         <v>33</v>
@@ -4562,10 +4815,10 @@
         <v>35</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="R28" s="1" t="s">
         <v>38</v>
@@ -4580,10 +4833,10 @@
         <v>107</v>
       </c>
       <c r="V28" s="1" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="W28" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4594,16 +4847,16 @@
         <v>302</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>28</v>
@@ -4615,13 +4868,13 @@
         <v>82</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>33</v>
@@ -4633,10 +4886,10 @@
         <v>35</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="R29" s="1" t="s">
         <v>38</v>
@@ -4651,10 +4904,10 @@
         <v>107</v>
       </c>
       <c r="V29" s="1" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="W29" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4665,16 +4918,16 @@
         <v>304</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>28</v>
@@ -4686,13 +4939,13 @@
         <v>82</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="M30" s="1" t="s">
         <v>33</v>
@@ -4704,10 +4957,10 @@
         <v>35</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="Q30" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="R30" s="1" t="s">
         <v>38</v>
@@ -4722,10 +4975,10 @@
         <v>107</v>
       </c>
       <c r="V30" s="1" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="W30" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4736,16 +4989,16 @@
         <v>305</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>28</v>
@@ -4757,13 +5010,13 @@
         <v>82</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="M31" s="1" t="s">
         <v>33</v>
@@ -4775,10 +5028,10 @@
         <v>35</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="Q31" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="R31" s="1" t="s">
         <v>38</v>
@@ -4793,7 +5046,7 @@
         <v>107</v>
       </c>
       <c r="V31" s="1" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4804,16 +5057,16 @@
         <v>306</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>28</v>
@@ -4825,13 +5078,13 @@
         <v>46</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="M32" s="1" t="s">
         <v>33</v>
@@ -4843,10 +5096,10 @@
         <v>35</v>
       </c>
       <c r="P32" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="Q32" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="R32" s="1" t="s">
         <v>38</v>
@@ -4861,45 +5114,40 @@
         <v>107</v>
       </c>
       <c r="V32" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="n">
-        <v>31</v>
-      </c>
+        <v>132</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="1" t="n">
-        <v>401</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>115</v>
+        <v>307</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>161</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>116</v>
+        <v>162</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>232</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>235</v>
+        <v>126</v>
+      </c>
+      <c r="I33" s="5"/>
+      <c r="J33" s="3" t="s">
+        <v>233</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>236</v>
+        <v>129</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="M33" s="1" t="s">
         <v>33</v>
@@ -4910,12 +5158,7 @@
       <c r="O33" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P33" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="Q33" s="1" t="s">
-        <v>237</v>
-      </c>
+      <c r="P33" s="2"/>
       <c r="R33" s="1" t="s">
         <v>38</v>
       </c>
@@ -4923,36 +5166,34 @@
         <v>39</v>
       </c>
       <c r="T33" s="1" t="s">
-        <v>159</v>
+        <v>40</v>
       </c>
       <c r="U33" s="1" t="s">
         <v>107</v>
       </c>
       <c r="V33" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="W33" s="1" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="13.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>132</v>
+      </c>
+      <c r="W33" s="1"/>
+    </row>
+    <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B34" s="1" t="n">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>240</v>
+        <v>109</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>28</v>
@@ -4960,17 +5201,17 @@
       <c r="H34" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I34" s="2" t="s">
-        <v>241</v>
+      <c r="I34" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="M34" s="1" t="s">
         <v>33</v>
@@ -4979,52 +5220,51 @@
         <v>33</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="P34" s="2" t="s">
-        <v>245</v>
+        <v>35</v>
+      </c>
+      <c r="P34" s="1" t="s">
+        <v>166</v>
       </c>
       <c r="Q34" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="R34" s="1" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="S34" s="1" t="s">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="T34" s="1" t="s">
-        <v>40</v>
+        <v>156</v>
       </c>
       <c r="U34" s="1" t="s">
         <v>107</v>
       </c>
       <c r="V34" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="W34" s="1"/>
-      <c r="X34" s="1" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>132</v>
+      </c>
+      <c r="W34" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="13.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B35" s="1" t="n">
-        <v>500</v>
+        <v>402</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>248</v>
+        <v>108</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>250</v>
+        <v>109</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>241</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>28</v>
@@ -5032,32 +5272,32 @@
       <c r="H35" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I35" s="1" t="s">
-        <v>251</v>
+      <c r="I35" s="2" t="s">
+        <v>242</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>196</v>
+        <v>130</v>
       </c>
       <c r="M35" s="1" t="s">
         <v>33</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q35" s="1" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="R35" s="1" t="s">
         <v>67</v>
@@ -5066,140 +5306,141 @@
         <v>68</v>
       </c>
       <c r="T35" s="1" t="s">
-        <v>159</v>
+        <v>40</v>
       </c>
       <c r="U35" s="1" t="s">
         <v>107</v>
       </c>
       <c r="V35" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="W35" s="1" t="s">
-        <v>255</v>
+        <v>247</v>
+      </c>
+      <c r="W35" s="1"/>
+      <c r="X35" s="1" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B36" s="1" t="n">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>110</v>
+        <v>28</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>113</v>
+        <v>193</v>
       </c>
       <c r="M36" s="1" t="s">
         <v>33</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="P36" s="1" t="s">
-        <v>157</v>
+        <v>245</v>
+      </c>
+      <c r="P36" s="2" t="s">
+        <v>246</v>
       </c>
       <c r="Q36" s="1" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="R36" s="1" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="S36" s="1" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="T36" s="1" t="s">
-        <v>40</v>
+        <v>156</v>
       </c>
       <c r="U36" s="1" t="s">
         <v>107</v>
       </c>
       <c r="V36" s="1" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="W36" s="1" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B37" s="1" t="n">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>28</v>
+        <v>126</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="M37" s="1" t="s">
         <v>33</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O37" s="1" t="s">
         <v>35</v>
       </c>
       <c r="P37" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="Q37" s="1" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="R37" s="1" t="s">
         <v>38</v>
@@ -5214,27 +5455,30 @@
         <v>107</v>
       </c>
       <c r="V37" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>132</v>
+      </c>
+      <c r="W37" s="1" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B38" s="1" t="n">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>28</v>
@@ -5243,19 +5487,19 @@
         <v>28</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>82</v>
+        <v>266</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>32</v>
+        <v>130</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N38" s="1" t="s">
         <v>34</v>
@@ -5263,64 +5507,61 @@
       <c r="O38" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="Q38" s="3" t="s">
-        <v>273</v>
+      <c r="P38" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q38" s="1" t="s">
+        <v>269</v>
       </c>
       <c r="R38" s="1" t="s">
         <v>38</v>
       </c>
       <c r="S38" s="1" t="s">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="T38" s="1" t="s">
         <v>40</v>
       </c>
       <c r="U38" s="1" t="s">
-        <v>41</v>
+        <v>107</v>
       </c>
       <c r="V38" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="W38" s="1" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B39" s="1" t="n">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>275</v>
+        <v>162</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>270</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>110</v>
+        <v>28</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="L39" s="1" t="s">
         <v>32</v>
@@ -5334,17 +5575,17 @@
       <c r="O39" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P39" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="Q39" s="1" t="s">
-        <v>279</v>
+      <c r="P39" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q39" s="3" t="s">
+        <v>274</v>
       </c>
       <c r="R39" s="1" t="s">
         <v>38</v>
       </c>
       <c r="S39" s="1" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="T39" s="1" t="s">
         <v>40</v>
@@ -5356,42 +5597,42 @@
         <v>42</v>
       </c>
       <c r="W39" s="1" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B40" s="1" t="n">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>281</v>
+        <v>249</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>282</v>
+        <v>162</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>276</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>28</v>
+        <v>126</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>284</v>
+        <v>54</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="L40" s="1" t="s">
         <v>32</v>
@@ -5403,19 +5644,19 @@
         <v>34</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="P40" s="2" t="s">
-        <v>245</v>
+        <v>35</v>
+      </c>
+      <c r="P40" s="1" t="s">
+        <v>166</v>
       </c>
       <c r="Q40" s="1" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="R40" s="1" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="S40" s="1" t="s">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="T40" s="1" t="s">
         <v>40</v>
@@ -5424,78 +5665,148 @@
         <v>41</v>
       </c>
       <c r="V40" s="1" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="W40" s="1" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="1" t="n">
+        <v>38</v>
+      </c>
       <c r="B41" s="1" t="n">
-        <v>400</v>
+        <v>505</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>115</v>
+        <v>282</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>116</v>
+        <v>162</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>240</v>
+        <v>284</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>28</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>290</v>
+        <v>285</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>287</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>113</v>
+        <v>32</v>
       </c>
       <c r="M41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="P41" s="1" t="s">
-        <v>169</v>
+        <v>64</v>
+      </c>
+      <c r="P41" s="2" t="s">
+        <v>246</v>
       </c>
       <c r="Q41" s="1" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="S41" s="1" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="T41" s="1" t="s">
         <v>40</v>
       </c>
       <c r="U41" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="V41" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="W41" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="1" t="n">
+        <v>400</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="M42" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N42" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O42" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="P42" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q42" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="R42" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="S42" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="T42" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="U42" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="V41" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="W41" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="X41" s="1" t="s">
+      <c r="V42" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="W42" s="1" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="X42" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -5527,40 +5838,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5568,34 +5879,34 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5603,31 +5914,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5635,34 +5946,34 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5670,34 +5981,34 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5705,34 +6016,34 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5740,37 +6051,37 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>340</v>
+        <v>314</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>341</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5778,28 +6089,28 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5807,34 +6118,34 @@
         <v>100</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5842,34 +6153,34 @@
         <v>101</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="E10" s="8" t="s">
         <v>354</v>
       </c>
+      <c r="E10" s="9" t="s">
+        <v>355</v>
+      </c>
       <c r="F10" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5877,34 +6188,34 @@
         <v>102</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="L11" s="1" t="s">
         <v>358</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5912,34 +6223,34 @@
         <v>103</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5947,34 +6258,34 @@
         <v>104</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5982,34 +6293,34 @@
         <v>105</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6017,31 +6328,31 @@
         <v>106</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6049,34 +6360,34 @@
         <v>107</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6084,34 +6395,34 @@
         <v>108</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6119,34 +6430,34 @@
         <v>109</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6154,34 +6465,34 @@
         <v>110</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6189,34 +6500,34 @@
         <v>111</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6224,34 +6535,34 @@
         <v>112</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6259,34 +6570,34 @@
         <v>113</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6294,34 +6605,34 @@
         <v>114</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6329,37 +6640,37 @@
         <v>115</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="L24" s="1" t="s">
         <v>420</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>422</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="J24" s="5" t="s">
-        <v>423</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="L24" s="1" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6367,34 +6678,34 @@
         <v>116</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6402,34 +6713,34 @@
         <v>117</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6437,34 +6748,34 @@
         <v>118</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6472,34 +6783,34 @@
         <v>119</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="L28" s="1" t="s">
         <v>431</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="L28" s="1" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6507,34 +6818,34 @@
         <v>120</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6542,34 +6853,34 @@
         <v>129</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6577,34 +6888,34 @@
         <v>121</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6612,28 +6923,28 @@
         <v>122</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="29.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6641,37 +6952,37 @@
         <v>123</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>452</v>
+        <v>310</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>453</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="K33" s="5" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6679,34 +6990,34 @@
         <v>124</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6714,34 +7025,34 @@
         <v>125</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6749,34 +7060,34 @@
         <v>126</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6784,34 +7095,34 @@
         <v>127</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6819,34 +7130,34 @@
         <v>128</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6854,31 +7165,31 @@
         <v>130</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6886,37 +7197,37 @@
         <v>131</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>483</v>
+        <v>354</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>484</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J40" s="5" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6924,31 +7235,31 @@
         <v>132</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="K41" s="2"/>
     </row>
@@ -6989,496 +7300,496 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="C1" s="9" t="s">
         <v>490</v>
       </c>
+      <c r="C1" s="10" t="s">
+        <v>491</v>
+      </c>
       <c r="D1" s="3" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>493</v>
-      </c>
-      <c r="G1" s="9" t="s">
         <v>494</v>
       </c>
+      <c r="G1" s="10" t="s">
+        <v>495</v>
+      </c>
       <c r="H1" s="3" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="10" t="s">
-        <v>497</v>
+      <c r="C2" s="11" t="s">
+        <v>498</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="G2" s="9"/>
+        <v>126</v>
+      </c>
+      <c r="G2" s="10"/>
       <c r="H2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="11" t="s">
-        <v>500</v>
-      </c>
-      <c r="D3" s="11" t="s">
+      <c r="C3" s="12" t="s">
         <v>501</v>
       </c>
+      <c r="D3" s="12" t="s">
+        <v>502</v>
+      </c>
       <c r="E3" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="11" t="s">
-        <v>505</v>
+      <c r="C4" s="12" t="s">
+        <v>506</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>20</v>
@@ -7487,355 +7798,355 @@
         <v>20</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="G23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>563</v>
-      </c>
       <c r="E24" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="G24" s="3"/>
     </row>
     <row r="25" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>566</v>
-      </c>
-      <c r="D25" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="C25" s="12" t="s">
         <v>567</v>
       </c>
+      <c r="D25" s="12" t="s">
+        <v>568</v>
+      </c>
       <c r="E25" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>569</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>569</v>
+        <v>297</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>570</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>570</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>520</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>580</v>
+        <v>521</v>
+      </c>
+      <c r="H31" s="14" t="s">
+        <v>581</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>503</v>
-      </c>
-      <c r="H33" s="14" t="s">
-        <v>586</v>
+        <v>504</v>
+      </c>
+      <c r="H33" s="15" t="s">
+        <v>587</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7886,7 +8197,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -7895,16 +8206,16 @@
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7921,7 +8232,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>33</v>
@@ -7941,7 +8252,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>33</v>
@@ -7961,7 +8272,7 @@
         <v>2</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>33</v>
@@ -7981,7 +8292,7 @@
         <v>2</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>33</v>
@@ -8001,7 +8312,7 @@
         <v>2</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>33</v>
@@ -8021,7 +8332,7 @@
         <v>2</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>33</v>
@@ -8041,7 +8352,7 @@
         <v>3</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>33</v>
@@ -8061,7 +8372,7 @@
         <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>33</v>
@@ -8075,13 +8386,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>5</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>33</v>
@@ -8095,13 +8406,13 @@
         <v>10</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>5</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>33</v>
@@ -8115,13 +8426,13 @@
         <v>100</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>100</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>33</v>
@@ -8135,13 +8446,13 @@
         <v>101</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>101</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>33</v>
@@ -8155,13 +8466,13 @@
         <v>101</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>102</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>33</v>
@@ -8175,13 +8486,13 @@
         <v>101</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>103</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>33</v>
@@ -8195,13 +8506,13 @@
         <v>102</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>104</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>33</v>
@@ -8212,16 +8523,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="n">
-        <v>103</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>144</v>
+        <v>104</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>146</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>105</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>368</v>
+        <v>595</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>33</v>
@@ -8234,14 +8545,14 @@
       <c r="B18" s="1" t="n">
         <v>104</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>594</v>
+      <c r="C18" s="6" t="s">
+        <v>146</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>106</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>373</v>
+      <c r="E18" s="16" t="s">
+        <v>374</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>33</v>
@@ -8255,19 +8566,19 @@
         <v>105</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>107</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>33</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8278,19 +8589,19 @@
         <v>105</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D20" s="1" t="n">
         <v>108</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>33</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8301,13 +8612,13 @@
         <v>106</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D21" s="1" t="n">
         <v>109</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>33</v>
@@ -8321,19 +8632,19 @@
         <v>107</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D22" s="1" t="n">
         <v>107</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>33</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8344,13 +8655,13 @@
         <v>200</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D23" s="1" t="n">
         <v>110</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>33</v>
@@ -8364,13 +8675,13 @@
         <v>201</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D24" s="1" t="n">
         <v>111</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>33</v>
@@ -8384,19 +8695,19 @@
         <v>202</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D25" s="1" t="n">
         <v>107</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>33</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8407,13 +8718,13 @@
         <v>202</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D26" s="1" t="n">
         <v>108</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>33</v>
@@ -8427,13 +8738,13 @@
         <v>203</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D27" s="1" t="n">
         <v>112</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>33</v>
@@ -8447,13 +8758,13 @@
         <v>204</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D28" s="1" t="n">
         <v>113</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>33</v>
@@ -8467,16 +8778,16 @@
         <v>300</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D29" s="1" t="n">
         <v>114</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8487,13 +8798,13 @@
         <v>300</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D30" s="1" t="n">
         <v>115</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>33</v>
@@ -8507,13 +8818,13 @@
         <v>300</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D31" s="1" t="n">
         <v>116</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>33</v>
@@ -8527,13 +8838,13 @@
         <v>300</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D32" s="1" t="n">
         <v>117</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>33</v>
@@ -8547,13 +8858,13 @@
         <v>301</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D33" s="1" t="n">
         <v>107</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>33</v>
@@ -8567,13 +8878,13 @@
         <v>301</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D34" s="1" t="n">
         <v>118</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>33</v>
@@ -8587,13 +8898,13 @@
         <v>301</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D35" s="1" t="n">
         <v>119</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>34</v>
@@ -8607,13 +8918,13 @@
         <v>302</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D36" s="1" t="n">
         <v>120</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>33</v>
@@ -8627,13 +8938,13 @@
         <v>302</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D37" s="1" t="n">
         <v>129</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>33</v>
@@ -8647,13 +8958,13 @@
         <v>304</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D38" s="1" t="n">
         <v>128</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>33</v>
@@ -8667,13 +8978,13 @@
         <v>305</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D39" s="1" t="n">
         <v>121</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>33</v>
@@ -8687,13 +8998,13 @@
         <v>305</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D40" s="1" t="n">
         <v>122</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>33</v>
@@ -8707,13 +9018,13 @@
         <v>306</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D41" s="1" t="n">
         <v>121</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>33</v>
@@ -8727,13 +9038,13 @@
         <v>402</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D42" s="1" t="n">
         <v>123</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>33</v>
@@ -8747,13 +9058,13 @@
         <v>401</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D43" s="1" t="n">
         <v>124</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>33</v>
@@ -8767,19 +9078,19 @@
         <v>401</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D44" s="1" t="n">
         <v>125</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>34</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8790,13 +9101,13 @@
         <v>500</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D45" s="1" t="n">
         <v>6</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>33</v>
@@ -8810,13 +9121,13 @@
         <v>501</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D46" s="1" t="n">
         <v>126</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>33</v>
@@ -8830,13 +9141,13 @@
         <v>502</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D47" s="1" t="n">
         <v>127</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>33</v>
@@ -8850,13 +9161,13 @@
         <v>503</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D48" s="1" t="n">
         <v>3</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>33</v>
@@ -8870,13 +9181,13 @@
         <v>504</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D49" s="1" t="n">
         <v>3</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>33</v>
@@ -8890,13 +9201,13 @@
         <v>505</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D50" s="1" t="n">
         <v>7</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>33</v>
@@ -8910,13 +9221,13 @@
         <v>11</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D51" s="1" t="n">
         <v>130</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>33</v>
@@ -8927,16 +9238,16 @@
         <v>51</v>
       </c>
       <c r="B52" s="1" t="n">
-        <v>12</v>
+        <v>307</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D52" s="1" t="n">
         <v>131</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>33</v>
@@ -8947,16 +9258,16 @@
         <v>51</v>
       </c>
       <c r="B53" s="1" t="n">
-        <v>13</v>
+        <v>307</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D53" s="1" t="n">
         <v>131</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>33</v>
@@ -8989,19 +9300,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="32.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="87.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9011,14 +9322,14 @@
       <c r="B2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="15" t="s">
-        <v>611</v>
+      <c r="C2" s="17" t="s">
+        <v>612</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="F2" s="3"/>
       <c r="H2" s="1"/>
@@ -9028,16 +9339,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>613</v>
+        <v>123</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>614</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="F3" s="3"/>
       <c r="H3" s="1"/>
@@ -9047,16 +9358,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>615</v>
+        <v>168</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>616</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="F4" s="3"/>
       <c r="H4" s="1"/>
@@ -9066,16 +9377,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>617</v>
+        <v>161</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>618</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H5" s="1"/>
     </row>
@@ -9084,16 +9395,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>619</v>
+        <v>108</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>620</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H6" s="1"/>
     </row>
@@ -9102,16 +9413,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>621</v>
+        <v>249</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>622</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H7" s="1"/>
     </row>
@@ -9120,21 +9431,21 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>623</v>
+        <v>282</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>624</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H8" s="1"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="16"/>
+      <c r="B11" s="18"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="3"/>
@@ -9156,7 +9467,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="29.56"/>
@@ -9171,441 +9482,585 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>630</v>
-      </c>
-      <c r="C2" s="1" t="n">
+      <c r="B2" s="19" t="s">
+        <v>631</v>
+      </c>
+      <c r="C2" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>631</v>
-      </c>
-      <c r="F2" s="3" t="s">
+      <c r="E2" s="20" t="s">
         <v>632</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="F2" s="20" t="s">
         <v>633</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="G2" s="19" t="s">
         <v>634</v>
       </c>
+      <c r="H2" s="20" t="s">
+        <v>635</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>635</v>
-      </c>
-      <c r="C3" s="4" t="n">
+      <c r="B3" s="21" t="s">
+        <v>636</v>
+      </c>
+      <c r="C3" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>636</v>
-      </c>
-      <c r="F3" s="1" t="s">
+      <c r="E3" s="19" t="s">
         <v>637</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="F3" s="19" t="s">
         <v>638</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="G3" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="H3" s="19" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>640</v>
+      </c>
+      <c r="C4" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>641</v>
+      </c>
+      <c r="F4" s="19" t="s">
         <v>638</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
+      <c r="G4" s="20" t="s">
+        <v>642</v>
+      </c>
+      <c r="H4" s="20" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>644</v>
+      </c>
+      <c r="C5" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>645</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>633</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>646</v>
+      </c>
+      <c r="H5" s="20" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>648</v>
+      </c>
+      <c r="C6" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>649</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>650</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>651</v>
+      </c>
+      <c r="H6" s="19" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>652</v>
+      </c>
+      <c r="C7" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>653</v>
+      </c>
+      <c r="F7" s="22" t="s">
+        <v>650</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>654</v>
+      </c>
+      <c r="H7" s="19" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>655</v>
+      </c>
+      <c r="C8" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>656</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>633</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>657</v>
+      </c>
+      <c r="H8" s="19" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>658</v>
+      </c>
+      <c r="C9" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>639</v>
-      </c>
-      <c r="C4" s="1" t="n">
+      <c r="D9" s="22" t="s">
+        <v>168</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>659</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>650</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>660</v>
+      </c>
+      <c r="H9" s="19" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="19" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>661</v>
+      </c>
+      <c r="C10" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>168</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>662</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>650</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>663</v>
+      </c>
+      <c r="H10" s="19" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>664</v>
+      </c>
+      <c r="C11" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>665</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>638</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>666</v>
+      </c>
+      <c r="H11" s="19" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="19" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>667</v>
+      </c>
+      <c r="C12" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>668</v>
+      </c>
+      <c r="F12" s="22" t="s">
+        <v>650</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>669</v>
+      </c>
+      <c r="H12" s="19" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="41" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>670</v>
+      </c>
+      <c r="C13" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>671</v>
+      </c>
+      <c r="F13" s="22" t="s">
+        <v>650</v>
+      </c>
+      <c r="G13" s="19" t="s">
+        <v>672</v>
+      </c>
+      <c r="H13" s="19" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="19" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>673</v>
+      </c>
+      <c r="C14" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>674</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>638</v>
+      </c>
+      <c r="G14" s="19" t="s">
+        <v>675</v>
+      </c>
+      <c r="H14" s="20" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>677</v>
+      </c>
+      <c r="C15" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>678</v>
+      </c>
+      <c r="F15" s="22" t="s">
+        <v>650</v>
+      </c>
+      <c r="G15" s="19" t="s">
+        <v>679</v>
+      </c>
+      <c r="H15" s="20" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="19" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>681</v>
+      </c>
+      <c r="C16" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>682</v>
+      </c>
+      <c r="F16" s="20" t="s">
+        <v>633</v>
+      </c>
+      <c r="G16" s="19" t="s">
+        <v>683</v>
+      </c>
+      <c r="H16" s="19"/>
+    </row>
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="19" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>684</v>
+      </c>
+      <c r="C17" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>282</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>685</v>
+      </c>
+      <c r="F17" s="19" t="s">
+        <v>638</v>
+      </c>
+      <c r="G17" s="19" t="s">
+        <v>686</v>
+      </c>
+      <c r="H17" s="20" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="23" t="s">
+        <v>688</v>
+      </c>
+      <c r="C18" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D18" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>640</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>637</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>641</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
+    </row>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="25" t="s">
+        <v>689</v>
+      </c>
+      <c r="C19" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="24" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="23" t="s">
+        <v>690</v>
+      </c>
+      <c r="C20" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="24" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>691</v>
+      </c>
+      <c r="C21" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="24" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="27" t="s">
+        <v>692</v>
+      </c>
+      <c r="C22" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="28" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="29" t="s">
+        <v>693</v>
+      </c>
+      <c r="C23" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="30" t="s">
+        <v>695</v>
+      </c>
+      <c r="C24" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>643</v>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>644</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>632</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>645</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>647</v>
-      </c>
-      <c r="C6" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>648</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>649</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>650</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>651</v>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>649</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>654</v>
-      </c>
-      <c r="C8" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>655</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>632</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>656</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>657</v>
-      </c>
-      <c r="C9" s="1" t="n">
+      <c r="D24" s="31" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="32" t="s">
+        <v>696</v>
+      </c>
+      <c r="C25" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" s="31" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="33" t="s">
+        <v>697</v>
+      </c>
+      <c r="C26" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>658</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>649</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>659</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>660</v>
-      </c>
-      <c r="C10" s="1" t="n">
+      <c r="D26" s="34" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="35" t="s">
+        <v>681</v>
+      </c>
+      <c r="C27" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>661</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>649</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>662</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>663</v>
-      </c>
-      <c r="C11" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>664</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>637</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>665</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>666</v>
-      </c>
-      <c r="C12" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>667</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>649</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>668</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="41" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>669</v>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>670</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>649</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>671</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>672</v>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>673</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>637</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>674</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>676</v>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>677</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>649</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>678</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>680</v>
-      </c>
-      <c r="C16" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>681</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>632</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>683</v>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>684</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>637</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>685</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>686</v>
+      <c r="D27" s="34" t="s">
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -9635,156 +10090,156 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>687</v>
+        <v>698</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>688</v>
+        <v>699</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>689</v>
+        <v>700</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>690</v>
+        <v>701</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>691</v>
+        <v>702</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>692</v>
+        <v>703</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>693</v>
+        <v>704</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>694</v>
+        <v>705</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>691</v>
+        <v>702</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>695</v>
+        <v>706</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>696</v>
+        <v>707</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>697</v>
+        <v>708</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>691</v>
+        <v>702</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>698</v>
+        <v>709</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>699</v>
+        <v>710</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>700</v>
+        <v>711</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>691</v>
+        <v>702</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>701</v>
+        <v>712</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>702</v>
+        <v>713</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>203</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>703</v>
+        <v>714</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>704</v>
+        <v>715</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>703</v>
+        <v>714</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>706</v>
+        <v>717</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>707</v>
+        <v>718</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>708</v>
+        <v>719</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>691</v>
+        <v>702</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>709</v>
+        <v>720</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>710</v>
+        <v>721</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>711</v>
+        <v>722</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>703</v>
+        <v>714</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>712</v>
+        <v>723</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>713</v>
+        <v>724</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>714</v>
+        <v>725</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>691</v>
+        <v>702</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>715</v>
+        <v>726</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>716</v>
+        <v>727</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>717</v>
+        <v>728</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>691</v>
+        <v>702</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>718</v>
+        <v>729</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9837,11 +10292,15 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="1" width="38.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="25.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="38.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="38.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="33.27"/>
   </cols>
   <sheetData>
@@ -9853,16 +10312,16 @@
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>719</v>
+        <v>730</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>720</v>
+        <v>731</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>719</v>
+        <v>730</v>
       </c>
       <c r="H1" s="1"/>
       <c r="I1" s="4"/>
@@ -9876,16 +10335,16 @@
         <v>26</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H2" s="1"/>
       <c r="J2" s="1"/>
@@ -9897,17 +10356,17 @@
       <c r="B3" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C3" s="1" t="n">
-        <v>2</v>
+      <c r="C3" s="0" t="n">
+        <v>18</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="E3" s="1" t="n">
         <v>2</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H3" s="1"/>
       <c r="J3" s="1"/>
@@ -9919,17 +10378,17 @@
       <c r="B4" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="1" t="n">
-        <v>1</v>
+      <c r="C4" s="0" t="n">
+        <v>18</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H4" s="1"/>
       <c r="J4" s="1"/>
@@ -9942,16 +10401,16 @@
         <v>59</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>3</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H5" s="1"/>
       <c r="J5" s="1"/>
@@ -9963,17 +10422,17 @@
       <c r="B6" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C6" s="1" t="n">
-        <v>1</v>
+      <c r="C6" s="0" t="n">
+        <v>19</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H6" s="1"/>
       <c r="J6" s="1"/>
@@ -9986,16 +10445,16 @@
         <v>80</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H7" s="1"/>
       <c r="J7" s="1"/>
@@ -10008,16 +10467,16 @@
         <v>88</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>3</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H8" s="1"/>
       <c r="J8" s="1"/>
@@ -10030,60 +10489,60 @@
         <v>95</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>3</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H9" s="1"/>
       <c r="J9" s="1"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+      <c r="A10" s="1" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C10" s="1" t="n">
-        <v>4</v>
+        <v>110</v>
+      </c>
+      <c r="C10" s="0" t="n">
+        <v>19</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>721</v>
+        <v>732</v>
       </c>
       <c r="E10" s="1" t="n">
         <v>4</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>721</v>
+        <v>732</v>
       </c>
       <c r="H10" s="1"/>
       <c r="J10" s="1"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+      <c r="A11" s="1" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>721</v>
+        <v>732</v>
       </c>
       <c r="E11" s="1" t="n">
         <v>4</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>721</v>
+        <v>732</v>
       </c>
       <c r="H11" s="1"/>
       <c r="J11" s="1"/>
@@ -10093,19 +10552,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>722</v>
+        <v>733</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="E12" s="1" t="n">
         <v>3</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H12" s="1"/>
       <c r="J12" s="1"/>
@@ -10115,19 +10574,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>108</v>
+        <v>231</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>3</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H13" s="1"/>
       <c r="J13" s="1"/>
@@ -10137,19 +10596,19 @@
         <v>100</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>5</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="4"/>
@@ -10160,19 +10619,19 @@
         <v>101</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>5</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="4"/>
@@ -10183,19 +10642,19 @@
         <v>102</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E16" s="1" t="n">
         <v>6</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="4"/>
@@ -10206,19 +10665,19 @@
         <v>103</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E17" s="1" t="n">
         <v>6</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H17" s="1"/>
       <c r="J17" s="1"/>
@@ -10227,20 +10686,20 @@
       <c r="A18" s="1" t="n">
         <v>104</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>594</v>
+      <c r="B18" s="6" t="s">
+        <v>146</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E18" s="1" t="n">
         <v>6</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H18" s="1"/>
       <c r="J18" s="1"/>
@@ -10250,19 +10709,19 @@
         <v>105</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="E19" s="1" t="n">
         <v>7</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H19" s="1"/>
       <c r="J19" s="1"/>
@@ -10272,19 +10731,19 @@
         <v>106</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="E20" s="1" t="n">
         <v>7</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H20" s="1"/>
       <c r="J20" s="1"/>
@@ -10294,19 +10753,19 @@
         <v>107</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E21" s="1" t="n">
         <v>10</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10314,19 +10773,19 @@
         <v>200</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="E22" s="1" t="n">
         <v>8</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
@@ -10336,19 +10795,19 @@
         <v>201</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E23" s="1" t="n">
         <v>9</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10356,19 +10815,19 @@
         <v>202</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E24" s="1" t="n">
         <v>9</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10376,19 +10835,19 @@
         <v>203</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="E25" s="1" t="n">
         <v>9</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10396,19 +10855,19 @@
         <v>204</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E26" s="1" t="n">
         <v>8</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10416,19 +10875,19 @@
         <v>300</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E27" s="1" t="n">
         <v>10</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10436,19 +10895,19 @@
         <v>301</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>205</v>
+        <v>734</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E28" s="1" t="n">
         <v>10</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10456,19 +10915,19 @@
         <v>302</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C29" s="1" t="n">
         <v>11</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="E29" s="1" t="n">
         <v>11</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10476,19 +10935,19 @@
         <v>304</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="E30" s="1" t="n">
         <v>11</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10496,19 +10955,19 @@
         <v>305</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>723</v>
+        <v>735</v>
       </c>
       <c r="E31" s="1" t="n">
         <v>12</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>723</v>
+        <v>735</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10516,19 +10975,19 @@
         <v>306</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>723</v>
+        <v>735</v>
       </c>
       <c r="E32" s="1" t="n">
         <v>12</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>723</v>
+        <v>735</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10536,19 +10995,19 @@
         <v>401</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="E33" s="1" t="n">
         <v>15</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10556,19 +11015,19 @@
         <v>402</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C34" s="1" t="n">
         <v>15</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="E34" s="1" t="n">
         <v>15</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10576,19 +11035,19 @@
         <v>500</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="E35" s="1" t="n">
         <v>13</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10596,19 +11055,19 @@
         <v>501</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C36" s="1" t="n">
         <v>14</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E36" s="1" t="n">
         <v>14</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10616,19 +11075,19 @@
         <v>502</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C37" s="1" t="n">
         <v>14</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E37" s="1" t="n">
         <v>14</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10636,19 +11095,19 @@
         <v>503</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C38" s="1" t="n">
         <v>13</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="E38" s="1" t="n">
         <v>13</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10656,19 +11115,19 @@
         <v>504</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C39" s="1" t="n">
         <v>13</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="E39" s="1" t="n">
         <v>13</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10676,19 +11135,159 @@
         <v>505</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C40" s="1" t="n">
         <v>16</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>724</v>
+        <v>736</v>
       </c>
       <c r="E40" s="1" t="n">
         <v>16</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>724</v>
+        <v>736</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B43" s="23" t="s">
+        <v>688</v>
+      </c>
+      <c r="C43" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" s="24" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>689</v>
+      </c>
+      <c r="C44" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="24" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B45" s="23" t="s">
+        <v>690</v>
+      </c>
+      <c r="C45" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" s="24" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>691</v>
+      </c>
+      <c r="C46" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" s="24" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B47" s="27" t="s">
+        <v>692</v>
+      </c>
+      <c r="C47" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D47" s="28" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B48" s="29" t="s">
+        <v>693</v>
+      </c>
+      <c r="C48" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D48" s="28" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B49" s="30" t="s">
+        <v>695</v>
+      </c>
+      <c r="C49" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="D49" s="31" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B50" s="32" t="s">
+        <v>696</v>
+      </c>
+      <c r="C50" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="D50" s="31" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B51" s="33" t="s">
+        <v>697</v>
+      </c>
+      <c r="C51" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="D51" s="34" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B52" s="35" t="s">
+        <v>681</v>
+      </c>
+      <c r="C52" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="D52" s="34" t="s">
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -10717,19 +11316,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>725</v>
+        <v>737</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>726</v>
+        <v>738</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>727</v>
+        <v>739</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10740,13 +11339,13 @@
         <v>25</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>728</v>
+        <v>740</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>729</v>
+        <v>741</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>730</v>
+        <v>742</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="87.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10754,16 +11353,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>731</v>
+        <v>743</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>732</v>
+        <v>744</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>733</v>
+        <v>745</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="89.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10771,16 +11370,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>734</v>
+        <v>746</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>735</v>
+        <v>747</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>736</v>
+        <v>748</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10788,16 +11387,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>737</v>
+        <v>749</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>738</v>
+        <v>750</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>739</v>
+        <v>751</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>740</v>
+        <v>752</v>
       </c>
     </row>
   </sheetData>

--- a/fiches indicateurs.xlsx
+++ b/fiches indicateurs.xlsx
@@ -17,6 +17,7 @@
     <sheet name="vigilances" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="relation groupe objectifs" sheetId="8" state="visible" r:id="rId10"/>
     <sheet name="Familles" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Feuille10" sheetId="10" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">sources!$A$1:$L$38</definedName>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2046" uniqueCount="753">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2129" uniqueCount="753">
   <si>
     <t xml:space="preserve">fiche_indicateur</t>
   </si>
@@ -39,10 +40,10 @@
     <t xml:space="preserve">id_indicateur</t>
   </si>
   <si>
-    <t xml:space="preserve">Nom_theme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">famille_indicateur</t>
+    <t xml:space="preserve">enjeux-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Famille-indicateur-</t>
   </si>
   <si>
     <t xml:space="preserve">nom_indicateur</t>
@@ -471,23 +472,7 @@
     <t xml:space="preserve">Forte richesse en espèces menacées = criticité faible bien que enjeu fort (à confirmer)</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Espèces rares et menacées dont f</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">orêt sèche</t>
-    </r>
+    <t xml:space="preserve">Espèces rares et menacées dont forêt sèche</t>
   </si>
   <si>
     <t xml:space="preserve">Superficie des intersections des patchs de forêt sèche additionné aux zones potentielles de présence d’éspèces rares et menacées</t>
@@ -655,10 +640,7 @@
     <t xml:space="preserve">Données dispersées (provinces). Besoin typologie ICPE. Difficulté accès + structuration.</t>
   </si>
   <si>
-    <t xml:space="preserve">re</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Activité minière</t>
+    <t xml:space="preserve">Zone d’exploitation minière</t>
   </si>
   <si>
     <t xml:space="preserve">Surface occupée par les activités minières.</t>
@@ -1575,6 +1557,9 @@
 </t>
   </si>
   <si>
+    <t xml:space="preserve">Nom_theme</t>
+  </si>
+  <si>
     <t xml:space="preserve">Thématique</t>
   </si>
   <si>
@@ -1583,6 +1568,9 @@
   <si>
     <t xml:space="preserve">Enjeux AEP / Enjeux Environnementaux / Pressions Environnementales / Pressions Anthropiques / Vulnérabilité / Pressions Quantitatives / Pressions Qualitatives
 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">famille_indicateur</t>
   </si>
   <si>
     <t xml:space="preserve">Famille</t>
@@ -1923,6 +1911,9 @@
     <t xml:space="preserve">Libelle_objectif</t>
   </si>
   <si>
+    <t xml:space="preserve">id_famille</t>
+  </si>
+  <si>
     <t xml:space="preserve">Définition</t>
   </si>
   <si>
@@ -2157,13 +2148,13 @@
     <t xml:space="preserve">Importance captage</t>
   </si>
   <si>
-    <t xml:space="preserve">Niveau infrastrutures</t>
+    <t xml:space="preserve">Niveau infrastructures</t>
   </si>
   <si>
     <t xml:space="preserve">Vulnérabilité structurelle</t>
   </si>
   <si>
-    <t xml:space="preserve">Sécurité sanitaire et reglementaire</t>
+    <t xml:space="preserve">Sécurité sanitaire et règlementaire</t>
   </si>
   <si>
     <t xml:space="preserve">Zone naturelle</t>
@@ -2178,7 +2169,7 @@
     <t xml:space="preserve">Activités à risque </t>
   </si>
   <si>
-    <t xml:space="preserve">Infractrustures et usages</t>
+    <t xml:space="preserve">Infrastructures et usages</t>
   </si>
   <si>
     <t xml:space="preserve">Perturbations environnementales </t>
@@ -2292,16 +2283,10 @@
     <t xml:space="preserve">Statut foncier</t>
   </si>
   <si>
-    <t xml:space="preserve">Zone d’exploitation minière</t>
-  </si>
-  <si>
     <t xml:space="preserve">Infrastructures et risques de dégradation des eaux</t>
   </si>
   <si>
     <t xml:space="preserve">État sanitaire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id_famille</t>
   </si>
   <si>
     <t xml:space="preserve">nom_famille</t>
@@ -2356,7 +2341,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="11">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -2390,11 +2375,6 @@
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2557,7 +2537,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="34">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2582,19 +2562,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2614,19 +2590,15 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2650,55 +2622,55 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2915,7 +2887,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="38.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="14.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="45.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="29.44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="117.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="85.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="24.29"/>
@@ -3635,27 +3607,6 @@
       </c>
       <c r="W10" s="1"/>
     </row>
-    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0"/>
-      <c r="B11" s="0"/>
-      <c r="C11" s="0"/>
-      <c r="D11" s="0"/>
-      <c r="E11" s="0"/>
-      <c r="F11" s="0"/>
-      <c r="G11" s="0"/>
-      <c r="H11" s="0"/>
-      <c r="I11" s="0"/>
-      <c r="J11" s="0"/>
-      <c r="K11" s="0"/>
-      <c r="N11" s="0"/>
-      <c r="O11" s="0"/>
-      <c r="P11" s="0"/>
-      <c r="Q11" s="0"/>
-      <c r="R11" s="0"/>
-      <c r="S11" s="0"/>
-      <c r="U11" s="0"/>
-      <c r="V11" s="0"/>
-    </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
         <v>9</v>
@@ -4083,7 +4034,7 @@
       <c r="D18" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="2" t="s">
         <v>146</v>
       </c>
       <c r="F18" s="1" t="s">
@@ -4772,8 +4723,8 @@
       <c r="A28" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>202</v>
+      <c r="B28" s="1" t="n">
+        <v>301</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>161</v>
@@ -4782,25 +4733,25 @@
         <v>162</v>
       </c>
       <c r="E28" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="F28" s="1" t="s">
         <v>203</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>204</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>126</v>
+        <v>28</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>127</v>
       </c>
       <c r="J28" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="K28" s="1" t="s">
         <v>205</v>
-      </c>
-      <c r="K28" s="1" t="s">
-        <v>206</v>
       </c>
       <c r="L28" s="1" t="s">
         <v>130</v>
@@ -4818,7 +4769,7 @@
         <v>166</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="R28" s="1" t="s">
         <v>38</v>
@@ -4836,7 +4787,7 @@
         <v>132</v>
       </c>
       <c r="W28" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4853,10 +4804,10 @@
         <v>162</v>
       </c>
       <c r="E29" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="F29" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>210</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>28</v>
@@ -4868,10 +4819,10 @@
         <v>82</v>
       </c>
       <c r="J29" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="K29" s="1" t="s">
         <v>211</v>
-      </c>
-      <c r="K29" s="1" t="s">
-        <v>212</v>
       </c>
       <c r="L29" s="1" t="s">
         <v>130</v>
@@ -4889,7 +4840,7 @@
         <v>166</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R29" s="1" t="s">
         <v>38</v>
@@ -4907,7 +4858,7 @@
         <v>132</v>
       </c>
       <c r="W29" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4924,10 +4875,10 @@
         <v>162</v>
       </c>
       <c r="E30" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="F30" s="1" t="s">
         <v>215</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>216</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>28</v>
@@ -4939,10 +4890,10 @@
         <v>82</v>
       </c>
       <c r="J30" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="K30" s="1" t="s">
         <v>217</v>
-      </c>
-      <c r="K30" s="1" t="s">
-        <v>218</v>
       </c>
       <c r="L30" s="1" t="s">
         <v>130</v>
@@ -4960,7 +4911,7 @@
         <v>166</v>
       </c>
       <c r="Q30" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="R30" s="1" t="s">
         <v>38</v>
@@ -4978,7 +4929,7 @@
         <v>132</v>
       </c>
       <c r="W30" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4995,10 +4946,10 @@
         <v>162</v>
       </c>
       <c r="E31" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="F31" s="1" t="s">
         <v>221</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>222</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>28</v>
@@ -5010,10 +4961,10 @@
         <v>82</v>
       </c>
       <c r="J31" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="K31" s="1" t="s">
         <v>223</v>
-      </c>
-      <c r="K31" s="1" t="s">
-        <v>224</v>
       </c>
       <c r="L31" s="1" t="s">
         <v>130</v>
@@ -5031,7 +4982,7 @@
         <v>166</v>
       </c>
       <c r="Q31" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="R31" s="1" t="s">
         <v>38</v>
@@ -5063,10 +5014,10 @@
         <v>162</v>
       </c>
       <c r="E32" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="F32" s="1" t="s">
         <v>226</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>227</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>28</v>
@@ -5078,10 +5029,10 @@
         <v>46</v>
       </c>
       <c r="J32" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="K32" s="1" t="s">
         <v>228</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>229</v>
       </c>
       <c r="L32" s="1" t="s">
         <v>130</v>
@@ -5099,7 +5050,7 @@
         <v>166</v>
       </c>
       <c r="Q32" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="R32" s="1" t="s">
         <v>38</v>
@@ -5117,7 +5068,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="1" t="n">
         <v>307</v>
       </c>
@@ -5128,10 +5079,10 @@
         <v>162</v>
       </c>
       <c r="E33" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="F33" s="6" t="s">
         <v>231</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>232</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>28</v>
@@ -5141,7 +5092,7 @@
       </c>
       <c r="I33" s="5"/>
       <c r="J33" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K33" s="1" t="s">
         <v>129</v>
@@ -5190,10 +5141,10 @@
         <v>109</v>
       </c>
       <c r="E34" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="F34" s="1" t="s">
         <v>234</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>235</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>28</v>
@@ -5205,10 +5156,10 @@
         <v>127</v>
       </c>
       <c r="J34" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="K34" s="1" t="s">
         <v>236</v>
-      </c>
-      <c r="K34" s="1" t="s">
-        <v>237</v>
       </c>
       <c r="L34" s="1" t="s">
         <v>130</v>
@@ -5226,7 +5177,7 @@
         <v>166</v>
       </c>
       <c r="Q34" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="R34" s="1" t="s">
         <v>38</v>
@@ -5244,7 +5195,7 @@
         <v>132</v>
       </c>
       <c r="W34" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5261,10 +5212,10 @@
         <v>109</v>
       </c>
       <c r="E35" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="F35" s="3" t="s">
         <v>240</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>241</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>28</v>
@@ -5273,13 +5224,13 @@
         <v>28</v>
       </c>
       <c r="I35" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="J35" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="J35" s="1" t="s">
+      <c r="K35" s="1" t="s">
         <v>243</v>
-      </c>
-      <c r="K35" s="1" t="s">
-        <v>244</v>
       </c>
       <c r="L35" s="1" t="s">
         <v>130</v>
@@ -5291,13 +5242,13 @@
         <v>33</v>
       </c>
       <c r="O35" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="P35" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="P35" s="2" t="s">
-        <v>246</v>
-      </c>
       <c r="Q35" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="R35" s="1" t="s">
         <v>67</v>
@@ -5312,11 +5263,11 @@
         <v>107</v>
       </c>
       <c r="V35" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="W35" s="1"/>
       <c r="X35" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5327,16 +5278,16 @@
         <v>500</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>162</v>
       </c>
       <c r="E36" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="F36" s="1" t="s">
         <v>250</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>251</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>28</v>
@@ -5345,13 +5296,13 @@
         <v>28</v>
       </c>
       <c r="I36" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="J36" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="J36" s="1" t="s">
+      <c r="K36" s="1" t="s">
         <v>253</v>
-      </c>
-      <c r="K36" s="1" t="s">
-        <v>254</v>
       </c>
       <c r="L36" s="1" t="s">
         <v>193</v>
@@ -5363,13 +5314,13 @@
         <v>34</v>
       </c>
       <c r="O36" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="P36" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="P36" s="2" t="s">
-        <v>246</v>
-      </c>
       <c r="Q36" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="R36" s="1" t="s">
         <v>67</v>
@@ -5387,7 +5338,7 @@
         <v>132</v>
       </c>
       <c r="W36" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5398,16 +5349,16 @@
         <v>501</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>162</v>
       </c>
       <c r="E37" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="F37" s="1" t="s">
         <v>257</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>258</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>28</v>
@@ -5416,13 +5367,13 @@
         <v>126</v>
       </c>
       <c r="I37" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="J37" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="J37" s="1" t="s">
+      <c r="K37" s="1" t="s">
         <v>260</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>261</v>
       </c>
       <c r="L37" s="1" t="s">
         <v>130</v>
@@ -5440,7 +5391,7 @@
         <v>154</v>
       </c>
       <c r="Q37" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="R37" s="1" t="s">
         <v>38</v>
@@ -5458,7 +5409,7 @@
         <v>132</v>
       </c>
       <c r="W37" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5469,31 +5420,31 @@
         <v>502</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>162</v>
       </c>
       <c r="E38" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="F38" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="F38" s="1" t="s">
-        <v>265</v>
-      </c>
       <c r="G38" s="1" t="s">
-        <v>28</v>
+        <v>126</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>28</v>
       </c>
       <c r="I38" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="J38" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="J38" s="1" t="s">
+      <c r="K38" s="1" t="s">
         <v>267</v>
-      </c>
-      <c r="K38" s="1" t="s">
-        <v>268</v>
       </c>
       <c r="L38" s="1" t="s">
         <v>130</v>
@@ -5511,7 +5462,7 @@
         <v>154</v>
       </c>
       <c r="Q38" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="R38" s="1" t="s">
         <v>38</v>
@@ -5537,16 +5488,16 @@
         <v>503</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>162</v>
       </c>
       <c r="E39" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="F39" s="1" t="s">
         <v>270</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>271</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>28</v>
@@ -5558,10 +5509,10 @@
         <v>82</v>
       </c>
       <c r="J39" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="K39" s="1" t="s">
         <v>272</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>273</v>
       </c>
       <c r="L39" s="1" t="s">
         <v>32</v>
@@ -5579,7 +5530,7 @@
         <v>154</v>
       </c>
       <c r="Q39" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="R39" s="1" t="s">
         <v>38</v>
@@ -5597,7 +5548,7 @@
         <v>42</v>
       </c>
       <c r="W39" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5608,31 +5559,31 @@
         <v>504</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>162</v>
       </c>
       <c r="E40" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="F40" s="1" t="s">
         <v>276</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>277</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>126</v>
+        <v>28</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>54</v>
       </c>
       <c r="J40" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="K40" s="1" t="s">
         <v>278</v>
-      </c>
-      <c r="K40" s="1" t="s">
-        <v>279</v>
       </c>
       <c r="L40" s="1" t="s">
         <v>32</v>
@@ -5650,7 +5601,7 @@
         <v>166</v>
       </c>
       <c r="Q40" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="R40" s="1" t="s">
         <v>38</v>
@@ -5668,7 +5619,7 @@
         <v>42</v>
       </c>
       <c r="W40" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5679,16 +5630,16 @@
         <v>505</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>162</v>
       </c>
       <c r="E41" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="F41" s="1" t="s">
         <v>283</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>284</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>126</v>
@@ -5697,13 +5648,13 @@
         <v>28</v>
       </c>
       <c r="I41" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="J41" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="J41" s="1" t="s">
+      <c r="K41" s="1" t="s">
         <v>286</v>
-      </c>
-      <c r="K41" s="1" t="s">
-        <v>287</v>
       </c>
       <c r="L41" s="1" t="s">
         <v>32</v>
@@ -5718,10 +5669,10 @@
         <v>64</v>
       </c>
       <c r="P41" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q41" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="R41" s="1" t="s">
         <v>67</v>
@@ -5739,7 +5690,7 @@
         <v>69</v>
       </c>
       <c r="W41" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5753,10 +5704,10 @@
         <v>109</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>126</v>
@@ -5765,7 +5716,7 @@
         <v>28</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L42" s="1" t="s">
         <v>130</v>
@@ -5777,13 +5728,13 @@
         <v>33</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P42" s="1" t="s">
         <v>166</v>
       </c>
       <c r="Q42" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="R42" s="1" t="s">
         <v>38</v>
@@ -5801,16 +5752,475 @@
         <v>132</v>
       </c>
       <c r="W42" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="X42" s="1" t="s">
         <v>294</v>
-      </c>
-      <c r="X42" s="1" t="s">
-        <v>295</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>630</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>633</v>
+      </c>
+      <c r="C2" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>634</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>635</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>636</v>
+      </c>
+      <c r="H2" s="18" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>638</v>
+      </c>
+      <c r="C3" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>639</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>640</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>641</v>
+      </c>
+      <c r="H3" s="17" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="169.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>642</v>
+      </c>
+      <c r="C4" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>643</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>640</v>
+      </c>
+      <c r="G4" s="18" t="s">
+        <v>644</v>
+      </c>
+      <c r="H4" s="18" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>646</v>
+      </c>
+      <c r="C5" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>647</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>635</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>648</v>
+      </c>
+      <c r="H5" s="18" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="C6" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>651</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>652</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>653</v>
+      </c>
+      <c r="H6" s="17" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>654</v>
+      </c>
+      <c r="C7" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>655</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>652</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="H7" s="17" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>657</v>
+      </c>
+      <c r="C8" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>658</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>635</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="H8" s="17" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="C9" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>661</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>652</v>
+      </c>
+      <c r="G9" s="17" t="s">
+        <v>662</v>
+      </c>
+      <c r="H9" s="17" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>663</v>
+      </c>
+      <c r="C10" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>664</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>652</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>665</v>
+      </c>
+      <c r="H10" s="17" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>666</v>
+      </c>
+      <c r="C11" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>667</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>640</v>
+      </c>
+      <c r="G11" s="17" t="s">
+        <v>668</v>
+      </c>
+      <c r="H11" s="17" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>669</v>
+      </c>
+      <c r="C12" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>670</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>652</v>
+      </c>
+      <c r="G12" s="17" t="s">
+        <v>671</v>
+      </c>
+      <c r="H12" s="17" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="41" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>672</v>
+      </c>
+      <c r="C13" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>673</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>652</v>
+      </c>
+      <c r="G13" s="17" t="s">
+        <v>674</v>
+      </c>
+      <c r="H13" s="17" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>675</v>
+      </c>
+      <c r="C14" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>676</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>640</v>
+      </c>
+      <c r="G14" s="17" t="s">
+        <v>677</v>
+      </c>
+      <c r="H14" s="18" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>679</v>
+      </c>
+      <c r="C15" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>680</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>652</v>
+      </c>
+      <c r="G15" s="17" t="s">
+        <v>681</v>
+      </c>
+      <c r="H15" s="18" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>683</v>
+      </c>
+      <c r="C16" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>684</v>
+      </c>
+      <c r="F16" s="18" t="s">
+        <v>635</v>
+      </c>
+      <c r="G16" s="17" t="s">
+        <v>685</v>
+      </c>
+      <c r="H16" s="17"/>
+    </row>
+    <row r="17" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>686</v>
+      </c>
+      <c r="C17" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>281</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>687</v>
+      </c>
+      <c r="F17" s="17" t="s">
+        <v>640</v>
+      </c>
+      <c r="G17" s="17" t="s">
+        <v>688</v>
+      </c>
+      <c r="H17" s="18" t="s">
+        <v>689</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Page &amp;P</oddFooter>
@@ -5838,40 +6248,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>306</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5879,34 +6289,34 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>316</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5914,31 +6324,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H3" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>323</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5946,34 +6356,34 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="J4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>329</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5981,34 +6391,34 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="J5" s="1" t="s">
+      <c r="L5" s="1" t="s">
         <v>333</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6016,34 +6426,34 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="J6" s="1" t="s">
+      <c r="L6" s="1" t="s">
         <v>337</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6051,37 +6461,37 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="J7" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="J7" s="8" t="s">
+      <c r="K7" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="L7" s="1" t="s">
         <v>342</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6089,28 +6499,28 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="J8" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="J8" s="1" t="s">
+      <c r="L8" s="1" t="s">
         <v>345</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6118,34 +6528,34 @@
         <v>100</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="E9" s="1" t="s">
+      <c r="F9" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="H9" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="H9" s="1" t="s">
+      <c r="I9" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="I9" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="J9" s="3" t="s">
+      <c r="L9" s="1" t="s">
         <v>351</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6153,34 +6563,34 @@
         <v>101</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="E10" s="8" t="s">
         <v>354</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="E10" s="9" t="s">
+      <c r="F10" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="G10" s="1" t="s">
+      <c r="H10" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="J10" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="J10" s="1" t="s">
+      <c r="L10" s="1" t="s">
         <v>357</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6188,34 +6598,34 @@
         <v>102</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>361</v>
-      </c>
       <c r="H11" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="I11" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="I11" s="1" t="s">
-        <v>315</v>
-      </c>
       <c r="J11" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="L11" s="1" t="s">
         <v>357</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6223,34 +6633,34 @@
         <v>103</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="D12" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>364</v>
-      </c>
       <c r="H12" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="I12" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="I12" s="1" t="s">
-        <v>315</v>
-      </c>
       <c r="J12" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="L12" s="1" t="s">
         <v>357</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6258,34 +6668,34 @@
         <v>104</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="E13" s="1" t="s">
+      <c r="F13" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="J13" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="F13" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="J13" s="1" t="s">
+      <c r="L13" s="1" t="s">
         <v>367</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6293,34 +6703,34 @@
         <v>105</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="E14" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="J14" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="J14" s="1" t="s">
+      <c r="L14" s="1" t="s">
         <v>372</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6328,31 +6738,31 @@
         <v>106</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="E15" s="1" t="s">
+      <c r="F15" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="L15" s="1" t="s">
         <v>375</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6360,34 +6770,34 @@
         <v>107</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="D16" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="E16" s="1" t="s">
+      <c r="F16" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="J16" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="J16" s="1" t="s">
+      <c r="L16" s="1" t="s">
         <v>380</v>
-      </c>
-      <c r="L16" s="1" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6395,34 +6805,34 @@
         <v>108</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="D17" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="E17" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="F17" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="H17" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="F17" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="H17" s="1" t="s">
+      <c r="I17" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="J17" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="J17" s="1" t="s">
+      <c r="L17" s="1" t="s">
         <v>388</v>
-      </c>
-      <c r="L17" s="1" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6430,34 +6840,34 @@
         <v>109</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="D18" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E18" s="1" t="s">
+      <c r="F18" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="H18" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="F18" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="H18" s="1" t="s">
+      <c r="I18" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="J18" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="I18" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="J18" s="1" t="s">
+      <c r="L18" s="1" t="s">
         <v>394</v>
-      </c>
-      <c r="L18" s="1" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6465,34 +6875,34 @@
         <v>110</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="D19" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="E19" s="1" t="s">
+      <c r="F19" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="H19" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="F19" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="H19" s="1" t="s">
+      <c r="I19" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="J19" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="I19" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="J19" s="1" t="s">
+      <c r="L19" s="1" t="s">
         <v>400</v>
-      </c>
-      <c r="L19" s="1" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6500,34 +6910,34 @@
         <v>111</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="E20" s="1" t="s">
+      <c r="F20" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="J20" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="F20" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="J20" s="1" t="s">
+      <c r="L20" s="1" t="s">
         <v>404</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6535,34 +6945,34 @@
         <v>112</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="D21" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="E21" s="1" t="s">
+      <c r="F21" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G21" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="G21" s="1" t="s">
+      <c r="H21" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="J21" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="H21" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="J21" s="1" t="s">
+      <c r="L21" s="1" t="s">
         <v>410</v>
-      </c>
-      <c r="L21" s="1" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6570,34 +6980,34 @@
         <v>113</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="E22" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="J22" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="J22" s="1" t="s">
+      <c r="L22" s="1" t="s">
         <v>415</v>
-      </c>
-      <c r="L22" s="1" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6605,34 +7015,34 @@
         <v>114</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="E23" s="1" t="s">
+      <c r="F23" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="J23" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="F23" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="J23" s="1" t="s">
+      <c r="L23" s="1" t="s">
         <v>419</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6640,37 +7050,37 @@
         <v>115</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="E24" s="1" t="s">
+      <c r="F24" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="H24" s="4" t="s">
         <v>422</v>
       </c>
-      <c r="F24" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="H24" s="4" t="s">
+      <c r="I24" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="J24" s="5" t="s">
         <v>423</v>
       </c>
-      <c r="I24" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="J24" s="5" t="s">
+      <c r="K24" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="K24" s="1" t="s">
-        <v>425</v>
-      </c>
       <c r="L24" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6678,34 +7088,34 @@
         <v>116</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C25" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="G25" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>361</v>
-      </c>
       <c r="H25" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="I25" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="I25" s="1" t="s">
-        <v>315</v>
-      </c>
       <c r="J25" s="5" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6713,34 +7123,34 @@
         <v>117</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C26" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="G26" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>364</v>
-      </c>
       <c r="H26" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="I26" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="I26" s="1" t="s">
-        <v>315</v>
-      </c>
       <c r="J26" s="5" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6748,34 +7158,34 @@
         <v>118</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="E27" s="1" t="s">
+      <c r="F27" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="J27" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="F27" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="J27" s="1" t="s">
+      <c r="L27" s="1" t="s">
         <v>430</v>
-      </c>
-      <c r="L27" s="1" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6783,34 +7193,34 @@
         <v>119</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="C28" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="E28" s="1" t="s">
+      <c r="F28" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="J28" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="F28" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>434</v>
-      </c>
       <c r="L28" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6818,34 +7228,34 @@
         <v>120</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="D29" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="D29" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="E29" s="1" t="s">
+      <c r="F29" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="J29" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="F29" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="J29" s="1" t="s">
+      <c r="L29" s="1" t="s">
         <v>438</v>
-      </c>
-      <c r="L29" s="1" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6853,34 +7263,34 @@
         <v>129</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="C30" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="E30" s="1" t="s">
+      <c r="F30" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="H30" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="F30" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="H30" s="1" t="s">
+      <c r="I30" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="J30" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="I30" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="J30" s="1" t="s">
+      <c r="L30" s="1" t="s">
         <v>443</v>
-      </c>
-      <c r="L30" s="1" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6888,34 +7298,34 @@
         <v>121</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="E31" s="1" t="s">
+      <c r="F31" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="J31" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="F31" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="J31" s="1" t="s">
+      <c r="L31" s="1" t="s">
         <v>447</v>
-      </c>
-      <c r="L31" s="1" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6923,28 +7333,28 @@
         <v>122</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="J32" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="C32" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="J32" s="1" t="s">
+      <c r="L32" s="1" t="s">
         <v>450</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="29.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6952,37 +7362,37 @@
         <v>123</v>
       </c>
       <c r="B33" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="E33" s="8" t="s">
         <v>452</v>
       </c>
-      <c r="C33" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="E33" s="9" t="s">
+      <c r="F33" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="J33" s="5" t="s">
         <v>453</v>
       </c>
-      <c r="F33" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="J33" s="5" t="s">
+      <c r="K33" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="K33" s="5" t="s">
+      <c r="L33" s="1" t="s">
         <v>455</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6990,34 +7400,34 @@
         <v>124</v>
       </c>
       <c r="B34" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="E34" s="1" t="s">
+      <c r="F34" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="J34" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="F34" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="J34" s="1" t="s">
+      <c r="L34" s="1" t="s">
         <v>459</v>
-      </c>
-      <c r="L34" s="1" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7025,34 +7435,34 @@
         <v>125</v>
       </c>
       <c r="B35" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="E35" s="1" t="s">
+      <c r="F35" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="J35" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="F35" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="I35" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="J35" s="1" t="s">
+      <c r="L35" s="1" t="s">
         <v>463</v>
-      </c>
-      <c r="L35" s="1" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7060,34 +7470,34 @@
         <v>126</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="D36" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="D36" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="E36" s="1" t="s">
+      <c r="F36" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="J36" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="F36" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="J36" s="1" t="s">
+      <c r="L36" s="1" t="s">
         <v>468</v>
-      </c>
-      <c r="L36" s="1" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7095,34 +7505,34 @@
         <v>127</v>
       </c>
       <c r="B37" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="C37" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="E37" s="1" t="s">
+      <c r="F37" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="H37" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="F37" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="G37" s="1" t="s">
+      <c r="I37" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="H37" s="1" t="s">
+      <c r="J37" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="I37" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="J37" s="1" t="s">
+      <c r="L37" s="1" t="s">
         <v>473</v>
-      </c>
-      <c r="L37" s="1" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7130,34 +7540,34 @@
         <v>128</v>
       </c>
       <c r="B38" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="D38" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="H38" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="D38" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="H38" s="1" t="s">
+      <c r="I38" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="J38" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="I38" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="J38" s="1" t="s">
+      <c r="L38" s="1" t="s">
         <v>478</v>
-      </c>
-      <c r="L38" s="1" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7165,31 +7575,31 @@
         <v>130</v>
       </c>
       <c r="B39" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="C39" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="E39" s="1" t="s">
+      <c r="F39" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="L39" s="3" t="s">
         <v>481</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="H39" s="4" t="s">
-        <v>423</v>
-      </c>
-      <c r="I39" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="L39" s="3" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7197,37 +7607,37 @@
         <v>131</v>
       </c>
       <c r="B40" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="E40" s="8" t="s">
         <v>483</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="E40" s="9" t="s">
+      <c r="F40" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="J40" s="5" t="s">
         <v>484</v>
       </c>
-      <c r="F40" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="I40" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="J40" s="5" t="s">
+      <c r="K40" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="K40" s="2" t="s">
+      <c r="L40" s="1" t="s">
         <v>486</v>
-      </c>
-      <c r="L40" s="1" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7235,31 +7645,31 @@
         <v>132</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="K41" s="2"/>
     </row>
@@ -7300,99 +7710,99 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="9" t="s">
         <v>490</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="D1" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="9" t="s">
         <v>494</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="H1" s="3" t="s">
         <v>495</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="10" t="s">
+        <v>497</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="1" t="s">
         <v>499</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>500</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="G2" s="10"/>
+      <c r="G2" s="9"/>
       <c r="H2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="11" t="s">
+        <v>500</v>
+      </c>
+      <c r="D3" s="11" t="s">
         <v>501</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="E3" s="1" t="s">
         <v>502</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>503</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G3" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>504</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="12" t="s">
+        <v>505</v>
+      </c>
+      <c r="C4" s="11" t="s">
         <v>506</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>507</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>508</v>
@@ -7400,396 +7810,396 @@
     </row>
     <row r="5" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>3</v>
+        <v>509</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>126</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>20</v>
@@ -7798,62 +8208,62 @@
         <v>20</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>126</v>
@@ -7862,19 +8272,19 @@
     </row>
     <row r="24" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>565</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>564</v>
-      </c>
       <c r="E24" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>126</v>
@@ -7883,270 +8293,270 @@
     </row>
     <row r="25" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>567</v>
-      </c>
-      <c r="D25" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="C25" s="11" t="s">
         <v>568</v>
       </c>
+      <c r="D25" s="11" t="s">
+        <v>569</v>
+      </c>
       <c r="E25" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="C26" s="13" t="s">
-        <v>570</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>570</v>
+        <v>296</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>571</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>571</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>126</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>126</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>521</v>
-      </c>
-      <c r="H31" s="14" t="s">
-        <v>581</v>
+        <v>522</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>582</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>504</v>
-      </c>
-      <c r="H33" s="15" t="s">
-        <v>587</v>
+        <v>503</v>
+      </c>
+      <c r="H33" s="14" t="s">
+        <v>588</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8197,7 +8607,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -8206,16 +8616,16 @@
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>296</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>297</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8232,7 +8642,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>33</v>
@@ -8252,7 +8662,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>33</v>
@@ -8272,7 +8682,7 @@
         <v>2</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>33</v>
@@ -8292,7 +8702,7 @@
         <v>2</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>33</v>
@@ -8312,7 +8722,7 @@
         <v>2</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>33</v>
@@ -8332,7 +8742,7 @@
         <v>2</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>33</v>
@@ -8352,7 +8762,7 @@
         <v>3</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>33</v>
@@ -8372,7 +8782,7 @@
         <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>33</v>
@@ -8392,7 +8802,7 @@
         <v>5</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>33</v>
@@ -8412,7 +8822,7 @@
         <v>5</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>33</v>
@@ -8432,7 +8842,7 @@
         <v>100</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>33</v>
@@ -8452,7 +8862,7 @@
         <v>101</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>33</v>
@@ -8472,7 +8882,7 @@
         <v>102</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>33</v>
@@ -8492,7 +8902,7 @@
         <v>103</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>33</v>
@@ -8512,7 +8922,7 @@
         <v>104</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>33</v>
@@ -8525,14 +8935,14 @@
       <c r="B17" s="1" t="n">
         <v>104</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="2" t="s">
         <v>146</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>105</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>33</v>
@@ -8545,14 +8955,14 @@
       <c r="B18" s="1" t="n">
         <v>104</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="2" t="s">
         <v>146</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>106</v>
       </c>
-      <c r="E18" s="16" t="s">
-        <v>374</v>
+      <c r="E18" s="2" t="s">
+        <v>373</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>33</v>
@@ -8572,13 +8982,13 @@
         <v>107</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>33</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8595,13 +9005,13 @@
         <v>108</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>33</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8618,7 +9028,7 @@
         <v>109</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>33</v>
@@ -8638,13 +9048,13 @@
         <v>107</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>33</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8661,7 +9071,7 @@
         <v>110</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>33</v>
@@ -8681,7 +9091,7 @@
         <v>111</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>33</v>
@@ -8701,13 +9111,13 @@
         <v>107</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>33</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8724,7 +9134,7 @@
         <v>108</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>33</v>
@@ -8744,7 +9154,7 @@
         <v>112</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>33</v>
@@ -8764,7 +9174,7 @@
         <v>113</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>33</v>
@@ -8784,7 +9194,7 @@
         <v>114</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>126</v>
@@ -8804,7 +9214,7 @@
         <v>115</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>33</v>
@@ -8824,7 +9234,7 @@
         <v>116</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>33</v>
@@ -8844,7 +9254,7 @@
         <v>117</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>33</v>
@@ -8858,13 +9268,13 @@
         <v>301</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D33" s="1" t="n">
         <v>107</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>33</v>
@@ -8878,13 +9288,13 @@
         <v>301</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D34" s="1" t="n">
         <v>118</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>33</v>
@@ -8898,13 +9308,13 @@
         <v>301</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D35" s="1" t="n">
         <v>119</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>34</v>
@@ -8918,13 +9328,13 @@
         <v>302</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D36" s="1" t="n">
         <v>120</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>33</v>
@@ -8938,13 +9348,13 @@
         <v>302</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D37" s="1" t="n">
         <v>129</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>33</v>
@@ -8958,13 +9368,13 @@
         <v>304</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D38" s="1" t="n">
         <v>128</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>33</v>
@@ -8978,13 +9388,13 @@
         <v>305</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D39" s="1" t="n">
         <v>121</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>33</v>
@@ -8998,13 +9408,13 @@
         <v>305</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D40" s="1" t="n">
         <v>122</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>33</v>
@@ -9018,13 +9428,13 @@
         <v>306</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D41" s="1" t="n">
         <v>121</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>33</v>
@@ -9038,13 +9448,13 @@
         <v>402</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D42" s="1" t="n">
         <v>123</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>33</v>
@@ -9058,13 +9468,13 @@
         <v>401</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D43" s="1" t="n">
         <v>124</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>33</v>
@@ -9078,19 +9488,19 @@
         <v>401</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D44" s="1" t="n">
         <v>125</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>34</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9101,13 +9511,13 @@
         <v>500</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D45" s="1" t="n">
         <v>6</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>33</v>
@@ -9121,13 +9531,13 @@
         <v>501</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D46" s="1" t="n">
         <v>126</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>33</v>
@@ -9141,13 +9551,13 @@
         <v>502</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D47" s="1" t="n">
         <v>127</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>33</v>
@@ -9161,13 +9571,13 @@
         <v>503</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D48" s="1" t="n">
         <v>3</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>33</v>
@@ -9181,13 +9591,13 @@
         <v>504</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D49" s="1" t="n">
         <v>3</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>33</v>
@@ -9201,13 +9611,13 @@
         <v>505</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D50" s="1" t="n">
         <v>7</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>33</v>
@@ -9221,13 +9631,13 @@
         <v>11</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D51" s="1" t="n">
         <v>130</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>33</v>
@@ -9241,13 +9651,13 @@
         <v>307</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D52" s="1" t="n">
         <v>131</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>33</v>
@@ -9261,13 +9671,13 @@
         <v>307</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D53" s="1" t="n">
         <v>131</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>33</v>
@@ -9290,29 +9700,32 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="1" width="28.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="42.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="46.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="1" width="28.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="42.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="46.25"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="32.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>505</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>509</v>
+        <v>612</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>611</v>
+        <v>510</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>613</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="87.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9322,17 +9735,20 @@
       <c r="B2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="17" t="s">
-        <v>612</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="C2" s="15" t="s">
+        <v>614</v>
+      </c>
+      <c r="D2" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>613</v>
-      </c>
-      <c r="F2" s="3"/>
-      <c r="H2" s="1"/>
+      <c r="F2" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="G2" s="3"/>
+      <c r="I2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
@@ -9341,17 +9757,20 @@
       <c r="B3" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C3" s="17" t="s">
-        <v>614</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="C3" s="15" t="s">
+        <v>616</v>
+      </c>
+      <c r="D3" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>615</v>
-      </c>
-      <c r="F3" s="3"/>
-      <c r="H3" s="1"/>
+      <c r="F3" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="G3" s="3"/>
+      <c r="I3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
@@ -9360,17 +9779,20 @@
       <c r="B4" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C4" s="17" t="s">
-        <v>616</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="C4" s="15" t="s">
+        <v>618</v>
+      </c>
+      <c r="D4" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>617</v>
-      </c>
-      <c r="F4" s="3"/>
-      <c r="H4" s="1"/>
+      <c r="F4" s="3" t="s">
+        <v>619</v>
+      </c>
+      <c r="G4" s="3"/>
+      <c r="I4" s="1"/>
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
@@ -9379,16 +9801,19 @@
       <c r="B5" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="C5" s="17" t="s">
-        <v>618</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="C5" s="15" t="s">
+        <v>620</v>
+      </c>
+      <c r="D5" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>619</v>
-      </c>
-      <c r="H5" s="1"/>
+      <c r="F5" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="I5" s="1"/>
     </row>
     <row r="6" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
@@ -9397,59 +9822,69 @@
       <c r="B6" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C6" s="17" t="s">
-        <v>620</v>
-      </c>
-      <c r="D6" s="1" t="s">
+      <c r="C6" s="15" t="s">
+        <v>622</v>
+      </c>
+      <c r="D6" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>621</v>
-      </c>
-      <c r="H6" s="1"/>
+      <c r="F6" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="I6" s="1"/>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>622</v>
-      </c>
-      <c r="D7" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>624</v>
+      </c>
+      <c r="D7" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>623</v>
-      </c>
-      <c r="H7" s="1"/>
+      <c r="F7" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="I7" s="1"/>
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>624</v>
-      </c>
-      <c r="D8" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>626</v>
+      </c>
+      <c r="D8" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>625</v>
-      </c>
-      <c r="H8" s="1"/>
+      <c r="F8" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="I8" s="1"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="18"/>
+      <c r="B11" s="16"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -9482,455 +9917,455 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>630</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>633</v>
+      </c>
+      <c r="C2" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>634</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>635</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>636</v>
+      </c>
+      <c r="H2" s="18" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>628</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>629</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="19" t="n">
+      <c r="B3" s="19" t="s">
+        <v>638</v>
+      </c>
+      <c r="C3" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="19" t="s">
-        <v>631</v>
-      </c>
-      <c r="C2" s="19" t="n">
+      <c r="D3" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>639</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>640</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>641</v>
+      </c>
+      <c r="H3" s="17" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>642</v>
+      </c>
+      <c r="C4" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D4" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="20" t="s">
-        <v>632</v>
-      </c>
-      <c r="F2" s="20" t="s">
-        <v>633</v>
-      </c>
-      <c r="G2" s="19" t="s">
-        <v>634</v>
-      </c>
-      <c r="H2" s="20" t="s">
+      <c r="E4" s="18" t="s">
+        <v>643</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>640</v>
+      </c>
+      <c r="G4" s="18" t="s">
+        <v>644</v>
+      </c>
+      <c r="H4" s="18" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>646</v>
+      </c>
+      <c r="C5" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>647</v>
+      </c>
+      <c r="F5" s="18" t="s">
         <v>635</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="19" t="n">
+      <c r="G5" s="17" t="s">
+        <v>648</v>
+      </c>
+      <c r="H5" s="18" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="C6" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="21" t="s">
-        <v>636</v>
-      </c>
-      <c r="C3" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>637</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>638</v>
-      </c>
-      <c r="G3" s="19" t="s">
-        <v>639</v>
-      </c>
-      <c r="H3" s="19" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="n">
+      <c r="D6" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>651</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>652</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>653</v>
+      </c>
+      <c r="H6" s="17" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>654</v>
+      </c>
+      <c r="C7" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>655</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>652</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="H7" s="17" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>657</v>
+      </c>
+      <c r="C8" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>658</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>635</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>659</v>
+      </c>
+      <c r="H8" s="17" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="C9" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="D9" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>661</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>652</v>
+      </c>
+      <c r="G9" s="17" t="s">
+        <v>662</v>
+      </c>
+      <c r="H9" s="17" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>663</v>
+      </c>
+      <c r="C10" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>664</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>652</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>665</v>
+      </c>
+      <c r="H10" s="17" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>666</v>
+      </c>
+      <c r="C11" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>667</v>
+      </c>
+      <c r="F11" s="17" t="s">
         <v>640</v>
       </c>
-      <c r="C4" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="20" t="s">
-        <v>641</v>
-      </c>
-      <c r="F4" s="19" t="s">
-        <v>638</v>
-      </c>
-      <c r="G4" s="20" t="s">
-        <v>642</v>
-      </c>
-      <c r="H4" s="20" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="n">
+      <c r="G11" s="17" t="s">
+        <v>668</v>
+      </c>
+      <c r="H11" s="17" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>669</v>
+      </c>
+      <c r="C12" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="19" t="s">
-        <v>644</v>
-      </c>
-      <c r="C5" s="19" t="n">
+      <c r="D12" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>670</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>652</v>
+      </c>
+      <c r="G12" s="17" t="s">
+        <v>671</v>
+      </c>
+      <c r="H12" s="17" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="41" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>672</v>
+      </c>
+      <c r="C13" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>673</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>652</v>
+      </c>
+      <c r="G13" s="17" t="s">
+        <v>674</v>
+      </c>
+      <c r="H13" s="17" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>675</v>
+      </c>
+      <c r="C14" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>676</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>640</v>
+      </c>
+      <c r="G14" s="17" t="s">
+        <v>677</v>
+      </c>
+      <c r="H14" s="18" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>679</v>
+      </c>
+      <c r="C15" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>680</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>652</v>
+      </c>
+      <c r="G15" s="17" t="s">
+        <v>681</v>
+      </c>
+      <c r="H15" s="18" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>683</v>
+      </c>
+      <c r="C16" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D16" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="E5" s="19" t="s">
-        <v>645</v>
-      </c>
-      <c r="F5" s="20" t="s">
-        <v>633</v>
-      </c>
-      <c r="G5" s="19" t="s">
-        <v>646</v>
-      </c>
-      <c r="H5" s="20" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>648</v>
-      </c>
-      <c r="C6" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>649</v>
-      </c>
-      <c r="F6" s="22" t="s">
-        <v>650</v>
-      </c>
-      <c r="G6" s="19" t="s">
-        <v>651</v>
-      </c>
-      <c r="H6" s="19" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>652</v>
-      </c>
-      <c r="C7" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>653</v>
-      </c>
-      <c r="F7" s="22" t="s">
-        <v>650</v>
-      </c>
-      <c r="G7" s="19" t="s">
-        <v>654</v>
-      </c>
-      <c r="H7" s="19" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="n">
+      <c r="E16" s="17" t="s">
+        <v>684</v>
+      </c>
+      <c r="F16" s="18" t="s">
+        <v>635</v>
+      </c>
+      <c r="G16" s="17" t="s">
+        <v>685</v>
+      </c>
+      <c r="H16" s="17"/>
+    </row>
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>686</v>
+      </c>
+      <c r="C17" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="19" t="s">
-        <v>655</v>
-      </c>
-      <c r="C8" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>656</v>
-      </c>
-      <c r="F8" s="20" t="s">
-        <v>633</v>
-      </c>
-      <c r="G8" s="19" t="s">
-        <v>657</v>
-      </c>
-      <c r="H8" s="19" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>658</v>
-      </c>
-      <c r="C9" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="D9" s="22" t="s">
-        <v>168</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>659</v>
-      </c>
-      <c r="F9" s="22" t="s">
-        <v>650</v>
-      </c>
-      <c r="G9" s="19" t="s">
-        <v>660</v>
-      </c>
-      <c r="H9" s="19" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="19" t="s">
-        <v>661</v>
-      </c>
-      <c r="C10" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="D10" s="22" t="s">
-        <v>168</v>
-      </c>
-      <c r="E10" s="19" t="s">
-        <v>662</v>
-      </c>
-      <c r="F10" s="22" t="s">
-        <v>650</v>
-      </c>
-      <c r="G10" s="19" t="s">
-        <v>663</v>
-      </c>
-      <c r="H10" s="19" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>664</v>
-      </c>
-      <c r="C11" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="D11" s="20" t="s">
-        <v>161</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>665</v>
-      </c>
-      <c r="F11" s="19" t="s">
-        <v>638</v>
-      </c>
-      <c r="G11" s="19" t="s">
-        <v>666</v>
-      </c>
-      <c r="H11" s="19" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>667</v>
-      </c>
-      <c r="C12" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>161</v>
-      </c>
-      <c r="E12" s="19" t="s">
-        <v>668</v>
-      </c>
-      <c r="F12" s="22" t="s">
-        <v>650</v>
-      </c>
-      <c r="G12" s="19" t="s">
-        <v>669</v>
-      </c>
-      <c r="H12" s="19" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="41" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="20" t="s">
-        <v>670</v>
-      </c>
-      <c r="C13" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>161</v>
-      </c>
-      <c r="E13" s="20" t="s">
-        <v>671</v>
-      </c>
-      <c r="F13" s="22" t="s">
-        <v>650</v>
-      </c>
-      <c r="G13" s="19" t="s">
-        <v>672</v>
-      </c>
-      <c r="H13" s="19" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>673</v>
-      </c>
-      <c r="C14" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>249</v>
-      </c>
-      <c r="E14" s="19" t="s">
-        <v>674</v>
-      </c>
-      <c r="F14" s="19" t="s">
-        <v>638</v>
-      </c>
-      <c r="G14" s="19" t="s">
-        <v>675</v>
-      </c>
-      <c r="H14" s="20" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="20" t="s">
-        <v>677</v>
-      </c>
-      <c r="C15" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="D15" s="19" t="s">
-        <v>249</v>
-      </c>
-      <c r="E15" s="20" t="s">
-        <v>678</v>
-      </c>
-      <c r="F15" s="22" t="s">
-        <v>650</v>
-      </c>
-      <c r="G15" s="19" t="s">
-        <v>679</v>
-      </c>
-      <c r="H15" s="20" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="19" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>681</v>
-      </c>
-      <c r="C16" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="D16" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="E16" s="19" t="s">
-        <v>682</v>
-      </c>
-      <c r="F16" s="20" t="s">
-        <v>633</v>
-      </c>
-      <c r="G16" s="19" t="s">
-        <v>683</v>
-      </c>
-      <c r="H16" s="19"/>
-    </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="19" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>684</v>
-      </c>
-      <c r="C17" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="D17" s="19" t="s">
-        <v>282</v>
-      </c>
-      <c r="E17" s="20" t="s">
-        <v>685</v>
-      </c>
-      <c r="F17" s="19" t="s">
-        <v>638</v>
-      </c>
-      <c r="G17" s="19" t="s">
-        <v>686</v>
-      </c>
-      <c r="H17" s="20" t="s">
+      <c r="D17" s="17" t="s">
+        <v>281</v>
+      </c>
+      <c r="E17" s="18" t="s">
         <v>687</v>
+      </c>
+      <c r="F17" s="17" t="s">
+        <v>640</v>
+      </c>
+      <c r="G17" s="17" t="s">
+        <v>688</v>
+      </c>
+      <c r="H17" s="18" t="s">
+        <v>689</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="23" t="s">
-        <v>688</v>
-      </c>
-      <c r="C18" s="24" t="n">
+      <c r="B18" s="21" t="s">
+        <v>690</v>
+      </c>
+      <c r="C18" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="24" t="s">
+      <c r="D18" s="22" t="s">
         <v>24</v>
       </c>
     </row>
@@ -9938,13 +10373,13 @@
       <c r="A19" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="25" t="s">
-        <v>689</v>
-      </c>
-      <c r="C19" s="24" t="n">
+      <c r="B19" s="23" t="s">
+        <v>691</v>
+      </c>
+      <c r="C19" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="24" t="s">
+      <c r="D19" s="22" t="s">
         <v>24</v>
       </c>
     </row>
@@ -9952,13 +10387,13 @@
       <c r="A20" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="23" t="s">
-        <v>690</v>
-      </c>
-      <c r="C20" s="24" t="n">
+      <c r="B20" s="21" t="s">
+        <v>692</v>
+      </c>
+      <c r="C20" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="24" t="s">
+      <c r="D20" s="22" t="s">
         <v>24</v>
       </c>
     </row>
@@ -9966,13 +10401,13 @@
       <c r="A21" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="26" t="s">
-        <v>691</v>
-      </c>
-      <c r="C21" s="24" t="n">
+      <c r="B21" s="24" t="s">
+        <v>693</v>
+      </c>
+      <c r="C21" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="24" t="s">
+      <c r="D21" s="22" t="s">
         <v>24</v>
       </c>
     </row>
@@ -9980,13 +10415,13 @@
       <c r="A22" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="27" t="s">
-        <v>692</v>
-      </c>
-      <c r="C22" s="28" t="n">
+      <c r="B22" s="25" t="s">
+        <v>694</v>
+      </c>
+      <c r="C22" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="D22" s="28" t="s">
+      <c r="D22" s="26" t="s">
         <v>123</v>
       </c>
     </row>
@@ -9994,30 +10429,30 @@
       <c r="A23" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="29" t="s">
-        <v>693</v>
-      </c>
-      <c r="C23" s="28" t="n">
+      <c r="B23" s="27" t="s">
+        <v>695</v>
+      </c>
+      <c r="C23" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="28" t="s">
+      <c r="D23" s="26" t="s">
         <v>123</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="30" t="s">
-        <v>695</v>
-      </c>
-      <c r="C24" s="31" t="n">
+      <c r="B24" s="28" t="s">
+        <v>697</v>
+      </c>
+      <c r="C24" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="D24" s="31" t="s">
+      <c r="D24" s="29" t="s">
         <v>161</v>
       </c>
     </row>
@@ -10025,13 +10460,13 @@
       <c r="A25" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="32" t="s">
-        <v>696</v>
-      </c>
-      <c r="C25" s="31" t="n">
+      <c r="B25" s="30" t="s">
+        <v>698</v>
+      </c>
+      <c r="C25" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="D25" s="31" t="s">
+      <c r="D25" s="29" t="s">
         <v>161</v>
       </c>
     </row>
@@ -10039,13 +10474,13 @@
       <c r="A26" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="33" t="s">
-        <v>697</v>
-      </c>
-      <c r="C26" s="34" t="n">
+      <c r="B26" s="31" t="s">
+        <v>699</v>
+      </c>
+      <c r="C26" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="D26" s="34" t="s">
+      <c r="D26" s="32" t="s">
         <v>168</v>
       </c>
     </row>
@@ -10053,13 +10488,13 @@
       <c r="A27" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="35" t="s">
-        <v>681</v>
-      </c>
-      <c r="C27" s="34" t="n">
+      <c r="B27" s="33" t="s">
+        <v>683</v>
+      </c>
+      <c r="C27" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="D27" s="34" t="s">
+      <c r="D27" s="32" t="s">
         <v>168</v>
       </c>
     </row>
@@ -10090,156 +10525,156 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>704</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>705</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>702</v>
-      </c>
       <c r="D3" s="1" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>203</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10292,7 +10727,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.18"/>
@@ -10312,16 +10747,16 @@
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="H1" s="1"/>
       <c r="I1" s="4"/>
@@ -10338,13 +10773,13 @@
         <v>17</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="E2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="H2" s="1"/>
       <c r="J2" s="1"/>
@@ -10356,17 +10791,17 @@
       <c r="B3" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="1" t="n">
         <v>18</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="E3" s="1" t="n">
         <v>2</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="H3" s="1"/>
       <c r="J3" s="1"/>
@@ -10378,17 +10813,17 @@
       <c r="B4" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="1" t="n">
         <v>18</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="H4" s="1"/>
       <c r="J4" s="1"/>
@@ -10404,13 +10839,13 @@
         <v>20</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>3</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="H5" s="1"/>
       <c r="J5" s="1"/>
@@ -10422,17 +10857,17 @@
       <c r="B6" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="1" t="n">
         <v>19</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="H6" s="1"/>
       <c r="J6" s="1"/>
@@ -10448,13 +10883,13 @@
         <v>17</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="H7" s="1"/>
       <c r="J7" s="1"/>
@@ -10470,13 +10905,13 @@
         <v>20</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>3</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="H8" s="1"/>
       <c r="J8" s="1"/>
@@ -10492,13 +10927,13 @@
         <v>20</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>3</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="H9" s="1"/>
       <c r="J9" s="1"/>
@@ -10510,17 +10945,17 @@
       <c r="B10" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C10" s="0" t="n">
+      <c r="C10" s="1" t="n">
         <v>19</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E10" s="1" t="n">
         <v>4</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="H10" s="1"/>
       <c r="J10" s="1"/>
@@ -10536,13 +10971,13 @@
         <v>17</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E11" s="1" t="n">
         <v>4</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="H11" s="1"/>
       <c r="J11" s="1"/>
@@ -10552,41 +10987,41 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>20</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="E12" s="1" t="n">
         <v>3</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="H12" s="1"/>
       <c r="J12" s="1"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
-        <v>12</v>
+        <v>307</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>3</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="H13" s="1"/>
       <c r="J13" s="1"/>
@@ -10602,13 +11037,13 @@
         <v>22</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>5</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="4"/>
@@ -10625,13 +11060,13 @@
         <v>22</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>5</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="4"/>
@@ -10648,13 +11083,13 @@
         <v>22</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="E16" s="1" t="n">
         <v>6</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="4"/>
@@ -10671,13 +11106,13 @@
         <v>22</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="E17" s="1" t="n">
         <v>6</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="H17" s="1"/>
       <c r="J17" s="1"/>
@@ -10686,20 +11121,20 @@
       <c r="A18" s="1" t="n">
         <v>104</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="2" t="s">
         <v>146</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>22</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="E18" s="1" t="n">
         <v>6</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="H18" s="1"/>
       <c r="J18" s="1"/>
@@ -10715,13 +11150,13 @@
         <v>21</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="E19" s="1" t="n">
         <v>7</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="H19" s="1"/>
       <c r="J19" s="1"/>
@@ -10737,13 +11172,13 @@
         <v>21</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="E20" s="1" t="n">
         <v>7</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="H20" s="1"/>
       <c r="J20" s="1"/>
@@ -10759,13 +11194,13 @@
         <v>23</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="E21" s="1" t="n">
         <v>10</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10779,13 +11214,13 @@
         <v>25</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="E22" s="1" t="n">
         <v>8</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
@@ -10801,13 +11236,13 @@
         <v>25</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="E23" s="1" t="n">
         <v>9</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10821,13 +11256,13 @@
         <v>25</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="E24" s="1" t="n">
         <v>9</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10841,13 +11276,13 @@
         <v>26</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="E25" s="1" t="n">
         <v>9</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10861,13 +11296,13 @@
         <v>25</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="E26" s="1" t="n">
         <v>8</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10881,13 +11316,13 @@
         <v>23</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="E27" s="1" t="n">
         <v>10</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10895,19 +11330,19 @@
         <v>301</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>734</v>
+        <v>202</v>
       </c>
       <c r="C28" s="1" t="n">
         <v>23</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="E28" s="1" t="n">
         <v>10</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10915,19 +11350,19 @@
         <v>302</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="E29" s="1" t="n">
         <v>11</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10935,19 +11370,19 @@
         <v>304</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C30" s="1" t="n">
         <v>24</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="E30" s="1" t="n">
         <v>11</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10955,19 +11390,19 @@
         <v>305</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C31" s="1" t="n">
         <v>24</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="E31" s="1" t="n">
         <v>12</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10975,59 +11410,59 @@
         <v>306</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C32" s="1" t="n">
         <v>24</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="E32" s="1" t="n">
         <v>12</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C33" s="1" t="n">
         <v>26</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="E33" s="1" t="n">
         <v>15</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="n">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="E34" s="1" t="n">
         <v>15</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11035,19 +11470,19 @@
         <v>500</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C35" s="1" t="n">
         <v>26</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E35" s="1" t="n">
         <v>13</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11055,19 +11490,19 @@
         <v>501</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="E36" s="1" t="n">
         <v>14</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11075,19 +11510,19 @@
         <v>502</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C37" s="1" t="n">
         <v>14</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="E37" s="1" t="n">
         <v>14</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11095,19 +11530,19 @@
         <v>503</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E38" s="1" t="n">
         <v>13</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11115,19 +11550,19 @@
         <v>504</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E39" s="1" t="n">
         <v>13</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11135,160 +11570,118 @@
         <v>505</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="E40" s="1" t="n">
         <v>16</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B43" s="23" t="s">
-        <v>688</v>
-      </c>
-      <c r="C43" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="D43" s="24" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="B44" s="25" t="s">
-        <v>689</v>
-      </c>
-      <c r="C44" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="D44" s="24" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="B45" s="23" t="s">
-        <v>690</v>
-      </c>
-      <c r="C45" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="D45" s="24" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="B46" s="26" t="s">
-        <v>691</v>
-      </c>
-      <c r="C46" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="D46" s="24" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="B47" s="27" t="s">
-        <v>692</v>
-      </c>
-      <c r="C47" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="D47" s="28" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="B48" s="29" t="s">
-        <v>693</v>
-      </c>
-      <c r="C48" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="D48" s="28" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="B49" s="30" t="s">
-        <v>695</v>
-      </c>
-      <c r="C49" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="D49" s="31" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="B50" s="32" t="s">
-        <v>696</v>
-      </c>
-      <c r="C50" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="D50" s="31" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="B51" s="33" t="s">
-        <v>697</v>
-      </c>
-      <c r="C51" s="34" t="n">
-        <v>3</v>
-      </c>
-      <c r="D51" s="34" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="B52" s="35" t="s">
-        <v>681</v>
-      </c>
-      <c r="C52" s="34" t="n">
-        <v>3</v>
-      </c>
-      <c r="D52" s="34" t="s">
-        <v>168</v>
-      </c>
+        <v>737</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="0"/>
+      <c r="B42" s="0"/>
+      <c r="C42" s="0"/>
+      <c r="D42" s="0"/>
+      <c r="E42" s="0"/>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="0"/>
+      <c r="B43" s="0"/>
+      <c r="C43" s="0"/>
+      <c r="D43" s="0"/>
+      <c r="E43" s="0"/>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="0"/>
+      <c r="B44" s="0"/>
+      <c r="C44" s="0"/>
+      <c r="D44" s="0"/>
+      <c r="E44" s="0"/>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="0"/>
+      <c r="B45" s="0"/>
+      <c r="C45" s="0"/>
+      <c r="D45" s="0"/>
+      <c r="E45" s="0"/>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="0"/>
+      <c r="B46" s="0"/>
+      <c r="C46" s="0"/>
+      <c r="D46" s="0"/>
+      <c r="E46" s="0"/>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="0"/>
+      <c r="B47" s="0"/>
+      <c r="C47" s="0"/>
+      <c r="D47" s="0"/>
+      <c r="E47" s="0"/>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="0"/>
+      <c r="B48" s="0"/>
+      <c r="C48" s="0"/>
+      <c r="D48" s="0"/>
+      <c r="E48" s="0"/>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="0"/>
+      <c r="B49" s="0"/>
+      <c r="C49" s="0"/>
+      <c r="D49" s="0"/>
+      <c r="E49" s="0"/>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="0"/>
+      <c r="B50" s="0"/>
+      <c r="C50" s="0"/>
+      <c r="D50" s="0"/>
+      <c r="E50" s="0"/>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="0"/>
+      <c r="B51" s="0"/>
+      <c r="C51" s="0"/>
+      <c r="D51" s="0"/>
+      <c r="E51" s="0"/>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="0"/>
+      <c r="B52" s="0"/>
+      <c r="C52" s="0"/>
+      <c r="D52" s="0"/>
+      <c r="E52" s="0"/>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="0"/>
+      <c r="B53" s="0"/>
+      <c r="C53" s="0"/>
+      <c r="D53" s="0"/>
+      <c r="E53" s="0"/>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="0"/>
+      <c r="B54" s="0"/>
+      <c r="C54" s="0"/>
+      <c r="D54" s="0"/>
+      <c r="E54" s="0"/>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="0"/>
+      <c r="B55" s="0"/>
+      <c r="C55" s="0"/>
+      <c r="D55" s="0"/>
+      <c r="E55" s="0"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -11316,13 +11709,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>737</v>
+        <v>612</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>738</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>9</v>

--- a/fiches indicateurs.xlsx
+++ b/fiches indicateurs.xlsx
@@ -43,7 +43,7 @@
     <author>tc={F5739EF8-0550-45D2-9DA7-791FCFE79548}</author>
   </authors>
   <commentList>
-    <comment ref="G13" authorId="2">
+    <comment ref="G14" authorId="2">
       <text>
         <r>
           <rPr>
@@ -58,7 +58,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G18" authorId="1">
+    <comment ref="G19" authorId="1">
       <text>
         <r>
           <rPr>
@@ -73,7 +73,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G20" authorId="3">
+    <comment ref="G21" authorId="3">
       <text>
         <r>
           <rPr>
@@ -93,7 +93,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G22" authorId="4">
+    <comment ref="G23" authorId="4">
       <text>
         <r>
           <rPr>
@@ -108,7 +108,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G25" authorId="6">
+    <comment ref="G26" authorId="6">
       <text>
         <r>
           <rPr>
@@ -123,7 +123,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G28" authorId="5">
+    <comment ref="G29" authorId="5">
       <text>
         <r>
           <rPr>
@@ -140,7 +140,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G34" authorId="0">
+    <comment ref="G35" authorId="0">
       <text>
         <r>
           <rPr>
@@ -161,7 +161,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2189" uniqueCount="797">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2217" uniqueCount="801">
   <si>
     <t xml:space="preserve">fiche_indicateur</t>
   </si>
@@ -515,6 +515,18 @@
   </si>
   <si>
     <t xml:space="preserve">Zonal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Établissements sensibles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre d’établissements sensible alimentées par la ressource.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimation du nombre d’établissement sensible rattachés à l'unité de distribution (UD) alimentés par la ressource</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comparer les captages selon le nombre d’établissement public sensibles (Hôpitaux, dispensaires, centres de dyalise, établissements scolaires ou de formation … ) dépendants afin d’identifier les ressources les plus stratégiques pour l’alimentation en eau.</t>
   </si>
   <si>
     <t xml:space="preserve">Vulnérabilité Intrinsèque</t>
@@ -3738,7 +3750,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Y42"/>
+  <dimension ref="A1:Y43"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="15.18"/>
@@ -3747,7 +3759,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="38.95"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="35.12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="38.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="3.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="8.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="16.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="29.44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="117.14"/>
@@ -4499,27 +4511,24 @@
       </c>
       <c r="X10" s="1"/>
     </row>
-    <row r="11" customFormat="false" ht="48.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="n">
-        <v>9</v>
-      </c>
+    <row r="11" customFormat="false" ht="36.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="F11" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="G11" s="5" t="s">
         <v>120</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>122</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>30</v>
@@ -4528,16 +4537,16 @@
         <v>30</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="K11" s="10" t="s">
-        <v>124</v>
+        <v>89</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>121</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="N11" s="1" t="s">
         <v>35</v>
@@ -4546,19 +4555,19 @@
         <v>36</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q11" s="3" t="s">
-        <v>108</v>
+        <v>37</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>125</v>
+        <v>93</v>
       </c>
       <c r="S11" s="1" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="T11" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="U11" s="1" t="s">
         <v>42</v>
@@ -4567,33 +4576,33 @@
         <v>43</v>
       </c>
       <c r="W11" s="1" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="X11" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="48.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G12" s="8" t="s">
         <v>126</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="60.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>129</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>30</v>
@@ -4602,19 +4611,19 @@
         <v>30</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>131</v>
+        <v>127</v>
+      </c>
+      <c r="K12" s="10" t="s">
+        <v>128</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>132</v>
+        <v>99</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>34</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O12" s="1" t="s">
         <v>36</v>
@@ -4626,7 +4635,7 @@
         <v>108</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="S12" s="1" t="s">
         <v>72</v>
@@ -4641,33 +4650,33 @@
         <v>43</v>
       </c>
       <c r="W12" s="1" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="X12" s="1" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="60.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>26</v>
+        <v>123</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>138</v>
+        <v>132</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>133</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>30</v>
@@ -4676,69 +4685,72 @@
         <v>30</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>142</v>
+        <v>34</v>
       </c>
       <c r="N13" s="1" t="s">
         <v>36</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q13" s="1" t="s">
-        <v>38</v>
+        <v>69</v>
+      </c>
+      <c r="Q13" s="3" t="s">
+        <v>108</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="U13" s="1" t="s">
         <v>42</v>
       </c>
       <c r="V13" s="1" t="s">
-        <v>117</v>
+        <v>43</v>
       </c>
       <c r="W13" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>84</v>
+      </c>
+      <c r="X13" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>30</v>
@@ -4747,16 +4759,16 @@
         <v>30</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>148</v>
+        <v>143</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>144</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="N14" s="1" t="s">
         <v>36</v>
@@ -4771,7 +4783,7 @@
         <v>38</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="S14" s="1" t="s">
         <v>40</v>
@@ -4786,27 +4798,27 @@
         <v>117</v>
       </c>
       <c r="W14" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B15" s="1" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E15" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>151</v>
       </c>
       <c r="G15" s="11" t="s">
         <v>151</v>
@@ -4818,16 +4830,16 @@
         <v>30</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="K15" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="K15" s="4" t="s">
         <v>152</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="N15" s="1" t="s">
         <v>36</v>
@@ -4857,18 +4869,18 @@
         <v>117</v>
       </c>
       <c r="W15" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B16" s="1" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>26</v>
@@ -4879,23 +4891,26 @@
       <c r="F16" s="1" t="s">
         <v>155</v>
       </c>
+      <c r="G16" s="11" t="s">
+        <v>155</v>
+      </c>
       <c r="H16" s="1" t="s">
-        <v>156</v>
+        <v>30</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>30</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>89</v>
+        <v>143</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="N16" s="1" t="s">
         <v>36</v>
@@ -4910,13 +4925,13 @@
         <v>38</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S16" s="1" t="s">
         <v>40</v>
       </c>
       <c r="T16" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="U16" s="1" t="s">
         <v>42</v>
@@ -4925,51 +4940,45 @@
         <v>117</v>
       </c>
       <c r="W16" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="X16" s="0" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B17" s="1" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>161</v>
+      <c r="E17" s="1" t="s">
+        <v>158</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="G17" s="11" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>30</v>
+        <v>160</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>30</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>139</v>
+        <v>89</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="N17" s="1" t="s">
         <v>36</v>
@@ -4981,16 +4990,16 @@
         <v>37</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>164</v>
+        <v>38</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="S17" s="1" t="s">
         <v>40</v>
       </c>
       <c r="T17" s="1" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="U17" s="1" t="s">
         <v>42</v>
@@ -4999,30 +5008,33 @@
         <v>117</v>
       </c>
       <c r="W17" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
+      </c>
+      <c r="X17" s="0" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B18" s="1" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E18" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="F18" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="G18" s="12" t="s">
-        <v>168</v>
+      <c r="G18" s="11" t="s">
+        <v>166</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>30</v>
@@ -5031,19 +5043,19 @@
         <v>30</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O18" s="1" t="s">
         <v>35</v>
@@ -5052,10 +5064,10 @@
         <v>37</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="S18" s="1" t="s">
         <v>40</v>
@@ -5064,36 +5076,36 @@
         <v>41</v>
       </c>
       <c r="U18" s="1" t="s">
-        <v>172</v>
+        <v>42</v>
       </c>
       <c r="V18" s="1" t="s">
         <v>117</v>
       </c>
       <c r="W18" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B19" s="1" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>30</v>
@@ -5102,16 +5114,16 @@
         <v>30</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="N19" s="1" t="s">
         <v>35</v>
@@ -5123,10 +5135,10 @@
         <v>37</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S19" s="1" t="s">
         <v>40</v>
@@ -5135,36 +5147,36 @@
         <v>41</v>
       </c>
       <c r="U19" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="V19" s="1" t="s">
         <v>117</v>
       </c>
       <c r="W19" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20" s="1" t="n">
-        <v>107</v>
-      </c>
-      <c r="C20" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="G20" s="12" t="s">
         <v>179</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="G20" s="13" t="s">
-        <v>182</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>30</v>
@@ -5173,16 +5185,16 @@
         <v>30</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="N20" s="1" t="s">
         <v>35</v>
@@ -5194,10 +5206,10 @@
         <v>37</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="S20" s="1" t="s">
         <v>40</v>
@@ -5206,36 +5218,36 @@
         <v>41</v>
       </c>
       <c r="U20" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="V20" s="1" t="s">
         <v>117</v>
       </c>
       <c r="W20" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B21" s="1" t="n">
-        <v>200</v>
-      </c>
-      <c r="C21" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="G21" s="13" t="s">
         <v>186</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="G21" s="14" t="s">
-        <v>189</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>30</v>
@@ -5244,16 +5256,16 @@
         <v>30</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>191</v>
+        <v>145</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="N21" s="1" t="s">
         <v>35</v>
@@ -5265,10 +5277,10 @@
         <v>37</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="S21" s="1" t="s">
         <v>40</v>
@@ -5277,57 +5289,54 @@
         <v>41</v>
       </c>
       <c r="U21" s="1" t="s">
-        <v>42</v>
+        <v>176</v>
       </c>
       <c r="V21" s="1" t="s">
         <v>117</v>
       </c>
       <c r="W21" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="X21" s="1" t="s">
-        <v>193</v>
+        <v>148</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B22" s="1" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="G22" s="15" t="s">
-        <v>196</v>
+        <v>192</v>
+      </c>
+      <c r="G22" s="14" t="s">
+        <v>193</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>30</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>156</v>
+        <v>30</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>141</v>
+        <v>195</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="N22" s="1" t="s">
         <v>35</v>
@@ -5339,10 +5348,10 @@
         <v>37</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="S22" s="1" t="s">
         <v>40</v>
@@ -5357,51 +5366,51 @@
         <v>117</v>
       </c>
       <c r="W22" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="X22" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="1" t="n">
+        <v>201</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="72.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" s="1" t="n">
-        <v>202</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="E23" s="1" t="s">
+      <c r="G23" s="15" t="s">
         <v>200</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="G23" s="14" t="s">
-        <v>202</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>30</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>30</v>
+        <v>160</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="N23" s="1" t="s">
         <v>35</v>
@@ -5413,10 +5422,10 @@
         <v>37</v>
       </c>
       <c r="Q23" s="1" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="S23" s="1" t="s">
         <v>40</v>
@@ -5431,33 +5440,33 @@
         <v>117</v>
       </c>
       <c r="W23" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="X23" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="72.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="1" t="n">
+        <v>202</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="36.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" s="1" t="n">
-        <v>203</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="E24" s="1" t="s">
+      <c r="F24" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="G24" s="14" t="s">
         <v>206</v>
-      </c>
-      <c r="G24" s="16" t="s">
-        <v>207</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>30</v>
@@ -5466,16 +5475,16 @@
         <v>30</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="N24" s="1" t="s">
         <v>35</v>
@@ -5487,10 +5496,10 @@
         <v>37</v>
       </c>
       <c r="Q24" s="1" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="R24" s="1" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="S24" s="1" t="s">
         <v>40</v>
@@ -5505,33 +5514,33 @@
         <v>117</v>
       </c>
       <c r="W24" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="X24" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="36.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="1" t="n">
+        <v>203</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="25" customFormat="false" ht="48.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" s="1" t="n">
-        <v>204</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="E25" s="1" t="s">
+      <c r="F25" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="G25" s="16" t="s">
         <v>211</v>
-      </c>
-      <c r="G25" s="15" t="s">
-        <v>212</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>30</v>
@@ -5540,37 +5549,37 @@
         <v>30</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>213</v>
+        <v>143</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>215</v>
+        <v>145</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>216</v>
+        <v>146</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P25" s="1" t="s">
         <v>37</v>
       </c>
       <c r="Q25" s="1" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="R25" s="1" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="S25" s="1" t="s">
         <v>40</v>
       </c>
       <c r="T25" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="U25" s="1" t="s">
         <v>42</v>
@@ -5579,33 +5588,33 @@
         <v>117</v>
       </c>
       <c r="W25" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="X25" s="1" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="48.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B26" s="1" t="n">
-        <v>300</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>178</v>
+        <v>204</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>190</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="G26" s="13" t="s">
-        <v>221</v>
+        <v>215</v>
+      </c>
+      <c r="G26" s="15" t="s">
+        <v>216</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>30</v>
@@ -5614,31 +5623,31 @@
         <v>30</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>89</v>
+        <v>217</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>142</v>
+        <v>220</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P26" s="1" t="s">
         <v>37</v>
       </c>
       <c r="Q26" s="1" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="S26" s="1" t="s">
         <v>40</v>
@@ -5653,33 +5662,33 @@
         <v>117</v>
       </c>
       <c r="W26" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="X26" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B27" s="1" t="n">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>30</v>
@@ -5688,16 +5697,16 @@
         <v>30</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>139</v>
+        <v>89</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="N27" s="1" t="s">
         <v>35</v>
@@ -5709,16 +5718,16 @@
         <v>37</v>
       </c>
       <c r="Q27" s="1" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="R27" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="S27" s="1" t="s">
         <v>40</v>
       </c>
       <c r="T27" s="1" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="U27" s="1" t="s">
         <v>42</v>
@@ -5727,33 +5736,33 @@
         <v>117</v>
       </c>
       <c r="W27" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="X27" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>301</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="G28" s="13" t="s">
         <v>232</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="48.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" s="1" t="n">
-        <v>302</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="G28" s="17" t="s">
-        <v>235</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>30</v>
@@ -5762,16 +5771,16 @@
         <v>30</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>89</v>
+        <v>143</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="N28" s="1" t="s">
         <v>35</v>
@@ -5783,16 +5792,16 @@
         <v>37</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="R28" s="1" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="S28" s="1" t="s">
         <v>40</v>
       </c>
       <c r="T28" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="U28" s="1" t="s">
         <v>42</v>
@@ -5801,33 +5810,33 @@
         <v>117</v>
       </c>
       <c r="W28" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="X28" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="48.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" s="1" t="n">
+        <v>302</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="G29" s="17" t="s">
         <v>239</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="60.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="1" t="n">
-        <v>304</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="G29" s="17" t="s">
-        <v>242</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>30</v>
@@ -5839,13 +5848,13 @@
         <v>89</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="N29" s="1" t="s">
         <v>35</v>
@@ -5857,10 +5866,10 @@
         <v>37</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="S29" s="1" t="s">
         <v>40</v>
@@ -5875,33 +5884,33 @@
         <v>117</v>
       </c>
       <c r="W29" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="X29" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="60.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="1" t="n">
+        <v>304</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="G30" s="17" t="s">
         <v>246</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="95.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="1" t="n">
-        <v>305</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="G30" s="17" t="s">
-        <v>249</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>30</v>
@@ -5913,13 +5922,13 @@
         <v>89</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="N30" s="1" t="s">
         <v>35</v>
@@ -5931,10 +5940,10 @@
         <v>37</v>
       </c>
       <c r="Q30" s="1" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="R30" s="1" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="S30" s="1" t="s">
         <v>40</v>
@@ -5949,30 +5958,33 @@
         <v>117</v>
       </c>
       <c r="W30" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>148</v>
+      </c>
+      <c r="X30" s="1" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="95.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31" s="1" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E31" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G31" s="17" t="s">
         <v>253</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="G31" s="17" t="s">
-        <v>255</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>30</v>
@@ -5981,16 +5993,16 @@
         <v>30</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="N31" s="1" t="s">
         <v>35</v>
@@ -6002,16 +6014,16 @@
         <v>37</v>
       </c>
       <c r="Q31" s="1" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="R31" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="S31" s="1" t="s">
         <v>40</v>
       </c>
       <c r="T31" s="1" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="U31" s="1" t="s">
         <v>42</v>
@@ -6020,45 +6032,48 @@
         <v>117</v>
       </c>
       <c r="W31" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="n">
+        <v>30</v>
+      </c>
       <c r="B32" s="1" t="n">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E32" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G32" s="17" t="s">
         <v>259</v>
-      </c>
-      <c r="F32" s="18" t="s">
-        <v>260</v>
-      </c>
-      <c r="G32" s="19" t="s">
-        <v>261</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>30</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>156</v>
+        <v>30</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="K32" s="4" t="s">
-        <v>262</v>
+        <v>49</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>260</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>141</v>
+        <v>261</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="N32" s="1" t="s">
         <v>35</v>
@@ -6069,7 +6084,12 @@
       <c r="P32" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="Q32" s="3"/>
+      <c r="Q32" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="R32" s="1" t="s">
+        <v>262</v>
+      </c>
       <c r="S32" s="1" t="s">
         <v>40</v>
       </c>
@@ -6083,19 +6103,18 @@
         <v>117</v>
       </c>
       <c r="W32" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="X32" s="1"/>
-    </row>
-    <row r="33" customFormat="false" ht="95.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="1" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>263</v>
@@ -6103,26 +6122,26 @@
       <c r="F33" s="18" t="s">
         <v>264</v>
       </c>
-      <c r="G33" s="20" t="s">
+      <c r="G33" s="19" t="s">
         <v>265</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>30</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>30</v>
+        <v>160</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="K33" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="K33" s="4" t="s">
         <v>266</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>267</v>
+        <v>145</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="N33" s="1" t="s">
         <v>35</v>
@@ -6133,17 +6152,12 @@
       <c r="P33" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="Q33" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="R33" s="1" t="s">
-        <v>268</v>
-      </c>
+      <c r="Q33" s="3"/>
       <c r="S33" s="1" t="s">
         <v>40</v>
       </c>
       <c r="T33" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="U33" s="1" t="s">
         <v>42</v>
@@ -6152,49 +6166,46 @@
         <v>117</v>
       </c>
       <c r="W33" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="X33" s="1"/>
     </row>
-    <row r="34" customFormat="false" ht="48.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="n">
-        <v>31</v>
-      </c>
+    <row r="34" customFormat="false" ht="95.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="1" t="n">
-        <v>401</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>118</v>
+        <v>308</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>182</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>119</v>
+        <v>183</v>
       </c>
       <c r="E34" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="F34" s="18" t="s">
+        <v>268</v>
+      </c>
+      <c r="G34" s="20" t="s">
         <v>269</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="G34" s="16" t="s">
-        <v>271</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>30</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>156</v>
+        <v>30</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>139</v>
+        <v>89</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="N34" s="1" t="s">
         <v>35</v>
@@ -6206,69 +6217,67 @@
         <v>37</v>
       </c>
       <c r="Q34" s="1" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="R34" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="S34" s="1" t="s">
         <v>40</v>
       </c>
       <c r="T34" s="1" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="U34" s="1" t="s">
-        <v>172</v>
+        <v>42</v>
       </c>
       <c r="V34" s="1" t="s">
         <v>117</v>
       </c>
       <c r="W34" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="X34" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="X34" s="1"/>
+    </row>
+    <row r="35" customFormat="false" ht="48.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="1" t="n">
+        <v>401</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="G35" s="16" t="s">
         <v>275</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="27.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="B35" s="1" t="n">
-        <v>402</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="G35" s="16" t="s">
-        <v>278</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>279</v>
+        <v>160</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>143</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="N35" s="1" t="s">
         <v>35</v>
@@ -6277,55 +6286,54 @@
         <v>35</v>
       </c>
       <c r="P35" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="Q35" s="3" t="s">
-        <v>283</v>
+        <v>37</v>
+      </c>
+      <c r="Q35" s="1" t="s">
+        <v>188</v>
       </c>
       <c r="R35" s="1" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="S35" s="1" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="T35" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="U35" s="1" t="s">
-        <v>42</v>
+        <v>176</v>
       </c>
       <c r="V35" s="1" t="s">
         <v>117</v>
       </c>
       <c r="W35" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="X35" s="1"/>
-      <c r="Y35" s="1" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="83.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>148</v>
+      </c>
+      <c r="X35" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="27.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B36" s="1" t="n">
-        <v>500</v>
+        <v>402</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>286</v>
+        <v>122</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>288</v>
+        <v>123</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>281</v>
       </c>
       <c r="G36" s="16" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>30</v>
@@ -6333,32 +6341,32 @@
       <c r="I36" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="J36" s="1" t="s">
-        <v>290</v>
+      <c r="J36" s="3" t="s">
+        <v>283</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>216</v>
+        <v>146</v>
       </c>
       <c r="N36" s="1" t="s">
         <v>35</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="Q36" s="3" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="R36" s="1" t="s">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="S36" s="1" t="s">
         <v>72</v>
@@ -6367,143 +6375,147 @@
         <v>73</v>
       </c>
       <c r="U36" s="1" t="s">
-        <v>172</v>
+        <v>42</v>
       </c>
       <c r="V36" s="1" t="s">
         <v>117</v>
       </c>
       <c r="W36" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="X36" s="1" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>288</v>
+      </c>
+      <c r="X36" s="1"/>
+      <c r="Y36" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="83.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B37" s="1" t="n">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="G37" s="16" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>30</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>156</v>
+        <v>30</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>142</v>
+        <v>220</v>
       </c>
       <c r="N37" s="1" t="s">
         <v>35</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P37" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q37" s="1" t="s">
-        <v>170</v>
+        <v>286</v>
+      </c>
+      <c r="Q37" s="3" t="s">
+        <v>287</v>
       </c>
       <c r="R37" s="1" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="S37" s="1" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="T37" s="1" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="U37" s="1" t="s">
-        <v>42</v>
+        <v>176</v>
       </c>
       <c r="V37" s="1" t="s">
         <v>117</v>
       </c>
       <c r="W37" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="X37" s="1" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="24.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="1" t="n">
+        <v>501</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="G38" s="16" t="s">
+        <v>301</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="J38" s="1" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="n">
+      <c r="K38" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="M38" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="N38" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B38" s="1" t="n">
-        <v>502</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="J38" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="K38" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="L38" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="M38" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="N38" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="O38" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P38" s="1" t="s">
         <v>37</v>
       </c>
       <c r="Q38" s="1" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="R38" s="1" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="S38" s="1" t="s">
         <v>40</v>
@@ -6518,51 +6530,51 @@
         <v>117</v>
       </c>
       <c r="W38" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>148</v>
+      </c>
+      <c r="X38" s="1" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="1" t="n">
+        <v>502</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="M39" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="N39" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="B39" s="1" t="n">
-        <v>503</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="G39" s="17" t="s">
-        <v>311</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I39" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="J39" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="L39" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="M39" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="N39" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="O39" s="1" t="s">
         <v>36</v>
@@ -6570,67 +6582,64 @@
       <c r="P39" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="Q39" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="R39" s="4" t="s">
-        <v>314</v>
+      <c r="Q39" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="R39" s="1" t="s">
+        <v>312</v>
       </c>
       <c r="S39" s="1" t="s">
         <v>40</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="U39" s="1" t="s">
         <v>42</v>
       </c>
       <c r="V39" s="1" t="s">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="W39" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="X39" s="1" t="s">
-        <v>315</v>
+        <v>148</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B40" s="1" t="n">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>316</v>
+        <v>183</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>313</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="G40" s="17" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>30</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>30</v>
+        <v>160</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="M40" s="1" t="s">
         <v>34</v>
@@ -6644,17 +6653,17 @@
       <c r="P40" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="Q40" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="R40" s="1" t="s">
-        <v>321</v>
+      <c r="Q40" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="R40" s="4" t="s">
+        <v>318</v>
       </c>
       <c r="S40" s="1" t="s">
         <v>40</v>
       </c>
       <c r="T40" s="1" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="U40" s="1" t="s">
         <v>42</v>
@@ -6666,42 +6675,45 @@
         <v>44</v>
       </c>
       <c r="X40" s="1" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="1" t="n">
+        <v>504</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="G41" s="17" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="n">
-        <v>38</v>
-      </c>
-      <c r="B41" s="1" t="n">
-        <v>505</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>325</v>
-      </c>
       <c r="H41" s="1" t="s">
-        <v>156</v>
+        <v>30</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>30</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>326</v>
+        <v>58</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="M41" s="1" t="s">
         <v>34</v>
@@ -6713,19 +6725,19 @@
         <v>36</v>
       </c>
       <c r="P41" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q41" s="3" t="s">
-        <v>283</v>
+        <v>37</v>
+      </c>
+      <c r="Q41" s="1" t="s">
+        <v>188</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="S41" s="1" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="U41" s="1" t="s">
         <v>42</v>
@@ -6734,75 +6746,146 @@
         <v>43</v>
       </c>
       <c r="W41" s="1" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="X41" s="1" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="1" t="n">
+        <v>38</v>
+      </c>
       <c r="B42" s="1" t="n">
-        <v>400</v>
+        <v>505</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>118</v>
+        <v>327</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>119</v>
+        <v>183</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>277</v>
+        <v>329</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I42" s="1" t="s">
         <v>30</v>
       </c>
       <c r="J42" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="L42" s="1" t="s">
         <v>332</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>142</v>
+        <v>34</v>
       </c>
       <c r="N42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P42" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q42" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="R42" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="Q42" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="R42" s="1" t="s">
-        <v>334</v>
-      </c>
       <c r="S42" s="1" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="U42" s="1" t="s">
         <v>42</v>
       </c>
       <c r="V42" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="W42" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="X42" s="1" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B43" s="1" t="n">
+        <v>400</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="M43" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="N43" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O43" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="P43" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="Q43" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="R43" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="S43" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="T43" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="U43" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="V43" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="W42" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="X42" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="Y42" s="1" t="s">
-        <v>336</v>
+      <c r="W43" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="X43" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="Y43" s="1" t="s">
+        <v>340</v>
       </c>
     </row>
   </sheetData>
@@ -6826,32 +6909,35 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="35.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="54.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="46.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="35.82"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6859,7 +6945,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="C2" s="31" t="n">
         <v>1</v>
@@ -6868,16 +6954,16 @@
         <v>25</v>
       </c>
       <c r="E2" s="32" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="F2" s="32" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="G2" s="31" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="H2" s="32" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6885,7 +6971,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="C3" s="33" t="n">
         <v>1</v>
@@ -6894,16 +6980,16 @@
         <v>25</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="F3" s="31" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="G3" s="31" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="H3" s="31" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="169.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6911,7 +6997,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="C4" s="31" t="n">
         <v>1</v>
@@ -6920,16 +7006,16 @@
         <v>25</v>
       </c>
       <c r="E4" s="32" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="G4" s="32" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="H4" s="32" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6937,25 +7023,25 @@
         <v>4</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="C5" s="31" t="n">
         <v>5</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="F5" s="32" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="G5" s="31" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="H5" s="32" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6963,25 +7049,25 @@
         <v>5</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="C6" s="31" t="n">
         <v>2</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="F6" s="34" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="G6" s="31" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="H6" s="31" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6989,25 +7075,25 @@
         <v>6</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="C7" s="31" t="n">
         <v>2</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="F7" s="34" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="G7" s="31" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="H7" s="31" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7015,25 +7101,25 @@
         <v>7</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="C8" s="31" t="n">
         <v>2</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="F8" s="32" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="G8" s="31" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="H8" s="31" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7041,25 +7127,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="C9" s="31" t="n">
         <v>3</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="F9" s="34" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="G9" s="31" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="H9" s="31" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7067,25 +7153,25 @@
         <v>9</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="C10" s="31" t="n">
         <v>3</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="F10" s="34" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="G10" s="31" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="H10" s="31" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7093,25 +7179,25 @@
         <v>10</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="C11" s="31" t="n">
         <v>4</v>
       </c>
       <c r="D11" s="32" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E11" s="31" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="F11" s="31" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="G11" s="31" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="H11" s="31" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7119,25 +7205,25 @@
         <v>11</v>
       </c>
       <c r="B12" s="31" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="C12" s="31" t="n">
         <v>4</v>
       </c>
       <c r="D12" s="32" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="F12" s="34" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="G12" s="31" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="H12" s="31" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="41" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7145,25 +7231,25 @@
         <v>12</v>
       </c>
       <c r="B13" s="32" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="C13" s="32" t="n">
         <v>4</v>
       </c>
       <c r="D13" s="32" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E13" s="32" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="F13" s="34" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="G13" s="31" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="H13" s="31" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7171,25 +7257,25 @@
         <v>13</v>
       </c>
       <c r="B14" s="32" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="C14" s="32" t="n">
         <v>6</v>
       </c>
       <c r="D14" s="31" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="E14" s="31" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="F14" s="31" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="G14" s="31" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="H14" s="32" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7197,25 +7283,25 @@
         <v>14</v>
       </c>
       <c r="B15" s="32" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="C15" s="32" t="n">
         <v>7</v>
       </c>
       <c r="D15" s="31" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="E15" s="32" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="F15" s="34" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="G15" s="31" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="H15" s="32" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7223,22 +7309,22 @@
         <v>15</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="C16" s="31" t="n">
         <v>5</v>
       </c>
       <c r="D16" s="31" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E16" s="31" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="F16" s="32" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="G16" s="31" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="H16" s="31"/>
     </row>
@@ -7247,25 +7333,25 @@
         <v>16</v>
       </c>
       <c r="B17" s="32" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="C17" s="32" t="n">
         <v>7</v>
       </c>
       <c r="D17" s="31" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="E17" s="32" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="F17" s="31" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="G17" s="31" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="H17" s="32" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
     </row>
   </sheetData>
@@ -7284,7 +7370,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="88.58"/>
@@ -7299,40 +7385,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7340,34 +7426,34 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7375,31 +7461,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>355</v>
-      </c>
       <c r="I3" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7407,34 +7493,34 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7442,34 +7528,34 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7477,34 +7563,34 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7512,37 +7598,37 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="J7" s="21" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7550,28 +7636,28 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7579,34 +7665,34 @@
         <v>100</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7614,34 +7700,34 @@
         <v>101</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7649,34 +7735,34 @@
         <v>102</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="G11" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="J11" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="H11" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>398</v>
-      </c>
       <c r="L11" s="1" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7684,34 +7770,34 @@
         <v>103</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="L12" s="1" t="s">
         <v>403</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7719,34 +7805,34 @@
         <v>104</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7754,34 +7840,34 @@
         <v>105</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7789,31 +7875,31 @@
         <v>106</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7821,34 +7907,34 @@
         <v>107</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7856,34 +7942,34 @@
         <v>108</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7891,34 +7977,34 @@
         <v>109</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="I18" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>428</v>
-      </c>
       <c r="J18" s="1" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7926,34 +8012,34 @@
         <v>110</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7961,34 +8047,34 @@
         <v>111</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7996,34 +8082,34 @@
         <v>112</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8031,34 +8117,34 @@
         <v>113</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8066,34 +8152,34 @@
         <v>114</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8101,37 +8187,37 @@
         <v>115</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="J24" s="10" t="s">
+        <v>469</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="L24" s="1" t="s">
         <v>465</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="L24" s="1" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8139,34 +8225,34 @@
         <v>116</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="J25" s="10" t="s">
+        <v>469</v>
+      </c>
+      <c r="L25" s="1" t="s">
         <v>465</v>
-      </c>
-      <c r="L25" s="1" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8174,34 +8260,34 @@
         <v>117</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="J26" s="10" t="s">
+        <v>469</v>
+      </c>
+      <c r="L26" s="1" t="s">
         <v>465</v>
-      </c>
-      <c r="L26" s="1" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8209,34 +8295,34 @@
         <v>118</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8244,34 +8330,34 @@
         <v>119</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8279,34 +8365,34 @@
         <v>120</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8314,34 +8400,34 @@
         <v>129</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="C30" s="1" t="s">
-        <v>477</v>
-      </c>
       <c r="D30" s="1" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8349,34 +8435,34 @@
         <v>121</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8384,28 +8470,28 @@
         <v>122</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="29.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8413,37 +8499,37 @@
         <v>123</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="E33" s="22" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8451,34 +8537,34 @@
         <v>124</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8486,34 +8572,34 @@
         <v>125</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8521,34 +8607,34 @@
         <v>126</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8556,34 +8642,34 @@
         <v>127</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8591,34 +8677,34 @@
         <v>128</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8626,31 +8712,31 @@
         <v>130</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="L39" s="4" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8658,37 +8744,37 @@
         <v>131</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="E40" s="22" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8696,33 +8782,49 @@
         <v>132</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="J41" s="10" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="K41" s="3"/>
+    </row>
+    <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="0" t="n">
+        <v>133</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="0" t="n">
+        <v>134</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>267</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L38"/>
@@ -8761,496 +8863,496 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="C1" s="23" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="G1" s="23" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="G2" s="23"/>
       <c r="H2" s="4"/>
     </row>
     <row r="3" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="25" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="D3" s="25" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>30</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="C4" s="25" t="s">
+        <v>552</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>548</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>549</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>544</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>30</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>30</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>30</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>30</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>30</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>30</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>30</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>30</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>30</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>30</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C15" s="4" t="s">
+        <v>589</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>585</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>586</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>581</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>30</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>30</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>30</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>30</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>30</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>30</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>21</v>
@@ -9259,355 +9361,355 @@
         <v>21</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>30</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B22" s="10" t="s">
         <v>22</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>30</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="G23" s="4"/>
     </row>
     <row r="24" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="G24" s="4"/>
     </row>
     <row r="25" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C25" s="25" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="D25" s="25" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>30</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="C26" s="26" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D26" s="26" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>30</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>30</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>30</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>30</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="H31" s="27" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>30</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>30</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="H33" s="28" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>30</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9658,7 +9760,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -9667,16 +9769,16 @@
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9693,7 +9795,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>35</v>
@@ -9713,7 +9815,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>35</v>
@@ -9733,7 +9835,7 @@
         <v>2</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>35</v>
@@ -9753,7 +9855,7 @@
         <v>2</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>35</v>
@@ -9773,7 +9875,7 @@
         <v>2</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>35</v>
@@ -9793,7 +9895,7 @@
         <v>2</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>35</v>
@@ -9813,7 +9915,7 @@
         <v>3</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>35</v>
@@ -9833,7 +9935,7 @@
         <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>35</v>
@@ -9847,13 +9949,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>5</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>35</v>
@@ -9867,13 +9969,13 @@
         <v>10</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>5</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>35</v>
@@ -9887,13 +9989,13 @@
         <v>100</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>100</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>35</v>
@@ -9907,13 +10009,13 @@
         <v>101</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>101</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>35</v>
@@ -9927,13 +10029,13 @@
         <v>101</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>102</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>35</v>
@@ -9947,13 +10049,13 @@
         <v>101</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>103</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>35</v>
@@ -9967,13 +10069,13 @@
         <v>102</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>104</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>35</v>
@@ -9987,13 +10089,13 @@
         <v>104</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>105</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>35</v>
@@ -10007,13 +10109,13 @@
         <v>104</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>106</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>35</v>
@@ -10027,19 +10129,19 @@
         <v>105</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>107</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10050,19 +10152,19 @@
         <v>105</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D20" s="1" t="n">
         <v>108</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10073,13 +10175,13 @@
         <v>106</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D21" s="1" t="n">
         <v>109</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>35</v>
@@ -10093,19 +10195,19 @@
         <v>107</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="D22" s="1" t="n">
         <v>107</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10116,13 +10218,13 @@
         <v>200</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D23" s="1" t="n">
         <v>110</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>35</v>
@@ -10136,13 +10238,13 @@
         <v>201</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D24" s="1" t="n">
         <v>111</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>35</v>
@@ -10156,19 +10258,19 @@
         <v>202</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="D25" s="1" t="n">
         <v>107</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10179,13 +10281,13 @@
         <v>202</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="D26" s="1" t="n">
         <v>108</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>35</v>
@@ -10199,13 +10301,13 @@
         <v>203</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="D27" s="1" t="n">
         <v>112</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>35</v>
@@ -10219,13 +10321,13 @@
         <v>204</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="D28" s="1" t="n">
         <v>113</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>35</v>
@@ -10239,16 +10341,16 @@
         <v>300</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D29" s="1" t="n">
         <v>114</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10259,13 +10361,13 @@
         <v>300</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D30" s="1" t="n">
         <v>115</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>35</v>
@@ -10279,13 +10381,13 @@
         <v>300</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D31" s="1" t="n">
         <v>116</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>35</v>
@@ -10299,13 +10401,13 @@
         <v>300</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D32" s="1" t="n">
         <v>117</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>35</v>
@@ -10319,13 +10421,13 @@
         <v>301</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D33" s="1" t="n">
         <v>107</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>35</v>
@@ -10339,13 +10441,13 @@
         <v>301</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D34" s="1" t="n">
         <v>118</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>35</v>
@@ -10359,13 +10461,13 @@
         <v>301</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D35" s="1" t="n">
         <v>119</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>36</v>
@@ -10379,13 +10481,13 @@
         <v>302</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D36" s="1" t="n">
         <v>120</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>35</v>
@@ -10399,13 +10501,13 @@
         <v>302</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D37" s="1" t="n">
         <v>129</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>35</v>
@@ -10419,13 +10521,13 @@
         <v>304</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D38" s="1" t="n">
         <v>128</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>35</v>
@@ -10439,13 +10541,13 @@
         <v>305</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="D39" s="1" t="n">
         <v>121</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>35</v>
@@ -10459,13 +10561,13 @@
         <v>305</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="D40" s="1" t="n">
         <v>122</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>35</v>
@@ -10479,13 +10581,13 @@
         <v>306</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="D41" s="1" t="n">
         <v>121</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>35</v>
@@ -10499,13 +10601,13 @@
         <v>402</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D42" s="1" t="n">
         <v>123</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>35</v>
@@ -10519,13 +10621,13 @@
         <v>401</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D43" s="1" t="n">
         <v>124</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>35</v>
@@ -10539,19 +10641,19 @@
         <v>401</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D44" s="1" t="n">
         <v>125</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10562,13 +10664,13 @@
         <v>500</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="D45" s="1" t="n">
         <v>6</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>35</v>
@@ -10582,13 +10684,13 @@
         <v>501</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="D46" s="1" t="n">
         <v>126</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>35</v>
@@ -10602,13 +10704,13 @@
         <v>502</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="D47" s="1" t="n">
         <v>127</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>35</v>
@@ -10622,13 +10724,13 @@
         <v>503</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="D48" s="1" t="n">
         <v>3</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>35</v>
@@ -10642,13 +10744,13 @@
         <v>504</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="D49" s="1" t="n">
         <v>3</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>35</v>
@@ -10662,13 +10764,13 @@
         <v>505</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D50" s="1" t="n">
         <v>7</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>35</v>
@@ -10682,13 +10784,13 @@
         <v>11</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="D51" s="1" t="n">
         <v>130</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>35</v>
@@ -10702,13 +10804,13 @@
         <v>307</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="D52" s="1" t="n">
         <v>131</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>35</v>
@@ -10722,15 +10824,43 @@
         <v>307</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="D53" s="1" t="n">
         <v>131</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="F53" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B54" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D54" s="0" t="n">
+        <v>133</v>
+      </c>
+      <c r="F54" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B55" s="1" t="n">
+        <v>308</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="D55" s="0" t="n">
+        <v>134</v>
+      </c>
+      <c r="F55" s="0" t="s">
         <v>35</v>
       </c>
     </row>
@@ -10761,22 +10891,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="32.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="87.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10787,7 +10917,7 @@
         <v>25</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="D2" s="29" t="n">
         <v>1</v>
@@ -10796,7 +10926,7 @@
         <v>26</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="G2" s="4"/>
       <c r="I2" s="1"/>
@@ -10806,10 +10936,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="D3" s="29" t="n">
         <v>1</v>
@@ -10818,7 +10948,7 @@
         <v>26</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="G3" s="4"/>
       <c r="I3" s="1"/>
@@ -10828,19 +10958,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="D4" s="29" t="n">
         <v>2</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="G4" s="4"/>
       <c r="I4" s="1"/>
@@ -10850,19 +10980,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="D5" s="29" t="n">
         <v>2</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="I5" s="1"/>
     </row>
@@ -10871,19 +11001,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="D6" s="29" t="n">
         <v>3</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="I6" s="1"/>
     </row>
@@ -10892,19 +11022,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C7" s="29" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="D7" s="29" t="n">
         <v>2</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="I7" s="1"/>
     </row>
@@ -10913,19 +11043,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="D8" s="29" t="n">
         <v>2</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="I8" s="1"/>
     </row>
@@ -10968,28 +11098,28 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10997,7 +11127,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="C2" s="31" t="n">
         <v>1</v>
@@ -11006,16 +11136,16 @@
         <v>25</v>
       </c>
       <c r="E2" s="32" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="F2" s="32" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="G2" s="31" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="H2" s="32" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11023,7 +11153,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="C3" s="33" t="n">
         <v>1</v>
@@ -11032,16 +11162,16 @@
         <v>25</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="F3" s="31" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="G3" s="31" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="H3" s="31" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11049,7 +11179,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="C4" s="31" t="n">
         <v>1</v>
@@ -11058,16 +11188,16 @@
         <v>25</v>
       </c>
       <c r="E4" s="32" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="G4" s="32" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="H4" s="32" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11075,25 +11205,25 @@
         <v>4</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="C5" s="31" t="n">
         <v>5</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="F5" s="32" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="G5" s="31" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="H5" s="32" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11101,25 +11231,25 @@
         <v>5</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="C6" s="31" t="n">
         <v>2</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="F6" s="34" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="G6" s="31" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="H6" s="31" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11127,25 +11257,25 @@
         <v>6</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="C7" s="31" t="n">
         <v>2</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="F7" s="34" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="G7" s="31" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="H7" s="31" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11153,25 +11283,25 @@
         <v>7</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="C8" s="31" t="n">
         <v>2</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="F8" s="32" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="G8" s="31" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="H8" s="31" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11179,25 +11309,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="C9" s="31" t="n">
         <v>3</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="F9" s="34" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="G9" s="31" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="H9" s="31" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11205,25 +11335,25 @@
         <v>9</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="C10" s="31" t="n">
         <v>3</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="F10" s="34" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="G10" s="31" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="H10" s="31" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11231,25 +11361,25 @@
         <v>10</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="C11" s="31" t="n">
         <v>4</v>
       </c>
       <c r="D11" s="32" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E11" s="31" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="F11" s="31" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="G11" s="31" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="H11" s="31" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11257,25 +11387,25 @@
         <v>11</v>
       </c>
       <c r="B12" s="31" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="C12" s="31" t="n">
         <v>4</v>
       </c>
       <c r="D12" s="32" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="F12" s="34" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="G12" s="31" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="H12" s="31" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="41" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11283,25 +11413,25 @@
         <v>12</v>
       </c>
       <c r="B13" s="32" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="C13" s="32" t="n">
         <v>4</v>
       </c>
       <c r="D13" s="32" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E13" s="32" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="F13" s="34" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="G13" s="31" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="H13" s="31" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11309,25 +11439,25 @@
         <v>13</v>
       </c>
       <c r="B14" s="32" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="C14" s="32" t="n">
         <v>6</v>
       </c>
       <c r="D14" s="31" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="E14" s="31" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="F14" s="31" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="G14" s="31" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="H14" s="32" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11335,25 +11465,25 @@
         <v>14</v>
       </c>
       <c r="B15" s="32" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="C15" s="32" t="n">
         <v>7</v>
       </c>
       <c r="D15" s="31" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="E15" s="32" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="F15" s="34" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="G15" s="31" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="H15" s="32" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11361,22 +11491,22 @@
         <v>15</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="C16" s="31" t="n">
         <v>5</v>
       </c>
       <c r="D16" s="31" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E16" s="31" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="F16" s="32" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="G16" s="31" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="H16" s="31"/>
     </row>
@@ -11385,25 +11515,25 @@
         <v>16</v>
       </c>
       <c r="B17" s="32" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="C17" s="32" t="n">
         <v>7</v>
       </c>
       <c r="D17" s="31" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="E17" s="32" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="F17" s="31" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="G17" s="31" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="H17" s="32" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11411,7 +11541,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="35" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="C18" s="36" t="n">
         <v>1</v>
@@ -11425,7 +11555,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="37" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="C19" s="36" t="n">
         <v>1</v>
@@ -11439,7 +11569,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="35" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="C20" s="36" t="n">
         <v>1</v>
@@ -11453,7 +11583,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="C21" s="36" t="n">
         <v>1</v>
@@ -11467,13 +11597,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="39" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="C22" s="40" t="n">
         <v>2</v>
       </c>
       <c r="D22" s="40" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11481,16 +11611,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="41" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="C23" s="40" t="n">
         <v>2</v>
       </c>
       <c r="D23" s="40" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11498,13 +11628,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="42" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="C24" s="43" t="n">
         <v>4</v>
       </c>
       <c r="D24" s="43" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11512,13 +11642,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="44" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="C25" s="43" t="n">
         <v>4</v>
       </c>
       <c r="D25" s="43" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11526,13 +11656,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="45" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="C26" s="46" t="n">
         <v>3</v>
       </c>
       <c r="D26" s="46" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11540,13 +11670,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="47" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="C27" s="46" t="n">
         <v>3</v>
       </c>
       <c r="D27" s="46" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -11576,156 +11706,156 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>203</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11798,16 +11928,16 @@
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="H1" s="1"/>
       <c r="I1" s="9"/>
@@ -11824,13 +11954,13 @@
         <v>17</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="E2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="H2" s="1"/>
       <c r="J2" s="1"/>
@@ -11846,13 +11976,13 @@
         <v>18</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="E3" s="1" t="n">
         <v>2</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="H3" s="1"/>
       <c r="J3" s="1"/>
@@ -11868,13 +11998,13 @@
         <v>18</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="H4" s="1"/>
       <c r="J4" s="1"/>
@@ -11890,13 +12020,13 @@
         <v>20</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>3</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="H5" s="1"/>
       <c r="J5" s="1"/>
@@ -11912,13 +12042,13 @@
         <v>19</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="H6" s="1"/>
       <c r="J6" s="1"/>
@@ -11934,13 +12064,13 @@
         <v>17</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="H7" s="1"/>
       <c r="J7" s="1"/>
@@ -11956,13 +12086,13 @@
         <v>20</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>3</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="H8" s="1"/>
       <c r="J8" s="1"/>
@@ -11978,13 +12108,13 @@
         <v>20</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>3</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="H9" s="1"/>
       <c r="J9" s="1"/>
@@ -11994,19 +12124,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>19</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="E10" s="1" t="n">
         <v>4</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="H10" s="1"/>
       <c r="J10" s="1"/>
@@ -12016,19 +12146,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>17</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="E11" s="1" t="n">
         <v>4</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="H11" s="1"/>
       <c r="J11" s="1"/>
@@ -12038,19 +12168,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>20</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="E12" s="1" t="n">
         <v>3</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="H12" s="1"/>
       <c r="J12" s="1"/>
@@ -12060,19 +12190,19 @@
         <v>307</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>24</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>3</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="H13" s="1"/>
       <c r="J13" s="1"/>
@@ -12082,19 +12212,19 @@
         <v>100</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>22</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>5</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="9"/>
@@ -12105,19 +12235,19 @@
         <v>101</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>22</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>5</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="9"/>
@@ -12128,19 +12258,19 @@
         <v>102</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>22</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="E16" s="1" t="n">
         <v>6</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="9"/>
@@ -12151,19 +12281,19 @@
         <v>103</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>22</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="E17" s="1" t="n">
         <v>6</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="H17" s="1"/>
       <c r="J17" s="1"/>
@@ -12173,19 +12303,19 @@
         <v>104</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>22</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="E18" s="1" t="n">
         <v>6</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="H18" s="1"/>
       <c r="J18" s="1"/>
@@ -12195,19 +12325,19 @@
         <v>105</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C19" s="1" t="n">
         <v>21</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="E19" s="1" t="n">
         <v>7</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="H19" s="1"/>
       <c r="J19" s="1"/>
@@ -12217,19 +12347,19 @@
         <v>106</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C20" s="1" t="n">
         <v>21</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="E20" s="1" t="n">
         <v>7</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="H20" s="1"/>
       <c r="J20" s="1"/>
@@ -12239,19 +12369,19 @@
         <v>107</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C21" s="1" t="n">
         <v>23</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="E21" s="1" t="n">
         <v>10</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12259,19 +12389,19 @@
         <v>200</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>25</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="E22" s="1" t="n">
         <v>8</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
@@ -12281,19 +12411,19 @@
         <v>201</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>25</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="E23" s="1" t="n">
         <v>9</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12301,19 +12431,19 @@
         <v>202</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>25</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="E24" s="1" t="n">
         <v>9</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12321,19 +12451,19 @@
         <v>203</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>26</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="E25" s="1" t="n">
         <v>9</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12341,19 +12471,19 @@
         <v>204</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C26" s="1" t="n">
         <v>25</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="E26" s="1" t="n">
         <v>8</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12361,19 +12491,19 @@
         <v>300</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>23</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="E27" s="1" t="n">
         <v>10</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12381,19 +12511,19 @@
         <v>301</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C28" s="1" t="n">
         <v>23</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="E28" s="1" t="n">
         <v>10</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12401,19 +12531,19 @@
         <v>302</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C29" s="1" t="n">
         <v>24</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="E29" s="1" t="n">
         <v>11</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12421,19 +12551,19 @@
         <v>304</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C30" s="1" t="n">
         <v>24</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="E30" s="1" t="n">
         <v>11</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12441,19 +12571,19 @@
         <v>305</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C31" s="1" t="n">
         <v>24</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="E31" s="1" t="n">
         <v>12</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12461,19 +12591,19 @@
         <v>306</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="C32" s="1" t="n">
         <v>24</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="E32" s="1" t="n">
         <v>12</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12481,19 +12611,19 @@
         <v>402</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="C33" s="1" t="n">
         <v>26</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="E33" s="1" t="n">
         <v>15</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12501,19 +12631,19 @@
         <v>401</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C34" s="1" t="n">
         <v>26</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="E34" s="1" t="n">
         <v>15</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12521,19 +12651,19 @@
         <v>500</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C35" s="1" t="n">
         <v>26</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="E35" s="1" t="n">
         <v>13</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12541,19 +12671,19 @@
         <v>501</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C36" s="1" t="n">
         <v>26</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="E36" s="1" t="n">
         <v>14</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12561,19 +12691,19 @@
         <v>502</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="C37" s="1" t="n">
         <v>14</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="E37" s="1" t="n">
         <v>14</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12581,19 +12711,19 @@
         <v>503</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="C38" s="1" t="n">
         <v>24</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="E38" s="1" t="n">
         <v>13</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12601,19 +12731,19 @@
         <v>504</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="C39" s="1" t="n">
         <v>24</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="E39" s="1" t="n">
         <v>13</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12621,19 +12751,19 @@
         <v>505</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="C40" s="1" t="n">
         <v>20</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="E40" s="1" t="n">
         <v>16</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
     </row>
   </sheetData>
@@ -12662,19 +12792,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12685,13 +12815,13 @@
         <v>26</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="87.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12699,16 +12829,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="89.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12716,16 +12846,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12733,16 +12863,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
     </row>
   </sheetData>

--- a/fiches indicateurs.xlsx
+++ b/fiches indicateurs.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc"/>
+  <fileVersion appName="Calc" lowestEdited="4"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="indicateurs" sheetId="1" state="visible" r:id="rId3"/>
@@ -24,14 +24,14 @@
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1"/>
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2086" uniqueCount="846">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2171" uniqueCount="873">
   <si>
     <t xml:space="preserve">fiche_indicateur</t>
   </si>
@@ -42,7 +42,7 @@
     <t xml:space="preserve">nom_indicateur</t>
   </si>
   <si>
-    <t xml:space="preserve">description_indicateur_technique</t>
+    <t xml:space="preserve">description_indicateur_legende</t>
   </si>
   <si>
     <t xml:space="preserve">description_indicateur_utilisateur</t>
@@ -1737,6 +1737,87 @@
   </si>
   <si>
     <t xml:space="preserve">Établissements sensibles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Références hydrographiques (fond imagerie / cartographie / terrain / bassin versant)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://georep-dtsi-sgt.opendata.arcgis.com/datasets/dtsi-sgt::références-hydrographiques-1/about?layer=0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nouvelle-Calédonie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jamais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Référentiel hydrographique de Nouvelle-Calédonie (réseau hydrographique, bassins versants) utilisé comme fond de référence : imagerie / cartographie / terrain / bassin versant.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grille tuile H3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grille de tuiles H3 (maillage hexagone) utilisée comme référentiel d'agrégation spatiale des indicateurs. Indexée en base sur les identifiants des cellules. Affichage côté client uniquement — accès serveur non implémenté pour le moment.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Réseau Hydrographique Modélisé (RHM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">peu fréquente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maillage généralisé découpant le territoire en bassins versants élémentaires (souvent de l'ordre de 0,1 km² / 10 ha ou à seuil spécifique) à partir d'un Modèle Numérique de Terrain (MNT). Référentiel géographique pour exploiter les données en lien entre captage et bassins versants.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Description détaillée à obtenir dans la documentation BDLISA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maillage communal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maillage géographique des communes de Nouvelle-Calédonie, niveau de restitution géographique commun.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Province</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Provinces (Sud, Nord, Îles)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maillage géographique des 3 provinces de Nouvelle-Calédonie (Sud, Nord, Îles Loyauté).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hydro-écorégion (HER)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Découpage hydro-écologique du territoire en hydro-écorégions pour la caractérisation des milieux aquatiques et l'agrégation des indicateurs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aire coutumière</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Institutions coutumières</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maillage géographique des 8 aires coutumières de Nouvelle-Calédonie, niveau de restitution institutionnel coutumier.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tribu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maillage géographique des tribus (unités coutumières), niveau de restitution fin.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bassins versants DAVAR (bassins de référence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maillage hydrologique institutionnel des bassins versants de référence utilisés par la DAVAR (bassins des stations hydrométriques), distinct du RHM élémentaire.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unités hydrogéologiques / masses d'eau (BDLISA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Référentiel des unités hydrogéologiques et masses d'eau souterraines (BDLISA-NC). Documentation de référence pour la description du RHM.</t>
   </si>
   <si>
     <t xml:space="preserve">table</t>
@@ -1925,36 +2006,9 @@
     <t xml:space="preserve">Sens de l’indicateur</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Orientation statistique ou logique de la donnée. 
--</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> Pour une donnée quantitative </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">:  indique si une valeur élevée est bénéfique (Positif, ex: capacité de production) ou préjudiciable (Négatif, ex: surface incendiée).
+    <t xml:space="preserve">Orientation statistique ou logique de la donnée. 
+- Pour une donnée quantitative :  indique si une valeur élevée est bénéfique (Positif, ex: capacité de production) ou préjudiciable (Négatif, ex: surface incendiée).
 - Pour une donnée qualitative : indique si l'état ou la classe de l'indicateur est perçu comme favorable (Positif, ex: présence d'un traitement ou d'un secours) ou défavorable (Négatif, ex: absence de protection réglementaire) pour la gestion du captage</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">Positif / Négatif / Neutre</t>
@@ -2830,7 +2884,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2851,16 +2905,16 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -2913,10 +2967,6 @@
     </xf>
     <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -3072,37 +3122,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -3181,9 +3231,9 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="27.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="35.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="38.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="56.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="51.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14.25"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="16.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="57.62"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="55.99"/>
@@ -3198,7 +3248,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="21" style="1" width="16"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="42.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3229,7 +3279,7 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
@@ -3268,11 +3318,11 @@
       <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="5" t="s">
+      <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
@@ -3343,7 +3393,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>5</v>
       </c>
@@ -3414,7 +3464,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>6</v>
       </c>
@@ -3485,7 +3535,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>7</v>
       </c>
@@ -3556,7 +3606,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>11</v>
       </c>
@@ -3627,7 +3677,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>2</v>
       </c>
@@ -3698,7 +3748,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
         <v>8</v>
       </c>
@@ -3769,7 +3819,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>9</v>
       </c>
@@ -3840,7 +3890,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>12</v>
       </c>
@@ -3886,7 +3936,7 @@
       <c r="O10" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="P10" s="5" t="s">
+      <c r="P10" s="1" t="s">
         <v>113</v>
       </c>
       <c r="Q10" s="1" t="s">
@@ -3911,7 +3961,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>3</v>
       </c>
@@ -3957,7 +4007,7 @@
       <c r="O11" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="P11" s="5" t="s">
+      <c r="P11" s="1" t="s">
         <v>113</v>
       </c>
       <c r="Q11" s="1" t="s">
@@ -3982,7 +4032,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
@@ -3992,7 +4042,7 @@
       <c r="C12" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="5" t="s">
         <v>134</v>
       </c>
       <c r="E12" s="1" t="s">
@@ -4028,7 +4078,7 @@
       <c r="O12" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="P12" s="5" t="s">
+      <c r="P12" s="1" t="s">
         <v>113</v>
       </c>
       <c r="Q12" s="1" t="s">
@@ -4051,7 +4101,7 @@
       </c>
       <c r="W12" s="1"/>
     </row>
-    <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>4</v>
       </c>
@@ -4122,7 +4172,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>15</v>
       </c>
@@ -4190,7 +4240,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>16</v>
       </c>
@@ -4258,7 +4308,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
         <v>17</v>
       </c>
@@ -4326,7 +4376,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="1" t="n">
         <v>103</v>
       </c>
@@ -4394,14 +4444,14 @@
         <v>176</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
         <v>18</v>
       </c>
       <c r="B18" s="1" t="n">
         <v>104</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="1" t="s">
         <v>177</v>
       </c>
       <c r="D18" s="1" t="s">
@@ -4462,7 +4512,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
         <v>13</v>
       </c>
@@ -4530,7 +4580,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
         <v>14</v>
       </c>
@@ -4598,7 +4648,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
         <v>19</v>
       </c>
@@ -4666,7 +4716,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
         <v>30</v>
       </c>
@@ -4737,7 +4787,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
         <v>31</v>
       </c>
@@ -4805,7 +4855,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="n">
         <v>32</v>
       </c>
@@ -4876,7 +4926,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="n">
         <v>34</v>
       </c>
@@ -4947,7 +4997,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="n">
         <v>33</v>
       </c>
@@ -5018,7 +5068,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="n">
         <v>20</v>
       </c>
@@ -5089,7 +5139,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="n">
         <v>21</v>
       </c>
@@ -5160,7 +5210,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="n">
         <v>23</v>
       </c>
@@ -5231,7 +5281,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="n">
         <v>24</v>
       </c>
@@ -5302,7 +5352,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="n">
         <v>25</v>
       </c>
@@ -5370,7 +5420,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="n">
         <v>26</v>
       </c>
@@ -5438,7 +5488,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="n">
         <v>27</v>
       </c>
@@ -5448,7 +5498,7 @@
       <c r="C33" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="D33" s="6" t="s">
         <v>288</v>
       </c>
       <c r="E33" s="1" t="s">
@@ -5481,7 +5531,6 @@
       <c r="O33" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P33" s="5"/>
       <c r="R33" s="1" t="s">
         <v>38</v>
       </c>
@@ -5499,7 +5548,7 @@
       </c>
       <c r="W33" s="1"/>
     </row>
-    <row r="34" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="n">
         <v>22</v>
       </c>
@@ -5509,7 +5558,7 @@
       <c r="C34" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="D34" s="6" t="s">
         <v>292</v>
       </c>
       <c r="E34" s="1" t="s">
@@ -5568,7 +5617,7 @@
       </c>
       <c r="W34" s="1"/>
     </row>
-    <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="1" t="n">
         <v>400</v>
       </c>
@@ -5636,7 +5685,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="27.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="n">
         <v>35</v>
       </c>
@@ -5704,7 +5753,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="n">
         <v>36</v>
       </c>
@@ -5726,7 +5775,7 @@
       <c r="G37" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H37" s="5" t="s">
+      <c r="H37" s="1" t="s">
         <v>317</v>
       </c>
       <c r="I37" s="1" t="s">
@@ -5750,7 +5799,7 @@
       <c r="O37" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="P37" s="5" t="s">
+      <c r="P37" s="1" t="s">
         <v>322</v>
       </c>
       <c r="Q37" s="1" t="s">
@@ -5776,7 +5825,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="n">
         <v>37</v>
       </c>
@@ -5822,7 +5871,7 @@
       <c r="O38" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="P38" s="5" t="s">
+      <c r="P38" s="1" t="s">
         <v>322</v>
       </c>
       <c r="Q38" s="1" t="s">
@@ -5847,7 +5896,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="n">
         <v>38</v>
       </c>
@@ -5915,7 +5964,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="1" t="n">
         <v>502</v>
       </c>
@@ -5980,7 +6029,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="n">
         <v>28</v>
       </c>
@@ -6023,7 +6072,7 @@
       <c r="O41" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P41" s="5" t="s">
+      <c r="P41" s="1" t="s">
         <v>189</v>
       </c>
       <c r="Q41" s="3" t="s">
@@ -6048,14 +6097,14 @@
         <v>356</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="n">
         <v>29</v>
       </c>
       <c r="B42" s="1" t="n">
         <v>504</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="C42" s="1" t="s">
         <v>357</v>
       </c>
       <c r="D42" s="1" t="s">
@@ -6119,7 +6168,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="1" t="n">
         <v>505</v>
       </c>
@@ -6162,7 +6211,7 @@
       <c r="O43" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="P43" s="5" t="s">
+      <c r="P43" s="1" t="s">
         <v>322</v>
       </c>
       <c r="Q43" s="1" t="s">
@@ -6192,8 +6241,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12 &amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12 Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -6203,7 +6252,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L43"/>
+  <dimension ref="A1:L53"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="88.58"/>
@@ -6216,45 +6265,45 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="1" width="49.57"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
+    <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="7" t="s">
         <v>375</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="7" t="s">
         <v>376</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="7" t="s">
         <v>377</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="7" t="s">
         <v>378</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="7" t="s">
         <v>379</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="7" t="s">
         <v>380</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="7" t="s">
         <v>381</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="7" t="s">
         <v>382</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="7" t="s">
         <v>383</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="7" t="s">
         <v>384</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="7" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
@@ -6289,7 +6338,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
@@ -6299,6 +6348,9 @@
       <c r="C3" s="1" t="s">
         <v>397</v>
       </c>
+      <c r="D3" s="1" t="s">
+        <v>397</v>
+      </c>
       <c r="E3" s="1" t="s">
         <v>398</v>
       </c>
@@ -6321,7 +6373,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
@@ -6356,7 +6408,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
@@ -6391,7 +6443,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
@@ -6426,7 +6478,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
@@ -6464,7 +6516,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
         <v>7</v>
       </c>
@@ -6493,7 +6545,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>100</v>
       </c>
@@ -6528,7 +6580,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>101</v>
       </c>
@@ -6563,7 +6615,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>102</v>
       </c>
@@ -6598,7 +6650,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
         <v>103</v>
       </c>
@@ -6633,7 +6685,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>104</v>
       </c>
@@ -6668,7 +6720,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>105</v>
       </c>
@@ -6703,7 +6755,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>106</v>
       </c>
@@ -6735,7 +6787,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
         <v>107</v>
       </c>
@@ -6770,7 +6822,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
         <v>108</v>
       </c>
@@ -6805,7 +6857,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
         <v>109</v>
       </c>
@@ -6840,7 +6892,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
         <v>110</v>
       </c>
@@ -6875,7 +6927,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
         <v>111</v>
       </c>
@@ -6910,7 +6962,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
         <v>112</v>
       </c>
@@ -6945,7 +6997,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
         <v>113</v>
       </c>
@@ -6980,7 +7032,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
         <v>114</v>
       </c>
@@ -7015,7 +7067,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="n">
         <v>115</v>
       </c>
@@ -7037,7 +7089,7 @@
       <c r="G24" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="H24" s="6" t="s">
+      <c r="H24" s="5" t="s">
         <v>501</v>
       </c>
       <c r="I24" s="1" t="s">
@@ -7053,7 +7105,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="n">
         <v>116</v>
       </c>
@@ -7088,7 +7140,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="n">
         <v>117</v>
       </c>
@@ -7123,7 +7175,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="n">
         <v>118</v>
       </c>
@@ -7158,7 +7210,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="n">
         <v>119</v>
       </c>
@@ -7193,7 +7245,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="n">
         <v>120</v>
       </c>
@@ -7228,7 +7280,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="n">
         <v>129</v>
       </c>
@@ -7263,7 +7315,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="n">
         <v>121</v>
       </c>
@@ -7298,7 +7350,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="n">
         <v>122</v>
       </c>
@@ -7327,7 +7379,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="29.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="n">
         <v>123</v>
       </c>
@@ -7365,7 +7417,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="n">
         <v>124</v>
       </c>
@@ -7400,7 +7452,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="n">
         <v>125</v>
       </c>
@@ -7435,7 +7487,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="n">
         <v>126</v>
       </c>
@@ -7470,7 +7522,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="n">
         <v>127</v>
       </c>
@@ -7505,7 +7557,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="n">
         <v>128</v>
       </c>
@@ -7540,7 +7592,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="n">
         <v>130</v>
       </c>
@@ -7562,7 +7614,7 @@
       <c r="G39" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="H39" s="6" t="s">
+      <c r="H39" s="5" t="s">
         <v>501</v>
       </c>
       <c r="I39" s="1" t="s">
@@ -7572,7 +7624,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="n">
         <v>131</v>
       </c>
@@ -7603,14 +7655,14 @@
       <c r="J40" s="2" t="s">
         <v>563</v>
       </c>
-      <c r="K40" s="5" t="s">
+      <c r="K40" s="1" t="s">
         <v>564</v>
       </c>
       <c r="L40" s="1" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="n">
         <v>132</v>
       </c>
@@ -7641,22 +7693,323 @@
       <c r="J41" s="2" t="s">
         <v>563</v>
       </c>
-      <c r="K41" s="5"/>
-    </row>
-    <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="n">
         <v>133</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E42" s="1" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="n">
         <v>134</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="1" t="n">
+        <v>136</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="1" t="n">
+        <v>137</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="L46" s="1" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1" t="n">
+        <v>138</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="1" t="n">
+        <v>139</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="1" t="n">
+        <v>140</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="1" t="n">
+        <v>141</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="1" t="n">
+        <v>142</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="1" t="n">
+        <v>143</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="1" t="n">
+        <v>144</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>594</v>
       </c>
     </row>
   </sheetData>
@@ -7671,8 +8024,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12 &amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12 Page &amp;P</oddFooter>
   </headerFooter>
   <drawing r:id="rId5"/>
 </worksheet>
@@ -7684,7 +8037,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H1048576"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="14.3" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="20.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="34.71"/>
@@ -7694,47 +8047,47 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="56.29"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>568</v>
+        <v>595</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>569</v>
+        <v>596</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>570</v>
+        <v>597</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>571</v>
+        <v>598</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>572</v>
+        <v>599</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>573</v>
+        <v>600</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>574</v>
+        <v>601</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="B2" s="5" t="s">
+        <v>603</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>577</v>
+        <v>604</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>578</v>
+        <v>605</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>579</v>
+        <v>606</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>171</v>
@@ -7742,450 +8095,450 @@
       <c r="G2" s="10"/>
       <c r="H2" s="3"/>
     </row>
-    <row r="3" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>576</v>
+        <v>603</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>580</v>
+        <v>607</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>581</v>
+        <v>608</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>582</v>
+        <v>609</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>27</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>583</v>
+        <v>610</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>576</v>
+        <v>603</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>585</v>
+        <v>612</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>586</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>587</v>
+        <v>613</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>614</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>582</v>
+        <v>609</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>27</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>583</v>
+        <v>610</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>576</v>
+        <v>603</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>589</v>
+        <v>616</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>590</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>591</v>
+        <v>617</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>618</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>582</v>
+        <v>609</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>27</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>583</v>
+        <v>610</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>576</v>
+        <v>603</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>593</v>
+        <v>620</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>594</v>
+        <v>621</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>582</v>
+        <v>609</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>27</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>596</v>
+        <v>603</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>623</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>598</v>
+        <v>624</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>625</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>579</v>
+        <v>606</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>171</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>576</v>
+        <v>603</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>600</v>
+        <v>627</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>601</v>
+        <v>628</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>602</v>
+        <v>629</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>603</v>
+        <v>630</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>27</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>604</v>
+        <v>631</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>576</v>
+        <v>603</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>606</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>607</v>
+        <v>633</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>634</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>608</v>
+        <v>635</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>27</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>576</v>
+        <v>603</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>609</v>
+        <v>636</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>610</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>611</v>
+        <v>637</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>638</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>603</v>
+        <v>630</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>27</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>576</v>
+        <v>603</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>612</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>613</v>
+        <v>639</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>640</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>614</v>
+        <v>641</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>27</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>576</v>
+        <v>603</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>615</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>616</v>
+        <v>642</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>643</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>608</v>
+        <v>635</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>27</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>583</v>
+        <v>610</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>576</v>
+        <v>603</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>618</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>619</v>
+        <v>645</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>646</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>620</v>
+        <v>647</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>27</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>576</v>
+        <v>603</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>621</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>622</v>
+        <v>648</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>649</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>623</v>
+        <v>650</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>27</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>576</v>
+        <v>603</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>624</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>625</v>
+        <v>651</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>652</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>620</v>
+        <v>647</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>27</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>576</v>
+        <v>603</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>626</v>
+        <v>653</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>627</v>
+        <v>654</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>620</v>
+        <v>647</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>27</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>604</v>
+        <v>631</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>576</v>
+        <v>603</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>629</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>630</v>
+        <v>656</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>657</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>620</v>
+        <v>647</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>27</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>576</v>
+        <v>603</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>631</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>632</v>
+        <v>658</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>659</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>623</v>
+        <v>650</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>27</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>633</v>
+        <v>660</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>576</v>
+        <v>603</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>635</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>636</v>
+        <v>662</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>663</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>623</v>
+        <v>650</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>27</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>633</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>660</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>576</v>
+        <v>603</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>638</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>639</v>
+        <v>665</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>666</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>623</v>
+        <v>650</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>27</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>633</v>
+        <v>660</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>576</v>
+        <v>603</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>20</v>
@@ -8193,388 +8546,388 @@
       <c r="C21" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="5" t="s">
-        <v>641</v>
+      <c r="D21" s="1" t="s">
+        <v>668</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>623</v>
+        <v>650</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>27</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>633</v>
+        <v>660</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>576</v>
+        <v>603</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>643</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>644</v>
+        <v>670</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>671</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>645</v>
+        <v>672</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>27</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>633</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>660</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>576</v>
+        <v>603</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>647</v>
+        <v>674</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>648</v>
+        <v>675</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>603</v>
+        <v>630</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>171</v>
       </c>
       <c r="G23" s="3"/>
     </row>
-    <row r="24" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>576</v>
+        <v>603</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>649</v>
+        <v>676</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>648</v>
+        <v>675</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>603</v>
+        <v>630</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>171</v>
       </c>
       <c r="G24" s="3"/>
     </row>
-    <row r="25" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>650</v>
+        <v>677</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>374</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>651</v>
+        <v>678</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>652</v>
+        <v>679</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>582</v>
+        <v>609</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>27</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>583</v>
+        <v>610</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>650</v>
+        <v>677</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>375</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>654</v>
+        <v>681</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>654</v>
+        <v>681</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>582</v>
+        <v>609</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>171</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>650</v>
+        <v>677</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>383</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>597</v>
+        <v>624</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>655</v>
+        <v>682</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>656</v>
+        <v>683</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>171</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>650</v>
+        <v>677</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>376</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>657</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>658</v>
+        <v>684</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>685</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>579</v>
+        <v>606</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>27</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>650</v>
+        <v>677</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>377</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>659</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>660</v>
+        <v>686</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>687</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>579</v>
+        <v>606</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>27</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>650</v>
+        <v>677</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>378</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>661</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>662</v>
+        <v>688</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>689</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>579</v>
+        <v>606</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>27</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>650</v>
+        <v>677</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>379</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>663</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>664</v>
+        <v>690</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>691</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>603</v>
+        <v>630</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>27</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>604</v>
+        <v>631</v>
       </c>
       <c r="H31" s="14" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>650</v>
+        <v>677</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>380</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>666</v>
+        <v>693</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>667</v>
+        <v>694</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>603</v>
+        <v>630</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>604</v>
+        <v>631</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>650</v>
+        <v>677</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>381</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>669</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>670</v>
+        <v>696</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>697</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>656</v>
+        <v>683</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>583</v>
+        <v>610</v>
       </c>
       <c r="H33" s="15" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>650</v>
+        <v>677</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>382</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>672</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>673</v>
+        <v>699</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>700</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>623</v>
+        <v>650</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>27</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>583</v>
+        <v>610</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>650</v>
+        <v>677</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>385</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>675</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>676</v>
+        <v>702</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>703</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>603</v>
+        <v>630</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>27</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="6"/>
+        <v>631</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B36" s="5"/>
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
     </row>
-    <row r="37" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="6"/>
+    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B37" s="5"/>
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
     </row>
-    <row r="38" customFormat="false" ht="14.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="6"/>
+    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B38" s="5"/>
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
     </row>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12 &amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12 Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -8591,9 +8944,9 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="182"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>677</v>
+        <v>704</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -8611,10 +8964,10 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
@@ -8634,7 +8987,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
@@ -8654,7 +9007,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
@@ -8674,7 +9027,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
@@ -8694,7 +9047,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
@@ -8714,7 +9067,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
@@ -8734,7 +9087,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
         <v>7</v>
       </c>
@@ -8754,7 +9107,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
@@ -8774,7 +9127,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>9</v>
       </c>
@@ -8794,7 +9147,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>10</v>
       </c>
@@ -8814,7 +9167,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
         <v>11</v>
       </c>
@@ -8834,7 +9187,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>12</v>
       </c>
@@ -8854,7 +9207,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>13</v>
       </c>
@@ -8874,7 +9227,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>14</v>
       </c>
@@ -8894,7 +9247,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
         <v>15</v>
       </c>
@@ -8914,47 +9267,47 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="1" t="n">
         <v>104</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="1" t="s">
         <v>177</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>105</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>679</v>
+        <v>706</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="1" t="n">
         <v>104</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="1" t="s">
         <v>177</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>106</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="1" t="s">
         <v>452</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
         <v>18</v>
       </c>
@@ -8974,10 +9327,10 @@
         <v>33</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
         <v>19</v>
       </c>
@@ -8997,10 +9350,10 @@
         <v>33</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
         <v>20</v>
       </c>
@@ -9020,7 +9373,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
         <v>21</v>
       </c>
@@ -9040,10 +9393,10 @@
         <v>33</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
         <v>22</v>
       </c>
@@ -9063,7 +9416,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="n">
         <v>23</v>
       </c>
@@ -9083,7 +9436,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="n">
         <v>24</v>
       </c>
@@ -9103,10 +9456,10 @@
         <v>33</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="n">
         <v>25</v>
       </c>
@@ -9126,7 +9479,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="n">
         <v>26</v>
       </c>
@@ -9146,7 +9499,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="n">
         <v>27</v>
       </c>
@@ -9166,7 +9519,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="n">
         <v>28</v>
       </c>
@@ -9186,7 +9539,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="n">
         <v>29</v>
       </c>
@@ -9206,7 +9559,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="n">
         <v>30</v>
       </c>
@@ -9226,7 +9579,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="n">
         <v>31</v>
       </c>
@@ -9246,7 +9599,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="n">
         <v>32</v>
       </c>
@@ -9266,7 +9619,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="n">
         <v>33</v>
       </c>
@@ -9286,7 +9639,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="n">
         <v>34</v>
       </c>
@@ -9306,7 +9659,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="n">
         <v>35</v>
       </c>
@@ -9326,7 +9679,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="n">
         <v>36</v>
       </c>
@@ -9346,7 +9699,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="n">
         <v>37</v>
       </c>
@@ -9366,7 +9719,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="n">
         <v>38</v>
       </c>
@@ -9386,7 +9739,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="n">
         <v>39</v>
       </c>
@@ -9406,7 +9759,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="n">
         <v>40</v>
       </c>
@@ -9426,7 +9779,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="n">
         <v>41</v>
       </c>
@@ -9446,7 +9799,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="n">
         <v>42</v>
       </c>
@@ -9466,7 +9819,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="n">
         <v>43</v>
       </c>
@@ -9486,10 +9839,10 @@
         <v>34</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="n">
         <v>44</v>
       </c>
@@ -9503,13 +9856,13 @@
         <v>6</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>684</v>
+        <v>711</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="n">
         <v>45</v>
       </c>
@@ -9529,7 +9882,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="n">
         <v>46</v>
       </c>
@@ -9549,7 +9902,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="n">
         <v>47</v>
       </c>
@@ -9557,7 +9910,7 @@
         <v>503</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>685</v>
+        <v>712</v>
       </c>
       <c r="D48" s="1" t="n">
         <v>3</v>
@@ -9569,7 +9922,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="n">
         <v>48</v>
       </c>
@@ -9577,7 +9930,7 @@
         <v>504</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>686</v>
+        <v>713</v>
       </c>
       <c r="D49" s="1" t="n">
         <v>3</v>
@@ -9589,7 +9942,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="n">
         <v>49</v>
       </c>
@@ -9603,13 +9956,13 @@
         <v>7</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>687</v>
+        <v>714</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="n">
         <v>50</v>
       </c>
@@ -9617,19 +9970,19 @@
         <v>11</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>688</v>
+        <v>715</v>
       </c>
       <c r="D51" s="1" t="n">
         <v>130</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>689</v>
+        <v>716</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="n">
         <v>51</v>
       </c>
@@ -9637,19 +9990,19 @@
         <v>307</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>690</v>
+        <v>717</v>
       </c>
       <c r="D52" s="1" t="n">
         <v>131</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>691</v>
+        <v>718</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="n">
         <v>51</v>
       </c>
@@ -9657,19 +10010,19 @@
         <v>307</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>690</v>
+        <v>717</v>
       </c>
       <c r="D53" s="1" t="n">
         <v>131</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>692</v>
+        <v>719</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="1" t="n">
         <v>12</v>
       </c>
@@ -9683,7 +10036,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B55" s="1" t="n">
         <v>308</v>
       </c>
@@ -9697,14 +10050,14 @@
         <v>33</v>
       </c>
     </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12 &amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12 Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -9715,187 +10068,187 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I12"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="1" width="28.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="42.89"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="46.25"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="32.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>693</v>
+        <v>720</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>585</v>
+        <v>612</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>694</v>
+        <v>721</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>695</v>
+        <v>722</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>590</v>
+        <v>617</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="87.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>697</v>
+        <v>724</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>698</v>
+        <v>725</v>
       </c>
       <c r="D2" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>699</v>
+        <v>726</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>700</v>
+        <v>727</v>
       </c>
       <c r="G2" s="3"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>701</v>
+        <v>728</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>702</v>
+        <v>729</v>
       </c>
       <c r="D3" s="16" t="n">
         <v>1</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>699</v>
+        <v>726</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>703</v>
+        <v>730</v>
       </c>
       <c r="G3" s="3"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>704</v>
+        <v>731</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>705</v>
+        <v>732</v>
       </c>
       <c r="D4" s="16" t="n">
         <v>2</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>706</v>
+        <v>733</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>707</v>
+        <v>734</v>
       </c>
       <c r="G4" s="3"/>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>708</v>
+        <v>735</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>709</v>
+        <v>736</v>
       </c>
       <c r="D5" s="16" t="n">
         <v>2</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>706</v>
+        <v>733</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>710</v>
+        <v>737</v>
       </c>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>711</v>
+        <v>738</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>712</v>
+        <v>739</v>
       </c>
       <c r="D6" s="16" t="n">
         <v>3</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>713</v>
+        <v>740</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>714</v>
+        <v>741</v>
       </c>
       <c r="I6" s="1"/>
     </row>
-    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>715</v>
+        <v>742</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>716</v>
+        <v>743</v>
       </c>
       <c r="D7" s="16" t="n">
         <v>2</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>706</v>
+        <v>733</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>717</v>
+        <v>744</v>
       </c>
       <c r="I7" s="1"/>
     </row>
-    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>718</v>
+        <v>745</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>719</v>
+        <v>746</v>
       </c>
       <c r="D8" s="16" t="n">
         <v>2</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>706</v>
+        <v>733</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>720</v>
+        <v>747</v>
       </c>
       <c r="I8" s="1"/>
     </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="17"/>
     </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
@@ -9905,8 +10258,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12 &amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12 Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -9917,7 +10270,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H27"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="29.56"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="37.44"/>
@@ -9929,614 +10282,614 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="29.91"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>721</v>
+        <v>748</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>722</v>
+        <v>749</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>693</v>
+        <v>720</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>585</v>
+        <v>612</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>610</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>723</v>
+        <v>637</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>750</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>724</v>
+        <v>751</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="18" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>726</v>
+        <v>753</v>
       </c>
       <c r="C2" s="18" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="18" t="s">
-        <v>697</v>
+        <v>724</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>727</v>
+        <v>754</v>
       </c>
       <c r="F2" s="19" t="s">
-        <v>728</v>
+        <v>755</v>
       </c>
       <c r="G2" s="18" t="s">
-        <v>729</v>
+        <v>756</v>
       </c>
       <c r="H2" s="19" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="18" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>731</v>
+        <v>758</v>
       </c>
       <c r="C3" s="20" t="n">
         <v>1</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>697</v>
+        <v>724</v>
       </c>
       <c r="E3" s="18" t="s">
-        <v>732</v>
+        <v>759</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>733</v>
+        <v>760</v>
       </c>
       <c r="G3" s="18" t="s">
-        <v>734</v>
+        <v>761</v>
       </c>
       <c r="H3" s="18" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>735</v>
+        <v>762</v>
       </c>
       <c r="C4" s="18" t="n">
         <v>1</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>697</v>
+        <v>724</v>
       </c>
       <c r="E4" s="19" t="s">
-        <v>736</v>
+        <v>763</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>733</v>
+        <v>760</v>
       </c>
       <c r="G4" s="19" t="s">
-        <v>737</v>
+        <v>764</v>
       </c>
       <c r="H4" s="19" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>739</v>
+        <v>766</v>
       </c>
       <c r="C5" s="18" t="n">
         <v>5</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>711</v>
+        <v>738</v>
       </c>
       <c r="E5" s="18" t="s">
-        <v>740</v>
+        <v>767</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>728</v>
+        <v>755</v>
       </c>
       <c r="G5" s="18" t="s">
-        <v>741</v>
+        <v>768</v>
       </c>
       <c r="H5" s="19" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>743</v>
+        <v>770</v>
       </c>
       <c r="C6" s="18" t="n">
         <v>2</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>701</v>
+        <v>728</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>744</v>
-      </c>
-      <c r="F6" s="21" t="s">
-        <v>745</v>
+        <v>771</v>
+      </c>
+      <c r="F6" s="18" t="s">
+        <v>772</v>
       </c>
       <c r="G6" s="18" t="s">
-        <v>746</v>
+        <v>773</v>
       </c>
       <c r="H6" s="18" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>747</v>
+        <v>774</v>
       </c>
       <c r="C7" s="18" t="n">
         <v>2</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>701</v>
+        <v>728</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>748</v>
-      </c>
-      <c r="F7" s="21" t="s">
-        <v>745</v>
+        <v>775</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>772</v>
       </c>
       <c r="G7" s="18" t="s">
-        <v>749</v>
+        <v>776</v>
       </c>
       <c r="H7" s="18" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>750</v>
+        <v>777</v>
       </c>
       <c r="C8" s="18" t="n">
         <v>2</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>701</v>
+        <v>728</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>751</v>
+        <v>778</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>728</v>
+        <v>755</v>
       </c>
       <c r="G8" s="18" t="s">
-        <v>752</v>
+        <v>779</v>
       </c>
       <c r="H8" s="18" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>753</v>
+        <v>780</v>
       </c>
       <c r="C9" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="21" t="s">
-        <v>704</v>
+      <c r="D9" s="18" t="s">
+        <v>731</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>754</v>
-      </c>
-      <c r="F9" s="21" t="s">
-        <v>745</v>
+        <v>781</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>772</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>755</v>
+        <v>782</v>
       </c>
       <c r="H9" s="18" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>756</v>
+        <v>783</v>
       </c>
       <c r="C10" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="D10" s="21" t="s">
-        <v>704</v>
+      <c r="D10" s="18" t="s">
+        <v>731</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>757</v>
-      </c>
-      <c r="F10" s="21" t="s">
-        <v>745</v>
+        <v>784</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>772</v>
       </c>
       <c r="G10" s="18" t="s">
-        <v>758</v>
+        <v>785</v>
       </c>
       <c r="H10" s="18" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="18" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>759</v>
+        <v>786</v>
       </c>
       <c r="C11" s="18" t="n">
         <v>4</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>708</v>
+        <v>735</v>
       </c>
       <c r="E11" s="18" t="s">
+        <v>787</v>
+      </c>
+      <c r="F11" s="18" t="s">
         <v>760</v>
       </c>
-      <c r="F11" s="18" t="s">
-        <v>733</v>
-      </c>
       <c r="G11" s="18" t="s">
-        <v>761</v>
+        <v>788</v>
       </c>
       <c r="H11" s="18" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="18" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>762</v>
+        <v>789</v>
       </c>
       <c r="C12" s="18" t="n">
         <v>4</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>708</v>
+        <v>735</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>763</v>
-      </c>
-      <c r="F12" s="21" t="s">
-        <v>745</v>
+        <v>790</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>772</v>
       </c>
       <c r="G12" s="18" t="s">
-        <v>764</v>
+        <v>791</v>
       </c>
       <c r="H12" s="18" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="41" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="18" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>765</v>
+        <v>792</v>
       </c>
       <c r="C13" s="19" t="n">
         <v>4</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>708</v>
+        <v>735</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>766</v>
-      </c>
-      <c r="F13" s="21" t="s">
-        <v>745</v>
+        <v>793</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>772</v>
       </c>
       <c r="G13" s="18" t="s">
-        <v>767</v>
+        <v>794</v>
       </c>
       <c r="H13" s="18" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="18" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>768</v>
+        <v>795</v>
       </c>
       <c r="C14" s="19" t="n">
         <v>6</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>715</v>
+        <v>742</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>769</v>
+        <v>796</v>
       </c>
       <c r="F14" s="18" t="s">
-        <v>733</v>
+        <v>760</v>
       </c>
       <c r="G14" s="18" t="s">
-        <v>770</v>
+        <v>797</v>
       </c>
       <c r="H14" s="19" t="s">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="18" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>772</v>
+        <v>799</v>
       </c>
       <c r="C15" s="19" t="n">
         <v>7</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>715</v>
+        <v>742</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>773</v>
-      </c>
-      <c r="F15" s="21" t="s">
-        <v>745</v>
+        <v>800</v>
+      </c>
+      <c r="F15" s="18" t="s">
+        <v>772</v>
       </c>
       <c r="G15" s="18" t="s">
-        <v>774</v>
+        <v>801</v>
       </c>
       <c r="H15" s="19" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="18" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>776</v>
+        <v>803</v>
       </c>
       <c r="C16" s="18" t="n">
         <v>5</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>711</v>
+        <v>738</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>777</v>
+        <v>804</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>728</v>
+        <v>755</v>
       </c>
       <c r="G16" s="18" t="s">
-        <v>778</v>
+        <v>805</v>
       </c>
       <c r="H16" s="18"/>
     </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="18" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>779</v>
+        <v>806</v>
       </c>
       <c r="C17" s="19" t="n">
         <v>7</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>718</v>
+        <v>745</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>780</v>
+        <v>807</v>
       </c>
       <c r="F17" s="18" t="s">
-        <v>733</v>
+        <v>760</v>
       </c>
       <c r="G17" s="18" t="s">
-        <v>781</v>
+        <v>808</v>
       </c>
       <c r="H17" s="19" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="22" t="s">
-        <v>783</v>
-      </c>
-      <c r="C18" s="23" t="n">
+      <c r="B18" s="21" t="s">
+        <v>810</v>
+      </c>
+      <c r="C18" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="23" t="s">
-        <v>697</v>
+      <c r="D18" s="22" t="s">
+        <v>724</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="24" t="s">
-        <v>784</v>
-      </c>
-      <c r="C19" s="23" t="n">
+      <c r="B19" s="23" t="s">
+        <v>811</v>
+      </c>
+      <c r="C19" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="23" t="s">
-        <v>697</v>
+      <c r="D19" s="22" t="s">
+        <v>724</v>
       </c>
       <c r="E19" s="18" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="22" t="s">
-        <v>785</v>
-      </c>
-      <c r="C20" s="23" t="n">
+      <c r="B20" s="21" t="s">
+        <v>812</v>
+      </c>
+      <c r="C20" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="23" t="s">
-        <v>697</v>
+      <c r="D20" s="22" t="s">
+        <v>724</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="25" t="s">
-        <v>786</v>
-      </c>
-      <c r="C21" s="23" t="n">
+      <c r="B21" s="24" t="s">
+        <v>813</v>
+      </c>
+      <c r="C21" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="23" t="s">
-        <v>697</v>
+      <c r="D21" s="22" t="s">
+        <v>724</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="26" t="s">
-        <v>787</v>
-      </c>
-      <c r="C22" s="27" t="n">
+      <c r="B22" s="25" t="s">
+        <v>814</v>
+      </c>
+      <c r="C22" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="D22" s="27" t="s">
-        <v>701</v>
+      <c r="D22" s="26" t="s">
+        <v>728</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="28" t="s">
-        <v>788</v>
-      </c>
-      <c r="C23" s="27" t="n">
+      <c r="B23" s="27" t="s">
+        <v>815</v>
+      </c>
+      <c r="C23" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="27" t="s">
-        <v>701</v>
+      <c r="D23" s="26" t="s">
+        <v>728</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="29" t="s">
-        <v>790</v>
-      </c>
-      <c r="C24" s="30" t="n">
+      <c r="B24" s="28" t="s">
+        <v>817</v>
+      </c>
+      <c r="C24" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="D24" s="30" t="s">
-        <v>708</v>
+      <c r="D24" s="29" t="s">
+        <v>735</v>
       </c>
       <c r="E24" s="18" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="32.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="31" t="s">
-        <v>791</v>
-      </c>
-      <c r="C25" s="30" t="n">
+      <c r="B25" s="30" t="s">
+        <v>818</v>
+      </c>
+      <c r="C25" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="D25" s="30" t="s">
-        <v>708</v>
+      <c r="D25" s="29" t="s">
+        <v>735</v>
       </c>
       <c r="E25" s="19" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="32" t="s">
-        <v>792</v>
-      </c>
-      <c r="C26" s="33" t="n">
+      <c r="B26" s="31" t="s">
+        <v>819</v>
+      </c>
+      <c r="C26" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="D26" s="33" t="s">
-        <v>704</v>
+      <c r="D26" s="32" t="s">
+        <v>731</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="34" t="s">
-        <v>776</v>
-      </c>
-      <c r="C27" s="33" t="n">
+      <c r="B27" s="33" t="s">
+        <v>803</v>
+      </c>
+      <c r="C27" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="D27" s="33" t="s">
-        <v>704</v>
+      <c r="D27" s="32" t="s">
+        <v>731</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>777</v>
+        <v>804</v>
       </c>
     </row>
   </sheetData>
@@ -10544,8 +10897,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12 &amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12 Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -10556,7 +10909,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F33"/>
-  <sheetFormatPr defaultColWidth="24.109375" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="24.109375" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.22"/>
@@ -10564,192 +10917,192 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="134.94"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>677</v>
+        <v>704</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>793</v>
+        <v>820</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>794</v>
+        <v>821</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>795</v>
+        <v>822</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>796</v>
+        <v>823</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>797</v>
+        <v>824</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>799</v>
+        <v>826</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>800</v>
+        <v>827</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>797</v>
+        <v>824</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>802</v>
+        <v>829</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>803</v>
+        <v>830</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>797</v>
+        <v>824</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>805</v>
+        <v>832</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>806</v>
+        <v>833</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>797</v>
+        <v>824</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>808</v>
+        <v>835</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>203</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>809</v>
+        <v>836</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>811</v>
+        <v>838</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>809</v>
+        <v>836</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>813</v>
+        <v>840</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>814</v>
+        <v>841</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>797</v>
+        <v>824</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>816</v>
+        <v>843</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>817</v>
+        <v>844</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>809</v>
+        <v>836</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>819</v>
+        <v>846</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>820</v>
+        <v>847</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>797</v>
+        <v>824</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>822</v>
+        <v>849</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>823</v>
+        <v>850</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>797</v>
+        <v>824</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C23" s="1"/>
     </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C24" s="1"/>
     </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C25" s="1"/>
     </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C26" s="1"/>
     </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C27" s="1"/>
     </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C28" s="1"/>
     </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C29" s="1"/>
     </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C30" s="1"/>
     </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C31" s="1"/>
     </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C32" s="1"/>
       <c r="F32" s="1"/>
     </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C33" s="1"/>
     </row>
   </sheetData>
@@ -10757,8 +11110,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12 &amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12 Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -10769,7 +11122,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K42"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="25.74"/>
@@ -10780,7 +11133,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="33.27"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -10788,22 +11141,22 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>721</v>
+        <v>748</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>825</v>
+        <v>852</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>826</v>
+        <v>853</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>825</v>
+        <v>852</v>
       </c>
       <c r="H1" s="1"/>
-      <c r="I1" s="6"/>
+      <c r="I1" s="5"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
@@ -10814,18 +11167,18 @@
         <v>17</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>726</v>
+        <v>753</v>
       </c>
       <c r="E2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>726</v>
+        <v>753</v>
       </c>
       <c r="H2" s="1"/>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
@@ -10836,18 +11189,18 @@
         <v>18</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>731</v>
+        <v>758</v>
       </c>
       <c r="E3" s="1" t="n">
         <v>2</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>731</v>
+        <v>758</v>
       </c>
       <c r="H3" s="1"/>
       <c r="J3" s="1"/>
     </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
@@ -10858,18 +11211,18 @@
         <v>18</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>726</v>
+        <v>753</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>726</v>
+        <v>753</v>
       </c>
       <c r="H4" s="1"/>
       <c r="J4" s="1"/>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
@@ -10880,18 +11233,18 @@
         <v>20</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>735</v>
+        <v>762</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>3</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>735</v>
+        <v>762</v>
       </c>
       <c r="H5" s="1"/>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
@@ -10902,18 +11255,18 @@
         <v>19</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>726</v>
+        <v>753</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>726</v>
+        <v>753</v>
       </c>
       <c r="H6" s="1"/>
       <c r="J6" s="1"/>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
@@ -10924,18 +11277,18 @@
         <v>17</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>731</v>
+        <v>758</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>731</v>
+        <v>758</v>
       </c>
       <c r="H7" s="1"/>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
         <v>7</v>
       </c>
@@ -10946,18 +11299,18 @@
         <v>20</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>735</v>
+        <v>762</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>3</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>735</v>
+        <v>762</v>
       </c>
       <c r="H8" s="1"/>
       <c r="J8" s="1"/>
     </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
@@ -10968,18 +11321,18 @@
         <v>20</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>735</v>
+        <v>762</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>3</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>735</v>
+        <v>762</v>
       </c>
       <c r="H9" s="1"/>
       <c r="J9" s="1"/>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>9</v>
       </c>
@@ -10990,18 +11343,18 @@
         <v>19</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>827</v>
+        <v>854</v>
       </c>
       <c r="E10" s="1" t="n">
         <v>4</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>827</v>
+        <v>854</v>
       </c>
       <c r="H10" s="1"/>
       <c r="J10" s="1"/>
     </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>10</v>
       </c>
@@ -11012,40 +11365,40 @@
         <v>17</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>827</v>
+        <v>854</v>
       </c>
       <c r="E11" s="1" t="n">
         <v>4</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>827</v>
+        <v>854</v>
       </c>
       <c r="H11" s="1"/>
       <c r="J11" s="1"/>
     </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>828</v>
+        <v>855</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>20</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>735</v>
+        <v>762</v>
       </c>
       <c r="E12" s="1" t="n">
         <v>3</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>735</v>
+        <v>762</v>
       </c>
       <c r="H12" s="1"/>
       <c r="J12" s="1"/>
     </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>12</v>
       </c>
@@ -11056,18 +11409,18 @@
         <v>17</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>731</v>
+        <v>758</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>2</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>731</v>
+        <v>758</v>
       </c>
       <c r="H13" s="1"/>
       <c r="J13" s="1"/>
     </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>307</v>
       </c>
@@ -11078,18 +11431,18 @@
         <v>24</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>735</v>
+        <v>762</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>3</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>735</v>
+        <v>762</v>
       </c>
       <c r="H14" s="1"/>
       <c r="J14" s="1"/>
     </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>100</v>
       </c>
@@ -11100,19 +11453,19 @@
         <v>22</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>743</v>
+        <v>770</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>5</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>743</v>
+        <v>770</v>
       </c>
       <c r="H15" s="1"/>
-      <c r="I15" s="6"/>
+      <c r="I15" s="5"/>
       <c r="J15" s="1"/>
     </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
         <v>101</v>
       </c>
@@ -11123,19 +11476,19 @@
         <v>22</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>743</v>
+        <v>770</v>
       </c>
       <c r="E16" s="1" t="n">
         <v>5</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>743</v>
+        <v>770</v>
       </c>
       <c r="H16" s="1"/>
-      <c r="I16" s="6"/>
+      <c r="I16" s="5"/>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
         <v>102</v>
       </c>
@@ -11146,19 +11499,19 @@
         <v>22</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>747</v>
+        <v>774</v>
       </c>
       <c r="E17" s="1" t="n">
         <v>6</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>747</v>
+        <v>774</v>
       </c>
       <c r="H17" s="1"/>
-      <c r="I17" s="6"/>
+      <c r="I17" s="5"/>
       <c r="J17" s="1"/>
     </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
         <v>103</v>
       </c>
@@ -11169,40 +11522,40 @@
         <v>22</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>747</v>
+        <v>774</v>
       </c>
       <c r="E18" s="1" t="n">
         <v>6</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>747</v>
+        <v>774</v>
       </c>
       <c r="H18" s="1"/>
       <c r="J18" s="1"/>
     </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
         <v>104</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="1" t="s">
         <v>177</v>
       </c>
       <c r="C19" s="1" t="n">
         <v>22</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>747</v>
+        <v>774</v>
       </c>
       <c r="E19" s="1" t="n">
         <v>6</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>747</v>
+        <v>774</v>
       </c>
       <c r="H19" s="1"/>
       <c r="J19" s="1"/>
     </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
         <v>105</v>
       </c>
@@ -11213,18 +11566,18 @@
         <v>21</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>750</v>
+        <v>777</v>
       </c>
       <c r="E20" s="1" t="n">
         <v>7</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>750</v>
+        <v>777</v>
       </c>
       <c r="H20" s="1"/>
       <c r="J20" s="1"/>
     </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
         <v>106</v>
       </c>
@@ -11235,18 +11588,18 @@
         <v>21</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>750</v>
+        <v>777</v>
       </c>
       <c r="E21" s="1" t="n">
         <v>7</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>750</v>
+        <v>777</v>
       </c>
       <c r="H21" s="1"/>
       <c r="J21" s="1"/>
     </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
         <v>107</v>
       </c>
@@ -11257,16 +11610,16 @@
         <v>23</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>759</v>
+        <v>786</v>
       </c>
       <c r="E22" s="1" t="n">
         <v>10</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
         <v>200</v>
       </c>
@@ -11277,18 +11630,18 @@
         <v>25</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>753</v>
+        <v>780</v>
       </c>
       <c r="E23" s="1" t="n">
         <v>8</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>753</v>
+        <v>780</v>
       </c>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
     </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="n">
         <v>201</v>
       </c>
@@ -11299,16 +11652,16 @@
         <v>25</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>756</v>
+        <v>783</v>
       </c>
       <c r="E24" s="1" t="n">
         <v>9</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="n">
         <v>202</v>
       </c>
@@ -11319,16 +11672,16 @@
         <v>25</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>756</v>
+        <v>783</v>
       </c>
       <c r="E25" s="1" t="n">
         <v>9</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="n">
         <v>203</v>
       </c>
@@ -11339,16 +11692,16 @@
         <v>26</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>753</v>
+        <v>780</v>
       </c>
       <c r="E26" s="1" t="n">
         <v>9</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="n">
         <v>204</v>
       </c>
@@ -11359,16 +11712,16 @@
         <v>25</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>756</v>
+        <v>783</v>
       </c>
       <c r="E27" s="1" t="n">
         <v>8</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="n">
         <v>300</v>
       </c>
@@ -11379,16 +11732,16 @@
         <v>23</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>759</v>
+        <v>786</v>
       </c>
       <c r="E28" s="1" t="n">
         <v>10</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="n">
         <v>301</v>
       </c>
@@ -11399,16 +11752,16 @@
         <v>23</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>759</v>
+        <v>786</v>
       </c>
       <c r="E29" s="1" t="n">
         <v>10</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="n">
         <v>302</v>
       </c>
@@ -11419,16 +11772,16 @@
         <v>24</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>762</v>
+        <v>789</v>
       </c>
       <c r="E30" s="1" t="n">
         <v>11</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="n">
         <v>304</v>
       </c>
@@ -11439,16 +11792,16 @@
         <v>24</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>762</v>
+        <v>789</v>
       </c>
       <c r="E31" s="1" t="n">
         <v>11</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="n">
         <v>305</v>
       </c>
@@ -11459,16 +11812,16 @@
         <v>24</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>829</v>
+        <v>856</v>
       </c>
       <c r="E32" s="1" t="n">
         <v>12</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="n">
         <v>306</v>
       </c>
@@ -11479,16 +11832,16 @@
         <v>24</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>829</v>
+        <v>856</v>
       </c>
       <c r="E33" s="1" t="n">
         <v>12</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="n">
         <v>308</v>
       </c>
@@ -11499,36 +11852,36 @@
         <v>23</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>759</v>
+        <v>786</v>
       </c>
       <c r="E34" s="1" t="n">
         <v>10</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="n">
         <v>402</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="1" t="s">
         <v>315</v>
       </c>
       <c r="C35" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="D35" s="5" t="s">
-        <v>776</v>
+      <c r="D35" s="1" t="s">
+        <v>803</v>
       </c>
       <c r="E35" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="F35" s="5" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F35" s="1" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="n">
         <v>401</v>
       </c>
@@ -11538,17 +11891,17 @@
       <c r="C36" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="D36" s="5" t="s">
-        <v>776</v>
+      <c r="D36" s="1" t="s">
+        <v>803</v>
       </c>
       <c r="E36" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="F36" s="5" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F36" s="1" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="n">
         <v>500</v>
       </c>
@@ -11559,16 +11912,16 @@
         <v>26</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>768</v>
+        <v>795</v>
       </c>
       <c r="E37" s="1" t="n">
         <v>13</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="n">
         <v>501</v>
       </c>
@@ -11579,16 +11932,16 @@
         <v>26</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>772</v>
+        <v>799</v>
       </c>
       <c r="E38" s="1" t="n">
         <v>14</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="n">
         <v>502</v>
       </c>
@@ -11599,56 +11952,56 @@
         <v>14</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>772</v>
+        <v>799</v>
       </c>
       <c r="E39" s="1" t="n">
         <v>14</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="n">
         <v>503</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>685</v>
+        <v>712</v>
       </c>
       <c r="C40" s="1" t="n">
         <v>24</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>768</v>
+        <v>795</v>
       </c>
       <c r="E40" s="1" t="n">
         <v>13</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="n">
         <v>504</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>686</v>
+        <v>713</v>
       </c>
       <c r="C41" s="1" t="n">
         <v>24</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>768</v>
+        <v>795</v>
       </c>
       <c r="E41" s="1" t="n">
         <v>13</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="n">
         <v>505</v>
       </c>
@@ -11659,13 +12012,13 @@
         <v>20</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>830</v>
+        <v>857</v>
       </c>
       <c r="E42" s="1" t="n">
         <v>16</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>830</v>
+        <v>857</v>
       </c>
     </row>
   </sheetData>
@@ -11673,8 +12026,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12 &amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12 Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -11685,96 +12038,96 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="28.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="42.89"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="25.62"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>695</v>
+        <v>722</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>831</v>
+        <v>858</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>696</v>
+        <v>723</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>609</v>
+        <v>636</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>832</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>699</v>
+        <v>726</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>833</v>
+        <v>860</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>834</v>
+        <v>861</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="87.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>706</v>
+        <v>733</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>836</v>
+        <v>863</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>837</v>
+        <v>864</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="89.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="89.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>713</v>
+        <v>740</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>839</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>840</v>
+        <v>866</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>867</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>842</v>
+        <v>869</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>843</v>
+        <v>870</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>844</v>
+        <v>871</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>845</v>
+        <v>872</v>
       </c>
     </row>
   </sheetData>
@@ -11782,324 +12135,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12 &amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12 Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2f842a33-3492-4161-bd34-44903e55dc8c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="713e08b7-8a49-4321-b04f-10cd9150d160" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F257B8F9AEFA2D459CCC5BA0DA793E2F" ma:contentTypeVersion="22" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="958509f91a1e9ecb817b6d20de74d0bc">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="2f842a33-3492-4161-bd34-44903e55dc8c" xmlns:ns3="713e08b7-8a49-4321-b04f-10cd9150d160" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e0c53704d33f8404479bcf633108a604" ns1:_="" ns2:_="" ns3:_="">
-    <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
-    <xsd:import namespace="2f842a33-3492-4161-bd34-44903e55dc8c"/>
-    <xsd:import namespace="713e08b7-8a49-4321-b04f-10cd9150d160"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns1:_dlc_ExpireDateSaved" minOccurs="0"/>
-                <xsd:element ref="ns1:_dlc_ExpireDate" minOccurs="0"/>
-                <xsd:element ref="ns1:_dlc_Exempt" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_dlc_ExpireDateSaved" ma:index="12" nillable="true" ma:displayName="Date d’expiration d’origine" ma:hidden="true" ma:internalName="_dlc_ExpireDateSaved" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:DateTime"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="_dlc_ExpireDate" ma:index="13" nillable="true" ma:displayName="Date d’expiration" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="_dlc_ExpireDate" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:DateTime"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="_dlc_Exempt" ma:index="14" nillable="true" ma:displayName="Exempt de la stratégie" ma:hidden="true" ma:internalName="_dlc_Exempt" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="2f842a33-3492-4161-bd34-44903e55dc8c" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="10" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="11" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="18" nillable="true" ma:displayName="MediaServiceAutoTags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="19" nillable="true" ma:displayName="MediaServiceOCR" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="20" nillable="true" ma:displayName="MediaServiceLocation" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="21" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="22" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="23" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="25" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Balises d’images" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="9ab06ea2-2b14-4c82-a9fe-956051591d02" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="27" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="28" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceBillingMetadata" ma:index="29" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="713e08b7-8a49-4321-b04f-10cd9150d160" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="15" nillable="true" ma:displayName="Partagé avec" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="16" nillable="true" ma:displayName="Partagé avec détails" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="26" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{e9f826f1-3fcf-4ca9-9df5-8617a2561da1}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="713e08b7-8a49-4321-b04f-10cd9150d160">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Type de contenu"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Titre"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C079963-A03D-47C3-AB25-CCEF3BD23F36}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F5A8CA8-C17C-4568-8550-DBD3E7C414FA}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2D0858B-1CFB-4E30-BC0B-20AEBA244DD4}"/>
 </file>